--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="297">
   <si>
     <t>parameter</t>
   </si>
@@ -947,13 +947,23 @@
   <si>
     <t>adjusted to match prod.</t>
   </si>
+  <si>
+    <t>Poultry meat and products</t>
+  </si>
+  <si>
+    <t>poultry</t>
+  </si>
+  <si>
+    <t>By-products??</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1079,8 +1089,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1361,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N344"/>
+  <dimension ref="A1:N349"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -1440,7 +1450,7 @@
       <c r="J3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="32">
         <f>(5222847+5156448)/1000000</f>
         <v>10.379295000000001</v>
       </c>
@@ -2090,7 +2100,7 @@
       <c r="J41" t="s">
         <v>18</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="31">
         <f>0.8+0.3/0.35+0.3</f>
         <v>1.9571428571428573</v>
       </c>
@@ -2149,7 +2159,7 @@
       <c r="J44" t="s">
         <v>18</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="31">
         <f>0.5</f>
         <v>0.5</v>
       </c>
@@ -2396,26 +2406,25 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
+      <c r="A58" t="s">
+        <v>294</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="J58" t="s">
+        <v>18</v>
+      </c>
+      <c r="K58">
+        <v>49.5</v>
+      </c>
+      <c r="L58" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2433,7 +2442,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2450,25 +2459,26 @@
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>219</v>
-      </c>
-      <c r="B61" t="s">
-        <v>224</v>
-      </c>
-      <c r="J61" t="s">
-        <v>18</v>
-      </c>
-      <c r="K61">
-        <v>4.5</v>
-      </c>
-      <c r="L61" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="27" t="s">
-        <v>220</v>
       </c>
       <c r="B62" t="s">
         <v>224</v>
@@ -2476,8 +2486,8 @@
       <c r="J62" t="s">
         <v>18</v>
       </c>
-      <c r="K62" s="7">
-        <v>0</v>
+      <c r="K62">
+        <v>4.5</v>
       </c>
       <c r="L62" t="s">
         <v>19</v>
@@ -2485,7 +2495,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
         <v>224</v>
@@ -2493,8 +2503,8 @@
       <c r="J63" t="s">
         <v>18</v>
       </c>
-      <c r="K63">
-        <v>0.7</v>
+      <c r="K63" s="7">
+        <v>0</v>
       </c>
       <c r="L63" t="s">
         <v>19</v>
@@ -2502,7 +2512,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" t="s">
         <v>224</v>
@@ -2511,7 +2521,7 @@
         <v>18</v>
       </c>
       <c r="K64">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L64" t="s">
         <v>19</v>
@@ -2519,7 +2529,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
         <v>224</v>
@@ -2528,33 +2538,32 @@
         <v>18</v>
       </c>
       <c r="K65">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="L65" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
+      <c r="A66" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B66" t="s">
+        <v>224</v>
+      </c>
+      <c r="J66" t="s">
+        <v>18</v>
+      </c>
+      <c r="K66">
+        <v>0.6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2571,106 +2580,107 @@
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>138</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>139</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J69" t="s">
         <v>18</v>
       </c>
-      <c r="K68" s="14">
+      <c r="K69" s="14">
         <f>6+4.4/3+13*0.6</f>
         <v>15.266666666666666</v>
       </c>
-      <c r="L68" t="s">
+      <c r="L69" t="s">
         <v>19</v>
       </c>
-      <c r="M68" s="7" t="s">
+      <c r="M69" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>145</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>139</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J70" t="s">
         <v>18</v>
       </c>
-      <c r="K69" s="23">
+      <c r="K70" s="23">
         <f>8.2+4.4/3</f>
         <v>9.6666666666666661</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L70" t="s">
         <v>19</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M70" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>146</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>139</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J71" t="s">
         <v>18</v>
       </c>
-      <c r="K70" s="23">
+      <c r="K71" s="23">
         <f>2.8+4.4/3</f>
         <v>4.2666666666666666</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L71" t="s">
         <v>19</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M71" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="6"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>234</v>
-      </c>
-      <c r="B72" t="s">
-        <v>237</v>
-      </c>
-      <c r="J72" t="s">
-        <v>18</v>
-      </c>
-      <c r="K72">
-        <v>79.3</v>
-      </c>
-      <c r="L72" t="s">
-        <v>19</v>
-      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B73" t="s">
         <v>237</v>
@@ -2679,18 +2689,15 @@
         <v>18</v>
       </c>
       <c r="K73">
-        <v>10</v>
+        <v>79.3</v>
       </c>
       <c r="L73" t="s">
         <v>19</v>
       </c>
-      <c r="M73" t="s">
-        <v>240</v>
-      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
         <v>237</v>
@@ -2699,50 +2706,53 @@
         <v>18</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="s">
         <v>19</v>
       </c>
+      <c r="M74" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="A75" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" t="s">
+        <v>237</v>
+      </c>
+      <c r="J75" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>245</v>
-      </c>
-      <c r="B76" t="s">
-        <v>118</v>
-      </c>
-      <c r="J76" t="s">
-        <v>18</v>
-      </c>
-      <c r="K76">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="L76" t="s">
-        <v>19</v>
-      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s">
         <v>118</v>
@@ -2751,7 +2761,7 @@
         <v>18</v>
       </c>
       <c r="K77">
-        <v>125.5</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="L77" t="s">
         <v>19</v>
@@ -2759,7 +2769,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B78" t="s">
         <v>118</v>
@@ -2768,18 +2778,15 @@
         <v>18</v>
       </c>
       <c r="K78">
-        <v>6.9</v>
+        <v>125.5</v>
       </c>
       <c r="L78" t="s">
         <v>19</v>
       </c>
-      <c r="M78" t="s">
-        <v>247</v>
-      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B79" t="s">
         <v>118</v>
@@ -2788,36 +2795,38 @@
         <v>18</v>
       </c>
       <c r="K79">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="L79" t="s">
         <v>19</v>
       </c>
       <c r="M79" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>249</v>
+      </c>
+      <c r="B80" t="s">
+        <v>118</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80">
+        <v>7.9</v>
+      </c>
+      <c r="L80" t="s">
+        <v>19</v>
+      </c>
+      <c r="M80" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2835,7 +2844,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2853,7 +2862,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2869,44 +2878,45 @@
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>208</v>
-      </c>
-      <c r="B86" t="s">
-        <v>217</v>
-      </c>
-      <c r="J86" t="s">
-        <v>213</v>
-      </c>
-      <c r="K86" s="7">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
-        <v>204</v>
-      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B87" t="s">
         <v>217</v>
@@ -2914,112 +2924,112 @@
       <c r="J87" t="s">
         <v>213</v>
       </c>
-      <c r="K87">
-        <v>10000</v>
+      <c r="K87" s="7">
+        <v>0</v>
       </c>
       <c r="L87" t="s">
         <v>204</v>
       </c>
-      <c r="M87" t="s">
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>209</v>
+      </c>
+      <c r="B88" t="s">
+        <v>217</v>
+      </c>
+      <c r="J88" t="s">
+        <v>213</v>
+      </c>
+      <c r="K88">
+        <v>10000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>204</v>
+      </c>
+      <c r="M88" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>107</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>217</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J90" t="s">
         <v>213</v>
       </c>
-      <c r="K89">
+      <c r="K90">
         <v>30000</v>
       </c>
-      <c r="L89" t="s">
+      <c r="L90" t="s">
         <v>204</v>
       </c>
-      <c r="M89" t="s">
+      <c r="M90" t="s">
         <v>211</v>
       </c>
-      <c r="N89" t="s">
+      <c r="N90" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J92" t="s">
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J93" t="s">
         <v>214</v>
       </c>
-      <c r="L92" t="s">
+      <c r="L93" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>26</v>
-      </c>
-      <c r="I95" t="s">
-        <v>53</v>
-      </c>
-      <c r="J95" t="s">
-        <v>56</v>
-      </c>
-      <c r="K95">
-        <v>25</v>
-      </c>
-      <c r="L95" t="s">
-        <v>39</v>
-      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="I96" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J96" t="s">
         <v>56</v>
       </c>
       <c r="K96">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L96" t="s">
         <v>39</v>
@@ -3030,36 +3040,36 @@
         <v>26</v>
       </c>
       <c r="I97" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J97" t="s">
         <v>56</v>
       </c>
-      <c r="K97" s="7">
-        <v>10.5</v>
+      <c r="K97">
+        <v>2</v>
       </c>
       <c r="L97" t="s">
         <v>39</v>
-      </c>
-      <c r="M97" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="I98" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J98" t="s">
         <v>56</v>
       </c>
-      <c r="K98">
-        <v>17</v>
+      <c r="K98" s="7">
+        <v>10.5</v>
       </c>
       <c r="L98" t="s">
         <v>39</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.25">
@@ -3067,13 +3077,13 @@
         <v>109</v>
       </c>
       <c r="I99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J99" t="s">
         <v>56</v>
       </c>
       <c r="K99">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L99" t="s">
         <v>39</v>
@@ -3084,36 +3094,36 @@
         <v>109</v>
       </c>
       <c r="I100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J100" t="s">
         <v>56</v>
       </c>
-      <c r="K100" s="7">
-        <v>15</v>
+      <c r="K100">
+        <v>7</v>
       </c>
       <c r="L100" t="s">
         <v>39</v>
-      </c>
-      <c r="M100" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="101" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I101" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J101" t="s">
         <v>56</v>
       </c>
-      <c r="K101">
-        <v>19</v>
+      <c r="K101" s="7">
+        <v>15</v>
       </c>
       <c r="L101" t="s">
         <v>39</v>
+      </c>
+      <c r="M101" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="2:13" x14ac:dyDescent="0.25">
@@ -3121,13 +3131,13 @@
         <v>114</v>
       </c>
       <c r="I102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J102" t="s">
         <v>56</v>
       </c>
       <c r="K102">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L102" t="s">
         <v>39</v>
@@ -3138,36 +3148,36 @@
         <v>114</v>
       </c>
       <c r="I103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J103" t="s">
         <v>56</v>
       </c>
-      <c r="K103" s="7">
-        <v>2</v>
+      <c r="K103">
+        <v>10</v>
       </c>
       <c r="L103" t="s">
         <v>39</v>
-      </c>
-      <c r="M103" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="104" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="I104" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J104" t="s">
         <v>56</v>
       </c>
-      <c r="K104">
-        <v>19</v>
+      <c r="K104" s="7">
+        <v>2</v>
       </c>
       <c r="L104" t="s">
         <v>39</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="2:13" x14ac:dyDescent="0.25">
@@ -3175,13 +3185,13 @@
         <v>262</v>
       </c>
       <c r="I105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J105" t="s">
         <v>56</v>
       </c>
       <c r="K105">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L105" t="s">
         <v>39</v>
@@ -3192,36 +3202,36 @@
         <v>262</v>
       </c>
       <c r="I106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J106" t="s">
         <v>56</v>
       </c>
-      <c r="K106" s="7">
-        <v>2</v>
+      <c r="K106">
+        <v>10</v>
       </c>
       <c r="L106" t="s">
         <v>39</v>
-      </c>
-      <c r="M106" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="107" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="I107" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J107" t="s">
         <v>56</v>
       </c>
-      <c r="K107">
-        <v>11</v>
+      <c r="K107" s="7">
+        <v>2</v>
       </c>
       <c r="L107" t="s">
         <v>39</v>
+      </c>
+      <c r="M107" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="2:13" x14ac:dyDescent="0.25">
@@ -3229,14 +3239,13 @@
         <v>84</v>
       </c>
       <c r="I108" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J108" t="s">
         <v>56</v>
       </c>
       <c r="K108">
-        <f>0.5</f>
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L108" t="s">
         <v>39</v>
@@ -3247,36 +3256,37 @@
         <v>84</v>
       </c>
       <c r="I109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J109" t="s">
         <v>56</v>
       </c>
-      <c r="K109" s="7">
-        <v>1</v>
+      <c r="K109">
+        <f>0.5</f>
+        <v>0.5</v>
       </c>
       <c r="L109" t="s">
         <v>39</v>
-      </c>
-      <c r="M109" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="110" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="I110" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J110" t="s">
         <v>56</v>
       </c>
-      <c r="K110">
-        <v>11</v>
+      <c r="K110" s="7">
+        <v>1</v>
       </c>
       <c r="L110" t="s">
         <v>39</v>
+      </c>
+      <c r="M110" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="2:13" x14ac:dyDescent="0.25">
@@ -3284,13 +3294,13 @@
         <v>58</v>
       </c>
       <c r="I111" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J111" t="s">
         <v>56</v>
       </c>
       <c r="K111">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L111" t="s">
         <v>39</v>
@@ -3301,36 +3311,36 @@
         <v>58</v>
       </c>
       <c r="I112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J112" t="s">
         <v>56</v>
       </c>
-      <c r="K112" s="7">
-        <v>5</v>
+      <c r="K112">
+        <v>4</v>
       </c>
       <c r="L112" t="s">
         <v>39</v>
-      </c>
-      <c r="M112" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="I113" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J113" t="s">
         <v>56</v>
       </c>
-      <c r="K113">
-        <v>4</v>
+      <c r="K113" s="7">
+        <v>5</v>
       </c>
       <c r="L113" t="s">
         <v>39</v>
+      </c>
+      <c r="M113" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -3338,13 +3348,13 @@
         <v>224</v>
       </c>
       <c r="I114" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J114" t="s">
         <v>56</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L114" t="s">
         <v>39</v>
@@ -3355,36 +3365,36 @@
         <v>224</v>
       </c>
       <c r="I115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J115" t="s">
         <v>56</v>
       </c>
-      <c r="K115" s="7">
-        <v>5</v>
+      <c r="K115">
+        <v>1</v>
       </c>
       <c r="L115" t="s">
         <v>39</v>
-      </c>
-      <c r="M115" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="I116" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J116" t="s">
         <v>56</v>
       </c>
-      <c r="K116">
-        <v>4</v>
+      <c r="K116" s="7">
+        <v>5</v>
       </c>
       <c r="L116" t="s">
         <v>39</v>
+      </c>
+      <c r="M116" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -3392,13 +3402,13 @@
         <v>139</v>
       </c>
       <c r="I117" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J117" t="s">
         <v>56</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L117" t="s">
         <v>39</v>
@@ -3409,36 +3419,36 @@
         <v>139</v>
       </c>
       <c r="I118" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J118" t="s">
         <v>56</v>
       </c>
-      <c r="K118" s="7">
-        <v>5</v>
+      <c r="K118">
+        <v>1</v>
       </c>
       <c r="L118" t="s">
         <v>39</v>
-      </c>
-      <c r="M118" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J119" t="s">
         <v>56</v>
       </c>
-      <c r="K119">
-        <v>13</v>
+      <c r="K119" s="7">
+        <v>5</v>
       </c>
       <c r="L119" t="s">
         <v>39</v>
+      </c>
+      <c r="M119" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -3446,13 +3456,13 @@
         <v>237</v>
       </c>
       <c r="I120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J120" t="s">
         <v>56</v>
       </c>
       <c r="K120">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L120" t="s">
         <v>39</v>
@@ -3463,36 +3473,36 @@
         <v>237</v>
       </c>
       <c r="I121" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J121" t="s">
         <v>56</v>
       </c>
-      <c r="K121" s="7">
+      <c r="K121">
         <v>5</v>
       </c>
       <c r="L121" t="s">
         <v>39</v>
-      </c>
-      <c r="M121" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J122" t="s">
         <v>56</v>
       </c>
-      <c r="K122">
-        <v>0</v>
+      <c r="K122" s="7">
+        <v>5</v>
       </c>
       <c r="L122" t="s">
         <v>39</v>
+      </c>
+      <c r="M122" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -3500,13 +3510,13 @@
         <v>118</v>
       </c>
       <c r="I123" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J123" t="s">
         <v>56</v>
       </c>
       <c r="K123">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L123" t="s">
         <v>39</v>
@@ -3517,56 +3527,59 @@
         <v>118</v>
       </c>
       <c r="I124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J124" t="s">
         <v>56</v>
       </c>
-      <c r="K124" s="7">
+      <c r="K124">
         <v>5</v>
       </c>
       <c r="L124" t="s">
         <v>39</v>
       </c>
-      <c r="M124" s="7" t="s">
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>118</v>
+      </c>
+      <c r="I125" t="s">
+        <v>55</v>
+      </c>
+      <c r="J125" t="s">
+        <v>56</v>
+      </c>
+      <c r="K125" s="7">
+        <v>5</v>
+      </c>
+      <c r="L125" t="s">
+        <v>39</v>
+      </c>
+      <c r="M125" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="3"/>
-      <c r="J126" s="4"/>
-      <c r="K126" s="4"/>
-      <c r="L126" s="4"/>
-      <c r="M126" s="4"/>
-      <c r="N126" s="4"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J127" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K127" s="8">
-        <v>0</v>
-      </c>
-      <c r="L127" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M127" s="8" t="s">
-        <v>46</v>
-      </c>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J128" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K128" s="8">
         <v>0</v>
@@ -3579,42 +3592,36 @@
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
+      <c r="J129" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K129" s="8">
+        <v>0</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M129" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
-      <c r="M129" s="6"/>
-      <c r="N129" s="6"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>192</v>
-      </c>
-      <c r="C130" t="s">
-        <v>38</v>
-      </c>
-      <c r="J130" t="s">
-        <v>88</v>
-      </c>
-      <c r="K130">
-        <v>79</v>
-      </c>
-      <c r="L130" t="s">
-        <v>39</v>
-      </c>
-      <c r="N130" t="s">
-        <v>98</v>
-      </c>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="6"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="6"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
@@ -3623,14 +3630,11 @@
       <c r="C131" t="s">
         <v>38</v>
       </c>
-      <c r="F131" t="s">
-        <v>122</v>
-      </c>
       <c r="J131" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K131">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="L131" t="s">
         <v>39</v>
@@ -3647,13 +3651,13 @@
         <v>38</v>
       </c>
       <c r="F132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J132" t="s">
         <v>89</v>
       </c>
       <c r="K132">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L132" t="s">
         <v>39</v>
@@ -3664,16 +3668,19 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C133" t="s">
         <v>38</v>
       </c>
+      <c r="F133" t="s">
+        <v>123</v>
+      </c>
       <c r="J133" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K133">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="L133" t="s">
         <v>39</v>
@@ -3683,29 +3690,21 @@
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A134" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+      <c r="A134" t="s">
+        <v>197</v>
+      </c>
+      <c r="C134" t="s">
+        <v>38</v>
+      </c>
       <c r="J134" t="s">
         <v>88</v>
       </c>
-      <c r="K134" s="9">
-        <v>72</v>
-      </c>
-      <c r="L134" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M134" s="9"/>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134" t="s">
+        <v>39</v>
+      </c>
       <c r="N134" t="s">
         <v>98</v>
       </c>
@@ -3720,17 +3719,15 @@
       </c>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
-      <c r="F135" s="9" t="s">
-        <v>124</v>
-      </c>
+      <c r="F135" s="9"/>
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="9"/>
       <c r="J135" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K135" s="9">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="L135" s="9" t="s">
         <v>39</v>
@@ -3751,7 +3748,7 @@
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
       <c r="F136" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
@@ -3760,7 +3757,7 @@
         <v>89</v>
       </c>
       <c r="K136" s="9">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L136" s="9" t="s">
         <v>39</v>
@@ -3772,7 +3769,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B137" s="9"/>
       <c r="C137" s="9" t="s">
@@ -3780,15 +3777,17 @@
       </c>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
+      <c r="F137" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" t="s">
-        <v>88</v>
-      </c>
-      <c r="K137" s="10">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="K137" s="9">
+        <v>9</v>
       </c>
       <c r="L137" s="9" t="s">
         <v>39</v>
@@ -3808,19 +3807,17 @@
       </c>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
-      <c r="F138" s="9" t="s">
-        <v>125</v>
-      </c>
+      <c r="F138" s="9"/>
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
       <c r="J138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K138" s="10">
-        <v>9</v>
-      </c>
-      <c r="L138" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L138" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M138" s="9"/>
@@ -3829,24 +3826,26 @@
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>194</v>
+      <c r="A139" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="B139" s="9"/>
-      <c r="C139" s="10" t="s">
-        <v>96</v>
+      <c r="C139" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
+      <c r="F139" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K139" s="10">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="L139" s="10" t="s">
         <v>39</v>
@@ -3866,17 +3865,15 @@
       </c>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
-      <c r="F140" s="10" t="s">
-        <v>126</v>
-      </c>
+      <c r="F140" s="9"/>
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="9"/>
       <c r="J140" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K140" s="10">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L140" s="10" t="s">
         <v>39</v>
@@ -3888,7 +3885,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B141" s="9"/>
       <c r="C141" s="10" t="s">
@@ -3896,15 +3893,17 @@
       </c>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
-      <c r="F141" s="10"/>
+      <c r="F141" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="9"/>
       <c r="J141" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K141" s="10">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L141" s="10" t="s">
         <v>39</v>
@@ -3916,15 +3915,15 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B142" s="9"/>
       <c r="C142" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
+      <c r="F142" s="10"/>
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
@@ -3932,7 +3931,7 @@
         <v>88</v>
       </c>
       <c r="K142" s="10">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="L142" s="10" t="s">
         <v>39</v>
@@ -3952,17 +3951,15 @@
       </c>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
-      <c r="F143" s="10" t="s">
-        <v>127</v>
-      </c>
+      <c r="F143" s="9"/>
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K143" s="10">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="L143" s="10" t="s">
         <v>39</v>
@@ -3983,7 +3980,7 @@
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
       <c r="F144" s="10" t="s">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
@@ -3992,7 +3989,7 @@
         <v>89</v>
       </c>
       <c r="K144" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L144" s="10" t="s">
         <v>39</v>
@@ -4004,7 +4001,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B145" s="9"/>
       <c r="C145" s="10" t="s">
@@ -4012,15 +4009,17 @@
       </c>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
-      <c r="F145" s="10"/>
+      <c r="F145" s="10" t="s">
+        <v>191</v>
+      </c>
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
       <c r="J145" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K145" s="10">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="L145" s="10" t="s">
         <v>39</v>
@@ -4040,17 +4039,15 @@
       </c>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
-      <c r="F146" s="10" t="s">
-        <v>191</v>
-      </c>
+      <c r="F146" s="10"/>
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
       <c r="J146" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K146" s="10">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="L146" s="10" t="s">
         <v>39</v>
@@ -4061,53 +4058,56 @@
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
+      <c r="A147" t="s">
+        <v>200</v>
+      </c>
+      <c r="B147" s="9"/>
+      <c r="C147" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D147" s="9"/>
+      <c r="E147" s="9"/>
+      <c r="F147" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G147" s="9"/>
+      <c r="H147" s="9"/>
+      <c r="I147" s="9"/>
+      <c r="J147" t="s">
+        <v>89</v>
+      </c>
+      <c r="K147" s="10">
+        <v>27</v>
+      </c>
+      <c r="L147" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M147" s="9"/>
+      <c r="N147" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="5"/>
-      <c r="H147" s="5"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
-      <c r="L147" s="6"/>
-      <c r="M147" s="6"/>
-      <c r="N147" s="6"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B148" s="9"/>
-      <c r="C148" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="10"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="9"/>
-      <c r="J148" t="s">
-        <v>88</v>
-      </c>
-      <c r="K148" s="12">
-        <v>100</v>
-      </c>
-      <c r="L148" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M148" s="11" t="s">
-        <v>110</v>
-      </c>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="6"/>
+      <c r="K148" s="6"/>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="6"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B149" s="9"/>
       <c r="C149" s="10" t="s">
@@ -4122,13 +4122,15 @@
       <c r="J149" t="s">
         <v>88</v>
       </c>
-      <c r="K149" s="10">
-        <v>50</v>
+      <c r="K149" s="12">
+        <v>100</v>
       </c>
       <c r="L149" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M149" s="9"/>
+      <c r="M149" s="11" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
@@ -4140,14 +4142,12 @@
       </c>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
-      <c r="F150" s="10" t="s">
-        <v>128</v>
-      </c>
+      <c r="F150" s="10"/>
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="9"/>
       <c r="J150" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K150" s="10">
         <v>50</v>
@@ -4159,37 +4159,37 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="B151" s="9"/>
-      <c r="C151" s="12" t="s">
-        <v>112</v>
+      <c r="C151" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
-      <c r="F151" s="10"/>
+      <c r="F151" s="10" t="s">
+        <v>128</v>
+      </c>
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" t="s">
-        <v>88</v>
-      </c>
-      <c r="K151" s="19">
-        <v>20</v>
+        <v>89</v>
+      </c>
+      <c r="K151" s="10">
+        <v>50</v>
       </c>
       <c r="L151" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M151" s="11" t="s">
-        <v>227</v>
-      </c>
+      <c r="M151" s="9"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="18" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="B152" s="9"/>
-      <c r="C152" s="10" t="s">
+      <c r="C152" s="12" t="s">
         <v>112</v>
       </c>
       <c r="D152" s="9"/>
@@ -4202,12 +4202,14 @@
         <v>88</v>
       </c>
       <c r="K152" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L152" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M152" s="20"/>
+      <c r="M152" s="11" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
@@ -4219,70 +4221,78 @@
       </c>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
-      <c r="F153" t="s">
-        <v>205</v>
-      </c>
+      <c r="F153" s="10"/>
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
       <c r="J153" t="s">
+        <v>88</v>
+      </c>
+      <c r="K153" s="19">
+        <v>19</v>
+      </c>
+      <c r="L153" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M153" s="20"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B154" s="9"/>
+      <c r="C154" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D154" s="9"/>
+      <c r="E154" s="9"/>
+      <c r="F154" t="s">
+        <v>205</v>
+      </c>
+      <c r="G154" s="9"/>
+      <c r="H154" s="9"/>
+      <c r="I154" s="9"/>
+      <c r="J154" t="s">
         <v>89</v>
       </c>
-      <c r="K153" s="29">
+      <c r="K154" s="29">
         <f>0.02*0.5*100/(844/1000)/0.9</f>
         <v>1.3164823591363877</v>
       </c>
-      <c r="L153" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M153" s="20" t="s">
+      <c r="L154" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M154" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="N153" s="10" t="s">
+      <c r="N154" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B154" s="5"/>
-      <c r="C154" s="5"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
-      <c r="G154" s="5"/>
-      <c r="H154" s="5"/>
-      <c r="I154" s="5"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
-      <c r="L154" s="6"/>
-      <c r="M154" s="6"/>
-      <c r="N154" s="6"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J155" t="s">
-        <v>88</v>
-      </c>
-      <c r="K155" s="19">
-        <v>100</v>
-      </c>
-      <c r="L155" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="6"/>
+      <c r="K155" s="6"/>
+      <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
+      <c r="N155" s="6"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J156" t="s">
         <v>88</v>
@@ -4296,10 +4306,10 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J157" t="s">
         <v>88</v>
@@ -4313,10 +4323,10 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J158" t="s">
         <v>88</v>
@@ -4330,10 +4340,10 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J159" t="s">
         <v>88</v>
@@ -4347,10 +4357,10 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J160" t="s">
         <v>88</v>
@@ -4364,18 +4374,11 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B161" s="9"/>
+        <v>152</v>
+      </c>
       <c r="C161" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
-      <c r="F161" s="10"/>
-      <c r="G161" s="9"/>
-      <c r="H161" s="9"/>
-      <c r="I161" s="9"/>
+        <v>154</v>
+      </c>
       <c r="J161" t="s">
         <v>88</v>
       </c>
@@ -4385,15 +4388,14 @@
       <c r="L161" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M161" s="11"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B162" s="9"/>
       <c r="C162" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -4414,11 +4416,11 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="B163" s="9"/>
       <c r="C163" s="10" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -4438,43 +4440,51 @@
       <c r="M163" s="11"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B164" s="9"/>
+      <c r="C164" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D164" s="9"/>
+      <c r="E164" s="9"/>
+      <c r="F164" s="10"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" t="s">
+        <v>88</v>
+      </c>
+      <c r="K164" s="19">
+        <v>100</v>
+      </c>
+      <c r="L164" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M164" s="11"/>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="5"/>
-      <c r="G164" s="5"/>
-      <c r="H164" s="5"/>
-      <c r="I164" s="5"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
-      <c r="L164" s="6"/>
-      <c r="M164" s="6"/>
-      <c r="N164" s="6"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="C165" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="J165" t="s">
-        <v>88</v>
-      </c>
-      <c r="K165" s="18">
-        <v>100</v>
-      </c>
-      <c r="L165" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="6"/>
+      <c r="K165" s="6"/>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="6"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>256</v>
@@ -4483,13 +4493,10 @@
         <v>88</v>
       </c>
       <c r="K166" s="18">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="L166" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="N166" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -4499,14 +4506,11 @@
       <c r="C167" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F167" s="20" t="s">
-        <v>257</v>
-      </c>
       <c r="J167" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K167" s="18">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="L167" s="18" t="s">
         <v>39</v>
@@ -4517,16 +4521,19 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>256</v>
       </c>
+      <c r="F168" s="20" t="s">
+        <v>257</v>
+      </c>
       <c r="J168" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K168" s="18">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L168" s="18" t="s">
         <v>39</v>
@@ -4542,14 +4549,11 @@
       <c r="C169" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F169" s="20" t="s">
-        <v>257</v>
-      </c>
       <c r="J169" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K169" s="18">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L169" s="18" t="s">
         <v>39</v>
@@ -4560,27 +4564,33 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>265</v>
+        <v>256</v>
+      </c>
+      <c r="F170" s="20" t="s">
+        <v>257</v>
       </c>
       <c r="J170" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K170" s="18">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L170" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="N170" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="J171" t="s">
         <v>88</v>
@@ -4594,10 +4604,10 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J172" t="s">
         <v>88</v>
@@ -4611,10 +4621,10 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J173" t="s">
         <v>88</v>
@@ -4628,10 +4638,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J174" t="s">
         <v>88</v>
@@ -4644,55 +4654,39 @@
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" s="5" t="s">
+      <c r="A175" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="J175" t="s">
+        <v>88</v>
+      </c>
+      <c r="K175" s="18">
+        <v>100</v>
+      </c>
+      <c r="L175" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
-      <c r="G175" s="5"/>
-      <c r="H175" s="5"/>
-      <c r="I175" s="5"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
-      <c r="M175" s="6"/>
-      <c r="N175" s="6"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B176" s="11"/>
-      <c r="C176" s="11"/>
-      <c r="D176" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E176" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F176" s="11"/>
-      <c r="G176" s="11"/>
-      <c r="H176" s="11"/>
-      <c r="I176" s="11"/>
-      <c r="J176" t="s">
-        <v>88</v>
-      </c>
-      <c r="K176" s="13">
-        <f>100-K177</f>
-        <v>90.75</v>
-      </c>
-      <c r="L176" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M176" t="s">
-        <v>74</v>
-      </c>
-      <c r="N176" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="6"/>
+      <c r="K176" s="6"/>
+      <c r="L176" s="6"/>
+      <c r="M176" s="6"/>
+      <c r="N176" s="6"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
@@ -4706,21 +4700,22 @@
       <c r="E177" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F177" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="F177" s="11"/>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
       <c r="J177" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K177" s="13">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
+        <f>100-K178</f>
+        <v>90.75</v>
       </c>
       <c r="L177" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="M177" t="s">
+        <v>74</v>
       </c>
       <c r="N177" s="9" t="s">
         <v>99</v>
@@ -4728,7 +4723,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B178" s="11"/>
       <c r="C178" s="11"/>
@@ -4738,22 +4733,21 @@
       <c r="E178" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F178" s="11"/>
+      <c r="F178" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
       <c r="J178" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K178" s="13">
-        <f>100-K179</f>
-        <v>93.25</v>
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="L178" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M178" t="s">
-        <v>75</v>
       </c>
       <c r="N178" s="9" t="s">
         <v>99</v>
@@ -4771,21 +4765,22 @@
       <c r="E179" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F179" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="F179" s="11"/>
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
       <c r="J179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K179" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>100-K180</f>
+        <v>93.25</v>
       </c>
       <c r="L179" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="M179" t="s">
+        <v>75</v>
       </c>
       <c r="N179" s="9" t="s">
         <v>99</v>
@@ -4793,7 +4788,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B180" s="11"/>
       <c r="C180" s="11"/>
@@ -4803,22 +4798,21 @@
       <c r="E180" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F180" s="11"/>
+      <c r="F180" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
       <c r="J180" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K180" s="13">
-        <f>100-K181</f>
-        <v>93.25</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L180" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M180" t="s">
-        <v>76</v>
       </c>
       <c r="N180" s="9" t="s">
         <v>99</v>
@@ -4836,21 +4830,22 @@
       <c r="E181" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F181" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="F181" s="11"/>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
       <c r="J181" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K181" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>100-K182</f>
+        <v>93.25</v>
       </c>
       <c r="L181" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="M181" t="s">
+        <v>76</v>
       </c>
       <c r="N181" s="9" t="s">
         <v>99</v>
@@ -4858,7 +4853,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B182" s="11"/>
       <c r="C182" s="11"/>
@@ -4868,22 +4863,21 @@
       <c r="E182" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F182" s="11"/>
+      <c r="F182" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
       <c r="J182" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K182" s="13">
-        <f>(100-K183)*0.1</f>
-        <v>9.3250000000000011</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L182" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M182" t="s">
-        <v>83</v>
       </c>
       <c r="N182" s="9" t="s">
         <v>99</v>
@@ -4901,21 +4895,22 @@
       <c r="E183" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F183" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="F183" s="11"/>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
       <c r="J183" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K183" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>(100-K184)*0.1</f>
+        <v>9.3250000000000011</v>
       </c>
       <c r="L183" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="M183" t="s">
+        <v>83</v>
       </c>
       <c r="N183" s="9" t="s">
         <v>99</v>
@@ -4934,7 +4929,7 @@
         <v>62</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
@@ -4943,8 +4938,8 @@
         <v>89</v>
       </c>
       <c r="K184" s="13">
-        <f>(100-K183)*0.9</f>
-        <v>83.924999999999997</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L184" s="11" t="s">
         <v>39</v>
@@ -4955,7 +4950,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4963,32 +4958,31 @@
         <v>82</v>
       </c>
       <c r="E185" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F185" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="F185" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
       <c r="J185" t="s">
-        <v>88</v>
-      </c>
-      <c r="K185" s="11">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+        <v>89</v>
+      </c>
+      <c r="K185" s="13">
+        <f>(100-K184)*0.9</f>
+        <v>83.924999999999997</v>
       </c>
       <c r="L185" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M185" t="s">
-        <v>81</v>
       </c>
       <c r="N185" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="12" t="s">
-        <v>72</v>
+      <c r="A186" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="B186" s="11"/>
       <c r="C186" s="11"/>
@@ -5005,23 +4999,23 @@
       <c r="J186" t="s">
         <v>88</v>
       </c>
-      <c r="K186" s="13">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+      <c r="K186" s="11">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M186" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N186" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="11" t="s">
-        <v>69</v>
+      <c r="A187" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B187" s="11"/>
       <c r="C187" s="11"/>
@@ -5039,14 +5033,14 @@
         <v>88</v>
       </c>
       <c r="K187" s="13">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
       </c>
       <c r="L187" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M187" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N187" s="9" t="s">
         <v>99</v>
@@ -5054,7 +5048,7 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B188" s="11"/>
       <c r="C188" s="11"/>
@@ -5071,15 +5065,15 @@
       <c r="J188" t="s">
         <v>88</v>
       </c>
-      <c r="K188" s="11">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+      <c r="K188" s="13">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
       </c>
       <c r="L188" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M188" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N188" s="9" t="s">
         <v>99</v>
@@ -5087,7 +5081,7 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="11"/>
@@ -5104,15 +5098,15 @@
       <c r="J189" t="s">
         <v>88</v>
       </c>
-      <c r="K189" s="13">
-        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
-        <v>49.367088607594937</v>
+      <c r="K189" s="11">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
       </c>
       <c r="L189" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N189" s="9" t="s">
         <v>99</v>
@@ -5122,84 +5116,87 @@
       <c r="A190" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11"/>
       <c r="D190" s="11" t="s">
         <v>82</v>
       </c>
       <c r="E190" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F190" s="11" t="s">
+      <c r="F190" s="11"/>
+      <c r="G190" s="11"/>
+      <c r="H190" s="11"/>
+      <c r="I190" s="11"/>
+      <c r="J190" t="s">
+        <v>88</v>
+      </c>
+      <c r="K190" s="13">
+        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
+        <v>49.367088607594937</v>
+      </c>
+      <c r="L190" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M190" t="s">
+        <v>80</v>
+      </c>
+      <c r="N190" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E191" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F191" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
-      <c r="I190" s="9"/>
-      <c r="J190" t="s">
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
+      <c r="I191" s="9"/>
+      <c r="J191" t="s">
         <v>89</v>
       </c>
-      <c r="K190" s="15">
+      <c r="K191" s="15">
         <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
         <v>50.632911392405056</v>
       </c>
-      <c r="L190" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M190" s="9" t="s">
+      <c r="L191" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M191" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="N190" s="9" t="s">
+      <c r="N191" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
-      <c r="H191" s="5"/>
-      <c r="I191" s="5"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
-      <c r="M191" s="6"/>
-      <c r="N191" s="6"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E192" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
-      <c r="I192" s="9"/>
-      <c r="J192" t="s">
-        <v>88</v>
-      </c>
-      <c r="K192" s="10">
-        <v>73</v>
-      </c>
-      <c r="L192" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M192" s="9"/>
-      <c r="N192" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="5"/>
+      <c r="J192" s="6"/>
+      <c r="K192" s="6"/>
+      <c r="L192" s="6"/>
+      <c r="M192" s="6"/>
+      <c r="N192" s="6"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
@@ -5213,25 +5210,20 @@
       <c r="E193" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F193" s="9" t="s">
-        <v>129</v>
-      </c>
+      <c r="F193" s="9"/>
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="9"/>
       <c r="J193" t="s">
-        <v>89</v>
-      </c>
-      <c r="K193" s="17">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
+        <v>88</v>
+      </c>
+      <c r="K193" s="10">
+        <v>73</v>
       </c>
       <c r="L193" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M193" s="10" t="s">
-        <v>102</v>
-      </c>
+      <c r="M193" s="9"/>
       <c r="N193" s="9" t="s">
         <v>98</v>
       </c>
@@ -5249,7 +5241,7 @@
         <v>58</v>
       </c>
       <c r="F194" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
@@ -5258,8 +5250,8 @@
         <v>89</v>
       </c>
       <c r="K194" s="17">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="L194" s="9" t="s">
         <v>39</v>
@@ -5284,7 +5276,7 @@
         <v>58</v>
       </c>
       <c r="F195" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
@@ -5293,8 +5285,8 @@
         <v>89</v>
       </c>
       <c r="K195" s="17">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
       </c>
       <c r="L195" s="9" t="s">
         <v>39</v>
@@ -5319,7 +5311,7 @@
         <v>58</v>
       </c>
       <c r="F196" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
@@ -5327,40 +5319,45 @@
       <c r="J196" t="s">
         <v>89</v>
       </c>
-      <c r="K196" s="10">
-        <v>18</v>
+      <c r="K196" s="17">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
       </c>
       <c r="L196" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M196" s="9"/>
+      <c r="M196" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="N196" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>101</v>
+      <c r="A197" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
-      <c r="D197" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E197" s="10" t="s">
+      <c r="D197" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E197" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F197" s="9"/>
+      <c r="F197" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="9"/>
       <c r="J197" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K197" s="10">
-        <v>71</v>
-      </c>
-      <c r="L197" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L197" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M197" s="9"/>
@@ -5380,25 +5377,20 @@
       <c r="E198" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F198" s="10" t="s">
-        <v>133</v>
-      </c>
+      <c r="F198" s="9"/>
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="9"/>
       <c r="J198" t="s">
-        <v>89</v>
-      </c>
-      <c r="K198" s="17">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
+        <v>88</v>
+      </c>
+      <c r="K198" s="10">
+        <v>71</v>
       </c>
       <c r="L198" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M198" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="M198" s="9"/>
       <c r="N198" s="9" t="s">
         <v>98</v>
       </c>
@@ -5415,8 +5407,8 @@
       <c r="E199" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F199" s="9" t="s">
-        <v>134</v>
+      <c r="F199" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
@@ -5425,8 +5417,8 @@
         <v>89</v>
       </c>
       <c r="K199" s="17">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
       </c>
       <c r="L199" s="10" t="s">
         <v>39</v>
@@ -5450,8 +5442,8 @@
       <c r="E200" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F200" s="10" t="s">
-        <v>135</v>
+      <c r="F200" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
@@ -5460,8 +5452,8 @@
         <v>89</v>
       </c>
       <c r="K200" s="17">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
       </c>
       <c r="L200" s="10" t="s">
         <v>39</v>
@@ -5485,8 +5477,8 @@
       <c r="E201" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F201" s="9" t="s">
-        <v>136</v>
+      <c r="F201" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
@@ -5494,197 +5486,209 @@
       <c r="J201" t="s">
         <v>89</v>
       </c>
-      <c r="K201" s="10">
-        <v>12</v>
+      <c r="K201" s="17">
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
       </c>
       <c r="L201" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M201" s="9"/>
+      <c r="M201" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="N201" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B202" s="5"/>
-      <c r="C202" s="5"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="5"/>
-      <c r="F202" s="5"/>
-      <c r="G202" s="5"/>
-      <c r="H202" s="5"/>
-      <c r="I202" s="5"/>
-      <c r="J202" s="6"/>
-      <c r="K202" s="6"/>
-      <c r="L202" s="6"/>
-      <c r="M202" s="6"/>
-      <c r="N202" s="6"/>
+      <c r="A202" t="s">
+        <v>101</v>
+      </c>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9"/>
+      <c r="I202" s="9"/>
+      <c r="J202" t="s">
+        <v>89</v>
+      </c>
+      <c r="K202" s="10">
+        <v>12</v>
+      </c>
+      <c r="L202" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M202" s="9"/>
+      <c r="N202" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>219</v>
-      </c>
-      <c r="C203" t="s">
-        <v>228</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9"/>
+      <c r="I203" s="9"/>
       <c r="J203" t="s">
         <v>88</v>
       </c>
-      <c r="K203">
+      <c r="K203" s="10">
+        <v>77</v>
+      </c>
+      <c r="L203" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M203" s="9"/>
+      <c r="N203" s="9"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B204" s="11"/>
+      <c r="C204" s="11"/>
+      <c r="D204" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E204" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9"/>
+      <c r="I204" s="9"/>
+      <c r="K204" s="10"/>
+      <c r="L204" s="10"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="9"/>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="5"/>
+      <c r="J205" s="6"/>
+      <c r="K205" s="6"/>
+      <c r="L205" s="6"/>
+      <c r="M205" s="6"/>
+      <c r="N205" s="6"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>219</v>
+      </c>
+      <c r="C206" t="s">
+        <v>228</v>
+      </c>
+      <c r="J206" t="s">
+        <v>88</v>
+      </c>
+      <c r="K206">
         <v>100</v>
       </c>
-      <c r="L203" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="27" t="s">
+      <c r="L206" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C207" t="s">
         <v>229</v>
       </c>
-      <c r="J204" t="s">
+      <c r="J207" t="s">
         <v>88</v>
       </c>
-      <c r="K204">
+      <c r="K207">
         <v>100</v>
       </c>
-      <c r="L204" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="27" t="s">
+      <c r="L207" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C208" t="s">
         <v>230</v>
       </c>
-      <c r="J205" t="s">
+      <c r="J208" t="s">
         <v>88</v>
       </c>
-      <c r="K205">
+      <c r="K208">
         <v>100</v>
       </c>
-      <c r="L205" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="7" t="s">
+      <c r="L208" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="7" t="s">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="10"/>
-      <c r="E207" s="10"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="9"/>
-      <c r="I207" s="9"/>
-      <c r="M207" s="9"/>
-      <c r="N207" s="9"/>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="5" t="s">
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="10"/>
+      <c r="F210" s="9"/>
+      <c r="G210" s="9"/>
+      <c r="H210" s="9"/>
+      <c r="I210" s="9"/>
+      <c r="M210" s="9"/>
+      <c r="N210" s="9"/>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
-      <c r="H208" s="5"/>
-      <c r="I208" s="5"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="6"/>
-      <c r="L208" s="6"/>
-      <c r="M208" s="6"/>
-      <c r="N208" s="6"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>138</v>
-      </c>
-      <c r="C209" t="s">
-        <v>140</v>
-      </c>
-      <c r="H209" t="s">
-        <v>47</v>
-      </c>
-      <c r="J209" t="s">
-        <v>88</v>
-      </c>
-      <c r="K209" s="22">
-        <v>38</v>
-      </c>
-      <c r="L209" t="s">
-        <v>39</v>
-      </c>
-      <c r="M209" s="12"/>
-      <c r="N209" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>138</v>
-      </c>
-      <c r="C210" t="s">
-        <v>140</v>
-      </c>
-      <c r="F210" t="s">
-        <v>141</v>
-      </c>
-      <c r="H210" t="s">
-        <v>47</v>
-      </c>
-      <c r="J210" t="s">
-        <v>89</v>
-      </c>
-      <c r="K210" s="22">
-        <v>60</v>
-      </c>
-      <c r="L210" t="s">
-        <v>39</v>
-      </c>
-      <c r="N210" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>138</v>
-      </c>
-      <c r="C211" t="s">
-        <v>140</v>
-      </c>
-      <c r="H211" t="s">
-        <v>45</v>
-      </c>
-      <c r="J211" t="s">
-        <v>88</v>
-      </c>
-      <c r="K211" s="22">
-        <v>32</v>
-      </c>
-      <c r="L211" t="s">
-        <v>39</v>
-      </c>
-      <c r="M211" t="s">
-        <v>143</v>
-      </c>
-      <c r="N211" s="9"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+      <c r="I211" s="5"/>
+      <c r="J211" s="6"/>
+      <c r="K211" s="6"/>
+      <c r="L211" s="6"/>
+      <c r="M211" s="6"/>
+      <c r="N211" s="6"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
@@ -5693,101 +5697,118 @@
       <c r="C212" t="s">
         <v>140</v>
       </c>
-      <c r="F212" t="s">
-        <v>142</v>
-      </c>
       <c r="H212" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J212" t="s">
+        <v>88</v>
+      </c>
+      <c r="K212" s="22">
+        <v>38</v>
+      </c>
+      <c r="L212" t="s">
+        <v>39</v>
+      </c>
+      <c r="M212" s="12"/>
+      <c r="N212" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>138</v>
+      </c>
+      <c r="C213" t="s">
+        <v>140</v>
+      </c>
+      <c r="F213" t="s">
+        <v>141</v>
+      </c>
+      <c r="H213" t="s">
+        <v>47</v>
+      </c>
+      <c r="J213" t="s">
         <v>89</v>
       </c>
-      <c r="K212" s="22">
-        <v>68</v>
-      </c>
-      <c r="L212" t="s">
-        <v>39</v>
-      </c>
-      <c r="N212" s="9"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
-      <c r="H213" s="5"/>
-      <c r="I213" s="5"/>
-      <c r="J213" s="6"/>
-      <c r="K213" s="6"/>
-      <c r="L213" s="6"/>
-      <c r="M213" s="6"/>
-      <c r="N213" s="6"/>
+      <c r="K213" s="22">
+        <v>60</v>
+      </c>
+      <c r="L213" t="s">
+        <v>39</v>
+      </c>
+      <c r="N213" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="C214" t="s">
-        <v>241</v>
+        <v>140</v>
+      </c>
+      <c r="H214" t="s">
+        <v>45</v>
       </c>
       <c r="J214" t="s">
         <v>88</v>
       </c>
       <c r="K214" s="22">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="L214" t="s">
         <v>39</v>
       </c>
+      <c r="M214" t="s">
+        <v>143</v>
+      </c>
+      <c r="N214" s="9"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="C215" t="s">
-        <v>241</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
-        <v>243</v>
+        <v>142</v>
+      </c>
+      <c r="H215" t="s">
+        <v>45</v>
       </c>
       <c r="J215" t="s">
         <v>89</v>
       </c>
       <c r="K215" s="22">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="L215" t="s">
         <v>39</v>
       </c>
+      <c r="N215" s="9"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>234</v>
-      </c>
-      <c r="C216" t="s">
-        <v>241</v>
-      </c>
-      <c r="F216" t="s">
-        <v>244</v>
-      </c>
-      <c r="J216" t="s">
-        <v>89</v>
-      </c>
-      <c r="K216" s="22">
-        <v>4</v>
-      </c>
-      <c r="L216" t="s">
-        <v>39</v>
-      </c>
+      <c r="A216" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B216" s="5"/>
+      <c r="C216" s="5"/>
+      <c r="D216" s="5"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="5"/>
+      <c r="G216" s="5"/>
+      <c r="H216" s="5"/>
+      <c r="I216" s="5"/>
+      <c r="J216" s="6"/>
+      <c r="K216" s="6"/>
+      <c r="L216" s="6"/>
+      <c r="M216" s="6"/>
+      <c r="N216" s="6"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C217" t="s">
         <v>241</v>
@@ -5795,19 +5816,16 @@
       <c r="J217" t="s">
         <v>88</v>
       </c>
-      <c r="K217" s="24">
+      <c r="K217" s="22">
         <v>13</v>
       </c>
       <c r="L217" t="s">
         <v>39</v>
-      </c>
-      <c r="M217" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C218" t="s">
         <v>241</v>
@@ -5827,7 +5845,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C219" t="s">
         <v>241</v>
@@ -5846,147 +5864,127 @@
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A220" s="7" t="s">
-        <v>235</v>
+      <c r="A220" t="s">
+        <v>236</v>
+      </c>
+      <c r="C220" t="s">
+        <v>241</v>
+      </c>
+      <c r="J220" t="s">
+        <v>88</v>
+      </c>
+      <c r="K220" s="24">
+        <v>13</v>
+      </c>
+      <c r="L220" t="s">
+        <v>39</v>
+      </c>
+      <c r="M220" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A221" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="5"/>
-      <c r="E221" s="5"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
-      <c r="H221" s="5"/>
-      <c r="I221" s="5"/>
-      <c r="J221" s="6"/>
-      <c r="K221" s="6"/>
-      <c r="L221" s="6"/>
-      <c r="M221" s="6"/>
-      <c r="N221" s="6"/>
+      <c r="A221" t="s">
+        <v>236</v>
+      </c>
+      <c r="C221" t="s">
+        <v>241</v>
+      </c>
+      <c r="F221" t="s">
+        <v>243</v>
+      </c>
+      <c r="J221" t="s">
+        <v>89</v>
+      </c>
+      <c r="K221" s="22">
+        <v>7</v>
+      </c>
+      <c r="L221" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>236</v>
+      </c>
+      <c r="C222" t="s">
+        <v>241</v>
+      </c>
+      <c r="F222" t="s">
+        <v>244</v>
+      </c>
+      <c r="J222" t="s">
+        <v>89</v>
+      </c>
+      <c r="K222" s="22">
+        <v>4</v>
+      </c>
+      <c r="L222" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B224" s="5"/>
+      <c r="C224" s="5"/>
+      <c r="D224" s="5"/>
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
+      <c r="G224" s="5"/>
+      <c r="H224" s="5"/>
+      <c r="I224" s="5"/>
+      <c r="J224" s="6"/>
+      <c r="K224" s="6"/>
+      <c r="L224" s="6"/>
+      <c r="M224" s="6"/>
+      <c r="N224" s="6"/>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>245</v>
       </c>
-      <c r="B222" s="11"/>
-      <c r="C222" s="9" t="s">
+      <c r="B225" s="11"/>
+      <c r="C225" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="D222" s="11"/>
-      <c r="E222" s="11"/>
-      <c r="F222" s="11"/>
-      <c r="G222" s="11"/>
-      <c r="H222" s="11"/>
-      <c r="I222" s="11"/>
-      <c r="J222" t="s">
-        <v>88</v>
-      </c>
-      <c r="K222" s="21">
-        <v>70</v>
-      </c>
-      <c r="L222" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M222" s="9"/>
-      <c r="N222" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>248</v>
-      </c>
-      <c r="B223" s="11"/>
-      <c r="C223" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D223" s="11"/>
-      <c r="E223" s="11"/>
-      <c r="F223" s="11"/>
-      <c r="G223" s="11"/>
-      <c r="H223" s="11"/>
-      <c r="I223" s="11"/>
-      <c r="J223" t="s">
-        <v>88</v>
-      </c>
-      <c r="K223" s="21">
-        <f>655*0.7</f>
-        <v>458.49999999999994</v>
-      </c>
-      <c r="L223" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M223" s="9"/>
-      <c r="N223" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>248</v>
-      </c>
-      <c r="B224" s="11"/>
-      <c r="C224" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D224" s="11"/>
-      <c r="E224" s="11"/>
-      <c r="F224" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="G224" s="11"/>
-      <c r="H224" s="11"/>
-      <c r="I224" s="11"/>
-      <c r="J224" t="s">
-        <v>89</v>
-      </c>
-      <c r="K224" s="21">
-        <f>1*(K223/100)*0.2*100</f>
-        <v>91.699999999999989</v>
-      </c>
-      <c r="L224" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M224" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="N224" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B225" s="11"/>
-      <c r="C225" s="9"/>
       <c r="D225" s="11"/>
       <c r="E225" s="11"/>
-      <c r="F225" s="11" t="s">
-        <v>188</v>
-      </c>
+      <c r="F225" s="11"/>
       <c r="G225" s="11"/>
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
-      <c r="K225" s="21"/>
-      <c r="L225" s="10"/>
-      <c r="M225" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="N225" s="9"/>
+      <c r="J225" t="s">
+        <v>88</v>
+      </c>
+      <c r="K225" s="21">
+        <v>70</v>
+      </c>
+      <c r="L225" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M225" s="9"/>
+      <c r="N225" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B226" s="11"/>
-      <c r="C226" s="10" t="s">
-        <v>256</v>
+      <c r="C226" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D226" s="11"/>
       <c r="E226" s="11"/>
-      <c r="F226" s="20"/>
+      <c r="F226" s="11"/>
       <c r="G226" s="11"/>
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
@@ -5994,7 +5992,8 @@
         <v>88</v>
       </c>
       <c r="K226" s="21">
-        <v>65</v>
+        <f>655*0.7</f>
+        <v>458.49999999999994</v>
       </c>
       <c r="L226" s="10" t="s">
         <v>39</v>
@@ -6006,16 +6005,16 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B227" s="11"/>
-      <c r="C227" s="10" t="s">
-        <v>256</v>
+      <c r="C227" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D227" s="11"/>
       <c r="E227" s="11"/>
       <c r="F227" s="20" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="G227" s="11"/>
       <c r="H227" s="11"/>
@@ -6024,65 +6023,56 @@
         <v>89</v>
       </c>
       <c r="K227" s="21">
-        <v>35</v>
+        <f>1*(K226/100)*0.2*100</f>
+        <v>91.699999999999989</v>
       </c>
       <c r="L227" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M227" s="9"/>
+      <c r="M227" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="N227" s="9" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>249</v>
-      </c>
       <c r="B228" s="11"/>
-      <c r="C228" s="10" t="s">
-        <v>38</v>
-      </c>
+      <c r="C228" s="9"/>
       <c r="D228" s="11"/>
       <c r="E228" s="11"/>
-      <c r="F228" s="20"/>
+      <c r="F228" s="11" t="s">
+        <v>188</v>
+      </c>
       <c r="G228" s="11"/>
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
-      <c r="J228" t="s">
-        <v>88</v>
-      </c>
-      <c r="K228" s="21">
-        <v>30</v>
-      </c>
-      <c r="L228" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M228" s="9"/>
-      <c r="N228" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="K228" s="21"/>
+      <c r="L228" s="10"/>
+      <c r="M228" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="N228" s="9"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B229" s="11"/>
       <c r="C229" s="10" t="s">
-        <v>38</v>
+        <v>256</v>
       </c>
       <c r="D229" s="11"/>
       <c r="E229" s="11"/>
-      <c r="F229" s="11" t="s">
-        <v>258</v>
-      </c>
+      <c r="F229" s="20"/>
       <c r="G229" s="11"/>
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
       <c r="J229" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K229" s="21">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="L229" s="10" t="s">
         <v>39</v>
@@ -6093,192 +6083,234 @@
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="5"/>
-      <c r="E230" s="5"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
-      <c r="H230" s="5"/>
-      <c r="I230" s="5"/>
-      <c r="J230" s="6"/>
-      <c r="K230" s="6"/>
-      <c r="L230" s="6"/>
-      <c r="M230" s="6"/>
-      <c r="N230" s="6"/>
+      <c r="A230" t="s">
+        <v>246</v>
+      </c>
+      <c r="B230" s="11"/>
+      <c r="C230" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D230" s="11"/>
+      <c r="E230" s="11"/>
+      <c r="F230" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="G230" s="11"/>
+      <c r="H230" s="11"/>
+      <c r="I230" s="11"/>
+      <c r="J230" t="s">
+        <v>89</v>
+      </c>
+      <c r="K230" s="21">
+        <v>35</v>
+      </c>
+      <c r="L230" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M230" s="9"/>
+      <c r="N230" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="B231" s="11"/>
-      <c r="C231" t="s">
-        <v>140</v>
-      </c>
+      <c r="C231" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D231" s="11"/>
+      <c r="E231" s="11"/>
+      <c r="F231" s="20"/>
+      <c r="G231" s="11"/>
+      <c r="H231" s="11"/>
+      <c r="I231" s="11"/>
       <c r="J231" t="s">
         <v>88</v>
       </c>
-      <c r="K231" s="22">
-        <v>38</v>
-      </c>
-      <c r="L231" t="s">
-        <v>39</v>
-      </c>
-      <c r="M231" s="12" t="s">
-        <v>218</v>
-      </c>
+      <c r="K231" s="21">
+        <v>30</v>
+      </c>
+      <c r="L231" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M231" s="9"/>
       <c r="N231" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="B232" s="11"/>
-      <c r="C232" t="s">
-        <v>140</v>
-      </c>
-      <c r="F232" t="s">
-        <v>141</v>
-      </c>
+      <c r="C232" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D232" s="11"/>
+      <c r="E232" s="11"/>
+      <c r="F232" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="G232" s="11"/>
+      <c r="H232" s="11"/>
+      <c r="I232" s="11"/>
       <c r="J232" t="s">
         <v>89</v>
       </c>
-      <c r="K232" s="22">
-        <v>60</v>
-      </c>
-      <c r="L232" t="s">
-        <v>39</v>
-      </c>
+      <c r="K232" s="21">
+        <v>11</v>
+      </c>
+      <c r="L232" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M232" s="9"/>
       <c r="N232" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="11"/>
-      <c r="B233" s="11"/>
-      <c r="C233" s="11"/>
-      <c r="D233" s="11"/>
-      <c r="E233" s="11"/>
-      <c r="F233" s="11"/>
-      <c r="G233" s="11"/>
-      <c r="H233" s="11"/>
-      <c r="I233" s="11"/>
-      <c r="J233" s="11"/>
-      <c r="K233" s="11"/>
-      <c r="L233" s="9"/>
-      <c r="M233" s="9"/>
-      <c r="N233" s="9"/>
+      <c r="A233" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+      <c r="I233" s="5"/>
+      <c r="J233" s="6"/>
+      <c r="K233" s="6"/>
+      <c r="L233" s="6"/>
+      <c r="M233" s="6"/>
+      <c r="N233" s="6"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="s">
+      <c r="A234" t="s">
+        <v>209</v>
+      </c>
+      <c r="B234" s="11"/>
+      <c r="C234" t="s">
+        <v>140</v>
+      </c>
+      <c r="J234" t="s">
+        <v>88</v>
+      </c>
+      <c r="K234" s="22">
+        <v>38</v>
+      </c>
+      <c r="L234" t="s">
+        <v>39</v>
+      </c>
+      <c r="M234" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="N234" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>209</v>
+      </c>
+      <c r="B235" s="11"/>
+      <c r="C235" t="s">
+        <v>140</v>
+      </c>
+      <c r="F235" t="s">
+        <v>141</v>
+      </c>
+      <c r="J235" t="s">
+        <v>89</v>
+      </c>
+      <c r="K235" s="22">
+        <v>60</v>
+      </c>
+      <c r="L235" t="s">
+        <v>39</v>
+      </c>
+      <c r="N235" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A236" s="11"/>
+      <c r="B236" s="11"/>
+      <c r="C236" s="11"/>
+      <c r="D236" s="11"/>
+      <c r="E236" s="11"/>
+      <c r="F236" s="11"/>
+      <c r="G236" s="11"/>
+      <c r="H236" s="11"/>
+      <c r="I236" s="11"/>
+      <c r="J236" s="11"/>
+      <c r="K236" s="11"/>
+      <c r="L236" s="9"/>
+      <c r="M236" s="9"/>
+      <c r="N236" s="9"/>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B234" s="3"/>
-      <c r="C234" s="3"/>
-      <c r="D234" s="3"/>
-      <c r="E234" s="3"/>
-      <c r="F234" s="3"/>
-      <c r="G234" s="3"/>
-      <c r="H234" s="3"/>
-      <c r="I234" s="3"/>
-      <c r="J234" s="4"/>
-      <c r="K234" s="4"/>
-      <c r="L234" s="4"/>
-      <c r="M234" s="4"/>
-      <c r="N234" s="4"/>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J235" s="8" t="s">
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
+      <c r="E237" s="3"/>
+      <c r="F237" s="3"/>
+      <c r="G237" s="3"/>
+      <c r="H237" s="3"/>
+      <c r="I237" s="3"/>
+      <c r="J237" s="4"/>
+      <c r="K237" s="4"/>
+      <c r="L237" s="4"/>
+      <c r="M237" s="4"/>
+      <c r="N237" s="4"/>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J238" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K235" s="8">
+      <c r="K238" s="8">
         <v>100</v>
       </c>
-      <c r="L235" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M235" s="8" t="s">
+      <c r="L238" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M238" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" s="5" t="s">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
-      <c r="D236" s="5"/>
-      <c r="E236" s="5"/>
-      <c r="F236" s="5"/>
-      <c r="G236" s="5"/>
-      <c r="H236" s="5"/>
-      <c r="I236" s="5"/>
-      <c r="J236" s="6"/>
-      <c r="K236" s="6"/>
-      <c r="L236" s="6"/>
-      <c r="M236" s="6"/>
-      <c r="N236" s="6"/>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>192</v>
-      </c>
-      <c r="J237" t="s">
-        <v>41</v>
-      </c>
-      <c r="K237">
-        <v>22</v>
-      </c>
-      <c r="L237" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>197</v>
-      </c>
-      <c r="J238" t="s">
-        <v>41</v>
-      </c>
-      <c r="K238" s="28">
-        <f>K237</f>
-        <v>22</v>
-      </c>
-      <c r="L238" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M238" s="28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>44</v>
-      </c>
-      <c r="J239" t="s">
-        <v>41</v>
-      </c>
-      <c r="K239">
-        <v>100</v>
-      </c>
-      <c r="L239" t="s">
-        <v>39</v>
-      </c>
+      <c r="B239" s="5"/>
+      <c r="C239" s="5"/>
+      <c r="D239" s="5"/>
+      <c r="E239" s="5"/>
+      <c r="F239" s="5"/>
+      <c r="G239" s="5"/>
+      <c r="H239" s="5"/>
+      <c r="I239" s="5"/>
+      <c r="J239" s="6"/>
+      <c r="K239" s="6"/>
+      <c r="L239" s="6"/>
+      <c r="M239" s="6"/>
+      <c r="N239" s="6"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J240" t="s">
         <v>41</v>
       </c>
       <c r="K240">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L240" t="s">
         <v>39</v>
@@ -6286,14 +6318,14 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J241" t="s">
         <v>41</v>
       </c>
       <c r="K241" s="28">
         <f>K240</f>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L241" s="28" t="s">
         <v>39</v>
@@ -6304,7 +6336,7 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="J242" t="s">
         <v>41</v>
@@ -6318,13 +6350,13 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J243" t="s">
         <v>41</v>
       </c>
       <c r="K243">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L243" t="s">
         <v>39</v>
@@ -6332,14 +6364,14 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J244" t="s">
         <v>41</v>
       </c>
       <c r="K244" s="28">
         <f>K243</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L244" s="28" t="s">
         <v>39</v>
@@ -6350,13 +6382,13 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="J245" t="s">
         <v>41</v>
       </c>
       <c r="K245">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L245" t="s">
         <v>39</v>
@@ -6364,120 +6396,124 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J246" t="s">
         <v>41</v>
       </c>
-      <c r="K246" s="28">
-        <f>K245</f>
-        <v>1</v>
-      </c>
-      <c r="L246" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M246" s="28" t="s">
-        <v>233</v>
+      <c r="K246">
+        <v>8</v>
+      </c>
+      <c r="L246" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J247" t="s">
         <v>41</v>
       </c>
-      <c r="K247" s="7">
-        <v>22</v>
-      </c>
-      <c r="L247" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M247" t="s">
-        <v>161</v>
+      <c r="K247" s="28">
+        <f>K246</f>
+        <v>8</v>
+      </c>
+      <c r="L247" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M247" s="28" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J248" t="s">
         <v>41</v>
       </c>
-      <c r="K248" s="28">
-        <f>K247</f>
-        <v>22</v>
-      </c>
-      <c r="L248" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M248" s="28" t="s">
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>200</v>
+      </c>
+      <c r="J249" t="s">
+        <v>41</v>
+      </c>
+      <c r="K249" s="28">
+        <f>K248</f>
+        <v>1</v>
+      </c>
+      <c r="L249" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M249" s="28" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B249" s="5"/>
-      <c r="C249" s="5"/>
-      <c r="D249" s="5"/>
-      <c r="E249" s="5"/>
-      <c r="F249" s="5"/>
-      <c r="G249" s="5"/>
-      <c r="H249" s="5"/>
-      <c r="I249" s="5"/>
-      <c r="J249" s="6"/>
-      <c r="K249" s="6"/>
-      <c r="L249" s="6"/>
-      <c r="M249" s="6"/>
-      <c r="N249" s="6"/>
-    </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A250" s="18" t="s">
-        <v>105</v>
+      <c r="A250" t="s">
+        <v>196</v>
       </c>
       <c r="J250" t="s">
         <v>41</v>
       </c>
-      <c r="K250" s="18">
-        <v>16</v>
+      <c r="K250" s="7">
+        <v>22</v>
       </c>
       <c r="L250" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M250" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" s="18" t="s">
-        <v>106</v>
+      <c r="A251" t="s">
+        <v>202</v>
       </c>
       <c r="J251" t="s">
         <v>41</v>
       </c>
-      <c r="K251" s="18">
-        <v>16</v>
-      </c>
-      <c r="L251" s="18" t="s">
-        <v>39</v>
+      <c r="K251" s="28">
+        <f>K250</f>
+        <v>22</v>
+      </c>
+      <c r="L251" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M251" s="28" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="J252" t="s">
-        <v>41</v>
-      </c>
-      <c r="K252" s="18">
-        <v>16</v>
-      </c>
-      <c r="L252" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A252" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B252" s="5"/>
+      <c r="C252" s="5"/>
+      <c r="D252" s="5"/>
+      <c r="E252" s="5"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="5"/>
+      <c r="H252" s="5"/>
+      <c r="I252" s="5"/>
+      <c r="J252" s="6"/>
+      <c r="K252" s="6"/>
+      <c r="L252" s="6"/>
+      <c r="M252" s="6"/>
+      <c r="N252" s="6"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J253" t="s">
         <v>41</v>
@@ -6490,32 +6526,28 @@
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="5"/>
-      <c r="G254" s="5"/>
-      <c r="H254" s="5"/>
-      <c r="I254" s="5"/>
-      <c r="J254" s="6"/>
-      <c r="K254" s="6"/>
-      <c r="L254" s="6"/>
-      <c r="M254" s="6"/>
-      <c r="N254" s="6"/>
+      <c r="A254" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="J254" t="s">
+        <v>41</v>
+      </c>
+      <c r="K254" s="18">
+        <v>16</v>
+      </c>
+      <c r="L254" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="18" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="J255" t="s">
         <v>41</v>
       </c>
       <c r="K255" s="18">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L255" s="18" t="s">
         <v>39</v>
@@ -6523,41 +6555,45 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="18" t="s">
-        <v>260</v>
+        <v>107</v>
       </c>
       <c r="J256" t="s">
         <v>41</v>
       </c>
       <c r="K256" s="18">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L256" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A257" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="J257" t="s">
-        <v>41</v>
-      </c>
-      <c r="K257" s="18">
-        <v>85</v>
-      </c>
-      <c r="L257" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A257" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B257" s="5"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="5"/>
+      <c r="G257" s="5"/>
+      <c r="H257" s="5"/>
+      <c r="I257" s="5"/>
+      <c r="J257" s="6"/>
+      <c r="K257" s="6"/>
+      <c r="L257" s="6"/>
+      <c r="M257" s="6"/>
+      <c r="N257" s="6"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="18" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J258" t="s">
         <v>41</v>
       </c>
       <c r="K258" s="18">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L258" s="18" t="s">
         <v>39</v>
@@ -6565,30 +6601,27 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="18" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="J259" t="s">
         <v>41</v>
       </c>
-      <c r="K259" s="7">
-        <v>97</v>
+      <c r="K259" s="18">
+        <v>85</v>
       </c>
       <c r="L259" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M259" s="7" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="18" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="J260" t="s">
         <v>41</v>
       </c>
       <c r="K260" s="18">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="L260" s="18" t="s">
         <v>39</v>
@@ -6596,140 +6629,139 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C261" s="10"/>
+        <v>263</v>
+      </c>
       <c r="J261" t="s">
         <v>41</v>
       </c>
-      <c r="K261" s="7">
-        <v>50</v>
+      <c r="K261" s="18">
+        <v>95</v>
       </c>
       <c r="L261" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M261" s="7" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J262" t="s">
         <v>41</v>
       </c>
       <c r="K262" s="7">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L262" s="18" t="s">
         <v>39</v>
       </c>
       <c r="M262" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="5"/>
-      <c r="D263" s="5"/>
-      <c r="E263" s="5"/>
-      <c r="F263" s="5"/>
-      <c r="G263" s="5"/>
-      <c r="H263" s="5"/>
-      <c r="I263" s="5"/>
-      <c r="J263" s="6"/>
-      <c r="K263" s="6"/>
-      <c r="L263" s="6"/>
-      <c r="M263" s="6"/>
-      <c r="N263" s="6"/>
+      <c r="A263" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J263" t="s">
+        <v>41</v>
+      </c>
+      <c r="K263" s="18">
+        <v>29</v>
+      </c>
+      <c r="L263" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="18" t="s">
-        <v>147</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C264" s="10"/>
       <c r="J264" t="s">
         <v>41</v>
       </c>
-      <c r="K264">
-        <v>7</v>
+      <c r="K264" s="7">
+        <v>50</v>
       </c>
       <c r="L264" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="M264" s="7" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="18" t="s">
-        <v>153</v>
+        <v>283</v>
       </c>
       <c r="J265" t="s">
         <v>41</v>
       </c>
-      <c r="K265" s="18">
-        <v>35</v>
+      <c r="K265" s="7">
+        <v>90</v>
       </c>
       <c r="L265" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M265" s="7" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="J266" t="s">
-        <v>41</v>
-      </c>
-      <c r="K266" s="18">
-        <v>63</v>
-      </c>
-      <c r="L266" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A266" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266" s="5"/>
+      <c r="C266" s="5"/>
+      <c r="D266" s="5"/>
+      <c r="E266" s="5"/>
+      <c r="F266" s="5"/>
+      <c r="G266" s="5"/>
+      <c r="H266" s="5"/>
+      <c r="I266" s="5"/>
+      <c r="J266" s="6"/>
+      <c r="K266" s="6"/>
+      <c r="L266" s="6"/>
+      <c r="M266" s="6"/>
+      <c r="N266" s="6"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="18" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J267" t="s">
         <v>41</v>
       </c>
-      <c r="K267" s="18">
-        <v>54</v>
+      <c r="K267">
+        <v>7</v>
       </c>
       <c r="L267" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M267" s="7"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J268" t="s">
         <v>41</v>
       </c>
-      <c r="K268" s="7">
-        <v>75</v>
+      <c r="K268" s="18">
+        <v>35</v>
       </c>
       <c r="L268" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M268" s="7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J269" t="s">
         <v>41</v>
       </c>
       <c r="K269" s="18">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="L269" s="18" t="s">
         <v>39</v>
@@ -6737,41 +6769,45 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="18" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="J270" t="s">
         <v>41</v>
       </c>
       <c r="K270" s="18">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="L270" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M270" s="7"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="18" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="J271" t="s">
         <v>41</v>
       </c>
-      <c r="K271" s="18">
-        <v>46</v>
+      <c r="K271" s="7">
+        <v>75</v>
       </c>
       <c r="L271" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="M271" s="7" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="18" t="s">
-        <v>276</v>
+        <v>152</v>
       </c>
       <c r="J272" t="s">
         <v>41</v>
       </c>
       <c r="K272" s="18">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L272" s="18" t="s">
         <v>39</v>
@@ -6779,150 +6815,150 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="18" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="J273" t="s">
         <v>41</v>
       </c>
-      <c r="K273" s="7">
+      <c r="K273" s="18">
         <v>90</v>
       </c>
       <c r="L273" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M273" s="7" t="s">
-        <v>292</v>
-      </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5"/>
-      <c r="D274" s="5"/>
-      <c r="E274" s="5"/>
-      <c r="F274" s="5"/>
-      <c r="G274" s="5"/>
-      <c r="H274" s="5"/>
-      <c r="I274" s="5"/>
-      <c r="J274" s="6"/>
-      <c r="K274" s="6"/>
-      <c r="L274" s="6"/>
-      <c r="M274" s="6"/>
-      <c r="N274" s="6"/>
+      <c r="A274" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="J274" t="s">
+        <v>41</v>
+      </c>
+      <c r="K274" s="18">
+        <v>46</v>
+      </c>
+      <c r="L274" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A275" s="7" t="s">
-        <v>65</v>
+      <c r="A275" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="J275" t="s">
         <v>41</v>
       </c>
-      <c r="K275" s="14">
+      <c r="K275" s="18">
+        <v>100</v>
+      </c>
+      <c r="L275" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A276" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="J276" t="s">
+        <v>41</v>
+      </c>
+      <c r="K276" s="7">
+        <v>90</v>
+      </c>
+      <c r="L276" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M276" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B277" s="5"/>
+      <c r="C277" s="5"/>
+      <c r="D277" s="5"/>
+      <c r="E277" s="5"/>
+      <c r="F277" s="5"/>
+      <c r="G277" s="5"/>
+      <c r="H277" s="5"/>
+      <c r="I277" s="5"/>
+      <c r="J277" s="6"/>
+      <c r="K277" s="6"/>
+      <c r="L277" s="6"/>
+      <c r="M277" s="6"/>
+      <c r="N277" s="6"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A278" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J278" t="s">
+        <v>41</v>
+      </c>
+      <c r="K278" s="14">
         <f>8.5*20/(29.5+8.5)</f>
         <v>4.4736842105263159</v>
       </c>
-      <c r="L275" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" s="7" t="s">
+      <c r="L278" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J276" t="s">
+      <c r="J279" t="s">
         <v>41</v>
       </c>
-      <c r="K276" s="14">
+      <c r="K279" s="14">
         <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
         <v>2.981366459627329</v>
       </c>
-      <c r="L276" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" s="7" t="s">
+      <c r="L279" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J277" t="s">
+      <c r="J280" t="s">
         <v>41</v>
       </c>
-      <c r="K277" s="14">
+      <c r="K280" s="14">
         <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
         <v>7.723292469352014</v>
       </c>
-      <c r="L277" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" s="7" t="s">
+      <c r="L280" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A281" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J278" t="s">
+      <c r="J281" t="s">
         <v>41</v>
       </c>
-      <c r="K278">
+      <c r="K281">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="L278" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J279" t="s">
-        <v>41</v>
-      </c>
-      <c r="K279">
-        <v>0</v>
-      </c>
-      <c r="L279" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J280" t="s">
-        <v>41</v>
-      </c>
-      <c r="K280">
-        <v>20</v>
-      </c>
-      <c r="L280" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J281" t="s">
-        <v>41</v>
-      </c>
-      <c r="K281">
-        <v>20</v>
-      </c>
       <c r="L281" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J282" t="s">
         <v>41</v>
       </c>
       <c r="K282">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L282" t="s">
         <v>39</v>
@@ -6930,68 +6966,64 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J283" t="s">
         <v>41</v>
       </c>
       <c r="K283">
+        <v>20</v>
+      </c>
+      <c r="L283" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A284" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J284" t="s">
+        <v>41</v>
+      </c>
+      <c r="K284">
+        <v>20</v>
+      </c>
+      <c r="L284" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A285" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J285" t="s">
+        <v>41</v>
+      </c>
+      <c r="K285">
+        <v>20</v>
+      </c>
+      <c r="L285" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A286" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J286" t="s">
+        <v>41</v>
+      </c>
+      <c r="K286">
         <f>43</f>
         <v>43</v>
       </c>
-      <c r="L283" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B284" s="5"/>
-      <c r="C284" s="5"/>
-      <c r="D284" s="5"/>
-      <c r="E284" s="5"/>
-      <c r="F284" s="5"/>
-      <c r="G284" s="5"/>
-      <c r="H284" s="5"/>
-      <c r="I284" s="5"/>
-      <c r="J284" s="6"/>
-      <c r="K284" s="6"/>
-      <c r="L284" s="6"/>
-      <c r="M284" s="6"/>
-      <c r="N284" s="6"/>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>57</v>
-      </c>
-      <c r="J285" t="s">
-        <v>41</v>
-      </c>
-      <c r="K285">
-        <v>36</v>
-      </c>
-      <c r="L285" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>101</v>
-      </c>
-      <c r="J286" t="s">
-        <v>41</v>
-      </c>
-      <c r="K286" s="18">
-        <v>43</v>
-      </c>
       <c r="L286" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7009,190 +7041,183 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="J288" t="s">
         <v>41</v>
       </c>
       <c r="K288">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="L288" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A289" s="27" t="s">
-        <v>220</v>
+      <c r="A289" t="s">
+        <v>101</v>
       </c>
       <c r="J289" t="s">
         <v>41</v>
       </c>
-      <c r="K289">
-        <v>0.4</v>
+      <c r="K289" s="18">
+        <v>43</v>
       </c>
       <c r="L289" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A290" s="27" t="s">
-        <v>221</v>
+      <c r="A290" t="s">
+        <v>294</v>
       </c>
       <c r="J290" t="s">
         <v>41</v>
       </c>
-      <c r="K290" s="7">
-        <v>95</v>
+      <c r="K290" s="18">
+        <v>36</v>
       </c>
       <c r="L290" t="s">
         <v>39</v>
       </c>
-      <c r="M290" s="7" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A291" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="J291" t="s">
-        <v>41</v>
-      </c>
-      <c r="K291">
-        <v>100</v>
-      </c>
-      <c r="L291" t="s">
-        <v>39</v>
-      </c>
+      <c r="A291" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B291" s="5"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="5"/>
+      <c r="G291" s="5"/>
+      <c r="H291" s="5"/>
+      <c r="I291" s="5"/>
+      <c r="J291" s="6"/>
+      <c r="K291" s="6"/>
+      <c r="L291" s="6"/>
+      <c r="M291" s="6"/>
+      <c r="N291" s="6"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A292" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="B292" s="9"/>
-      <c r="C292" s="9"/>
-      <c r="D292" s="10"/>
-      <c r="E292" s="10"/>
-      <c r="F292" s="9"/>
-      <c r="G292" s="9"/>
-      <c r="H292" s="9"/>
-      <c r="I292" s="9"/>
+      <c r="A292" t="s">
+        <v>219</v>
+      </c>
       <c r="J292" t="s">
         <v>41</v>
       </c>
       <c r="K292">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L292" t="s">
         <v>39</v>
       </c>
-      <c r="M292" s="9"/>
-      <c r="N292" s="9"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A293" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B293" s="5"/>
-      <c r="C293" s="5"/>
-      <c r="D293" s="5"/>
-      <c r="E293" s="5"/>
-      <c r="F293" s="5"/>
-      <c r="G293" s="5"/>
-      <c r="H293" s="5"/>
-      <c r="I293" s="5"/>
-      <c r="J293" s="6"/>
-      <c r="K293" s="6"/>
-      <c r="L293" s="6"/>
-      <c r="M293" s="6"/>
-      <c r="N293" s="6"/>
+      <c r="A293" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="J293" t="s">
+        <v>41</v>
+      </c>
+      <c r="K293">
+        <v>0.4</v>
+      </c>
+      <c r="L293" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>138</v>
+      <c r="A294" s="27" t="s">
+        <v>221</v>
       </c>
       <c r="J294" t="s">
         <v>41</v>
       </c>
-      <c r="K294" s="16">
-        <v>52</v>
+      <c r="K294" s="7">
+        <v>95</v>
       </c>
       <c r="L294" t="s">
         <v>39</v>
       </c>
-      <c r="M294" s="25"/>
+      <c r="M294" s="7" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A295" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
-      <c r="D295" s="5"/>
-      <c r="E295" s="5"/>
-      <c r="F295" s="5"/>
-      <c r="G295" s="5"/>
-      <c r="H295" s="5"/>
-      <c r="I295" s="5"/>
-      <c r="J295" s="6"/>
-      <c r="K295" s="6"/>
-      <c r="L295" s="6"/>
-      <c r="M295" s="6"/>
-      <c r="N295" s="6"/>
+      <c r="A295" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="J295" t="s">
+        <v>41</v>
+      </c>
+      <c r="K295">
+        <v>100</v>
+      </c>
+      <c r="L295" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>234</v>
-      </c>
+      <c r="A296" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B296" s="9"/>
+      <c r="C296" s="9"/>
+      <c r="D296" s="10"/>
+      <c r="E296" s="10"/>
+      <c r="F296" s="9"/>
+      <c r="G296" s="9"/>
+      <c r="H296" s="9"/>
+      <c r="I296" s="9"/>
       <c r="J296" t="s">
         <v>41</v>
       </c>
-      <c r="K296" s="7">
-        <v>24</v>
+      <c r="K296">
+        <v>100</v>
       </c>
       <c r="L296" t="s">
         <v>39</v>
       </c>
-      <c r="M296" s="7" t="s">
-        <v>239</v>
-      </c>
+      <c r="M296" s="9"/>
+      <c r="N296" s="9"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>236</v>
-      </c>
-      <c r="J297" t="s">
-        <v>41</v>
-      </c>
-      <c r="K297" s="28">
-        <f>K296</f>
-        <v>24</v>
-      </c>
-      <c r="L297" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M297" s="28" t="s">
-        <v>238</v>
-      </c>
+      <c r="A297" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B297" s="5"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+      <c r="I297" s="5"/>
+      <c r="J297" s="6"/>
+      <c r="K297" s="6"/>
+      <c r="L297" s="6"/>
+      <c r="M297" s="6"/>
+      <c r="N297" s="6"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="J298" t="s">
         <v>41</v>
       </c>
-      <c r="K298">
-        <v>61</v>
+      <c r="K298" s="16">
+        <v>52</v>
       </c>
       <c r="L298" t="s">
         <v>39</v>
       </c>
+      <c r="M298" s="25"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -7210,250 +7235,213 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J300" t="s">
         <v>41</v>
       </c>
-      <c r="K300">
-        <v>100</v>
+      <c r="K300" s="7">
+        <v>24</v>
       </c>
       <c r="L300" t="s">
         <v>39</v>
+      </c>
+      <c r="M300" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J301" t="s">
         <v>41</v>
       </c>
-      <c r="K301">
-        <v>4</v>
-      </c>
-      <c r="L301" t="s">
-        <v>39</v>
-      </c>
-      <c r="M301" t="s">
-        <v>119</v>
+      <c r="K301" s="28">
+        <f>K300</f>
+        <v>24</v>
+      </c>
+      <c r="L301" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M301" s="28" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="J302" t="s">
         <v>41</v>
       </c>
       <c r="K302">
+        <v>61</v>
+      </c>
+      <c r="L302" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A303" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
+      <c r="D303" s="5"/>
+      <c r="E303" s="5"/>
+      <c r="F303" s="5"/>
+      <c r="G303" s="5"/>
+      <c r="H303" s="5"/>
+      <c r="I303" s="5"/>
+      <c r="J303" s="6"/>
+      <c r="K303" s="6"/>
+      <c r="L303" s="6"/>
+      <c r="M303" s="6"/>
+      <c r="N303" s="6"/>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>245</v>
+      </c>
+      <c r="J304" t="s">
+        <v>41</v>
+      </c>
+      <c r="K304">
+        <v>100</v>
+      </c>
+      <c r="L304" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>248</v>
+      </c>
+      <c r="J305" t="s">
+        <v>41</v>
+      </c>
+      <c r="K305">
+        <v>4</v>
+      </c>
+      <c r="L305" t="s">
+        <v>39</v>
+      </c>
+      <c r="M305" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>246</v>
+      </c>
+      <c r="J306" t="s">
+        <v>41</v>
+      </c>
+      <c r="K306">
         <v>85</v>
       </c>
-      <c r="L302" t="s">
-        <v>39</v>
-      </c>
-      <c r="M302" t="s">
+      <c r="L306" t="s">
+        <v>39</v>
+      </c>
+      <c r="M306" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
         <v>249</v>
       </c>
-      <c r="J303" t="s">
+      <c r="J307" t="s">
         <v>41</v>
       </c>
-      <c r="K303">
+      <c r="K307">
         <v>22</v>
       </c>
-      <c r="L303" t="s">
-        <v>39</v>
-      </c>
-      <c r="M303" t="s">
+      <c r="L307" t="s">
+        <v>39</v>
+      </c>
+      <c r="M307" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A305" s="3" t="s">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B305" s="3"/>
-      <c r="C305" s="3"/>
-      <c r="D305" s="3"/>
-      <c r="E305" s="3"/>
-      <c r="F305" s="3"/>
-      <c r="G305" s="3"/>
-      <c r="H305" s="3"/>
-      <c r="I305" s="3"/>
-      <c r="J305" s="4"/>
-      <c r="K305" s="4"/>
-      <c r="L305" s="4"/>
-      <c r="M305" s="4"/>
-      <c r="N305" s="4"/>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G306" s="8"/>
-      <c r="H306" s="8" t="s">
+      <c r="B309" s="3"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="3"/>
+      <c r="E309" s="3"/>
+      <c r="F309" s="3"/>
+      <c r="G309" s="3"/>
+      <c r="H309" s="3"/>
+      <c r="I309" s="3"/>
+      <c r="J309" s="4"/>
+      <c r="K309" s="4"/>
+      <c r="L309" s="4"/>
+      <c r="M309" s="4"/>
+      <c r="N309" s="4"/>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G310" s="8"/>
+      <c r="H310" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I306" s="8"/>
-      <c r="J306" s="8" t="s">
+      <c r="I310" s="8"/>
+      <c r="J310" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K306" s="8">
+      <c r="K310" s="8">
         <v>-100</v>
       </c>
-      <c r="L306" s="8" t="s">
+      <c r="L310" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M306" s="8" t="s">
+      <c r="M310" s="8" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G307" s="8"/>
-      <c r="H307" s="8" t="s">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G311" s="8"/>
+      <c r="H311" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I307" s="8"/>
-      <c r="J307" s="8" t="s">
+      <c r="I311" s="8"/>
+      <c r="J311" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K307" s="8">
+      <c r="K311" s="8">
         <v>0</v>
       </c>
-      <c r="L307" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M307" s="8" t="s">
+      <c r="L311" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M311" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A308" s="5" t="s">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A312" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B308" s="5"/>
-      <c r="C308" s="5"/>
-      <c r="D308" s="5"/>
-      <c r="E308" s="5"/>
-      <c r="F308" s="5"/>
-      <c r="G308" s="5"/>
-      <c r="H308" s="5"/>
-      <c r="I308" s="5"/>
-      <c r="J308" s="6"/>
-      <c r="K308" s="6"/>
-      <c r="L308" s="6"/>
-      <c r="M308" s="6"/>
-      <c r="N308" s="6"/>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>35</v>
-      </c>
-      <c r="G309" t="s">
-        <v>90</v>
-      </c>
-      <c r="H309" t="s">
-        <v>45</v>
-      </c>
-      <c r="J309" t="s">
-        <v>42</v>
-      </c>
-      <c r="K309" s="18">
-        <v>5.3</v>
-      </c>
-      <c r="L309" t="s">
-        <v>39</v>
-      </c>
-      <c r="M309" t="s">
-        <v>181</v>
-      </c>
-      <c r="N309" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>50</v>
-      </c>
-      <c r="G310" t="s">
-        <v>90</v>
-      </c>
-      <c r="H310" t="s">
-        <v>45</v>
-      </c>
-      <c r="J310" t="s">
-        <v>42</v>
-      </c>
-      <c r="K310" s="18">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L310" t="s">
-        <v>39</v>
-      </c>
-      <c r="M310" t="s">
-        <v>181</v>
-      </c>
-      <c r="N310" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>93</v>
-      </c>
-      <c r="G311" t="s">
-        <v>90</v>
-      </c>
-      <c r="H311" t="s">
-        <v>45</v>
-      </c>
-      <c r="J311" t="s">
-        <v>42</v>
-      </c>
-      <c r="K311" s="18">
-        <v>12.7</v>
-      </c>
-      <c r="L311" t="s">
-        <v>39</v>
-      </c>
-      <c r="M311" t="s">
-        <v>181</v>
-      </c>
-      <c r="N311" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>92</v>
-      </c>
-      <c r="G312" t="s">
-        <v>90</v>
-      </c>
-      <c r="H312" t="s">
-        <v>45</v>
-      </c>
-      <c r="J312" t="s">
-        <v>42</v>
-      </c>
-      <c r="K312" s="18">
-        <v>24</v>
-      </c>
-      <c r="L312" t="s">
-        <v>39</v>
-      </c>
-      <c r="M312" t="s">
-        <v>182</v>
-      </c>
-      <c r="N312" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="B312" s="5"/>
+      <c r="C312" s="5"/>
+      <c r="D312" s="5"/>
+      <c r="E312" s="5"/>
+      <c r="F312" s="5"/>
+      <c r="G312" s="5"/>
+      <c r="H312" s="5"/>
+      <c r="I312" s="5"/>
+      <c r="J312" s="6"/>
+      <c r="K312" s="6"/>
+      <c r="L312" s="6"/>
+      <c r="M312" s="6"/>
+      <c r="N312" s="6"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="G313" t="s">
         <v>90</v>
@@ -7464,34 +7452,48 @@
       <c r="J313" t="s">
         <v>42</v>
       </c>
-      <c r="K313" s="7">
-        <v>10</v>
+      <c r="K313" s="18">
+        <v>5.3</v>
       </c>
       <c r="L313" t="s">
         <v>39</v>
       </c>
+      <c r="M313" t="s">
+        <v>181</v>
+      </c>
+      <c r="N313" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A314" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B314" s="5"/>
-      <c r="C314" s="5"/>
-      <c r="D314" s="5"/>
-      <c r="E314" s="5"/>
-      <c r="F314" s="5"/>
-      <c r="G314" s="5"/>
-      <c r="H314" s="5"/>
-      <c r="I314" s="5"/>
-      <c r="J314" s="6"/>
-      <c r="K314" s="6"/>
-      <c r="L314" s="6"/>
-      <c r="M314" s="6"/>
-      <c r="N314" s="6"/>
+      <c r="A314" t="s">
+        <v>50</v>
+      </c>
+      <c r="G314" t="s">
+        <v>90</v>
+      </c>
+      <c r="H314" t="s">
+        <v>45</v>
+      </c>
+      <c r="J314" t="s">
+        <v>42</v>
+      </c>
+      <c r="K314" s="18">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L314" t="s">
+        <v>39</v>
+      </c>
+      <c r="M314" t="s">
+        <v>181</v>
+      </c>
+      <c r="N314" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A315" s="18" t="s">
-        <v>105</v>
+      <c r="A315" t="s">
+        <v>93</v>
       </c>
       <c r="G315" t="s">
         <v>90</v>
@@ -7503,18 +7505,21 @@
         <v>42</v>
       </c>
       <c r="K315" s="18">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="L315" t="s">
         <v>39</v>
       </c>
-      <c r="N315" s="27" t="s">
-        <v>179</v>
+      <c r="M315" t="s">
+        <v>181</v>
+      </c>
+      <c r="N315" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A316" s="18" t="s">
-        <v>106</v>
+      <c r="A316" t="s">
+        <v>92</v>
       </c>
       <c r="G316" t="s">
         <v>90</v>
@@ -7526,18 +7531,21 @@
         <v>42</v>
       </c>
       <c r="K316" s="18">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L316" t="s">
         <v>39</v>
+      </c>
+      <c r="M316" t="s">
+        <v>182</v>
       </c>
       <c r="N316" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A317" s="18" t="s">
-        <v>226</v>
+      <c r="A317" t="s">
+        <v>91</v>
       </c>
       <c r="G317" t="s">
         <v>90</v>
@@ -7548,54 +7556,57 @@
       <c r="J317" t="s">
         <v>42</v>
       </c>
-      <c r="K317" s="18">
-        <v>0</v>
+      <c r="K317" s="7">
+        <v>10</v>
       </c>
       <c r="L317" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A318" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G318" t="s">
+      <c r="A318" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B318" s="5"/>
+      <c r="C318" s="5"/>
+      <c r="D318" s="5"/>
+      <c r="E318" s="5"/>
+      <c r="F318" s="5"/>
+      <c r="G318" s="5"/>
+      <c r="H318" s="5"/>
+      <c r="I318" s="5"/>
+      <c r="J318" s="6"/>
+      <c r="K318" s="6"/>
+      <c r="L318" s="6"/>
+      <c r="M318" s="6"/>
+      <c r="N318" s="6"/>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A319" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G319" t="s">
         <v>90</v>
       </c>
-      <c r="H318" t="s">
+      <c r="H319" t="s">
         <v>45</v>
       </c>
-      <c r="J318" t="s">
+      <c r="J319" t="s">
         <v>42</v>
       </c>
-      <c r="K318" s="18">
-        <v>0</v>
-      </c>
-      <c r="L318" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A319" s="5" t="s">
+      <c r="K319" s="18">
         <v>12</v>
       </c>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
-      <c r="D319" s="5"/>
-      <c r="E319" s="5"/>
-      <c r="F319" s="5"/>
-      <c r="G319" s="5"/>
-      <c r="H319" s="5"/>
-      <c r="I319" s="5"/>
-      <c r="J319" s="6"/>
-      <c r="K319" s="6"/>
-      <c r="L319" s="6"/>
-      <c r="M319" s="6"/>
-      <c r="N319" s="6"/>
+      <c r="L319" t="s">
+        <v>39</v>
+      </c>
+      <c r="N319" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="G320" t="s">
         <v>90</v>
@@ -7607,13 +7618,10 @@
         <v>42</v>
       </c>
       <c r="K320" s="18">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L320" t="s">
         <v>39</v>
-      </c>
-      <c r="M320" t="s">
-        <v>184</v>
       </c>
       <c r="N320" s="27" t="s">
         <v>179</v>
@@ -7621,7 +7629,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="G321" t="s">
         <v>90</v>
@@ -7633,21 +7641,15 @@
         <v>42</v>
       </c>
       <c r="K321" s="18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L321" t="s">
         <v>39</v>
-      </c>
-      <c r="M321" t="s">
-        <v>185</v>
-      </c>
-      <c r="N321" s="27" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" s="18" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="G322" t="s">
         <v>90</v>
@@ -7659,47 +7661,33 @@
         <v>42</v>
       </c>
       <c r="K322" s="18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L322" t="s">
         <v>39</v>
       </c>
-      <c r="M322" t="s">
-        <v>183</v>
-      </c>
-      <c r="N322" s="27" t="s">
-        <v>179</v>
-      </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="G323" t="s">
-        <v>90</v>
-      </c>
-      <c r="H323" t="s">
-        <v>45</v>
-      </c>
-      <c r="J323" t="s">
-        <v>42</v>
-      </c>
-      <c r="K323" s="18">
-        <v>9</v>
-      </c>
-      <c r="L323" t="s">
-        <v>39</v>
-      </c>
-      <c r="M323" t="s">
-        <v>187</v>
-      </c>
-      <c r="N323" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="A323" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B323" s="5"/>
+      <c r="C323" s="5"/>
+      <c r="D323" s="5"/>
+      <c r="E323" s="5"/>
+      <c r="F323" s="5"/>
+      <c r="G323" s="5"/>
+      <c r="H323" s="5"/>
+      <c r="I323" s="5"/>
+      <c r="J323" s="6"/>
+      <c r="K323" s="6"/>
+      <c r="L323" s="6"/>
+      <c r="M323" s="6"/>
+      <c r="N323" s="6"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="18" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G324" t="s">
         <v>90</v>
@@ -7711,13 +7699,13 @@
         <v>42</v>
       </c>
       <c r="K324" s="18">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L324" t="s">
         <v>39</v>
       </c>
-      <c r="M324" s="27" t="s">
-        <v>186</v>
+      <c r="M324" t="s">
+        <v>184</v>
       </c>
       <c r="N324" s="27" t="s">
         <v>179</v>
@@ -7725,7 +7713,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G325" t="s">
         <v>90</v>
@@ -7736,37 +7724,51 @@
       <c r="J325" t="s">
         <v>42</v>
       </c>
-      <c r="K325" s="7">
-        <f>AVERAGE(K321:K324)</f>
+      <c r="K325" s="18">
         <v>13</v>
       </c>
       <c r="L325" t="s">
         <v>39</v>
       </c>
-      <c r="M325" s="27"/>
-      <c r="N325" s="27"/>
+      <c r="M325" t="s">
+        <v>185</v>
+      </c>
+      <c r="N325" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A326" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B326" s="5"/>
-      <c r="C326" s="5"/>
-      <c r="D326" s="5"/>
-      <c r="E326" s="5"/>
-      <c r="F326" s="5"/>
-      <c r="G326" s="5"/>
-      <c r="H326" s="5"/>
-      <c r="I326" s="5"/>
-      <c r="J326" s="6"/>
-      <c r="K326" s="6"/>
-      <c r="L326" s="6"/>
-      <c r="M326" s="6"/>
-      <c r="N326" s="6"/>
+      <c r="A326" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G326" t="s">
+        <v>90</v>
+      </c>
+      <c r="H326" t="s">
+        <v>45</v>
+      </c>
+      <c r="J326" t="s">
+        <v>42</v>
+      </c>
+      <c r="K326" s="18">
+        <v>19</v>
+      </c>
+      <c r="L326" t="s">
+        <v>39</v>
+      </c>
+      <c r="M326" t="s">
+        <v>183</v>
+      </c>
+      <c r="N326" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="18" t="s">
-        <v>259</v>
+        <v>113</v>
+      </c>
+      <c r="G327" t="s">
+        <v>90</v>
       </c>
       <c r="H327" t="s">
         <v>45</v>
@@ -7775,21 +7777,24 @@
         <v>42</v>
       </c>
       <c r="K327" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L327" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L327" t="s">
         <v>39</v>
       </c>
       <c r="M327" t="s">
-        <v>264</v>
-      </c>
-      <c r="N327" t="s">
+        <v>187</v>
+      </c>
+      <c r="N327" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="18" t="s">
-        <v>260</v>
+        <v>116</v>
+      </c>
+      <c r="G328" t="s">
+        <v>90</v>
       </c>
       <c r="H328" t="s">
         <v>45</v>
@@ -7798,21 +7803,24 @@
         <v>42</v>
       </c>
       <c r="K328" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L328" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M328" t="s">
-        <v>264</v>
-      </c>
-      <c r="N328" t="s">
+        <v>11</v>
+      </c>
+      <c r="L328" t="s">
+        <v>39</v>
+      </c>
+      <c r="M328" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="N328" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="18" t="s">
-        <v>261</v>
+        <v>160</v>
+      </c>
+      <c r="G329" t="s">
+        <v>90</v>
       </c>
       <c r="H329" t="s">
         <v>45</v>
@@ -7820,67 +7828,60 @@
       <c r="J329" t="s">
         <v>42</v>
       </c>
-      <c r="K329" s="18">
+      <c r="K329" s="7">
+        <f>AVERAGE(K325:K328)</f>
+        <v>13</v>
+      </c>
+      <c r="L329" t="s">
+        <v>39</v>
+      </c>
+      <c r="M329" s="27"/>
+      <c r="N329" s="27"/>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A330" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B330" s="5"/>
+      <c r="C330" s="5"/>
+      <c r="D330" s="5"/>
+      <c r="E330" s="5"/>
+      <c r="F330" s="5"/>
+      <c r="G330" s="5"/>
+      <c r="H330" s="5"/>
+      <c r="I330" s="5"/>
+      <c r="J330" s="6"/>
+      <c r="K330" s="6"/>
+      <c r="L330" s="6"/>
+      <c r="M330" s="6"/>
+      <c r="N330" s="6"/>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A331" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="H331" t="s">
+        <v>45</v>
+      </c>
+      <c r="J331" t="s">
+        <v>42</v>
+      </c>
+      <c r="K331" s="18">
         <v>7.9</v>
       </c>
-      <c r="L329" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M329" t="s">
+      <c r="L331" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M331" t="s">
         <v>264</v>
       </c>
-      <c r="N329" t="s">
+      <c r="N331" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="H330" t="s">
-        <v>45</v>
-      </c>
-      <c r="J330" t="s">
-        <v>42</v>
-      </c>
-      <c r="K330" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L330" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M330" t="s">
-        <v>264</v>
-      </c>
-      <c r="N330" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A331" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B331" s="5"/>
-      <c r="C331" s="5"/>
-      <c r="D331" s="5"/>
-      <c r="E331" s="5"/>
-      <c r="F331" s="5"/>
-      <c r="G331" s="5"/>
-      <c r="H331" s="5"/>
-      <c r="I331" s="5"/>
-      <c r="J331" s="6"/>
-      <c r="K331" s="6"/>
-      <c r="L331" s="6"/>
-      <c r="M331" s="6"/>
-      <c r="N331" s="6"/>
-    </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A332" s="7"/>
-      <c r="B332" t="s">
-        <v>84</v>
-      </c>
-      <c r="G332" t="s">
-        <v>90</v>
+      <c r="A332" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H332" t="s">
         <v>45</v>
@@ -7888,43 +7889,45 @@
       <c r="J332" t="s">
         <v>42</v>
       </c>
-      <c r="K332" s="16">
-        <v>17</v>
-      </c>
-      <c r="L332" t="s">
+      <c r="K332" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L332" s="18" t="s">
         <v>39</v>
       </c>
       <c r="M332" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="N332" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B333" s="5"/>
-      <c r="C333" s="5"/>
-      <c r="D333" s="5"/>
-      <c r="E333" s="5"/>
-      <c r="F333" s="5"/>
-      <c r="G333" s="5"/>
-      <c r="H333" s="5"/>
-      <c r="I333" s="5"/>
-      <c r="J333" s="6"/>
-      <c r="K333" s="6"/>
-      <c r="L333" s="6"/>
-      <c r="M333" s="6"/>
-      <c r="N333" s="6"/>
+      <c r="A333" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="H333" t="s">
+        <v>45</v>
+      </c>
+      <c r="J333" t="s">
+        <v>42</v>
+      </c>
+      <c r="K333" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L333" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M333" t="s">
+        <v>264</v>
+      </c>
+      <c r="N333" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>57</v>
-      </c>
-      <c r="G334" t="s">
-        <v>90</v>
+      <c r="A334" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="H334" t="s">
         <v>45</v>
@@ -7932,95 +7935,105 @@
       <c r="J334" t="s">
         <v>42</v>
       </c>
-      <c r="K334" s="7">
+      <c r="K334" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L334" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M334" t="s">
+        <v>264</v>
+      </c>
+      <c r="N334" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A335" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" s="5"/>
+      <c r="C335" s="5"/>
+      <c r="D335" s="5"/>
+      <c r="E335" s="5"/>
+      <c r="F335" s="5"/>
+      <c r="G335" s="5"/>
+      <c r="H335" s="5"/>
+      <c r="I335" s="5"/>
+      <c r="J335" s="6"/>
+      <c r="K335" s="6"/>
+      <c r="L335" s="6"/>
+      <c r="M335" s="6"/>
+      <c r="N335" s="6"/>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A336" s="7"/>
+      <c r="B336" t="s">
+        <v>84</v>
+      </c>
+      <c r="G336" t="s">
+        <v>90</v>
+      </c>
+      <c r="H336" t="s">
+        <v>45</v>
+      </c>
+      <c r="J336" t="s">
+        <v>42</v>
+      </c>
+      <c r="K336" s="16">
+        <v>17</v>
+      </c>
+      <c r="L336" t="s">
+        <v>39</v>
+      </c>
+      <c r="M336" t="s">
+        <v>180</v>
+      </c>
+      <c r="N336" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A337" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" s="5"/>
+      <c r="C337" s="5"/>
+      <c r="D337" s="5"/>
+      <c r="E337" s="5"/>
+      <c r="F337" s="5"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="5"/>
+      <c r="I337" s="5"/>
+      <c r="J337" s="6"/>
+      <c r="K337" s="6"/>
+      <c r="L337" s="6"/>
+      <c r="M337" s="6"/>
+      <c r="N337" s="6"/>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>57</v>
+      </c>
+      <c r="G338" t="s">
+        <v>90</v>
+      </c>
+      <c r="H338" t="s">
+        <v>45</v>
+      </c>
+      <c r="J338" t="s">
+        <v>42</v>
+      </c>
+      <c r="K338" s="7">
         <v>2.4</v>
       </c>
-      <c r="L334" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>101</v>
-      </c>
-      <c r="G335" t="s">
-        <v>90</v>
-      </c>
-      <c r="H335" t="s">
-        <v>45</v>
-      </c>
-      <c r="J335" t="s">
-        <v>42</v>
-      </c>
-      <c r="K335" s="7">
-        <v>15.4</v>
-      </c>
-      <c r="L335" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A336" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
-      <c r="D336" s="5"/>
-      <c r="E336" s="5"/>
-      <c r="F336" s="5"/>
-      <c r="G336" s="5"/>
-      <c r="H336" s="5"/>
-      <c r="I336" s="5"/>
-      <c r="J336" s="6"/>
-      <c r="K336" s="6"/>
-      <c r="L336" s="6"/>
-      <c r="M336" s="6"/>
-      <c r="N336" s="6"/>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B337" t="s">
-        <v>224</v>
-      </c>
-      <c r="H337" t="s">
-        <v>45</v>
-      </c>
-      <c r="J337" t="s">
-        <v>42</v>
-      </c>
-      <c r="K337">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="L337" t="s">
-        <v>39</v>
-      </c>
-      <c r="M337" t="s">
-        <v>231</v>
-      </c>
-      <c r="N337" s="27" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B338" s="5"/>
-      <c r="C338" s="5"/>
-      <c r="D338" s="5"/>
-      <c r="E338" s="5"/>
-      <c r="F338" s="5"/>
-      <c r="G338" s="5"/>
-      <c r="H338" s="5"/>
-      <c r="I338" s="5"/>
-      <c r="J338" s="6"/>
-      <c r="K338" s="6"/>
-      <c r="L338" s="6"/>
-      <c r="M338" s="6"/>
-      <c r="N338" s="6"/>
+      <c r="L338" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="G339" t="s">
         <v>90</v>
@@ -8031,57 +8044,54 @@
       <c r="J339" t="s">
         <v>42</v>
       </c>
-      <c r="K339" s="24">
-        <v>1</v>
+      <c r="K339" s="7">
+        <v>15.4</v>
       </c>
       <c r="L339" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B340" s="5"/>
-      <c r="C340" s="5"/>
-      <c r="D340" s="5"/>
-      <c r="E340" s="5"/>
-      <c r="F340" s="5"/>
-      <c r="G340" s="5"/>
-      <c r="H340" s="5"/>
-      <c r="I340" s="5"/>
-      <c r="J340" s="6"/>
-      <c r="K340" s="6"/>
-      <c r="L340" s="6"/>
-      <c r="M340" s="6"/>
-      <c r="N340" s="6"/>
+      <c r="A340" t="s">
+        <v>294</v>
+      </c>
+      <c r="G340" t="s">
+        <v>90</v>
+      </c>
+      <c r="H340" t="s">
+        <v>45</v>
+      </c>
+      <c r="J340" t="s">
+        <v>42</v>
+      </c>
+      <c r="K340" s="7">
+        <v>0</v>
+      </c>
+      <c r="L340" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>245</v>
-      </c>
-      <c r="H341" t="s">
-        <v>45</v>
-      </c>
-      <c r="J341" t="s">
-        <v>42</v>
-      </c>
-      <c r="K341" s="18">
-        <v>24.7</v>
-      </c>
-      <c r="L341" t="s">
-        <v>39</v>
-      </c>
-      <c r="M341" t="s">
-        <v>253</v>
-      </c>
-      <c r="N341" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="A341" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B341" s="5"/>
+      <c r="C341" s="5"/>
+      <c r="D341" s="5"/>
+      <c r="E341" s="5"/>
+      <c r="F341" s="5"/>
+      <c r="G341" s="5"/>
+      <c r="H341" s="5"/>
+      <c r="I341" s="5"/>
+      <c r="J341" s="6"/>
+      <c r="K341" s="6"/>
+      <c r="L341" s="6"/>
+      <c r="M341" s="6"/>
+      <c r="N341" s="6"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>248</v>
+      <c r="B342" t="s">
+        <v>224</v>
       </c>
       <c r="H342" t="s">
         <v>45</v>
@@ -8089,45 +8099,43 @@
       <c r="J342" t="s">
         <v>42</v>
       </c>
-      <c r="K342" s="18">
-        <v>8</v>
+      <c r="K342">
+        <v>34.200000000000003</v>
       </c>
       <c r="L342" t="s">
         <v>39</v>
       </c>
       <c r="M342" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="N342" s="27" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>246</v>
-      </c>
-      <c r="H343" t="s">
-        <v>45</v>
-      </c>
-      <c r="J343" t="s">
-        <v>42</v>
-      </c>
-      <c r="K343">
-        <v>7.9</v>
-      </c>
-      <c r="L343" t="s">
-        <v>39</v>
-      </c>
-      <c r="M343" t="s">
-        <v>266</v>
-      </c>
-      <c r="N343" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="A343" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B343" s="5"/>
+      <c r="C343" s="5"/>
+      <c r="D343" s="5"/>
+      <c r="E343" s="5"/>
+      <c r="F343" s="5"/>
+      <c r="G343" s="5"/>
+      <c r="H343" s="5"/>
+      <c r="I343" s="5"/>
+      <c r="J343" s="6"/>
+      <c r="K343" s="6"/>
+      <c r="L343" s="6"/>
+      <c r="M343" s="6"/>
+      <c r="N343" s="6"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>249</v>
+        <v>138</v>
+      </c>
+      <c r="G344" t="s">
+        <v>90</v>
       </c>
       <c r="H344" t="s">
         <v>45</v>
@@ -8135,16 +8143,120 @@
       <c r="J344" t="s">
         <v>42</v>
       </c>
-      <c r="K344">
+      <c r="K344" s="24">
+        <v>1</v>
+      </c>
+      <c r="L344" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A345" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B345" s="5"/>
+      <c r="C345" s="5"/>
+      <c r="D345" s="5"/>
+      <c r="E345" s="5"/>
+      <c r="F345" s="5"/>
+      <c r="G345" s="5"/>
+      <c r="H345" s="5"/>
+      <c r="I345" s="5"/>
+      <c r="J345" s="6"/>
+      <c r="K345" s="6"/>
+      <c r="L345" s="6"/>
+      <c r="M345" s="6"/>
+      <c r="N345" s="6"/>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>245</v>
+      </c>
+      <c r="H346" t="s">
+        <v>45</v>
+      </c>
+      <c r="J346" t="s">
+        <v>42</v>
+      </c>
+      <c r="K346" s="18">
+        <v>24.7</v>
+      </c>
+      <c r="L346" t="s">
+        <v>39</v>
+      </c>
+      <c r="M346" t="s">
+        <v>253</v>
+      </c>
+      <c r="N346" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>248</v>
+      </c>
+      <c r="H347" t="s">
+        <v>45</v>
+      </c>
+      <c r="J347" t="s">
+        <v>42</v>
+      </c>
+      <c r="K347" s="18">
+        <v>8</v>
+      </c>
+      <c r="L347" t="s">
+        <v>39</v>
+      </c>
+      <c r="M347" t="s">
+        <v>178</v>
+      </c>
+      <c r="N347" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>246</v>
+      </c>
+      <c r="H348" t="s">
+        <v>45</v>
+      </c>
+      <c r="J348" t="s">
+        <v>42</v>
+      </c>
+      <c r="K348">
+        <v>7.9</v>
+      </c>
+      <c r="L348" t="s">
+        <v>39</v>
+      </c>
+      <c r="M348" t="s">
+        <v>266</v>
+      </c>
+      <c r="N348" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>249</v>
+      </c>
+      <c r="H349" t="s">
+        <v>45</v>
+      </c>
+      <c r="J349" t="s">
+        <v>42</v>
+      </c>
+      <c r="K349">
         <v>4.7</v>
       </c>
-      <c r="L344" t="s">
-        <v>39</v>
-      </c>
-      <c r="M344" t="s">
+      <c r="L349" t="s">
+        <v>39</v>
+      </c>
+      <c r="M349" t="s">
         <v>254</v>
       </c>
-      <c r="N344" s="27" t="s">
+      <c r="N349" s="27" t="s">
         <v>179</v>
       </c>
     </row>
@@ -8156,7 +8268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -8215,29 +8327,29 @@
       <c r="F2" s="30">
         <v>1</v>
       </c>
-      <c r="G2" s="31">
-        <f>F2*(1.006^5)</f>
-        <v>1.030362166487776</v>
-      </c>
-      <c r="H2" s="31">
-        <f t="shared" ref="H2:L2" si="0">G2*(1.006^5)</f>
-        <v>1.0616461941293835</v>
-      </c>
-      <c r="I2" s="31">
-        <f t="shared" si="0"/>
-        <v>1.0938800726266538</v>
-      </c>
-      <c r="J2" s="31">
-        <f t="shared" si="0"/>
-        <v>1.1270926415094047</v>
-      </c>
-      <c r="K2" s="31">
-        <f t="shared" si="0"/>
-        <v>1.1613136159380604</v>
-      </c>
-      <c r="L2" s="31">
-        <f t="shared" si="0"/>
-        <v>1.1965736132896929</v>
+      <c r="G2" s="1">
+        <f>10642196/(5222847+5156448)</f>
+        <v>1.0253293696729884</v>
+      </c>
+      <c r="H2" s="1">
+        <f>10884214/(5222847+5156448)</f>
+        <v>1.048646752982741</v>
+      </c>
+      <c r="I2" s="1">
+        <f>11101837/(5222847+5156448)</f>
+        <v>1.0696137839805111</v>
+      </c>
+      <c r="J2" s="1">
+        <f>11328285/(5222847+5156448)</f>
+        <v>1.0914310654047312</v>
+      </c>
+      <c r="K2" s="1">
+        <f>11557052/(5222847+5156448)</f>
+        <v>1.1134717724084342</v>
+      </c>
+      <c r="L2" s="1">
+        <f>11761182/(5222847+5156448)</f>
+        <v>1.1331388114510668</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -8274,23 +8386,44 @@
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <f>F4*(0.99^5)</f>
-        <v>0.95099004989999991</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" ref="H4:J4" si="1">G4*(0.99^5)</f>
-        <v>0.9043820750088043</v>
+        <v>0.85</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="1"/>
-        <v>0.86005835464128821</v>
-      </c>
-      <c r="J4" s="1">
-        <f t="shared" si="1"/>
-        <v>0.81790693759723054</v>
+        <v>0.75</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0.7</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="9870"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="303">
   <si>
     <t>parameter</t>
   </si>
@@ -955,6 +955,24 @@
   </si>
   <si>
     <t>By-products??</t>
+  </si>
+  <si>
+    <t>horses</t>
+  </si>
+  <si>
+    <t>heads</t>
+  </si>
+  <si>
+    <t>Recreational horses</t>
+  </si>
+  <si>
+    <t>1000 heads</t>
+  </si>
+  <si>
+    <t>Current number of horses</t>
+  </si>
+  <si>
+    <t>Other non-food</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N349"/>
+  <dimension ref="A1:N353"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -2975,380 +2993,363 @@
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="A92" t="s">
+        <v>299</v>
+      </c>
+      <c r="B92" t="s">
+        <v>217</v>
+      </c>
+      <c r="J92" t="s">
+        <v>213</v>
+      </c>
+      <c r="K92">
+        <v>355.5</v>
+      </c>
+      <c r="L92" t="s">
+        <v>300</v>
+      </c>
+      <c r="M92" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J93" t="s">
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J95" t="s">
         <v>214</v>
       </c>
-      <c r="L93" t="s">
+      <c r="L95" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>26</v>
-      </c>
-      <c r="I96" t="s">
-        <v>53</v>
-      </c>
-      <c r="J96" t="s">
-        <v>56</v>
-      </c>
-      <c r="K96">
-        <v>25</v>
-      </c>
-      <c r="L96" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>26</v>
-      </c>
-      <c r="I97" t="s">
-        <v>54</v>
-      </c>
-      <c r="J97" t="s">
-        <v>56</v>
-      </c>
-      <c r="K97">
-        <v>2</v>
-      </c>
-      <c r="L97" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>26</v>
       </c>
       <c r="I98" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J98" t="s">
         <v>56</v>
       </c>
-      <c r="K98" s="7">
-        <v>10.5</v>
+      <c r="K98">
+        <v>25</v>
       </c>
       <c r="L98" t="s">
         <v>39</v>
       </c>
-      <c r="M98" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="I99" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J99" t="s">
         <v>56</v>
       </c>
       <c r="K99">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L99" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="I100" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J100" t="s">
         <v>56</v>
       </c>
-      <c r="K100">
-        <v>7</v>
+      <c r="K100" s="7">
+        <v>10.5</v>
       </c>
       <c r="L100" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M100" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>109</v>
       </c>
       <c r="I101" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J101" t="s">
         <v>56</v>
       </c>
-      <c r="K101" s="7">
-        <v>15</v>
+      <c r="K101">
+        <v>17</v>
       </c>
       <c r="L101" t="s">
         <v>39</v>
       </c>
-      <c r="M101" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I102" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J102" t="s">
         <v>56</v>
       </c>
       <c r="K102">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L102" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I103" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J103" t="s">
         <v>56</v>
       </c>
-      <c r="K103">
-        <v>10</v>
+      <c r="K103" s="7">
+        <v>15</v>
       </c>
       <c r="L103" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M103" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>114</v>
       </c>
       <c r="I104" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J104" t="s">
         <v>56</v>
       </c>
-      <c r="K104" s="7">
-        <v>2</v>
+      <c r="K104">
+        <v>19</v>
       </c>
       <c r="L104" t="s">
         <v>39</v>
       </c>
-      <c r="M104" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="I105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J105" t="s">
         <v>56</v>
       </c>
       <c r="K105">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L105" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="I106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J106" t="s">
         <v>56</v>
       </c>
-      <c r="K106">
-        <v>10</v>
+      <c r="K106" s="7">
+        <v>2</v>
       </c>
       <c r="L106" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M106" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>262</v>
       </c>
       <c r="I107" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J107" t="s">
         <v>56</v>
       </c>
-      <c r="K107" s="7">
-        <v>2</v>
+      <c r="K107">
+        <v>19</v>
       </c>
       <c r="L107" t="s">
         <v>39</v>
       </c>
-      <c r="M107" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J108" t="s">
         <v>56</v>
       </c>
       <c r="K108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L108" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="I109" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J109" t="s">
         <v>56</v>
       </c>
-      <c r="K109">
+      <c r="K109" s="7">
+        <v>2</v>
+      </c>
+      <c r="L109" t="s">
+        <v>39</v>
+      </c>
+      <c r="M109" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>84</v>
+      </c>
+      <c r="I110" t="s">
+        <v>53</v>
+      </c>
+      <c r="J110" t="s">
+        <v>56</v>
+      </c>
+      <c r="K110">
+        <v>11</v>
+      </c>
+      <c r="L110" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s">
+        <v>54</v>
+      </c>
+      <c r="J111" t="s">
+        <v>56</v>
+      </c>
+      <c r="K111">
         <f>0.5</f>
         <v>0.5</v>
       </c>
-      <c r="L109" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
+      <c r="L111" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
         <v>84</v>
       </c>
-      <c r="I110" t="s">
+      <c r="I112" t="s">
         <v>55</v>
-      </c>
-      <c r="J110" t="s">
-        <v>56</v>
-      </c>
-      <c r="K110" s="7">
-        <v>1</v>
-      </c>
-      <c r="L110" t="s">
-        <v>39</v>
-      </c>
-      <c r="M110" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
-        <v>58</v>
-      </c>
-      <c r="I111" t="s">
-        <v>53</v>
-      </c>
-      <c r="J111" t="s">
-        <v>56</v>
-      </c>
-      <c r="K111">
-        <v>11</v>
-      </c>
-      <c r="L111" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>58</v>
-      </c>
-      <c r="I112" t="s">
-        <v>54</v>
       </c>
       <c r="J112" t="s">
         <v>56</v>
       </c>
-      <c r="K112">
-        <v>4</v>
+      <c r="K112" s="7">
+        <v>1</v>
       </c>
       <c r="L112" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M112" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>58</v>
       </c>
       <c r="I113" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J113" t="s">
         <v>56</v>
       </c>
-      <c r="K113" s="7">
-        <v>5</v>
+      <c r="K113">
+        <v>11</v>
       </c>
       <c r="L113" t="s">
         <v>39</v>
       </c>
-      <c r="M113" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="I114" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J114" t="s">
         <v>56</v>
@@ -3360,311 +3361,305 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="I115" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J115" t="s">
         <v>56</v>
       </c>
-      <c r="K115">
-        <v>1</v>
+      <c r="K115" s="7">
+        <v>5</v>
       </c>
       <c r="L115" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M115" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>224</v>
       </c>
       <c r="I116" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J116" t="s">
         <v>56</v>
       </c>
-      <c r="K116" s="7">
-        <v>5</v>
+      <c r="K116">
+        <v>4</v>
       </c>
       <c r="L116" t="s">
         <v>39</v>
       </c>
-      <c r="M116" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="I117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J117" t="s">
         <v>56</v>
       </c>
       <c r="K117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L117" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="I118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J118" t="s">
         <v>56</v>
       </c>
-      <c r="K118">
-        <v>1</v>
+      <c r="K118" s="7">
+        <v>5</v>
       </c>
       <c r="L118" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M118" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>139</v>
       </c>
       <c r="I119" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J119" t="s">
         <v>56</v>
       </c>
-      <c r="K119" s="7">
-        <v>5</v>
+      <c r="K119">
+        <v>4</v>
       </c>
       <c r="L119" t="s">
         <v>39</v>
       </c>
-      <c r="M119" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="I120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J120" t="s">
         <v>56</v>
       </c>
       <c r="K120">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L120" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="I121" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J121" t="s">
         <v>56</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="7">
         <v>5</v>
       </c>
       <c r="L121" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M121" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>237</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J122" t="s">
         <v>56</v>
       </c>
-      <c r="K122" s="7">
-        <v>5</v>
+      <c r="K122">
+        <v>13</v>
       </c>
       <c r="L122" t="s">
         <v>39</v>
       </c>
-      <c r="M122" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="I123" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J123" t="s">
         <v>56</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L123" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="I124" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J124" t="s">
         <v>56</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="7">
         <v>5</v>
       </c>
       <c r="L124" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M124" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>118</v>
       </c>
       <c r="I125" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J125" t="s">
         <v>56</v>
       </c>
-      <c r="K125" s="7">
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>118</v>
+      </c>
+      <c r="I126" t="s">
+        <v>54</v>
+      </c>
+      <c r="J126" t="s">
+        <v>56</v>
+      </c>
+      <c r="K126">
         <v>5</v>
       </c>
-      <c r="L125" t="s">
-        <v>39</v>
-      </c>
-      <c r="M125" s="7" t="s">
+      <c r="L126" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>118</v>
+      </c>
+      <c r="I127" t="s">
+        <v>55</v>
+      </c>
+      <c r="J127" t="s">
+        <v>56</v>
+      </c>
+      <c r="K127" s="7">
+        <v>5</v>
+      </c>
+      <c r="L127" t="s">
+        <v>39</v>
+      </c>
+      <c r="M127" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
-      <c r="I127" s="3"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
-      <c r="N127" s="4"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J128" s="8" t="s">
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J130" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K128" s="8">
+      <c r="K130" s="8">
         <v>0</v>
       </c>
-      <c r="L128" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M128" s="8" t="s">
+      <c r="L130" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M130" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J129" s="8" t="s">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J131" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="K129" s="8">
+      <c r="K131" s="8">
         <v>0</v>
       </c>
-      <c r="L129" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M129" s="8" t="s">
+      <c r="L131" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M131" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="5"/>
-      <c r="I130" s="5"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="6"/>
-      <c r="N130" s="6"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>192</v>
-      </c>
-      <c r="C131" t="s">
-        <v>38</v>
-      </c>
-      <c r="J131" t="s">
-        <v>88</v>
-      </c>
-      <c r="K131">
-        <v>79</v>
-      </c>
-      <c r="L131" t="s">
-        <v>39</v>
-      </c>
-      <c r="N131" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>192</v>
-      </c>
-      <c r="C132" t="s">
-        <v>38</v>
-      </c>
-      <c r="F132" t="s">
-        <v>122</v>
-      </c>
-      <c r="J132" t="s">
-        <v>89</v>
-      </c>
-      <c r="K132">
-        <v>19</v>
-      </c>
-      <c r="L132" t="s">
-        <v>39</v>
-      </c>
-      <c r="N132" t="s">
-        <v>98</v>
-      </c>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="6"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="6"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
@@ -3673,14 +3668,11 @@
       <c r="C133" t="s">
         <v>38</v>
       </c>
-      <c r="F133" t="s">
-        <v>123</v>
-      </c>
       <c r="J133" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K133">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="L133" t="s">
         <v>39</v>
@@ -3691,16 +3683,19 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C134" t="s">
         <v>38</v>
       </c>
+      <c r="F134" t="s">
+        <v>122</v>
+      </c>
       <c r="J134" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K134">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="L134" t="s">
         <v>39</v>
@@ -3710,59 +3705,44 @@
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A135" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="9"/>
+      <c r="A135" t="s">
+        <v>192</v>
+      </c>
+      <c r="C135" t="s">
+        <v>38</v>
+      </c>
+      <c r="F135" t="s">
+        <v>123</v>
+      </c>
       <c r="J135" t="s">
-        <v>88</v>
-      </c>
-      <c r="K135" s="9">
-        <v>72</v>
-      </c>
-      <c r="L135" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M135" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135" t="s">
+        <v>39</v>
+      </c>
       <c r="N135" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A136" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="9"/>
+      <c r="A136" t="s">
+        <v>197</v>
+      </c>
+      <c r="C136" t="s">
+        <v>38</v>
+      </c>
       <c r="J136" t="s">
-        <v>89</v>
-      </c>
-      <c r="K136" s="9">
-        <v>19</v>
-      </c>
-      <c r="L136" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M136" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136" t="s">
+        <v>39</v>
+      </c>
       <c r="N136" t="s">
         <v>98</v>
       </c>
@@ -3777,17 +3757,15 @@
       </c>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
-      <c r="F137" s="9" t="s">
-        <v>125</v>
-      </c>
+      <c r="F137" s="9"/>
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K137" s="9">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="L137" s="9" t="s">
         <v>39</v>
@@ -3799,7 +3777,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B138" s="9"/>
       <c r="C138" s="9" t="s">
@@ -3807,15 +3785,17 @@
       </c>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
+      <c r="F138" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
       <c r="J138" t="s">
-        <v>88</v>
-      </c>
-      <c r="K138" s="10">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="K138" s="9">
+        <v>19</v>
       </c>
       <c r="L138" s="9" t="s">
         <v>39</v>
@@ -3827,7 +3807,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B139" s="9"/>
       <c r="C139" s="9" t="s">
@@ -3844,10 +3824,10 @@
       <c r="J139" t="s">
         <v>89</v>
       </c>
-      <c r="K139" s="10">
+      <c r="K139" s="9">
         <v>9</v>
       </c>
-      <c r="L139" s="10" t="s">
+      <c r="L139" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M139" s="9"/>
@@ -3856,12 +3836,12 @@
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>194</v>
+      <c r="A140" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="B140" s="9"/>
-      <c r="C140" s="10" t="s">
-        <v>96</v>
+      <c r="C140" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -3873,9 +3853,9 @@
         <v>88</v>
       </c>
       <c r="K140" s="10">
-        <v>80</v>
-      </c>
-      <c r="L140" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L140" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M140" s="9"/>
@@ -3884,17 +3864,17 @@
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>194</v>
+      <c r="A141" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="B141" s="9"/>
-      <c r="C141" s="10" t="s">
-        <v>96</v>
+      <c r="C141" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
-      <c r="F141" s="10" t="s">
-        <v>126</v>
+      <c r="F141" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
@@ -3903,7 +3883,7 @@
         <v>89</v>
       </c>
       <c r="K141" s="10">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L141" s="10" t="s">
         <v>39</v>
@@ -3915,7 +3895,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B142" s="9"/>
       <c r="C142" s="10" t="s">
@@ -3923,7 +3903,7 @@
       </c>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
-      <c r="F142" s="10"/>
+      <c r="F142" s="9"/>
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
@@ -3931,7 +3911,7 @@
         <v>88</v>
       </c>
       <c r="K142" s="10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L142" s="10" t="s">
         <v>39</v>
@@ -3943,23 +3923,25 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B143" s="9"/>
       <c r="C143" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
+      <c r="F143" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K143" s="10">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L143" s="10" t="s">
         <v>39</v>
@@ -3971,25 +3953,23 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B144" s="9"/>
       <c r="C144" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
-      <c r="F144" s="10" t="s">
-        <v>127</v>
-      </c>
+      <c r="F144" s="10"/>
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="9"/>
       <c r="J144" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K144" s="10">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L144" s="10" t="s">
         <v>39</v>
@@ -4009,17 +3989,15 @@
       </c>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
-      <c r="F145" s="10" t="s">
-        <v>191</v>
-      </c>
+      <c r="F145" s="9"/>
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
       <c r="J145" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K145" s="10">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L145" s="10" t="s">
         <v>39</v>
@@ -4031,7 +4009,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B146" s="9"/>
       <c r="C146" s="10" t="s">
@@ -4039,15 +4017,17 @@
       </c>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
-      <c r="F146" s="10"/>
+      <c r="F146" s="10" t="s">
+        <v>127</v>
+      </c>
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
       <c r="J146" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K146" s="10">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="L146" s="10" t="s">
         <v>39</v>
@@ -4059,7 +4039,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B147" s="9"/>
       <c r="C147" s="10" t="s">
@@ -4088,78 +4068,84 @@
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
-      <c r="M148" s="6"/>
-      <c r="N148" s="6"/>
+      <c r="A148" t="s">
+        <v>200</v>
+      </c>
+      <c r="B148" s="9"/>
+      <c r="C148" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" s="9"/>
+      <c r="E148" s="9"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="9"/>
+      <c r="I148" s="9"/>
+      <c r="J148" t="s">
+        <v>88</v>
+      </c>
+      <c r="K148" s="10">
+        <v>73</v>
+      </c>
+      <c r="L148" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M148" s="9"/>
+      <c r="N148" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" s="18" t="s">
-        <v>105</v>
+      <c r="A149" t="s">
+        <v>200</v>
       </c>
       <c r="B149" s="9"/>
       <c r="C149" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
-      <c r="F149" s="10"/>
+      <c r="F149" s="10" t="s">
+        <v>191</v>
+      </c>
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="9"/>
       <c r="J149" t="s">
-        <v>88</v>
-      </c>
-      <c r="K149" s="12">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="K149" s="10">
+        <v>27</v>
       </c>
       <c r="L149" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M149" s="11" t="s">
-        <v>110</v>
+      <c r="M149" s="9"/>
+      <c r="N149" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B150" s="9"/>
-      <c r="C150" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="10"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
-      <c r="I150" s="9"/>
-      <c r="J150" t="s">
-        <v>88</v>
-      </c>
-      <c r="K150" s="10">
-        <v>50</v>
-      </c>
-      <c r="L150" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M150" s="9"/>
+      <c r="A150" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="6"/>
+      <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
+      <c r="N150" s="6"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B151" s="9"/>
       <c r="C151" s="10" t="s">
@@ -4167,30 +4153,30 @@
       </c>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
-      <c r="F151" s="10" t="s">
-        <v>128</v>
-      </c>
+      <c r="F151" s="10"/>
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" t="s">
-        <v>89</v>
-      </c>
-      <c r="K151" s="10">
-        <v>50</v>
+        <v>88</v>
+      </c>
+      <c r="K151" s="12">
+        <v>100</v>
       </c>
       <c r="L151" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M151" s="9"/>
+      <c r="M151" s="11" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="18" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="B152" s="9"/>
-      <c r="C152" s="12" t="s">
-        <v>112</v>
+      <c r="C152" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -4201,132 +4187,150 @@
       <c r="J152" t="s">
         <v>88</v>
       </c>
-      <c r="K152" s="19">
-        <v>20</v>
+      <c r="K152" s="10">
+        <v>50</v>
       </c>
       <c r="L152" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M152" s="11" t="s">
-        <v>227</v>
-      </c>
+      <c r="M152" s="9"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B153" s="9"/>
       <c r="C153" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
-      <c r="F153" s="10"/>
+      <c r="F153" s="10" t="s">
+        <v>128</v>
+      </c>
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
       <c r="J153" t="s">
-        <v>88</v>
-      </c>
-      <c r="K153" s="19">
-        <v>19</v>
+        <v>89</v>
+      </c>
+      <c r="K153" s="10">
+        <v>50</v>
       </c>
       <c r="L153" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M153" s="20"/>
+      <c r="M153" s="9"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="B154" s="9"/>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="12" t="s">
         <v>112</v>
       </c>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
-      <c r="F154" t="s">
-        <v>205</v>
-      </c>
+      <c r="F154" s="10"/>
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
       <c r="J154" t="s">
+        <v>88</v>
+      </c>
+      <c r="K154" s="19">
+        <v>20</v>
+      </c>
+      <c r="L154" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M154" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B155" s="9"/>
+      <c r="C155" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D155" s="9"/>
+      <c r="E155" s="9"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
+      <c r="I155" s="9"/>
+      <c r="J155" t="s">
+        <v>88</v>
+      </c>
+      <c r="K155" s="19">
+        <v>19</v>
+      </c>
+      <c r="L155" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M155" s="20"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B156" s="9"/>
+      <c r="C156" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D156" s="9"/>
+      <c r="E156" s="9"/>
+      <c r="F156" t="s">
+        <v>205</v>
+      </c>
+      <c r="G156" s="9"/>
+      <c r="H156" s="9"/>
+      <c r="I156" s="9"/>
+      <c r="J156" t="s">
         <v>89</v>
       </c>
-      <c r="K154" s="29">
+      <c r="K156" s="29">
         <f>0.02*0.5*100/(844/1000)/0.9</f>
         <v>1.3164823591363877</v>
       </c>
-      <c r="L154" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M154" s="20" t="s">
+      <c r="L156" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M156" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="N154" s="10" t="s">
+      <c r="N156" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="5"/>
-      <c r="I155" s="5"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
-      <c r="L155" s="6"/>
-      <c r="M155" s="6"/>
-      <c r="N155" s="6"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C156" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J156" t="s">
-        <v>88</v>
-      </c>
-      <c r="K156" s="19">
-        <v>100</v>
-      </c>
-      <c r="L156" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="J157" t="s">
-        <v>88</v>
-      </c>
-      <c r="K157" s="19">
-        <v>100</v>
-      </c>
-      <c r="L157" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="6"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="6"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J158" t="s">
         <v>88</v>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J159" t="s">
         <v>88</v>
@@ -4357,10 +4361,10 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J160" t="s">
         <v>88</v>
@@ -4374,10 +4378,10 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J161" t="s">
         <v>88</v>
@@ -4391,18 +4395,11 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B162" s="9"/>
+        <v>151</v>
+      </c>
       <c r="C162" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="10"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
-      <c r="I162" s="9"/>
+        <v>157</v>
+      </c>
       <c r="J162" t="s">
         <v>88</v>
       </c>
@@ -4412,22 +4409,14 @@
       <c r="L162" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M162" s="11"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B163" s="9"/>
+        <v>152</v>
+      </c>
       <c r="C163" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="10"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="9"/>
-      <c r="I163" s="9"/>
+        <v>154</v>
+      </c>
       <c r="J163" t="s">
         <v>88</v>
       </c>
@@ -4437,15 +4426,14 @@
       <c r="L163" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M163" s="11"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="18" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B164" s="9"/>
       <c r="C164" s="10" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -4465,86 +4453,93 @@
       <c r="M164" s="11"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
-      <c r="D165" s="5"/>
-      <c r="E165" s="5"/>
-      <c r="F165" s="5"/>
-      <c r="G165" s="5"/>
-      <c r="H165" s="5"/>
-      <c r="I165" s="5"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
-      <c r="L165" s="6"/>
-      <c r="M165" s="6"/>
-      <c r="N165" s="6"/>
+      <c r="A165" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B165" s="9"/>
+      <c r="C165" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
+      <c r="I165" s="9"/>
+      <c r="J165" t="s">
+        <v>88</v>
+      </c>
+      <c r="K165" s="19">
+        <v>100</v>
+      </c>
+      <c r="L165" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M165" s="11"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
-        <v>259</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B166" s="9"/>
       <c r="C166" s="10" t="s">
-        <v>256</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D166" s="9"/>
+      <c r="E166" s="9"/>
+      <c r="F166" s="10"/>
+      <c r="G166" s="9"/>
+      <c r="H166" s="9"/>
+      <c r="I166" s="9"/>
       <c r="J166" t="s">
         <v>88</v>
       </c>
-      <c r="K166" s="18">
+      <c r="K166" s="19">
         <v>100</v>
       </c>
       <c r="L166" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M166" s="11"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="C167" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="J167" t="s">
-        <v>88</v>
-      </c>
-      <c r="K167" s="18">
-        <v>65</v>
-      </c>
-      <c r="L167" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="N167" t="s">
-        <v>98</v>
-      </c>
+      <c r="A167" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="6"/>
+      <c r="K167" s="6"/>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="6"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F168" s="20" t="s">
-        <v>257</v>
-      </c>
       <c r="J168" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K168" s="18">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L168" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="N168" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>256</v>
@@ -4553,7 +4548,7 @@
         <v>88</v>
       </c>
       <c r="K169" s="18">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="L169" s="18" t="s">
         <v>39</v>
@@ -4564,7 +4559,7 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>256</v>
@@ -4587,44 +4582,53 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J171" t="s">
         <v>88</v>
       </c>
       <c r="K171" s="18">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="L171" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="N171" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>286</v>
+        <v>256</v>
+      </c>
+      <c r="F172" s="20" t="s">
+        <v>257</v>
       </c>
       <c r="J172" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K172" s="18">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L172" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="N172" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="J173" t="s">
         <v>88</v>
@@ -4638,10 +4642,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J174" t="s">
         <v>88</v>
@@ -4655,10 +4659,10 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J175" t="s">
         <v>88</v>
@@ -4671,91 +4675,60 @@
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
-      <c r="I176" s="5"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
-      <c r="M176" s="6"/>
-      <c r="N176" s="6"/>
+      <c r="A176" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="J176" t="s">
+        <v>88</v>
+      </c>
+      <c r="K176" s="18">
+        <v>100</v>
+      </c>
+      <c r="L176" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B177" s="11"/>
-      <c r="C177" s="11"/>
-      <c r="D177" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E177" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F177" s="11"/>
-      <c r="G177" s="11"/>
-      <c r="H177" s="11"/>
-      <c r="I177" s="11"/>
+      <c r="A177" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>290</v>
+      </c>
       <c r="J177" t="s">
         <v>88</v>
       </c>
-      <c r="K177" s="13">
-        <f>100-K178</f>
-        <v>90.75</v>
-      </c>
-      <c r="L177" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M177" t="s">
-        <v>74</v>
-      </c>
-      <c r="N177" s="9" t="s">
-        <v>99</v>
+      <c r="K177" s="18">
+        <v>100</v>
+      </c>
+      <c r="L177" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B178" s="11"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E178" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F178" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G178" s="11"/>
-      <c r="H178" s="11"/>
-      <c r="I178" s="11"/>
-      <c r="J178" t="s">
-        <v>89</v>
-      </c>
-      <c r="K178" s="13">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
-      </c>
-      <c r="L178" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N178" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="A178" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="5"/>
+      <c r="J178" s="6"/>
+      <c r="K178" s="6"/>
+      <c r="L178" s="6"/>
+      <c r="M178" s="6"/>
+      <c r="N178" s="6"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B179" s="11"/>
       <c r="C179" s="11"/>
@@ -4774,13 +4747,13 @@
       </c>
       <c r="K179" s="13">
         <f>100-K180</f>
-        <v>93.25</v>
+        <v>90.75</v>
       </c>
       <c r="L179" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N179" s="9" t="s">
         <v>99</v>
@@ -4788,7 +4761,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B180" s="11"/>
       <c r="C180" s="11"/>
@@ -4808,8 +4781,8 @@
         <v>89</v>
       </c>
       <c r="K180" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="L180" s="11" t="s">
         <v>39</v>
@@ -4820,7 +4793,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B181" s="11"/>
       <c r="C181" s="11"/>
@@ -4845,7 +4818,7 @@
         <v>39</v>
       </c>
       <c r="M181" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N181" s="9" t="s">
         <v>99</v>
@@ -4853,7 +4826,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B182" s="11"/>
       <c r="C182" s="11"/>
@@ -4885,7 +4858,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -4903,14 +4876,14 @@
         <v>88</v>
       </c>
       <c r="K183" s="13">
-        <f>(100-K184)*0.1</f>
-        <v>9.3250000000000011</v>
+        <f>100-K184</f>
+        <v>93.25</v>
       </c>
       <c r="L183" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M183" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="N183" s="9" t="s">
         <v>99</v>
@@ -4918,7 +4891,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B184" s="11"/>
       <c r="C184" s="11"/>
@@ -4960,21 +4933,22 @@
       <c r="E185" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F185" s="11" t="s">
-        <v>73</v>
-      </c>
+      <c r="F185" s="11"/>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
       <c r="J185" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K185" s="13">
-        <f>(100-K184)*0.9</f>
-        <v>83.924999999999997</v>
+        <f>(100-K186)*0.1</f>
+        <v>9.3250000000000011</v>
       </c>
       <c r="L185" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="M185" t="s">
+        <v>83</v>
       </c>
       <c r="N185" s="9" t="s">
         <v>99</v>
@@ -4982,7 +4956,7 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B186" s="11"/>
       <c r="C186" s="11"/>
@@ -4990,32 +4964,31 @@
         <v>82</v>
       </c>
       <c r="E186" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F186" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F186" s="11"/>
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
       <c r="J186" t="s">
-        <v>88</v>
-      </c>
-      <c r="K186" s="11">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+        <v>89</v>
+      </c>
+      <c r="K186" s="13">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M186" t="s">
-        <v>81</v>
       </c>
       <c r="N186" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="12" t="s">
-        <v>72</v>
+      <c r="A187" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="B187" s="11"/>
       <c r="C187" s="11"/>
@@ -5023,24 +4996,23 @@
         <v>82</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F187" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="F187" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
       <c r="J187" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K187" s="13">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+        <f>(100-K186)*0.9</f>
+        <v>83.924999999999997</v>
       </c>
       <c r="L187" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M187" t="s">
-        <v>77</v>
       </c>
       <c r="N187" s="9" t="s">
         <v>99</v>
@@ -5048,7 +5020,7 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B188" s="11"/>
       <c r="C188" s="11"/>
@@ -5065,23 +5037,23 @@
       <c r="J188" t="s">
         <v>88</v>
       </c>
-      <c r="K188" s="13">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+      <c r="K188" s="11">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
       </c>
       <c r="L188" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M188" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N188" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="11" t="s">
-        <v>70</v>
+      <c r="A189" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="11"/>
@@ -5098,15 +5070,15 @@
       <c r="J189" t="s">
         <v>88</v>
       </c>
-      <c r="K189" s="11">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+      <c r="K189" s="13">
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
       </c>
       <c r="L189" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M189" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N189" s="9" t="s">
         <v>99</v>
@@ -5114,7 +5086,7 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B190" s="11"/>
       <c r="C190" s="11"/>
@@ -5132,136 +5104,137 @@
         <v>88</v>
       </c>
       <c r="K190" s="13">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
+      </c>
+      <c r="L190" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M190" t="s">
+        <v>78</v>
+      </c>
+      <c r="N190" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B191" s="11"/>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E191" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F191" s="11"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="11"/>
+      <c r="J191" t="s">
+        <v>88</v>
+      </c>
+      <c r="K191" s="11">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L191" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M191" t="s">
+        <v>79</v>
+      </c>
+      <c r="N191" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B192" s="11"/>
+      <c r="C192" s="11"/>
+      <c r="D192" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E192" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F192" s="11"/>
+      <c r="G192" s="11"/>
+      <c r="H192" s="11"/>
+      <c r="I192" s="11"/>
+      <c r="J192" t="s">
+        <v>88</v>
+      </c>
+      <c r="K192" s="13">
         <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
         <v>49.367088607594937</v>
       </c>
-      <c r="L190" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M190" t="s">
+      <c r="L192" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M192" t="s">
         <v>80</v>
       </c>
-      <c r="N190" s="9" t="s">
+      <c r="N192" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="11" t="s">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E191" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F191" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G191" s="9"/>
-      <c r="H191" s="9"/>
-      <c r="I191" s="9"/>
-      <c r="J191" t="s">
-        <v>89</v>
-      </c>
-      <c r="K191" s="15">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
-      </c>
-      <c r="L191" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M191" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="N191" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
-      <c r="G192" s="5"/>
-      <c r="H192" s="5"/>
-      <c r="I192" s="5"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
-      <c r="M192" s="6"/>
-      <c r="N192" s="6"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
-      <c r="D193" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E193" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F193" s="9"/>
+      <c r="D193" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E193" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F193" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="9"/>
       <c r="J193" t="s">
-        <v>88</v>
-      </c>
-      <c r="K193" s="10">
-        <v>73</v>
-      </c>
-      <c r="L193" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M193" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="K193" s="15">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="L193" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="N193" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F194" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G194" s="9"/>
-      <c r="H194" s="9"/>
-      <c r="I194" s="9"/>
-      <c r="J194" t="s">
-        <v>89</v>
-      </c>
-      <c r="K194" s="17">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="L194" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M194" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="N194" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="A194" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="6"/>
+      <c r="K194" s="6"/>
+      <c r="L194" s="6"/>
+      <c r="M194" s="6"/>
+      <c r="N194" s="6"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
@@ -5275,25 +5248,20 @@
       <c r="E195" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F195" s="9" t="s">
-        <v>130</v>
-      </c>
+      <c r="F195" s="9"/>
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="9"/>
       <c r="J195" t="s">
-        <v>89</v>
-      </c>
-      <c r="K195" s="17">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
+        <v>88</v>
+      </c>
+      <c r="K195" s="10">
+        <v>73</v>
       </c>
       <c r="L195" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M195" s="10" t="s">
-        <v>102</v>
-      </c>
+      <c r="M195" s="9"/>
       <c r="N195" s="9" t="s">
         <v>98</v>
       </c>
@@ -5311,7 +5279,7 @@
         <v>58</v>
       </c>
       <c r="F196" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
@@ -5320,8 +5288,8 @@
         <v>89</v>
       </c>
       <c r="K196" s="17">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="L196" s="9" t="s">
         <v>39</v>
@@ -5346,7 +5314,7 @@
         <v>58</v>
       </c>
       <c r="F197" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
@@ -5354,61 +5322,69 @@
       <c r="J197" t="s">
         <v>89</v>
       </c>
-      <c r="K197" s="10">
-        <v>18</v>
+      <c r="K197" s="17">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
       </c>
       <c r="L197" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M197" s="9"/>
+      <c r="M197" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="N197" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>101</v>
+      <c r="A198" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
-      <c r="D198" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E198" s="10" t="s">
+      <c r="D198" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E198" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F198" s="9"/>
+      <c r="F198" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="9"/>
       <c r="J198" t="s">
-        <v>88</v>
-      </c>
-      <c r="K198" s="10">
-        <v>71</v>
-      </c>
-      <c r="L198" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M198" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="K198" s="17">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L198" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M198" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="N198" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>101</v>
+      <c r="A199" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
-      <c r="D199" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E199" s="10" t="s">
+      <c r="D199" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E199" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F199" s="10" t="s">
-        <v>133</v>
+      <c r="F199" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
@@ -5416,16 +5392,13 @@
       <c r="J199" t="s">
         <v>89</v>
       </c>
-      <c r="K199" s="17">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
-      </c>
-      <c r="L199" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M199" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="K199" s="10">
+        <v>18</v>
+      </c>
+      <c r="L199" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M199" s="9"/>
       <c r="N199" s="9" t="s">
         <v>98</v>
       </c>
@@ -5442,25 +5415,20 @@
       <c r="E200" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F200" s="9" t="s">
-        <v>134</v>
-      </c>
+      <c r="F200" s="9"/>
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="9"/>
       <c r="J200" t="s">
-        <v>89</v>
-      </c>
-      <c r="K200" s="17">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
+        <v>88</v>
+      </c>
+      <c r="K200" s="10">
+        <v>71</v>
       </c>
       <c r="L200" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M200" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="M200" s="9"/>
       <c r="N200" s="9" t="s">
         <v>98</v>
       </c>
@@ -5478,7 +5446,7 @@
         <v>58</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
@@ -5487,8 +5455,8 @@
         <v>89</v>
       </c>
       <c r="K201" s="17">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
       </c>
       <c r="L201" s="10" t="s">
         <v>39</v>
@@ -5513,7 +5481,7 @@
         <v>58</v>
       </c>
       <c r="F202" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
@@ -5521,126 +5489,162 @@
       <c r="J202" t="s">
         <v>89</v>
       </c>
-      <c r="K202" s="10">
-        <v>12</v>
+      <c r="K202" s="17">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
       </c>
       <c r="L202" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M202" s="9"/>
+      <c r="M202" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="N202" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>294</v>
+        <v>101</v>
       </c>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="10" t="s">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F203" s="9"/>
+      <c r="F203" s="10" t="s">
+        <v>135</v>
+      </c>
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="9"/>
       <c r="J203" t="s">
-        <v>88</v>
-      </c>
-      <c r="K203" s="10">
-        <v>77</v>
+        <v>89</v>
+      </c>
+      <c r="K203" s="17">
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
       </c>
       <c r="L203" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M203" s="9"/>
-      <c r="N203" s="9"/>
+      <c r="M203" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="N203" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B204" s="11"/>
-      <c r="C204" s="11"/>
-      <c r="D204" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E204" s="12" t="s">
+      <c r="A204" t="s">
+        <v>101</v>
+      </c>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E204" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F204" s="12" t="s">
-        <v>296</v>
+      <c r="F204" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="9"/>
-      <c r="K204" s="10"/>
-      <c r="L204" s="10"/>
+      <c r="J204" t="s">
+        <v>89</v>
+      </c>
+      <c r="K204" s="10">
+        <v>12</v>
+      </c>
+      <c r="L204" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="M204" s="9"/>
-      <c r="N204" s="9"/>
+      <c r="N204" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="5" t="s">
+      <c r="A205" t="s">
+        <v>294</v>
+      </c>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9"/>
+      <c r="I205" s="9"/>
+      <c r="J205" t="s">
+        <v>88</v>
+      </c>
+      <c r="K205" s="10">
+        <v>77</v>
+      </c>
+      <c r="L205" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M205" s="9"/>
+      <c r="N205" s="9"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B206" s="11"/>
+      <c r="C206" s="11"/>
+      <c r="D206" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9"/>
+      <c r="I206" s="9"/>
+      <c r="K206" s="10"/>
+      <c r="L206" s="10"/>
+      <c r="M206" s="9"/>
+      <c r="N206" s="9"/>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-      <c r="H205" s="5"/>
-      <c r="I205" s="5"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
-      <c r="M205" s="6"/>
-      <c r="N205" s="6"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="B207" s="5"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
+      <c r="J207" s="6"/>
+      <c r="K207" s="6"/>
+      <c r="L207" s="6"/>
+      <c r="M207" s="6"/>
+      <c r="N207" s="6"/>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
         <v>219</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C208" t="s">
         <v>228</v>
-      </c>
-      <c r="J206" t="s">
-        <v>88</v>
-      </c>
-      <c r="K206">
-        <v>100</v>
-      </c>
-      <c r="L206" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="C207" t="s">
-        <v>229</v>
-      </c>
-      <c r="J207" t="s">
-        <v>88</v>
-      </c>
-      <c r="K207">
-        <v>100</v>
-      </c>
-      <c r="L207" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C208" t="s">
-        <v>230</v>
       </c>
       <c r="J208" t="s">
         <v>88</v>
@@ -5653,92 +5657,76 @@
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" s="7" t="s">
+      <c r="A209" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C209" t="s">
+        <v>229</v>
+      </c>
+      <c r="J209" t="s">
+        <v>88</v>
+      </c>
+      <c r="K209">
+        <v>100</v>
+      </c>
+      <c r="L209" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C210" t="s">
+        <v>230</v>
+      </c>
+      <c r="J210" t="s">
+        <v>88</v>
+      </c>
+      <c r="K210">
+        <v>100</v>
+      </c>
+      <c r="L210" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A210" s="7" t="s">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="10"/>
-      <c r="E210" s="10"/>
-      <c r="F210" s="9"/>
-      <c r="G210" s="9"/>
-      <c r="H210" s="9"/>
-      <c r="I210" s="9"/>
-      <c r="M210" s="9"/>
-      <c r="N210" s="9"/>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10"/>
+      <c r="F212" s="9"/>
+      <c r="G212" s="9"/>
+      <c r="H212" s="9"/>
+      <c r="I212" s="9"/>
+      <c r="M212" s="9"/>
+      <c r="N212" s="9"/>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
-      <c r="H211" s="5"/>
-      <c r="I211" s="5"/>
-      <c r="J211" s="6"/>
-      <c r="K211" s="6"/>
-      <c r="L211" s="6"/>
-      <c r="M211" s="6"/>
-      <c r="N211" s="6"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>138</v>
-      </c>
-      <c r="C212" t="s">
-        <v>140</v>
-      </c>
-      <c r="H212" t="s">
-        <v>47</v>
-      </c>
-      <c r="J212" t="s">
-        <v>88</v>
-      </c>
-      <c r="K212" s="22">
-        <v>38</v>
-      </c>
-      <c r="L212" t="s">
-        <v>39</v>
-      </c>
-      <c r="M212" s="12"/>
-      <c r="N212" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>138</v>
-      </c>
-      <c r="C213" t="s">
-        <v>140</v>
-      </c>
-      <c r="F213" t="s">
-        <v>141</v>
-      </c>
-      <c r="H213" t="s">
-        <v>47</v>
-      </c>
-      <c r="J213" t="s">
-        <v>89</v>
-      </c>
-      <c r="K213" s="22">
-        <v>60</v>
-      </c>
-      <c r="L213" t="s">
-        <v>39</v>
-      </c>
-      <c r="N213" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="5"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="5"/>
+      <c r="G213" s="5"/>
+      <c r="H213" s="5"/>
+      <c r="I213" s="5"/>
+      <c r="J213" s="6"/>
+      <c r="K213" s="6"/>
+      <c r="L213" s="6"/>
+      <c r="M213" s="6"/>
+      <c r="N213" s="6"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
@@ -5748,21 +5736,21 @@
         <v>140</v>
       </c>
       <c r="H214" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J214" t="s">
         <v>88</v>
       </c>
       <c r="K214" s="22">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L214" t="s">
         <v>39</v>
       </c>
-      <c r="M214" t="s">
-        <v>143</v>
-      </c>
-      <c r="N214" s="9"/>
+      <c r="M214" s="12"/>
+      <c r="N214" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
@@ -5772,76 +5760,89 @@
         <v>140</v>
       </c>
       <c r="F215" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H215" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J215" t="s">
         <v>89</v>
       </c>
       <c r="K215" s="22">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L215" t="s">
         <v>39</v>
       </c>
-      <c r="N215" s="9"/>
+      <c r="N215" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
-      <c r="D216" s="5"/>
-      <c r="E216" s="5"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="5"/>
-      <c r="H216" s="5"/>
-      <c r="I216" s="5"/>
-      <c r="J216" s="6"/>
-      <c r="K216" s="6"/>
-      <c r="L216" s="6"/>
-      <c r="M216" s="6"/>
-      <c r="N216" s="6"/>
+      <c r="A216" t="s">
+        <v>138</v>
+      </c>
+      <c r="C216" t="s">
+        <v>140</v>
+      </c>
+      <c r="H216" t="s">
+        <v>45</v>
+      </c>
+      <c r="J216" t="s">
+        <v>88</v>
+      </c>
+      <c r="K216" s="22">
+        <v>32</v>
+      </c>
+      <c r="L216" t="s">
+        <v>39</v>
+      </c>
+      <c r="M216" t="s">
+        <v>143</v>
+      </c>
+      <c r="N216" s="9"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="C217" t="s">
-        <v>241</v>
+        <v>140</v>
+      </c>
+      <c r="F217" t="s">
+        <v>142</v>
+      </c>
+      <c r="H217" t="s">
+        <v>45</v>
       </c>
       <c r="J217" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K217" s="22">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="L217" t="s">
         <v>39</v>
       </c>
+      <c r="N217" s="9"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>234</v>
-      </c>
-      <c r="C218" t="s">
-        <v>241</v>
-      </c>
-      <c r="F218" t="s">
-        <v>243</v>
-      </c>
-      <c r="J218" t="s">
-        <v>89</v>
-      </c>
-      <c r="K218" s="22">
-        <v>7</v>
-      </c>
-      <c r="L218" t="s">
-        <v>39</v>
-      </c>
+      <c r="A218" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
+      <c r="J218" s="6"/>
+      <c r="K218" s="6"/>
+      <c r="L218" s="6"/>
+      <c r="M218" s="6"/>
+      <c r="N218" s="6"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
@@ -5850,14 +5851,11 @@
       <c r="C219" t="s">
         <v>241</v>
       </c>
-      <c r="F219" t="s">
-        <v>244</v>
-      </c>
       <c r="J219" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K219" s="22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L219" t="s">
         <v>39</v>
@@ -5865,39 +5863,39 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C220" t="s">
         <v>241</v>
       </c>
+      <c r="F220" t="s">
+        <v>243</v>
+      </c>
       <c r="J220" t="s">
-        <v>88</v>
-      </c>
-      <c r="K220" s="24">
-        <v>13</v>
+        <v>89</v>
+      </c>
+      <c r="K220" s="22">
+        <v>7</v>
       </c>
       <c r="L220" t="s">
         <v>39</v>
-      </c>
-      <c r="M220" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C221" t="s">
         <v>241</v>
       </c>
       <c r="F221" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J221" t="s">
         <v>89</v>
       </c>
       <c r="K221" s="22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L221" t="s">
         <v>39</v>
@@ -5910,215 +5908,197 @@
       <c r="C222" t="s">
         <v>241</v>
       </c>
-      <c r="F222" t="s">
+      <c r="J222" t="s">
+        <v>88</v>
+      </c>
+      <c r="K222" s="24">
+        <v>13</v>
+      </c>
+      <c r="L222" t="s">
+        <v>39</v>
+      </c>
+      <c r="M222" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>236</v>
+      </c>
+      <c r="C223" t="s">
+        <v>241</v>
+      </c>
+      <c r="F223" t="s">
+        <v>243</v>
+      </c>
+      <c r="J223" t="s">
+        <v>89</v>
+      </c>
+      <c r="K223" s="22">
+        <v>7</v>
+      </c>
+      <c r="L223" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>236</v>
+      </c>
+      <c r="C224" t="s">
+        <v>241</v>
+      </c>
+      <c r="F224" t="s">
         <v>244</v>
       </c>
-      <c r="J222" t="s">
+      <c r="J224" t="s">
         <v>89</v>
       </c>
-      <c r="K222" s="22">
+      <c r="K224" s="22">
         <v>4</v>
       </c>
-      <c r="L222" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" s="7" t="s">
+      <c r="L224" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" s="5" t="s">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
-      <c r="H224" s="5"/>
-      <c r="I224" s="5"/>
-      <c r="J224" s="6"/>
-      <c r="K224" s="6"/>
-      <c r="L224" s="6"/>
-      <c r="M224" s="6"/>
-      <c r="N224" s="6"/>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>245</v>
-      </c>
-      <c r="B225" s="11"/>
-      <c r="C225" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D225" s="11"/>
-      <c r="E225" s="11"/>
-      <c r="F225" s="11"/>
-      <c r="G225" s="11"/>
-      <c r="H225" s="11"/>
-      <c r="I225" s="11"/>
-      <c r="J225" t="s">
-        <v>88</v>
-      </c>
-      <c r="K225" s="21">
-        <v>70</v>
-      </c>
-      <c r="L225" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M225" s="9"/>
-      <c r="N225" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>248</v>
-      </c>
-      <c r="B226" s="11"/>
-      <c r="C226" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D226" s="11"/>
-      <c r="E226" s="11"/>
-      <c r="F226" s="11"/>
-      <c r="G226" s="11"/>
-      <c r="H226" s="11"/>
-      <c r="I226" s="11"/>
-      <c r="J226" t="s">
-        <v>88</v>
-      </c>
-      <c r="K226" s="21">
-        <f>655*0.7</f>
-        <v>458.49999999999994</v>
-      </c>
-      <c r="L226" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M226" s="9"/>
-      <c r="N226" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="B226" s="5"/>
+      <c r="C226" s="5"/>
+      <c r="D226" s="5"/>
+      <c r="E226" s="5"/>
+      <c r="F226" s="5"/>
+      <c r="G226" s="5"/>
+      <c r="H226" s="5"/>
+      <c r="I226" s="5"/>
+      <c r="J226" s="6"/>
+      <c r="K226" s="6"/>
+      <c r="L226" s="6"/>
+      <c r="M226" s="6"/>
+      <c r="N226" s="6"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="9" t="s">
-        <v>51</v>
+        <v>255</v>
       </c>
       <c r="D227" s="11"/>
       <c r="E227" s="11"/>
-      <c r="F227" s="20" t="s">
-        <v>137</v>
-      </c>
+      <c r="F227" s="11"/>
       <c r="G227" s="11"/>
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
       <c r="J227" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K227" s="21">
-        <f>1*(K226/100)*0.2*100</f>
-        <v>91.699999999999989</v>
+        <v>70</v>
       </c>
       <c r="L227" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M227" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="M227" s="9"/>
       <c r="N227" s="9" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>248</v>
+      </c>
       <c r="B228" s="11"/>
-      <c r="C228" s="9"/>
+      <c r="C228" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="D228" s="11"/>
       <c r="E228" s="11"/>
-      <c r="F228" s="11" t="s">
-        <v>188</v>
-      </c>
+      <c r="F228" s="11"/>
       <c r="G228" s="11"/>
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
-      <c r="K228" s="21"/>
-      <c r="L228" s="10"/>
-      <c r="M228" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="N228" s="9"/>
+      <c r="J228" t="s">
+        <v>88</v>
+      </c>
+      <c r="K228" s="21">
+        <f>655*0.7</f>
+        <v>458.49999999999994</v>
+      </c>
+      <c r="L228" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M228" s="9"/>
+      <c r="N228" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B229" s="11"/>
-      <c r="C229" s="10" t="s">
-        <v>256</v>
+      <c r="C229" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D229" s="11"/>
       <c r="E229" s="11"/>
-      <c r="F229" s="20"/>
+      <c r="F229" s="20" t="s">
+        <v>137</v>
+      </c>
       <c r="G229" s="11"/>
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
       <c r="J229" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K229" s="21">
-        <v>65</v>
+        <f>1*(K228/100)*0.2*100</f>
+        <v>91.699999999999989</v>
       </c>
       <c r="L229" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M229" s="9"/>
+      <c r="M229" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="N229" s="9" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>246</v>
-      </c>
       <c r="B230" s="11"/>
-      <c r="C230" s="10" t="s">
-        <v>256</v>
-      </c>
+      <c r="C230" s="9"/>
       <c r="D230" s="11"/>
       <c r="E230" s="11"/>
-      <c r="F230" s="20" t="s">
-        <v>257</v>
+      <c r="F230" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="G230" s="11"/>
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
-      <c r="J230" t="s">
-        <v>89</v>
-      </c>
-      <c r="K230" s="21">
-        <v>35</v>
-      </c>
-      <c r="L230" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M230" s="9"/>
-      <c r="N230" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="K230" s="21"/>
+      <c r="L230" s="10"/>
+      <c r="M230" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="N230" s="9"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="10" t="s">
-        <v>38</v>
+        <v>256</v>
       </c>
       <c r="D231" s="11"/>
       <c r="E231" s="11"/>
@@ -6130,7 +6110,7 @@
         <v>88</v>
       </c>
       <c r="K231" s="21">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L231" s="10" t="s">
         <v>39</v>
@@ -6142,16 +6122,16 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B232" s="11"/>
       <c r="C232" s="10" t="s">
-        <v>38</v>
+        <v>256</v>
       </c>
       <c r="D232" s="11"/>
       <c r="E232" s="11"/>
-      <c r="F232" s="11" t="s">
-        <v>258</v>
+      <c r="F232" s="20" t="s">
+        <v>257</v>
       </c>
       <c r="G232" s="11"/>
       <c r="H232" s="11"/>
@@ -6160,7 +6140,7 @@
         <v>89</v>
       </c>
       <c r="K232" s="21">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L232" s="10" t="s">
         <v>39</v>
@@ -6171,238 +6151,282 @@
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="5"/>
-      <c r="I233" s="5"/>
-      <c r="J233" s="6"/>
-      <c r="K233" s="6"/>
-      <c r="L233" s="6"/>
-      <c r="M233" s="6"/>
-      <c r="N233" s="6"/>
+      <c r="A233" t="s">
+        <v>249</v>
+      </c>
+      <c r="B233" s="11"/>
+      <c r="C233" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D233" s="11"/>
+      <c r="E233" s="11"/>
+      <c r="F233" s="20"/>
+      <c r="G233" s="11"/>
+      <c r="H233" s="11"/>
+      <c r="I233" s="11"/>
+      <c r="J233" t="s">
+        <v>88</v>
+      </c>
+      <c r="K233" s="21">
+        <v>30</v>
+      </c>
+      <c r="L233" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M233" s="9"/>
+      <c r="N233" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="B234" s="11"/>
-      <c r="C234" t="s">
-        <v>140</v>
-      </c>
+      <c r="C234" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D234" s="11"/>
+      <c r="E234" s="11"/>
+      <c r="F234" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="G234" s="11"/>
+      <c r="H234" s="11"/>
+      <c r="I234" s="11"/>
       <c r="J234" t="s">
-        <v>88</v>
-      </c>
-      <c r="K234" s="22">
-        <v>38</v>
-      </c>
-      <c r="L234" t="s">
-        <v>39</v>
-      </c>
-      <c r="M234" s="12" t="s">
-        <v>218</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="K234" s="21">
+        <v>11</v>
+      </c>
+      <c r="L234" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M234" s="9"/>
       <c r="N234" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="A235" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B235" s="5"/>
+      <c r="C235" s="5"/>
+      <c r="D235" s="5"/>
+      <c r="E235" s="5"/>
+      <c r="F235" s="5"/>
+      <c r="G235" s="5"/>
+      <c r="H235" s="5"/>
+      <c r="I235" s="5"/>
+      <c r="J235" s="6"/>
+      <c r="K235" s="6"/>
+      <c r="L235" s="6"/>
+      <c r="M235" s="6"/>
+      <c r="N235" s="6"/>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
         <v>209</v>
       </c>
-      <c r="B235" s="11"/>
-      <c r="C235" t="s">
+      <c r="B236" s="11"/>
+      <c r="C236" t="s">
         <v>140</v>
       </c>
-      <c r="F235" t="s">
+      <c r="J236" t="s">
+        <v>88</v>
+      </c>
+      <c r="K236" s="22">
+        <v>38</v>
+      </c>
+      <c r="L236" t="s">
+        <v>39</v>
+      </c>
+      <c r="M236" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="N236" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>209</v>
+      </c>
+      <c r="B237" s="11"/>
+      <c r="C237" t="s">
+        <v>140</v>
+      </c>
+      <c r="F237" t="s">
         <v>141</v>
       </c>
-      <c r="J235" t="s">
+      <c r="J237" t="s">
         <v>89</v>
       </c>
-      <c r="K235" s="22">
+      <c r="K237" s="22">
         <v>60</v>
       </c>
-      <c r="L235" t="s">
-        <v>39</v>
-      </c>
-      <c r="N235" s="9" t="s">
+      <c r="L237" t="s">
+        <v>39</v>
+      </c>
+      <c r="N237" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" s="11"/>
-      <c r="B236" s="11"/>
-      <c r="C236" s="11"/>
-      <c r="D236" s="11"/>
-      <c r="E236" s="11"/>
-      <c r="F236" s="11"/>
-      <c r="G236" s="11"/>
-      <c r="H236" s="11"/>
-      <c r="I236" s="11"/>
-      <c r="J236" s="11"/>
-      <c r="K236" s="11"/>
-      <c r="L236" s="9"/>
-      <c r="M236" s="9"/>
-      <c r="N236" s="9"/>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="3" t="s">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A238" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B238" s="5"/>
+      <c r="C238" s="5"/>
+      <c r="D238" s="5"/>
+      <c r="E238" s="5"/>
+      <c r="F238" s="5"/>
+      <c r="G238" s="5"/>
+      <c r="H238" s="5"/>
+      <c r="I238" s="5"/>
+      <c r="J238" s="6"/>
+      <c r="K238" s="6"/>
+      <c r="L238" s="6"/>
+      <c r="M238" s="6"/>
+      <c r="N238" s="6"/>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>299</v>
+      </c>
+      <c r="B239" s="11"/>
+      <c r="C239" s="11"/>
+      <c r="D239" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E239" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="F239" s="11"/>
+      <c r="G239" s="11"/>
+      <c r="H239" s="11"/>
+      <c r="I239" s="11"/>
+      <c r="J239" t="s">
+        <v>88</v>
+      </c>
+      <c r="K239" s="20">
+        <v>100</v>
+      </c>
+      <c r="L239" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M239" s="9"/>
+      <c r="N239" s="9"/>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A240" s="11"/>
+      <c r="B240" s="11"/>
+      <c r="C240" s="11"/>
+      <c r="D240" s="11"/>
+      <c r="E240" s="11"/>
+      <c r="F240" s="11"/>
+      <c r="G240" s="11"/>
+      <c r="H240" s="11"/>
+      <c r="I240" s="11"/>
+      <c r="J240" s="11"/>
+      <c r="K240" s="11"/>
+      <c r="L240" s="9"/>
+      <c r="M240" s="9"/>
+      <c r="N240" s="9"/>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A241" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
-      <c r="D237" s="3"/>
-      <c r="E237" s="3"/>
-      <c r="F237" s="3"/>
-      <c r="G237" s="3"/>
-      <c r="H237" s="3"/>
-      <c r="I237" s="3"/>
-      <c r="J237" s="4"/>
-      <c r="K237" s="4"/>
-      <c r="L237" s="4"/>
-      <c r="M237" s="4"/>
-      <c r="N237" s="4"/>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J238" s="8" t="s">
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3"/>
+      <c r="H241" s="3"/>
+      <c r="I241" s="3"/>
+      <c r="J241" s="4"/>
+      <c r="K241" s="4"/>
+      <c r="L241" s="4"/>
+      <c r="M241" s="4"/>
+      <c r="N241" s="4"/>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J242" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K238" s="8">
+      <c r="K242" s="8">
         <v>100</v>
       </c>
-      <c r="L238" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M238" s="8" t="s">
+      <c r="L242" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M242" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" s="5" t="s">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A243" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="5"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
-      <c r="H239" s="5"/>
-      <c r="I239" s="5"/>
-      <c r="J239" s="6"/>
-      <c r="K239" s="6"/>
-      <c r="L239" s="6"/>
-      <c r="M239" s="6"/>
-      <c r="N239" s="6"/>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>192</v>
-      </c>
-      <c r="J240" t="s">
-        <v>41</v>
-      </c>
-      <c r="K240">
-        <v>22</v>
-      </c>
-      <c r="L240" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>197</v>
-      </c>
-      <c r="J241" t="s">
-        <v>41</v>
-      </c>
-      <c r="K241" s="28">
-        <f>K240</f>
-        <v>22</v>
-      </c>
-      <c r="L241" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M241" s="28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>44</v>
-      </c>
-      <c r="J242" t="s">
-        <v>41</v>
-      </c>
-      <c r="K242">
-        <v>100</v>
-      </c>
-      <c r="L242" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>193</v>
-      </c>
-      <c r="J243" t="s">
-        <v>41</v>
-      </c>
-      <c r="K243">
-        <v>4</v>
-      </c>
-      <c r="L243" t="s">
-        <v>39</v>
-      </c>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5"/>
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
+      <c r="I243" s="5"/>
+      <c r="J243" s="6"/>
+      <c r="K243" s="6"/>
+      <c r="L243" s="6"/>
+      <c r="M243" s="6"/>
+      <c r="N243" s="6"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J244" t="s">
         <v>41</v>
       </c>
-      <c r="K244" s="28">
-        <f>K243</f>
-        <v>4</v>
-      </c>
-      <c r="L244" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M244" s="28" t="s">
-        <v>233</v>
+      <c r="K244">
+        <v>22</v>
+      </c>
+      <c r="L244" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="J245" t="s">
         <v>41</v>
       </c>
-      <c r="K245">
-        <v>100</v>
-      </c>
-      <c r="L245" t="s">
-        <v>39</v>
+      <c r="K245" s="28">
+        <f>K244</f>
+        <v>22</v>
+      </c>
+      <c r="L245" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M245" s="28" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J246" t="s">
         <v>41</v>
       </c>
       <c r="K246">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="L246" t="s">
         <v>39</v>
@@ -6410,81 +6434,74 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J247" t="s">
         <v>41</v>
       </c>
-      <c r="K247" s="28">
-        <f>K246</f>
-        <v>8</v>
-      </c>
-      <c r="L247" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M247" s="28" t="s">
-        <v>233</v>
+      <c r="K247">
+        <v>4</v>
+      </c>
+      <c r="L247" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J248" t="s">
         <v>41</v>
       </c>
-      <c r="K248">
-        <v>1</v>
-      </c>
-      <c r="L248" t="s">
-        <v>39</v>
+      <c r="K248" s="28">
+        <f>K247</f>
+        <v>4</v>
+      </c>
+      <c r="L248" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M248" s="28" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>200</v>
+        <v>94</v>
       </c>
       <c r="J249" t="s">
         <v>41</v>
       </c>
-      <c r="K249" s="28">
-        <f>K248</f>
-        <v>1</v>
-      </c>
-      <c r="L249" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M249" s="28" t="s">
-        <v>233</v>
+      <c r="K249">
+        <v>100</v>
+      </c>
+      <c r="L249" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J250" t="s">
         <v>41</v>
       </c>
-      <c r="K250" s="7">
-        <v>22</v>
-      </c>
-      <c r="L250" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M250" t="s">
-        <v>161</v>
+      <c r="K250">
+        <v>8</v>
+      </c>
+      <c r="L250" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J251" t="s">
         <v>41</v>
       </c>
       <c r="K251" s="28">
         <f>K250</f>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L251" s="28" t="s">
         <v>39</v>
@@ -6494,106 +6511,113 @@
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="5"/>
-      <c r="E252" s="5"/>
-      <c r="F252" s="5"/>
-      <c r="G252" s="5"/>
-      <c r="H252" s="5"/>
-      <c r="I252" s="5"/>
-      <c r="J252" s="6"/>
-      <c r="K252" s="6"/>
-      <c r="L252" s="6"/>
-      <c r="M252" s="6"/>
-      <c r="N252" s="6"/>
+      <c r="A252" t="s">
+        <v>195</v>
+      </c>
+      <c r="J252" t="s">
+        <v>41</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" s="18" t="s">
-        <v>105</v>
+      <c r="A253" t="s">
+        <v>200</v>
       </c>
       <c r="J253" t="s">
         <v>41</v>
       </c>
-      <c r="K253" s="18">
-        <v>16</v>
-      </c>
-      <c r="L253" s="18" t="s">
-        <v>39</v>
+      <c r="K253" s="28">
+        <f>K252</f>
+        <v>1</v>
+      </c>
+      <c r="L253" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M253" s="28" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" s="18" t="s">
-        <v>106</v>
+      <c r="A254" t="s">
+        <v>196</v>
       </c>
       <c r="J254" t="s">
         <v>41</v>
       </c>
-      <c r="K254" s="18">
-        <v>16</v>
+      <c r="K254" s="7">
+        <v>22</v>
       </c>
       <c r="L254" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M254" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" s="18" t="s">
-        <v>226</v>
+      <c r="A255" t="s">
+        <v>202</v>
       </c>
       <c r="J255" t="s">
         <v>41</v>
       </c>
-      <c r="K255" s="18">
+      <c r="K255" s="28">
+        <f>K254</f>
+        <v>22</v>
+      </c>
+      <c r="L255" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M255" s="28" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A256" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B256" s="5"/>
+      <c r="C256" s="5"/>
+      <c r="D256" s="5"/>
+      <c r="E256" s="5"/>
+      <c r="F256" s="5"/>
+      <c r="G256" s="5"/>
+      <c r="H256" s="5"/>
+      <c r="I256" s="5"/>
+      <c r="J256" s="6"/>
+      <c r="K256" s="6"/>
+      <c r="L256" s="6"/>
+      <c r="M256" s="6"/>
+      <c r="N256" s="6"/>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A257" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="J257" t="s">
+        <v>41</v>
+      </c>
+      <c r="K257" s="18">
         <v>16</v>
       </c>
-      <c r="L255" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="J256" t="s">
-        <v>41</v>
-      </c>
-      <c r="K256" s="18">
-        <v>16</v>
-      </c>
-      <c r="L256" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A257" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B257" s="5"/>
-      <c r="C257" s="5"/>
-      <c r="D257" s="5"/>
-      <c r="E257" s="5"/>
-      <c r="F257" s="5"/>
-      <c r="G257" s="5"/>
-      <c r="H257" s="5"/>
-      <c r="I257" s="5"/>
-      <c r="J257" s="6"/>
-      <c r="K257" s="6"/>
-      <c r="L257" s="6"/>
-      <c r="M257" s="6"/>
-      <c r="N257" s="6"/>
+      <c r="L257" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="18" t="s">
-        <v>259</v>
+        <v>106</v>
       </c>
       <c r="J258" t="s">
         <v>41</v>
       </c>
       <c r="K258" s="18">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L258" s="18" t="s">
         <v>39</v>
@@ -6601,13 +6625,13 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="18" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="J259" t="s">
         <v>41</v>
       </c>
       <c r="K259" s="18">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L259" s="18" t="s">
         <v>39</v>
@@ -6615,58 +6639,59 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="18" t="s">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="J260" t="s">
         <v>41</v>
       </c>
       <c r="K260" s="18">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L260" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="J261" t="s">
-        <v>41</v>
-      </c>
-      <c r="K261" s="18">
-        <v>95</v>
-      </c>
-      <c r="L261" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A261" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B261" s="5"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="5"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5"/>
+      <c r="G261" s="5"/>
+      <c r="H261" s="5"/>
+      <c r="I261" s="5"/>
+      <c r="J261" s="6"/>
+      <c r="K261" s="6"/>
+      <c r="L261" s="6"/>
+      <c r="M261" s="6"/>
+      <c r="N261" s="6"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="18" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="J262" t="s">
         <v>41</v>
       </c>
-      <c r="K262" s="7">
-        <v>97</v>
+      <c r="K262" s="18">
+        <v>85</v>
       </c>
       <c r="L262" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M262" s="7" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="18" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="J263" t="s">
         <v>41</v>
       </c>
       <c r="K263" s="18">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="L263" s="18" t="s">
         <v>39</v>
@@ -6674,66 +6699,58 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C264" s="10"/>
+        <v>261</v>
+      </c>
       <c r="J264" t="s">
         <v>41</v>
       </c>
-      <c r="K264" s="7">
-        <v>50</v>
+      <c r="K264" s="18">
+        <v>85</v>
       </c>
       <c r="L264" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M264" s="7" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="18" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="J265" t="s">
         <v>41</v>
       </c>
-      <c r="K265" s="7">
-        <v>90</v>
+      <c r="K265" s="18">
+        <v>95</v>
       </c>
       <c r="L265" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M265" s="7" t="s">
-        <v>292</v>
-      </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5"/>
-      <c r="D266" s="5"/>
-      <c r="E266" s="5"/>
-      <c r="F266" s="5"/>
-      <c r="G266" s="5"/>
-      <c r="H266" s="5"/>
-      <c r="I266" s="5"/>
-      <c r="J266" s="6"/>
-      <c r="K266" s="6"/>
-      <c r="L266" s="6"/>
-      <c r="M266" s="6"/>
-      <c r="N266" s="6"/>
+      <c r="A266" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="J266" t="s">
+        <v>41</v>
+      </c>
+      <c r="K266" s="7">
+        <v>97</v>
+      </c>
+      <c r="L266" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M266" s="7" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="18" t="s">
-        <v>147</v>
+        <v>282</v>
       </c>
       <c r="J267" t="s">
         <v>41</v>
       </c>
-      <c r="K267">
-        <v>7</v>
+      <c r="K267" s="18">
+        <v>29</v>
       </c>
       <c r="L267" s="18" t="s">
         <v>39</v>
@@ -6741,73 +6758,80 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="18" t="s">
-        <v>153</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C268" s="10"/>
       <c r="J268" t="s">
         <v>41</v>
       </c>
-      <c r="K268" s="18">
-        <v>35</v>
+      <c r="K268" s="7">
+        <v>50</v>
       </c>
       <c r="L268" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="M268" s="7" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="18" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="J269" t="s">
         <v>41</v>
       </c>
-      <c r="K269" s="18">
-        <v>63</v>
+      <c r="K269" s="7">
+        <v>90</v>
       </c>
       <c r="L269" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M269" s="7" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A270" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="J270" t="s">
-        <v>41</v>
-      </c>
-      <c r="K270" s="18">
-        <v>54</v>
-      </c>
-      <c r="L270" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M270" s="7"/>
+      <c r="A270" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B270" s="5"/>
+      <c r="C270" s="5"/>
+      <c r="D270" s="5"/>
+      <c r="E270" s="5"/>
+      <c r="F270" s="5"/>
+      <c r="G270" s="5"/>
+      <c r="H270" s="5"/>
+      <c r="I270" s="5"/>
+      <c r="J270" s="6"/>
+      <c r="K270" s="6"/>
+      <c r="L270" s="6"/>
+      <c r="M270" s="6"/>
+      <c r="N270" s="6"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="18" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J271" t="s">
         <v>41</v>
       </c>
-      <c r="K271" s="7">
-        <v>75</v>
+      <c r="K271">
+        <v>7</v>
       </c>
       <c r="L271" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M271" s="7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J272" t="s">
         <v>41</v>
       </c>
       <c r="K272" s="18">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L272" s="18" t="s">
         <v>39</v>
@@ -6815,13 +6839,13 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="18" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="J273" t="s">
         <v>41</v>
       </c>
       <c r="K273" s="18">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="L273" s="18" t="s">
         <v>39</v>
@@ -6829,261 +6853,261 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="18" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="J274" t="s">
         <v>41</v>
       </c>
       <c r="K274" s="18">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L274" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M274" s="7"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="18" t="s">
-        <v>276</v>
+        <v>151</v>
       </c>
       <c r="J275" t="s">
         <v>41</v>
       </c>
-      <c r="K275" s="18">
-        <v>100</v>
+      <c r="K275" s="7">
+        <v>75</v>
       </c>
       <c r="L275" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="M275" s="7" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" s="18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="J276" t="s">
         <v>41</v>
       </c>
-      <c r="K276" s="7">
+      <c r="K276" s="18">
+        <v>10</v>
+      </c>
+      <c r="L276" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="J277" t="s">
+        <v>41</v>
+      </c>
+      <c r="K277" s="18">
         <v>90</v>
       </c>
-      <c r="L276" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M276" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B277" s="5"/>
-      <c r="C277" s="5"/>
-      <c r="D277" s="5"/>
-      <c r="E277" s="5"/>
-      <c r="F277" s="5"/>
-      <c r="G277" s="5"/>
-      <c r="H277" s="5"/>
-      <c r="I277" s="5"/>
-      <c r="J277" s="6"/>
-      <c r="K277" s="6"/>
-      <c r="L277" s="6"/>
-      <c r="M277" s="6"/>
-      <c r="N277" s="6"/>
+      <c r="L277" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" s="7" t="s">
-        <v>65</v>
+      <c r="A278" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="J278" t="s">
         <v>41</v>
       </c>
-      <c r="K278" s="14">
+      <c r="K278" s="18">
+        <v>46</v>
+      </c>
+      <c r="L278" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="J279" t="s">
+        <v>41</v>
+      </c>
+      <c r="K279" s="18">
+        <v>100</v>
+      </c>
+      <c r="L279" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="J280" t="s">
+        <v>41</v>
+      </c>
+      <c r="K280" s="7">
+        <v>90</v>
+      </c>
+      <c r="L280" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M280" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A281" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B281" s="5"/>
+      <c r="C281" s="5"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="5"/>
+      <c r="F281" s="5"/>
+      <c r="G281" s="5"/>
+      <c r="H281" s="5"/>
+      <c r="I281" s="5"/>
+      <c r="J281" s="6"/>
+      <c r="K281" s="6"/>
+      <c r="L281" s="6"/>
+      <c r="M281" s="6"/>
+      <c r="N281" s="6"/>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A282" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J282" t="s">
+        <v>41</v>
+      </c>
+      <c r="K282" s="14">
         <f>8.5*20/(29.5+8.5)</f>
         <v>4.4736842105263159</v>
       </c>
-      <c r="L278" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" s="7" t="s">
+      <c r="L282" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A283" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J279" t="s">
+      <c r="J283" t="s">
         <v>41</v>
       </c>
-      <c r="K279" s="14">
+      <c r="K283" s="14">
         <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
         <v>2.981366459627329</v>
       </c>
-      <c r="L279" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="7" t="s">
+      <c r="L283" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A284" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J280" t="s">
+      <c r="J284" t="s">
         <v>41</v>
       </c>
-      <c r="K280" s="14">
+      <c r="K284" s="14">
         <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
         <v>7.723292469352014</v>
       </c>
-      <c r="L280" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="7" t="s">
+      <c r="L284" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A285" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J281" t="s">
+      <c r="J285" t="s">
         <v>41</v>
       </c>
-      <c r="K281">
+      <c r="K285">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="L281" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J282" t="s">
-        <v>41</v>
-      </c>
-      <c r="K282">
-        <v>0</v>
-      </c>
-      <c r="L282" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J283" t="s">
-        <v>41</v>
-      </c>
-      <c r="K283">
-        <v>20</v>
-      </c>
-      <c r="L283" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J284" t="s">
-        <v>41</v>
-      </c>
-      <c r="K284">
-        <v>20</v>
-      </c>
-      <c r="L284" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A285" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J285" t="s">
-        <v>41</v>
-      </c>
-      <c r="K285">
-        <v>20</v>
-      </c>
       <c r="L285" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J286" t="s">
         <v>41</v>
       </c>
       <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A287" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J287" t="s">
+        <v>41</v>
+      </c>
+      <c r="K287">
+        <v>20</v>
+      </c>
+      <c r="L287" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A288" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J288" t="s">
+        <v>41</v>
+      </c>
+      <c r="K288">
+        <v>20</v>
+      </c>
+      <c r="L288" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A289" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J289" t="s">
+        <v>41</v>
+      </c>
+      <c r="K289">
+        <v>20</v>
+      </c>
+      <c r="L289" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A290" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J290" t="s">
+        <v>41</v>
+      </c>
+      <c r="K290">
         <f>43</f>
         <v>43</v>
       </c>
-      <c r="L286" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A287" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
-      <c r="D287" s="5"/>
-      <c r="E287" s="5"/>
-      <c r="F287" s="5"/>
-      <c r="G287" s="5"/>
-      <c r="H287" s="5"/>
-      <c r="I287" s="5"/>
-      <c r="J287" s="6"/>
-      <c r="K287" s="6"/>
-      <c r="L287" s="6"/>
-      <c r="M287" s="6"/>
-      <c r="N287" s="6"/>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>57</v>
-      </c>
-      <c r="J288" t="s">
-        <v>41</v>
-      </c>
-      <c r="K288">
-        <v>37</v>
-      </c>
-      <c r="L288" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>101</v>
-      </c>
-      <c r="J289" t="s">
-        <v>41</v>
-      </c>
-      <c r="K289" s="18">
-        <v>43</v>
-      </c>
-      <c r="L289" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>294</v>
-      </c>
-      <c r="J290" t="s">
-        <v>41</v>
-      </c>
-      <c r="K290" s="18">
-        <v>36</v>
-      </c>
       <c r="L290" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7101,190 +7125,183 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="J292" t="s">
         <v>41</v>
       </c>
       <c r="K292">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="L292" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A293" s="27" t="s">
-        <v>220</v>
+      <c r="A293" t="s">
+        <v>101</v>
       </c>
       <c r="J293" t="s">
         <v>41</v>
       </c>
-      <c r="K293">
-        <v>0.4</v>
+      <c r="K293" s="18">
+        <v>43</v>
       </c>
       <c r="L293" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A294" s="27" t="s">
-        <v>221</v>
+      <c r="A294" t="s">
+        <v>294</v>
       </c>
       <c r="J294" t="s">
         <v>41</v>
       </c>
-      <c r="K294" s="7">
-        <v>95</v>
+      <c r="K294" s="18">
+        <v>36</v>
       </c>
       <c r="L294" t="s">
         <v>39</v>
       </c>
-      <c r="M294" s="7" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A295" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="J295" t="s">
-        <v>41</v>
-      </c>
-      <c r="K295">
-        <v>100</v>
-      </c>
-      <c r="L295" t="s">
-        <v>39</v>
-      </c>
+      <c r="A295" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+      <c r="I295" s="5"/>
+      <c r="J295" s="6"/>
+      <c r="K295" s="6"/>
+      <c r="L295" s="6"/>
+      <c r="M295" s="6"/>
+      <c r="N295" s="6"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A296" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="B296" s="9"/>
-      <c r="C296" s="9"/>
-      <c r="D296" s="10"/>
-      <c r="E296" s="10"/>
-      <c r="F296" s="9"/>
-      <c r="G296" s="9"/>
-      <c r="H296" s="9"/>
-      <c r="I296" s="9"/>
+      <c r="A296" t="s">
+        <v>219</v>
+      </c>
       <c r="J296" t="s">
         <v>41</v>
       </c>
       <c r="K296">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L296" t="s">
         <v>39</v>
       </c>
-      <c r="M296" s="9"/>
-      <c r="N296" s="9"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A297" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B297" s="5"/>
-      <c r="C297" s="5"/>
-      <c r="D297" s="5"/>
-      <c r="E297" s="5"/>
-      <c r="F297" s="5"/>
-      <c r="G297" s="5"/>
-      <c r="H297" s="5"/>
-      <c r="I297" s="5"/>
-      <c r="J297" s="6"/>
-      <c r="K297" s="6"/>
-      <c r="L297" s="6"/>
-      <c r="M297" s="6"/>
-      <c r="N297" s="6"/>
+      <c r="A297" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="J297" t="s">
+        <v>41</v>
+      </c>
+      <c r="K297">
+        <v>0.4</v>
+      </c>
+      <c r="L297" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>138</v>
+      <c r="A298" s="27" t="s">
+        <v>221</v>
       </c>
       <c r="J298" t="s">
         <v>41</v>
       </c>
-      <c r="K298" s="16">
-        <v>52</v>
+      <c r="K298" s="7">
+        <v>95</v>
       </c>
       <c r="L298" t="s">
         <v>39</v>
       </c>
-      <c r="M298" s="25"/>
+      <c r="M298" s="7" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A299" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B299" s="5"/>
-      <c r="C299" s="5"/>
-      <c r="D299" s="5"/>
-      <c r="E299" s="5"/>
-      <c r="F299" s="5"/>
-      <c r="G299" s="5"/>
-      <c r="H299" s="5"/>
-      <c r="I299" s="5"/>
-      <c r="J299" s="6"/>
-      <c r="K299" s="6"/>
-      <c r="L299" s="6"/>
-      <c r="M299" s="6"/>
-      <c r="N299" s="6"/>
+      <c r="A299" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="J299" t="s">
+        <v>41</v>
+      </c>
+      <c r="K299">
+        <v>100</v>
+      </c>
+      <c r="L299" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>234</v>
-      </c>
+      <c r="A300" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B300" s="9"/>
+      <c r="C300" s="9"/>
+      <c r="D300" s="10"/>
+      <c r="E300" s="10"/>
+      <c r="F300" s="9"/>
+      <c r="G300" s="9"/>
+      <c r="H300" s="9"/>
+      <c r="I300" s="9"/>
       <c r="J300" t="s">
         <v>41</v>
       </c>
-      <c r="K300" s="7">
-        <v>24</v>
+      <c r="K300">
+        <v>100</v>
       </c>
       <c r="L300" t="s">
         <v>39</v>
       </c>
-      <c r="M300" s="7" t="s">
-        <v>239</v>
-      </c>
+      <c r="M300" s="9"/>
+      <c r="N300" s="9"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>236</v>
-      </c>
-      <c r="J301" t="s">
-        <v>41</v>
-      </c>
-      <c r="K301" s="28">
-        <f>K300</f>
-        <v>24</v>
-      </c>
-      <c r="L301" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="M301" s="28" t="s">
-        <v>238</v>
-      </c>
+      <c r="A301" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B301" s="5"/>
+      <c r="C301" s="5"/>
+      <c r="D301" s="5"/>
+      <c r="E301" s="5"/>
+      <c r="F301" s="5"/>
+      <c r="G301" s="5"/>
+      <c r="H301" s="5"/>
+      <c r="I301" s="5"/>
+      <c r="J301" s="6"/>
+      <c r="K301" s="6"/>
+      <c r="L301" s="6"/>
+      <c r="M301" s="6"/>
+      <c r="N301" s="6"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="J302" t="s">
         <v>41</v>
       </c>
-      <c r="K302">
-        <v>61</v>
+      <c r="K302" s="16">
+        <v>52</v>
       </c>
       <c r="L302" t="s">
         <v>39</v>
       </c>
+      <c r="M302" s="25"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -7302,250 +7319,213 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J304" t="s">
         <v>41</v>
       </c>
-      <c r="K304">
-        <v>100</v>
+      <c r="K304" s="7">
+        <v>24</v>
       </c>
       <c r="L304" t="s">
         <v>39</v>
+      </c>
+      <c r="M304" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J305" t="s">
         <v>41</v>
       </c>
-      <c r="K305">
-        <v>4</v>
-      </c>
-      <c r="L305" t="s">
-        <v>39</v>
-      </c>
-      <c r="M305" t="s">
-        <v>119</v>
+      <c r="K305" s="28">
+        <f>K304</f>
+        <v>24</v>
+      </c>
+      <c r="L305" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M305" s="28" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="J306" t="s">
         <v>41</v>
       </c>
       <c r="K306">
+        <v>61</v>
+      </c>
+      <c r="L306" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A307" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B307" s="5"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="5"/>
+      <c r="E307" s="5"/>
+      <c r="F307" s="5"/>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
+      <c r="I307" s="5"/>
+      <c r="J307" s="6"/>
+      <c r="K307" s="6"/>
+      <c r="L307" s="6"/>
+      <c r="M307" s="6"/>
+      <c r="N307" s="6"/>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>245</v>
+      </c>
+      <c r="J308" t="s">
+        <v>41</v>
+      </c>
+      <c r="K308">
+        <v>100</v>
+      </c>
+      <c r="L308" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>248</v>
+      </c>
+      <c r="J309" t="s">
+        <v>41</v>
+      </c>
+      <c r="K309">
+        <v>4</v>
+      </c>
+      <c r="L309" t="s">
+        <v>39</v>
+      </c>
+      <c r="M309" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>246</v>
+      </c>
+      <c r="J310" t="s">
+        <v>41</v>
+      </c>
+      <c r="K310">
         <v>85</v>
       </c>
-      <c r="L306" t="s">
-        <v>39</v>
-      </c>
-      <c r="M306" t="s">
+      <c r="L310" t="s">
+        <v>39</v>
+      </c>
+      <c r="M310" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
         <v>249</v>
       </c>
-      <c r="J307" t="s">
+      <c r="J311" t="s">
         <v>41</v>
       </c>
-      <c r="K307">
+      <c r="K311">
         <v>22</v>
       </c>
-      <c r="L307" t="s">
-        <v>39</v>
-      </c>
-      <c r="M307" t="s">
+      <c r="L311" t="s">
+        <v>39</v>
+      </c>
+      <c r="M311" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A309" s="3" t="s">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B309" s="3"/>
-      <c r="C309" s="3"/>
-      <c r="D309" s="3"/>
-      <c r="E309" s="3"/>
-      <c r="F309" s="3"/>
-      <c r="G309" s="3"/>
-      <c r="H309" s="3"/>
-      <c r="I309" s="3"/>
-      <c r="J309" s="4"/>
-      <c r="K309" s="4"/>
-      <c r="L309" s="4"/>
-      <c r="M309" s="4"/>
-      <c r="N309" s="4"/>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G310" s="8"/>
-      <c r="H310" s="8" t="s">
+      <c r="B313" s="3"/>
+      <c r="C313" s="3"/>
+      <c r="D313" s="3"/>
+      <c r="E313" s="3"/>
+      <c r="F313" s="3"/>
+      <c r="G313" s="3"/>
+      <c r="H313" s="3"/>
+      <c r="I313" s="3"/>
+      <c r="J313" s="4"/>
+      <c r="K313" s="4"/>
+      <c r="L313" s="4"/>
+      <c r="M313" s="4"/>
+      <c r="N313" s="4"/>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G314" s="8"/>
+      <c r="H314" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I310" s="8"/>
-      <c r="J310" s="8" t="s">
+      <c r="I314" s="8"/>
+      <c r="J314" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K310" s="8">
+      <c r="K314" s="8">
         <v>-100</v>
       </c>
-      <c r="L310" s="8" t="s">
+      <c r="L314" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M310" s="8" t="s">
+      <c r="M314" s="8" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G311" s="8"/>
-      <c r="H311" s="8" t="s">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G315" s="8"/>
+      <c r="H315" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I311" s="8"/>
-      <c r="J311" s="8" t="s">
+      <c r="I315" s="8"/>
+      <c r="J315" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K311" s="8">
+      <c r="K315" s="8">
         <v>0</v>
       </c>
-      <c r="L311" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M311" s="8" t="s">
+      <c r="L315" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M315" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A312" s="5" t="s">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A316" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B312" s="5"/>
-      <c r="C312" s="5"/>
-      <c r="D312" s="5"/>
-      <c r="E312" s="5"/>
-      <c r="F312" s="5"/>
-      <c r="G312" s="5"/>
-      <c r="H312" s="5"/>
-      <c r="I312" s="5"/>
-      <c r="J312" s="6"/>
-      <c r="K312" s="6"/>
-      <c r="L312" s="6"/>
-      <c r="M312" s="6"/>
-      <c r="N312" s="6"/>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>35</v>
-      </c>
-      <c r="G313" t="s">
-        <v>90</v>
-      </c>
-      <c r="H313" t="s">
-        <v>45</v>
-      </c>
-      <c r="J313" t="s">
-        <v>42</v>
-      </c>
-      <c r="K313" s="18">
-        <v>5.3</v>
-      </c>
-      <c r="L313" t="s">
-        <v>39</v>
-      </c>
-      <c r="M313" t="s">
-        <v>181</v>
-      </c>
-      <c r="N313" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>50</v>
-      </c>
-      <c r="G314" t="s">
-        <v>90</v>
-      </c>
-      <c r="H314" t="s">
-        <v>45</v>
-      </c>
-      <c r="J314" t="s">
-        <v>42</v>
-      </c>
-      <c r="K314" s="18">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L314" t="s">
-        <v>39</v>
-      </c>
-      <c r="M314" t="s">
-        <v>181</v>
-      </c>
-      <c r="N314" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>93</v>
-      </c>
-      <c r="G315" t="s">
-        <v>90</v>
-      </c>
-      <c r="H315" t="s">
-        <v>45</v>
-      </c>
-      <c r="J315" t="s">
-        <v>42</v>
-      </c>
-      <c r="K315" s="18">
-        <v>12.7</v>
-      </c>
-      <c r="L315" t="s">
-        <v>39</v>
-      </c>
-      <c r="M315" t="s">
-        <v>181</v>
-      </c>
-      <c r="N315" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>92</v>
-      </c>
-      <c r="G316" t="s">
-        <v>90</v>
-      </c>
-      <c r="H316" t="s">
-        <v>45</v>
-      </c>
-      <c r="J316" t="s">
-        <v>42</v>
-      </c>
-      <c r="K316" s="18">
-        <v>24</v>
-      </c>
-      <c r="L316" t="s">
-        <v>39</v>
-      </c>
-      <c r="M316" t="s">
-        <v>182</v>
-      </c>
-      <c r="N316" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="B316" s="5"/>
+      <c r="C316" s="5"/>
+      <c r="D316" s="5"/>
+      <c r="E316" s="5"/>
+      <c r="F316" s="5"/>
+      <c r="G316" s="5"/>
+      <c r="H316" s="5"/>
+      <c r="I316" s="5"/>
+      <c r="J316" s="6"/>
+      <c r="K316" s="6"/>
+      <c r="L316" s="6"/>
+      <c r="M316" s="6"/>
+      <c r="N316" s="6"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="G317" t="s">
         <v>90</v>
@@ -7556,34 +7536,48 @@
       <c r="J317" t="s">
         <v>42</v>
       </c>
-      <c r="K317" s="7">
-        <v>10</v>
+      <c r="K317" s="18">
+        <v>5.3</v>
       </c>
       <c r="L317" t="s">
         <v>39</v>
       </c>
+      <c r="M317" t="s">
+        <v>181</v>
+      </c>
+      <c r="N317" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A318" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B318" s="5"/>
-      <c r="C318" s="5"/>
-      <c r="D318" s="5"/>
-      <c r="E318" s="5"/>
-      <c r="F318" s="5"/>
-      <c r="G318" s="5"/>
-      <c r="H318" s="5"/>
-      <c r="I318" s="5"/>
-      <c r="J318" s="6"/>
-      <c r="K318" s="6"/>
-      <c r="L318" s="6"/>
-      <c r="M318" s="6"/>
-      <c r="N318" s="6"/>
+      <c r="A318" t="s">
+        <v>50</v>
+      </c>
+      <c r="G318" t="s">
+        <v>90</v>
+      </c>
+      <c r="H318" t="s">
+        <v>45</v>
+      </c>
+      <c r="J318" t="s">
+        <v>42</v>
+      </c>
+      <c r="K318" s="18">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L318" t="s">
+        <v>39</v>
+      </c>
+      <c r="M318" t="s">
+        <v>181</v>
+      </c>
+      <c r="N318" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A319" s="18" t="s">
-        <v>105</v>
+      <c r="A319" t="s">
+        <v>93</v>
       </c>
       <c r="G319" t="s">
         <v>90</v>
@@ -7595,18 +7589,21 @@
         <v>42</v>
       </c>
       <c r="K319" s="18">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="L319" t="s">
         <v>39</v>
       </c>
-      <c r="N319" s="27" t="s">
-        <v>179</v>
+      <c r="M319" t="s">
+        <v>181</v>
+      </c>
+      <c r="N319" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A320" s="18" t="s">
-        <v>106</v>
+      <c r="A320" t="s">
+        <v>92</v>
       </c>
       <c r="G320" t="s">
         <v>90</v>
@@ -7618,18 +7615,21 @@
         <v>42</v>
       </c>
       <c r="K320" s="18">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L320" t="s">
         <v>39</v>
+      </c>
+      <c r="M320" t="s">
+        <v>182</v>
       </c>
       <c r="N320" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A321" s="18" t="s">
-        <v>226</v>
+      <c r="A321" t="s">
+        <v>91</v>
       </c>
       <c r="G321" t="s">
         <v>90</v>
@@ -7640,54 +7640,57 @@
       <c r="J321" t="s">
         <v>42</v>
       </c>
-      <c r="K321" s="18">
-        <v>0</v>
+      <c r="K321" s="7">
+        <v>10</v>
       </c>
       <c r="L321" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G322" t="s">
+      <c r="A322" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B322" s="5"/>
+      <c r="C322" s="5"/>
+      <c r="D322" s="5"/>
+      <c r="E322" s="5"/>
+      <c r="F322" s="5"/>
+      <c r="G322" s="5"/>
+      <c r="H322" s="5"/>
+      <c r="I322" s="5"/>
+      <c r="J322" s="6"/>
+      <c r="K322" s="6"/>
+      <c r="L322" s="6"/>
+      <c r="M322" s="6"/>
+      <c r="N322" s="6"/>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A323" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G323" t="s">
         <v>90</v>
       </c>
-      <c r="H322" t="s">
+      <c r="H323" t="s">
         <v>45</v>
       </c>
-      <c r="J322" t="s">
+      <c r="J323" t="s">
         <v>42</v>
       </c>
-      <c r="K322" s="18">
-        <v>0</v>
-      </c>
-      <c r="L322" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="5" t="s">
+      <c r="K323" s="18">
         <v>12</v>
       </c>
-      <c r="B323" s="5"/>
-      <c r="C323" s="5"/>
-      <c r="D323" s="5"/>
-      <c r="E323" s="5"/>
-      <c r="F323" s="5"/>
-      <c r="G323" s="5"/>
-      <c r="H323" s="5"/>
-      <c r="I323" s="5"/>
-      <c r="J323" s="6"/>
-      <c r="K323" s="6"/>
-      <c r="L323" s="6"/>
-      <c r="M323" s="6"/>
-      <c r="N323" s="6"/>
+      <c r="L323" t="s">
+        <v>39</v>
+      </c>
+      <c r="N323" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="18" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="G324" t="s">
         <v>90</v>
@@ -7699,13 +7702,10 @@
         <v>42</v>
       </c>
       <c r="K324" s="18">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L324" t="s">
         <v>39</v>
-      </c>
-      <c r="M324" t="s">
-        <v>184</v>
       </c>
       <c r="N324" s="27" t="s">
         <v>179</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" s="18" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="G325" t="s">
         <v>90</v>
@@ -7725,21 +7725,15 @@
         <v>42</v>
       </c>
       <c r="K325" s="18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L325" t="s">
         <v>39</v>
-      </c>
-      <c r="M325" t="s">
-        <v>185</v>
-      </c>
-      <c r="N325" s="27" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="18" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="G326" t="s">
         <v>90</v>
@@ -7751,47 +7745,33 @@
         <v>42</v>
       </c>
       <c r="K326" s="18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L326" t="s">
         <v>39</v>
       </c>
-      <c r="M326" t="s">
-        <v>183</v>
-      </c>
-      <c r="N326" s="27" t="s">
-        <v>179</v>
-      </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A327" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="G327" t="s">
-        <v>90</v>
-      </c>
-      <c r="H327" t="s">
-        <v>45</v>
-      </c>
-      <c r="J327" t="s">
-        <v>42</v>
-      </c>
-      <c r="K327" s="18">
-        <v>9</v>
-      </c>
-      <c r="L327" t="s">
-        <v>39</v>
-      </c>
-      <c r="M327" t="s">
-        <v>187</v>
-      </c>
-      <c r="N327" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="A327" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B327" s="5"/>
+      <c r="C327" s="5"/>
+      <c r="D327" s="5"/>
+      <c r="E327" s="5"/>
+      <c r="F327" s="5"/>
+      <c r="G327" s="5"/>
+      <c r="H327" s="5"/>
+      <c r="I327" s="5"/>
+      <c r="J327" s="6"/>
+      <c r="K327" s="6"/>
+      <c r="L327" s="6"/>
+      <c r="M327" s="6"/>
+      <c r="N327" s="6"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="18" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G328" t="s">
         <v>90</v>
@@ -7803,13 +7783,13 @@
         <v>42</v>
       </c>
       <c r="K328" s="18">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L328" t="s">
         <v>39</v>
       </c>
-      <c r="M328" s="27" t="s">
-        <v>186</v>
+      <c r="M328" t="s">
+        <v>184</v>
       </c>
       <c r="N328" s="27" t="s">
         <v>179</v>
@@ -7817,7 +7797,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G329" t="s">
         <v>90</v>
@@ -7828,37 +7808,51 @@
       <c r="J329" t="s">
         <v>42</v>
       </c>
-      <c r="K329" s="7">
-        <f>AVERAGE(K325:K328)</f>
+      <c r="K329" s="18">
         <v>13</v>
       </c>
       <c r="L329" t="s">
         <v>39</v>
       </c>
-      <c r="M329" s="27"/>
-      <c r="N329" s="27"/>
+      <c r="M329" t="s">
+        <v>185</v>
+      </c>
+      <c r="N329" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B330" s="5"/>
-      <c r="C330" s="5"/>
-      <c r="D330" s="5"/>
-      <c r="E330" s="5"/>
-      <c r="F330" s="5"/>
-      <c r="G330" s="5"/>
-      <c r="H330" s="5"/>
-      <c r="I330" s="5"/>
-      <c r="J330" s="6"/>
-      <c r="K330" s="6"/>
-      <c r="L330" s="6"/>
-      <c r="M330" s="6"/>
-      <c r="N330" s="6"/>
+      <c r="A330" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G330" t="s">
+        <v>90</v>
+      </c>
+      <c r="H330" t="s">
+        <v>45</v>
+      </c>
+      <c r="J330" t="s">
+        <v>42</v>
+      </c>
+      <c r="K330" s="18">
+        <v>19</v>
+      </c>
+      <c r="L330" t="s">
+        <v>39</v>
+      </c>
+      <c r="M330" t="s">
+        <v>183</v>
+      </c>
+      <c r="N330" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="18" t="s">
-        <v>259</v>
+        <v>113</v>
+      </c>
+      <c r="G331" t="s">
+        <v>90</v>
       </c>
       <c r="H331" t="s">
         <v>45</v>
@@ -7867,21 +7861,24 @@
         <v>42</v>
       </c>
       <c r="K331" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L331" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L331" t="s">
         <v>39</v>
       </c>
       <c r="M331" t="s">
-        <v>264</v>
-      </c>
-      <c r="N331" t="s">
+        <v>187</v>
+      </c>
+      <c r="N331" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="18" t="s">
-        <v>260</v>
+        <v>116</v>
+      </c>
+      <c r="G332" t="s">
+        <v>90</v>
       </c>
       <c r="H332" t="s">
         <v>45</v>
@@ -7890,21 +7887,24 @@
         <v>42</v>
       </c>
       <c r="K332" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L332" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M332" t="s">
-        <v>264</v>
-      </c>
-      <c r="N332" t="s">
+        <v>11</v>
+      </c>
+      <c r="L332" t="s">
+        <v>39</v>
+      </c>
+      <c r="M332" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="N332" s="27" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" s="18" t="s">
-        <v>261</v>
+        <v>160</v>
+      </c>
+      <c r="G333" t="s">
+        <v>90</v>
       </c>
       <c r="H333" t="s">
         <v>45</v>
@@ -7912,67 +7912,60 @@
       <c r="J333" t="s">
         <v>42</v>
       </c>
-      <c r="K333" s="18">
+      <c r="K333" s="7">
+        <f>AVERAGE(K329:K332)</f>
+        <v>13</v>
+      </c>
+      <c r="L333" t="s">
+        <v>39</v>
+      </c>
+      <c r="M333" s="27"/>
+      <c r="N333" s="27"/>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A334" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B334" s="5"/>
+      <c r="C334" s="5"/>
+      <c r="D334" s="5"/>
+      <c r="E334" s="5"/>
+      <c r="F334" s="5"/>
+      <c r="G334" s="5"/>
+      <c r="H334" s="5"/>
+      <c r="I334" s="5"/>
+      <c r="J334" s="6"/>
+      <c r="K334" s="6"/>
+      <c r="L334" s="6"/>
+      <c r="M334" s="6"/>
+      <c r="N334" s="6"/>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A335" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="H335" t="s">
+        <v>45</v>
+      </c>
+      <c r="J335" t="s">
+        <v>42</v>
+      </c>
+      <c r="K335" s="18">
         <v>7.9</v>
       </c>
-      <c r="L333" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M333" t="s">
+      <c r="L335" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M335" t="s">
         <v>264</v>
       </c>
-      <c r="N333" t="s">
+      <c r="N335" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="H334" t="s">
-        <v>45</v>
-      </c>
-      <c r="J334" t="s">
-        <v>42</v>
-      </c>
-      <c r="K334" s="18">
-        <v>7.9</v>
-      </c>
-      <c r="L334" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M334" t="s">
-        <v>264</v>
-      </c>
-      <c r="N334" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A335" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B335" s="5"/>
-      <c r="C335" s="5"/>
-      <c r="D335" s="5"/>
-      <c r="E335" s="5"/>
-      <c r="F335" s="5"/>
-      <c r="G335" s="5"/>
-      <c r="H335" s="5"/>
-      <c r="I335" s="5"/>
-      <c r="J335" s="6"/>
-      <c r="K335" s="6"/>
-      <c r="L335" s="6"/>
-      <c r="M335" s="6"/>
-      <c r="N335" s="6"/>
-    </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A336" s="7"/>
-      <c r="B336" t="s">
-        <v>84</v>
-      </c>
-      <c r="G336" t="s">
-        <v>90</v>
+      <c r="A336" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H336" t="s">
         <v>45</v>
@@ -7980,43 +7973,45 @@
       <c r="J336" t="s">
         <v>42</v>
       </c>
-      <c r="K336" s="16">
-        <v>17</v>
-      </c>
-      <c r="L336" t="s">
+      <c r="K336" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L336" s="18" t="s">
         <v>39</v>
       </c>
       <c r="M336" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="N336" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A337" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B337" s="5"/>
-      <c r="C337" s="5"/>
-      <c r="D337" s="5"/>
-      <c r="E337" s="5"/>
-      <c r="F337" s="5"/>
-      <c r="G337" s="5"/>
-      <c r="H337" s="5"/>
-      <c r="I337" s="5"/>
-      <c r="J337" s="6"/>
-      <c r="K337" s="6"/>
-      <c r="L337" s="6"/>
-      <c r="M337" s="6"/>
-      <c r="N337" s="6"/>
+      <c r="A337" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="H337" t="s">
+        <v>45</v>
+      </c>
+      <c r="J337" t="s">
+        <v>42</v>
+      </c>
+      <c r="K337" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L337" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M337" t="s">
+        <v>264</v>
+      </c>
+      <c r="N337" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>57</v>
-      </c>
-      <c r="G338" t="s">
-        <v>90</v>
+      <c r="A338" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="H338" t="s">
         <v>45</v>
@@ -8024,36 +8019,41 @@
       <c r="J338" t="s">
         <v>42</v>
       </c>
-      <c r="K338" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="L338" t="s">
-        <v>39</v>
+      <c r="K338" s="18">
+        <v>7.9</v>
+      </c>
+      <c r="L338" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M338" t="s">
+        <v>264</v>
+      </c>
+      <c r="N338" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>101</v>
-      </c>
-      <c r="G339" t="s">
-        <v>90</v>
-      </c>
-      <c r="H339" t="s">
-        <v>45</v>
-      </c>
-      <c r="J339" t="s">
-        <v>42</v>
-      </c>
-      <c r="K339" s="7">
-        <v>15.4</v>
-      </c>
-      <c r="L339" t="s">
-        <v>39</v>
-      </c>
+      <c r="A339" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B339" s="5"/>
+      <c r="C339" s="5"/>
+      <c r="D339" s="5"/>
+      <c r="E339" s="5"/>
+      <c r="F339" s="5"/>
+      <c r="G339" s="5"/>
+      <c r="H339" s="5"/>
+      <c r="I339" s="5"/>
+      <c r="J339" s="6"/>
+      <c r="K339" s="6"/>
+      <c r="L339" s="6"/>
+      <c r="M339" s="6"/>
+      <c r="N339" s="6"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>294</v>
+      <c r="A340" s="7"/>
+      <c r="B340" t="s">
+        <v>84</v>
       </c>
       <c r="G340" t="s">
         <v>90</v>
@@ -8064,16 +8064,22 @@
       <c r="J340" t="s">
         <v>42</v>
       </c>
-      <c r="K340" s="7">
-        <v>0</v>
+      <c r="K340" s="16">
+        <v>17</v>
       </c>
       <c r="L340" t="s">
         <v>39</v>
+      </c>
+      <c r="M340" t="s">
+        <v>180</v>
+      </c>
+      <c r="N340" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8090,8 +8096,11 @@
       <c r="N341" s="6"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B342" t="s">
-        <v>224</v>
+      <c r="A342" t="s">
+        <v>57</v>
+      </c>
+      <c r="G342" t="s">
+        <v>90</v>
       </c>
       <c r="H342" t="s">
         <v>45</v>
@@ -8099,40 +8108,36 @@
       <c r="J342" t="s">
         <v>42</v>
       </c>
-      <c r="K342">
-        <v>34.200000000000003</v>
+      <c r="K342" s="7">
+        <v>2.4</v>
       </c>
       <c r="L342" t="s">
         <v>39</v>
       </c>
-      <c r="M342" t="s">
-        <v>231</v>
-      </c>
-      <c r="N342" s="27" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B343" s="5"/>
-      <c r="C343" s="5"/>
-      <c r="D343" s="5"/>
-      <c r="E343" s="5"/>
-      <c r="F343" s="5"/>
-      <c r="G343" s="5"/>
-      <c r="H343" s="5"/>
-      <c r="I343" s="5"/>
-      <c r="J343" s="6"/>
-      <c r="K343" s="6"/>
-      <c r="L343" s="6"/>
-      <c r="M343" s="6"/>
-      <c r="N343" s="6"/>
+      <c r="A343" t="s">
+        <v>101</v>
+      </c>
+      <c r="G343" t="s">
+        <v>90</v>
+      </c>
+      <c r="H343" t="s">
+        <v>45</v>
+      </c>
+      <c r="J343" t="s">
+        <v>42</v>
+      </c>
+      <c r="K343" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="L343" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="G344" t="s">
         <v>90</v>
@@ -8143,8 +8148,8 @@
       <c r="J344" t="s">
         <v>42</v>
       </c>
-      <c r="K344" s="24">
-        <v>1</v>
+      <c r="K344" s="7">
+        <v>0</v>
       </c>
       <c r="L344" t="s">
         <v>39</v>
@@ -8152,7 +8157,7 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -8169,8 +8174,8 @@
       <c r="N345" s="6"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>245</v>
+      <c r="B346" t="s">
+        <v>224</v>
       </c>
       <c r="H346" t="s">
         <v>45</v>
@@ -8178,45 +8183,43 @@
       <c r="J346" t="s">
         <v>42</v>
       </c>
-      <c r="K346" s="18">
-        <v>24.7</v>
+      <c r="K346">
+        <v>34.200000000000003</v>
       </c>
       <c r="L346" t="s">
         <v>39</v>
       </c>
       <c r="M346" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="N346" s="27" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>248</v>
-      </c>
-      <c r="H347" t="s">
-        <v>45</v>
-      </c>
-      <c r="J347" t="s">
-        <v>42</v>
-      </c>
-      <c r="K347" s="18">
-        <v>8</v>
-      </c>
-      <c r="L347" t="s">
-        <v>39</v>
-      </c>
-      <c r="M347" t="s">
-        <v>178</v>
-      </c>
-      <c r="N347" s="27" t="s">
-        <v>179</v>
-      </c>
+      <c r="A347" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B347" s="5"/>
+      <c r="C347" s="5"/>
+      <c r="D347" s="5"/>
+      <c r="E347" s="5"/>
+      <c r="F347" s="5"/>
+      <c r="G347" s="5"/>
+      <c r="H347" s="5"/>
+      <c r="I347" s="5"/>
+      <c r="J347" s="6"/>
+      <c r="K347" s="6"/>
+      <c r="L347" s="6"/>
+      <c r="M347" s="6"/>
+      <c r="N347" s="6"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>246</v>
+        <v>138</v>
+      </c>
+      <c r="G348" t="s">
+        <v>90</v>
       </c>
       <c r="H348" t="s">
         <v>45</v>
@@ -8224,39 +8227,120 @@
       <c r="J348" t="s">
         <v>42</v>
       </c>
-      <c r="K348">
+      <c r="K348" s="24">
+        <v>1</v>
+      </c>
+      <c r="L348" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A349" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B349" s="5"/>
+      <c r="C349" s="5"/>
+      <c r="D349" s="5"/>
+      <c r="E349" s="5"/>
+      <c r="F349" s="5"/>
+      <c r="G349" s="5"/>
+      <c r="H349" s="5"/>
+      <c r="I349" s="5"/>
+      <c r="J349" s="6"/>
+      <c r="K349" s="6"/>
+      <c r="L349" s="6"/>
+      <c r="M349" s="6"/>
+      <c r="N349" s="6"/>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>245</v>
+      </c>
+      <c r="H350" t="s">
+        <v>45</v>
+      </c>
+      <c r="J350" t="s">
+        <v>42</v>
+      </c>
+      <c r="K350" s="18">
+        <v>24.7</v>
+      </c>
+      <c r="L350" t="s">
+        <v>39</v>
+      </c>
+      <c r="M350" t="s">
+        <v>253</v>
+      </c>
+      <c r="N350" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>248</v>
+      </c>
+      <c r="H351" t="s">
+        <v>45</v>
+      </c>
+      <c r="J351" t="s">
+        <v>42</v>
+      </c>
+      <c r="K351" s="18">
+        <v>8</v>
+      </c>
+      <c r="L351" t="s">
+        <v>39</v>
+      </c>
+      <c r="M351" t="s">
+        <v>178</v>
+      </c>
+      <c r="N351" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>246</v>
+      </c>
+      <c r="H352" t="s">
+        <v>45</v>
+      </c>
+      <c r="J352" t="s">
+        <v>42</v>
+      </c>
+      <c r="K352">
         <v>7.9</v>
       </c>
-      <c r="L348" t="s">
-        <v>39</v>
-      </c>
-      <c r="M348" t="s">
+      <c r="L352" t="s">
+        <v>39</v>
+      </c>
+      <c r="M352" t="s">
         <v>266</v>
       </c>
-      <c r="N348" s="27" t="s">
+      <c r="N352" s="27" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
         <v>249</v>
       </c>
-      <c r="H349" t="s">
+      <c r="H353" t="s">
         <v>45</v>
       </c>
-      <c r="J349" t="s">
+      <c r="J353" t="s">
         <v>42</v>
       </c>
-      <c r="K349">
+      <c r="K353">
         <v>4.7</v>
       </c>
-      <c r="L349" t="s">
-        <v>39</v>
-      </c>
-      <c r="M349" t="s">
+      <c r="L353" t="s">
+        <v>39</v>
+      </c>
+      <c r="M353" t="s">
         <v>254</v>
       </c>
-      <c r="N349" s="27" t="s">
+      <c r="N353" s="27" t="s">
         <v>179</v>
       </c>
     </row>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -4877,7 +4877,7 @@
       </c>
       <c r="K183" s="13">
         <f>100-K184</f>
-        <v>93.25</v>
+        <v>97</v>
       </c>
       <c r="L183" s="11" t="s">
         <v>39</v>
@@ -4911,8 +4911,8 @@
         <v>89</v>
       </c>
       <c r="K184" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="L184" s="11" t="s">
         <v>39</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="K185" s="13">
         <f>(100-K186)*0.1</f>
-        <v>9.3250000000000011</v>
+        <v>9.7000000000000011</v>
       </c>
       <c r="L185" s="11" t="s">
         <v>39</v>
@@ -4976,8 +4976,8 @@
         <v>89</v>
       </c>
       <c r="K186" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>39</v>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K187" s="13">
         <f>(100-K186)*0.9</f>
-        <v>83.924999999999997</v>
+        <v>87.3</v>
       </c>
       <c r="L187" s="11" t="s">
         <v>39</v>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="9870"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="9870" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="303">
   <si>
     <t>parameter</t>
   </si>
@@ -8352,7 +8352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -8485,29 +8485,12 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="335">
   <si>
     <t>parameter</t>
   </si>
@@ -1067,6 +1067,9 @@
   </si>
   <si>
     <t>Majs</t>
+  </si>
+  <si>
+    <t>Use total exports as import accounted for in food demand. OK?</t>
   </si>
 </sst>
 </file>
@@ -3219,13 +3222,13 @@
         <v>318</v>
       </c>
       <c r="K97" s="22">
-        <v>22400.2</v>
+        <v>32965.800000000003</v>
       </c>
       <c r="L97" t="s">
         <v>204</v>
       </c>
       <c r="M97" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="N97" t="s">
         <v>319</v>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="338">
   <si>
     <t>parameter</t>
   </si>
@@ -1072,6 +1072,12 @@
   </si>
   <si>
     <t>flour of mixed grain, Assume 28% whole grain to reach 25% total whole grain share</t>
+  </si>
+  <si>
+    <t>eggs</t>
+  </si>
+  <si>
+    <t>"Ägg"</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N376"/>
+  <dimension ref="A1:N386"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -2630,26 +2636,25 @@
       <c r="N60" s="5"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>336</v>
+      </c>
+      <c r="J61" t="s">
+        <v>18</v>
+      </c>
+      <c r="K61">
+        <v>29.3</v>
+      </c>
+      <c r="L61" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2666,25 +2671,26 @@
       <c r="N62" s="5"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>209</v>
-      </c>
-      <c r="B63" t="s">
-        <v>214</v>
-      </c>
-      <c r="J63" t="s">
-        <v>18</v>
-      </c>
-      <c r="K63">
-        <v>4.5</v>
-      </c>
-      <c r="L63" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="26" t="s">
-        <v>210</v>
       </c>
       <c r="B64" t="s">
         <v>214</v>
@@ -2692,8 +2698,8 @@
       <c r="J64" t="s">
         <v>18</v>
       </c>
-      <c r="K64" s="6">
-        <v>0</v>
+      <c r="K64">
+        <v>4.5</v>
       </c>
       <c r="L64" t="s">
         <v>19</v>
@@ -2701,7 +2707,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
         <v>214</v>
@@ -2709,8 +2715,8 @@
       <c r="J65" t="s">
         <v>18</v>
       </c>
-      <c r="K65">
-        <v>0.7</v>
+      <c r="K65" s="6">
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>19</v>
@@ -2718,7 +2724,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" t="s">
         <v>214</v>
@@ -2727,7 +2733,7 @@
         <v>18</v>
       </c>
       <c r="K66">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L66" t="s">
         <v>19</v>
@@ -2735,7 +2741,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B67" t="s">
         <v>214</v>
@@ -2744,33 +2750,32 @@
         <v>18</v>
       </c>
       <c r="K67">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="L67" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
+      <c r="A68" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" t="s">
+        <v>214</v>
+      </c>
+      <c r="J68" t="s">
+        <v>18</v>
+      </c>
+      <c r="K68">
+        <v>0.6</v>
+      </c>
+      <c r="L68" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2787,106 +2792,107 @@
       <c r="N69" s="5"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>132</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>133</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J71" t="s">
         <v>18</v>
       </c>
-      <c r="K70" s="13">
+      <c r="K71" s="13">
         <f>6+4.4/3+13*0.6</f>
         <v>15.266666666666666</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L71" t="s">
         <v>19</v>
       </c>
-      <c r="M70" s="6" t="s">
+      <c r="M71" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>139</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>133</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J72" t="s">
         <v>18</v>
       </c>
-      <c r="K71" s="22">
+      <c r="K72" s="22">
         <f>8.2+4.4/3</f>
         <v>9.6666666666666661</v>
       </c>
-      <c r="L71" t="s">
+      <c r="L72" t="s">
         <v>19</v>
       </c>
-      <c r="M71" t="s">
+      <c r="M72" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>140</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>133</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J73" t="s">
         <v>18</v>
       </c>
-      <c r="K72" s="22">
+      <c r="K73" s="22">
         <f>2.8+4.4/3</f>
         <v>4.2666666666666666</v>
       </c>
-      <c r="L72" t="s">
+      <c r="L73" t="s">
         <v>19</v>
       </c>
-      <c r="M72" t="s">
+      <c r="M73" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>224</v>
-      </c>
-      <c r="B74" t="s">
-        <v>227</v>
-      </c>
-      <c r="J74" t="s">
-        <v>18</v>
-      </c>
-      <c r="K74">
-        <v>79.3</v>
-      </c>
-      <c r="L74" t="s">
-        <v>19</v>
-      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B75" t="s">
         <v>227</v>
@@ -2895,18 +2901,15 @@
         <v>18</v>
       </c>
       <c r="K75">
-        <v>10</v>
+        <v>79.3</v>
       </c>
       <c r="L75" t="s">
         <v>19</v>
       </c>
-      <c r="M75" t="s">
-        <v>230</v>
-      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B76" t="s">
         <v>227</v>
@@ -2915,50 +2918,53 @@
         <v>18</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L76" t="s">
         <v>19</v>
       </c>
+      <c r="M76" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A77" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" t="s">
+        <v>227</v>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>235</v>
-      </c>
-      <c r="B78" t="s">
-        <v>112</v>
-      </c>
-      <c r="J78" t="s">
-        <v>18</v>
-      </c>
-      <c r="K78">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="L78" t="s">
-        <v>19</v>
-      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B79" t="s">
         <v>112</v>
@@ -2967,7 +2973,7 @@
         <v>18</v>
       </c>
       <c r="K79">
-        <v>125.5</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="L79" t="s">
         <v>19</v>
@@ -2975,7 +2981,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B80" t="s">
         <v>112</v>
@@ -2984,18 +2990,15 @@
         <v>18</v>
       </c>
       <c r="K80">
-        <v>6.9</v>
+        <v>125.5</v>
       </c>
       <c r="L80" t="s">
         <v>19</v>
       </c>
-      <c r="M80" t="s">
-        <v>237</v>
-      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B81" t="s">
         <v>112</v>
@@ -3004,36 +3007,38 @@
         <v>18</v>
       </c>
       <c r="K81">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="L81" t="s">
         <v>19</v>
       </c>
       <c r="M81" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>239</v>
+      </c>
+      <c r="B82" t="s">
+        <v>112</v>
+      </c>
+      <c r="J82" t="s">
+        <v>18</v>
+      </c>
+      <c r="K82">
+        <v>7.9</v>
+      </c>
+      <c r="L82" t="s">
+        <v>19</v>
+      </c>
+      <c r="M82" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="5"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3051,7 +3056,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3069,7 +3074,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3085,50 +3090,45 @@
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>201</v>
-      </c>
-      <c r="B88" t="s">
-        <v>207</v>
-      </c>
-      <c r="H88" t="s">
-        <v>45</v>
-      </c>
-      <c r="J88" t="s">
-        <v>204</v>
-      </c>
-      <c r="K88" s="33">
-        <v>197000</v>
-      </c>
-      <c r="L88" t="s">
-        <v>197</v>
-      </c>
-      <c r="M88" s="17" t="s">
-        <v>327</v>
-      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B89" t="s">
         <v>207</v>
@@ -3140,120 +3140,117 @@
         <v>204</v>
       </c>
       <c r="K89" s="33">
-        <v>10000</v>
+        <v>197000</v>
       </c>
       <c r="L89" t="s">
         <v>197</v>
       </c>
-      <c r="M89" t="s">
+      <c r="M89" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" t="s">
+        <v>207</v>
+      </c>
+      <c r="H90" t="s">
+        <v>45</v>
+      </c>
+      <c r="J90" t="s">
+        <v>204</v>
+      </c>
+      <c r="K90" s="33">
+        <v>10000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>197</v>
+      </c>
+      <c r="M90" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K90" s="33"/>
-    </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="K91" s="33"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>101</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>207</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H92" t="s">
         <v>45</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J92" t="s">
         <v>204</v>
       </c>
-      <c r="K91" s="33">
+      <c r="K92" s="33">
         <v>34000</v>
       </c>
-      <c r="L91" t="s">
+      <c r="L92" t="s">
         <v>197</v>
       </c>
-      <c r="M91" t="s">
+      <c r="M92" t="s">
         <v>310</v>
       </c>
-      <c r="N91" t="s">
+      <c r="N92" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K92" s="33"/>
-    </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="K93" s="33"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>280</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>207</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H94" t="s">
         <v>45</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J94" t="s">
         <v>204</v>
       </c>
-      <c r="K93" s="37">
+      <c r="K94" s="37">
         <v>355.5</v>
       </c>
-      <c r="L93" t="s">
+      <c r="L94" t="s">
         <v>281</v>
       </c>
-      <c r="M93" t="s">
+      <c r="M94" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K94" s="33"/>
-    </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+      <c r="K95" s="33"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="36"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>297</v>
-      </c>
-      <c r="B96" t="s">
-        <v>301</v>
-      </c>
-      <c r="H96" t="s">
-        <v>45</v>
-      </c>
-      <c r="J96" t="s">
-        <v>302</v>
-      </c>
-      <c r="K96" s="33">
-        <v>558249.80000000005</v>
-      </c>
-      <c r="L96" t="s">
-        <v>197</v>
-      </c>
-      <c r="M96" t="s">
-        <v>305</v>
-      </c>
-      <c r="N96" t="s">
-        <v>303</v>
-      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="36"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B97" t="s">
         <v>301</v>
@@ -3265,7 +3262,7 @@
         <v>302</v>
       </c>
       <c r="K97" s="33">
-        <v>304650.40000000002</v>
+        <v>558249.80000000005</v>
       </c>
       <c r="L97" t="s">
         <v>197</v>
@@ -3279,7 +3276,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B98" t="s">
         <v>301</v>
@@ -3291,13 +3288,13 @@
         <v>302</v>
       </c>
       <c r="K98" s="33">
-        <v>32965.800000000003</v>
+        <v>304650.40000000002</v>
       </c>
       <c r="L98" t="s">
         <v>197</v>
       </c>
       <c r="M98" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="N98" t="s">
         <v>303</v>
@@ -3305,7 +3302,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B99" t="s">
         <v>301</v>
@@ -3317,13 +3314,13 @@
         <v>302</v>
       </c>
       <c r="K99" s="33">
-        <v>177249.6</v>
+        <v>32965.800000000003</v>
       </c>
       <c r="L99" t="s">
         <v>197</v>
       </c>
       <c r="M99" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="N99" t="s">
         <v>303</v>
@@ -3331,7 +3328,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="B100" t="s">
         <v>301</v>
@@ -3343,7 +3340,7 @@
         <v>302</v>
       </c>
       <c r="K100" s="33">
-        <v>22062.799999999999</v>
+        <v>177249.6</v>
       </c>
       <c r="L100" t="s">
         <v>197</v>
@@ -3357,7 +3354,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="B101" t="s">
         <v>301</v>
@@ -3369,65 +3366,74 @@
         <v>302</v>
       </c>
       <c r="K101" s="33">
-        <v>25000</v>
+        <v>22062.799999999999</v>
       </c>
       <c r="L101" t="s">
         <v>197</v>
       </c>
       <c r="M101" t="s">
+        <v>305</v>
+      </c>
+      <c r="N101" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>301</v>
+      </c>
+      <c r="H102" t="s">
+        <v>45</v>
+      </c>
+      <c r="J102" t="s">
+        <v>302</v>
+      </c>
+      <c r="K102" s="33">
+        <v>25000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>197</v>
+      </c>
+      <c r="M102" t="s">
         <v>307</v>
       </c>
-      <c r="N101" t="s">
+      <c r="N102" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>26</v>
-      </c>
-      <c r="I104" t="s">
-        <v>50</v>
-      </c>
-      <c r="J104" t="s">
-        <v>53</v>
-      </c>
-      <c r="K104">
-        <v>25</v>
-      </c>
-      <c r="L104" t="s">
-        <v>38</v>
-      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>26</v>
       </c>
       <c r="I105" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J105" t="s">
         <v>53</v>
       </c>
       <c r="K105">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L105" t="s">
         <v>38</v>
@@ -3438,36 +3444,36 @@
         <v>26</v>
       </c>
       <c r="I106" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J106" t="s">
         <v>53</v>
       </c>
-      <c r="K106" s="6">
-        <v>10.5</v>
+      <c r="K106">
+        <v>2</v>
       </c>
       <c r="L106" t="s">
         <v>38</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="I107" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J107" t="s">
         <v>53</v>
       </c>
-      <c r="K107">
-        <v>17</v>
+      <c r="K107" s="6">
+        <v>10.5</v>
       </c>
       <c r="L107" t="s">
         <v>38</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -3475,13 +3481,13 @@
         <v>103</v>
       </c>
       <c r="I108" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J108" t="s">
         <v>53</v>
       </c>
       <c r="K108">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L108" t="s">
         <v>38</v>
@@ -3492,36 +3498,36 @@
         <v>103</v>
       </c>
       <c r="I109" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J109" t="s">
         <v>53</v>
       </c>
-      <c r="K109" s="6">
-        <v>15</v>
+      <c r="K109">
+        <v>7</v>
       </c>
       <c r="L109" t="s">
         <v>38</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I110" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J110" t="s">
         <v>53</v>
       </c>
-      <c r="K110">
-        <v>19</v>
+      <c r="K110" s="6">
+        <v>15</v>
       </c>
       <c r="L110" t="s">
         <v>38</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -3529,13 +3535,13 @@
         <v>108</v>
       </c>
       <c r="I111" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J111" t="s">
         <v>53</v>
       </c>
       <c r="K111">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L111" t="s">
         <v>38</v>
@@ -3546,36 +3552,36 @@
         <v>108</v>
       </c>
       <c r="I112" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J112" t="s">
         <v>53</v>
       </c>
-      <c r="K112" s="6">
-        <v>2</v>
+      <c r="K112">
+        <v>10</v>
       </c>
       <c r="L112" t="s">
         <v>38</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>252</v>
+        <v>108</v>
       </c>
       <c r="I113" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J113" t="s">
         <v>53</v>
       </c>
-      <c r="K113">
-        <v>19</v>
+      <c r="K113" s="6">
+        <v>2</v>
       </c>
       <c r="L113" t="s">
         <v>38</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.25">
@@ -3583,13 +3589,13 @@
         <v>252</v>
       </c>
       <c r="I114" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J114" t="s">
         <v>53</v>
       </c>
       <c r="K114">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L114" t="s">
         <v>38</v>
@@ -3600,36 +3606,36 @@
         <v>252</v>
       </c>
       <c r="I115" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J115" t="s">
         <v>53</v>
       </c>
-      <c r="K115" s="6">
-        <v>2</v>
+      <c r="K115">
+        <v>10</v>
       </c>
       <c r="L115" t="s">
         <v>38</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="I116" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J116" t="s">
         <v>53</v>
       </c>
-      <c r="K116">
-        <v>11</v>
+      <c r="K116" s="6">
+        <v>2</v>
       </c>
       <c r="L116" t="s">
         <v>38</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="117" spans="2:13" x14ac:dyDescent="0.25">
@@ -3637,14 +3643,13 @@
         <v>81</v>
       </c>
       <c r="I117" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J117" t="s">
         <v>53</v>
       </c>
       <c r="K117">
-        <f>0.5</f>
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L117" t="s">
         <v>38</v>
@@ -3655,36 +3660,37 @@
         <v>81</v>
       </c>
       <c r="I118" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J118" t="s">
         <v>53</v>
       </c>
-      <c r="K118" s="6">
-        <v>1</v>
+      <c r="K118">
+        <f>0.5</f>
+        <v>0.5</v>
       </c>
       <c r="L118" t="s">
         <v>38</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="I119" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J119" t="s">
         <v>53</v>
       </c>
-      <c r="K119">
-        <v>11</v>
+      <c r="K119" s="6">
+        <v>1</v>
       </c>
       <c r="L119" t="s">
         <v>38</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="2:13" x14ac:dyDescent="0.25">
@@ -3692,13 +3698,13 @@
         <v>55</v>
       </c>
       <c r="I120" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J120" t="s">
         <v>53</v>
       </c>
       <c r="K120">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L120" t="s">
         <v>38</v>
@@ -3709,50 +3715,50 @@
         <v>55</v>
       </c>
       <c r="I121" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J121" t="s">
         <v>53</v>
       </c>
-      <c r="K121" s="6">
-        <v>5</v>
+      <c r="K121">
+        <v>4</v>
       </c>
       <c r="L121" t="s">
         <v>38</v>
-      </c>
-      <c r="M121" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="I122" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J122" t="s">
         <v>53</v>
       </c>
-      <c r="K122">
-        <v>4</v>
+      <c r="K122" s="6">
+        <v>5</v>
       </c>
       <c r="L122" t="s">
         <v>38</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="I123" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J123" t="s">
         <v>53</v>
       </c>
       <c r="K123">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L123" t="s">
         <v>38</v>
@@ -3760,53 +3766,53 @@
     </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="I124" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J124" t="s">
         <v>53</v>
       </c>
-      <c r="K124" s="6">
-        <v>5</v>
+      <c r="K124">
+        <v>4</v>
       </c>
       <c r="L124" t="s">
         <v>38</v>
-      </c>
-      <c r="M124" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="125" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>133</v>
+        <v>336</v>
       </c>
       <c r="I125" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J125" t="s">
         <v>53</v>
       </c>
-      <c r="K125">
-        <v>4</v>
+      <c r="K125" s="6">
+        <v>5</v>
       </c>
       <c r="L125" t="s">
         <v>38</v>
+      </c>
+      <c r="M125" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="126" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="I126" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J126" t="s">
         <v>53</v>
       </c>
       <c r="K126">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L126" t="s">
         <v>38</v>
@@ -3814,53 +3820,53 @@
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="I127" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J127" t="s">
         <v>53</v>
       </c>
-      <c r="K127" s="6">
-        <v>5</v>
+      <c r="K127">
+        <v>1</v>
       </c>
       <c r="L127" t="s">
         <v>38</v>
-      </c>
-      <c r="M127" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="I128" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J128" t="s">
         <v>53</v>
       </c>
-      <c r="K128">
-        <v>13</v>
+      <c r="K128" s="6">
+        <v>5</v>
       </c>
       <c r="L128" t="s">
         <v>38</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="I129" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J129" t="s">
         <v>53</v>
       </c>
       <c r="K129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L129" t="s">
         <v>38</v>
@@ -3868,53 +3874,53 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="I130" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J130" t="s">
         <v>53</v>
       </c>
-      <c r="K130" s="6">
-        <v>5</v>
+      <c r="K130">
+        <v>1</v>
       </c>
       <c r="L130" t="s">
         <v>38</v>
-      </c>
-      <c r="M130" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="I131" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J131" t="s">
         <v>53</v>
       </c>
-      <c r="K131">
-        <v>0</v>
+      <c r="K131" s="6">
+        <v>5</v>
       </c>
       <c r="L131" t="s">
         <v>38</v>
+      </c>
+      <c r="M131" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="I132" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J132" t="s">
         <v>53</v>
       </c>
       <c r="K132">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L132" t="s">
         <v>38</v>
@@ -3922,151 +3928,158 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="I133" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J133" t="s">
         <v>53</v>
       </c>
-      <c r="K133" s="6">
+      <c r="K133">
         <v>5</v>
       </c>
       <c r="L133" t="s">
         <v>38</v>
       </c>
-      <c r="M133" s="6" t="s">
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>227</v>
+      </c>
+      <c r="I134" t="s">
+        <v>52</v>
+      </c>
+      <c r="J134" t="s">
+        <v>53</v>
+      </c>
+      <c r="K134" s="6">
+        <v>5</v>
+      </c>
+      <c r="L134" t="s">
+        <v>38</v>
+      </c>
+      <c r="M134" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K134" s="6"/>
-      <c r="M134" s="6"/>
-    </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
+      <c r="B135" t="s">
+        <v>112</v>
+      </c>
+      <c r="I135" t="s">
+        <v>50</v>
+      </c>
+      <c r="J135" t="s">
+        <v>53</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>112</v>
+      </c>
+      <c r="I136" t="s">
+        <v>51</v>
+      </c>
+      <c r="J136" t="s">
+        <v>53</v>
+      </c>
+      <c r="K136">
+        <v>5</v>
+      </c>
+      <c r="L136" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>112</v>
+      </c>
+      <c r="I137" t="s">
+        <v>52</v>
+      </c>
+      <c r="J137" t="s">
+        <v>53</v>
+      </c>
+      <c r="K137" s="6">
+        <v>5</v>
+      </c>
+      <c r="L137" t="s">
+        <v>38</v>
+      </c>
+      <c r="M137" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K138" s="6"/>
+      <c r="M138" s="6"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-      <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
-      <c r="L135" s="3"/>
-      <c r="M135" s="3"/>
-      <c r="N135" s="3"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J136" s="7" t="s">
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J140" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K136" s="7">
+      <c r="K140" s="7">
         <v>100</v>
       </c>
-      <c r="L136" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M136" s="7" t="s">
+      <c r="L140" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M140" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="5"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="5"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>186</v>
-      </c>
-      <c r="J138" t="s">
-        <v>40</v>
-      </c>
-      <c r="K138">
-        <v>22</v>
-      </c>
-      <c r="L138" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>191</v>
-      </c>
-      <c r="J139" t="s">
-        <v>40</v>
-      </c>
-      <c r="K139" s="27">
-        <f>K138</f>
-        <v>22</v>
-      </c>
-      <c r="L139" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M139" s="27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>328</v>
-      </c>
-      <c r="J140" t="s">
-        <v>40</v>
-      </c>
-      <c r="K140">
-        <v>100</v>
-      </c>
-      <c r="L140" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>329</v>
-      </c>
-      <c r="J141" t="s">
-        <v>40</v>
-      </c>
-      <c r="K141" s="27">
-        <f>K140</f>
-        <v>100</v>
-      </c>
-      <c r="L141" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M141" s="27" t="s">
-        <v>223</v>
-      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5"/>
+      <c r="L141" s="5"/>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J142" t="s">
         <v>40</v>
       </c>
       <c r="K142">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L142" t="s">
         <v>38</v>
@@ -4074,14 +4087,14 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J143" t="s">
         <v>40</v>
       </c>
       <c r="K143" s="27">
         <f>K142</f>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L143" s="27" t="s">
         <v>38</v>
@@ -4092,7 +4105,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>88</v>
+        <v>328</v>
       </c>
       <c r="J144" t="s">
         <v>40</v>
@@ -4106,95 +4119,92 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="J145" t="s">
         <v>40</v>
       </c>
-      <c r="K145">
-        <v>8</v>
-      </c>
-      <c r="L145" t="s">
-        <v>38</v>
+      <c r="K145" s="27">
+        <f>K144</f>
+        <v>100</v>
+      </c>
+      <c r="L145" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M145" s="27" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J146" t="s">
         <v>40</v>
       </c>
-      <c r="K146" s="27">
-        <f>K145</f>
-        <v>8</v>
-      </c>
-      <c r="L146" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M146" s="27" t="s">
-        <v>223</v>
+      <c r="K146">
+        <v>4</v>
+      </c>
+      <c r="L146" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J147" t="s">
         <v>40</v>
       </c>
-      <c r="K147">
-        <v>1</v>
-      </c>
-      <c r="L147" t="s">
-        <v>38</v>
+      <c r="K147" s="27">
+        <f>K146</f>
+        <v>4</v>
+      </c>
+      <c r="L147" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M147" s="27" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="J148" t="s">
         <v>40</v>
       </c>
-      <c r="K148" s="27">
-        <f>K147</f>
-        <v>1</v>
-      </c>
-      <c r="L148" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M148" s="27" t="s">
-        <v>223</v>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J149" t="s">
         <v>40</v>
       </c>
-      <c r="K149" s="6">
-        <v>22</v>
-      </c>
-      <c r="L149" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M149" t="s">
-        <v>155</v>
+      <c r="K149">
+        <v>8</v>
+      </c>
+      <c r="L149" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J150" t="s">
         <v>40</v>
       </c>
       <c r="K150" s="27">
         <f>K149</f>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L150" s="27" t="s">
         <v>38</v>
@@ -4204,106 +4214,113 @@
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
-      <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="5"/>
-      <c r="K151" s="5"/>
-      <c r="L151" s="5"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="5"/>
+      <c r="A151" t="s">
+        <v>189</v>
+      </c>
+      <c r="J151" t="s">
+        <v>40</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A152" s="17" t="s">
-        <v>99</v>
+      <c r="A152" t="s">
+        <v>194</v>
       </c>
       <c r="J152" t="s">
         <v>40</v>
       </c>
-      <c r="K152" s="17">
-        <v>16</v>
-      </c>
-      <c r="L152" s="17" t="s">
-        <v>38</v>
+      <c r="K152" s="27">
+        <f>K151</f>
+        <v>1</v>
+      </c>
+      <c r="L152" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M152" s="27" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A153" s="17" t="s">
-        <v>100</v>
+      <c r="A153" t="s">
+        <v>190</v>
       </c>
       <c r="J153" t="s">
         <v>40</v>
       </c>
-      <c r="K153" s="17">
-        <v>16</v>
+      <c r="K153" s="6">
+        <v>22</v>
       </c>
       <c r="L153" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M153" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" s="17" t="s">
-        <v>216</v>
+      <c r="A154" t="s">
+        <v>195</v>
       </c>
       <c r="J154" t="s">
         <v>40</v>
       </c>
-      <c r="K154" s="17">
+      <c r="K154" s="27">
+        <f>K153</f>
+        <v>22</v>
+      </c>
+      <c r="L154" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M154" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="J156" t="s">
+        <v>40</v>
+      </c>
+      <c r="K156" s="17">
         <v>16</v>
       </c>
-      <c r="L154" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="J155" t="s">
-        <v>40</v>
-      </c>
-      <c r="K155" s="17">
-        <v>16</v>
-      </c>
-      <c r="L155" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="5"/>
-      <c r="K156" s="5"/>
-      <c r="L156" s="5"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="5"/>
+      <c r="L156" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="J157" t="s">
         <v>40</v>
       </c>
       <c r="K157" s="17">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L157" s="17" t="s">
         <v>38</v>
@@ -4311,13 +4328,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="17" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="J158" t="s">
         <v>40</v>
       </c>
       <c r="K158" s="17">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L158" s="17" t="s">
         <v>38</v>
@@ -4325,58 +4342,59 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="J159" t="s">
         <v>40</v>
       </c>
       <c r="K159" s="17">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L159" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="J160" t="s">
-        <v>40</v>
-      </c>
-      <c r="K160" s="17">
-        <v>95</v>
-      </c>
-      <c r="L160" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A160" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="5"/>
+      <c r="K160" s="5"/>
+      <c r="L160" s="5"/>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="J161" t="s">
         <v>40</v>
       </c>
-      <c r="K161" s="6">
-        <v>97</v>
+      <c r="K161" s="17">
+        <v>85</v>
       </c>
       <c r="L161" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M161" s="6" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="J162" t="s">
         <v>40</v>
       </c>
       <c r="K162" s="17">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="L162" s="17" t="s">
         <v>38</v>
@@ -4384,66 +4402,58 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="C163" s="9"/>
+        <v>251</v>
+      </c>
       <c r="J163" t="s">
         <v>40</v>
       </c>
-      <c r="K163" s="6">
-        <v>50</v>
+      <c r="K163" s="17">
+        <v>85</v>
       </c>
       <c r="L163" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M163" s="6" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="17" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="J164" t="s">
         <v>40</v>
       </c>
-      <c r="K164" s="6">
-        <v>90</v>
+      <c r="K164" s="17">
+        <v>95</v>
       </c>
       <c r="L164" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M164" s="6" t="s">
-        <v>273</v>
-      </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="5"/>
-      <c r="K165" s="5"/>
-      <c r="L165" s="5"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="5"/>
+      <c r="A165" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="J165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K165" s="6">
+        <v>97</v>
+      </c>
+      <c r="L165" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M165" s="6" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="17" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="J166" t="s">
         <v>40</v>
       </c>
-      <c r="K166">
-        <v>7</v>
+      <c r="K166" s="17">
+        <v>29</v>
       </c>
       <c r="L166" s="17" t="s">
         <v>38</v>
@@ -4451,73 +4461,80 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>147</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="C167" s="9"/>
       <c r="J167" t="s">
         <v>40</v>
       </c>
-      <c r="K167" s="17">
-        <v>35</v>
+      <c r="K167" s="6">
+        <v>50</v>
       </c>
       <c r="L167" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="M167" s="6" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="17" t="s">
-        <v>143</v>
+        <v>264</v>
       </c>
       <c r="J168" t="s">
         <v>40</v>
       </c>
-      <c r="K168" s="17">
-        <v>63</v>
+      <c r="K168" s="6">
+        <v>90</v>
       </c>
       <c r="L168" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M168" s="6" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="J169" t="s">
-        <v>40</v>
-      </c>
-      <c r="K169" s="17">
-        <v>54</v>
-      </c>
-      <c r="L169" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M169" s="6"/>
+      <c r="A169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" s="4"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="5"/>
+      <c r="K169" s="5"/>
+      <c r="L169" s="5"/>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J170" t="s">
         <v>40</v>
       </c>
-      <c r="K170" s="6">
-        <v>75</v>
+      <c r="K170">
+        <v>7</v>
       </c>
       <c r="L170" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M170" s="6" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J171" t="s">
         <v>40</v>
       </c>
       <c r="K171" s="17">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L171" s="17" t="s">
         <v>38</v>
@@ -4525,13 +4542,13 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="J172" t="s">
         <v>40</v>
       </c>
       <c r="K172" s="17">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="L172" s="17" t="s">
         <v>38</v>
@@ -4539,261 +4556,261 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="J173" t="s">
         <v>40</v>
       </c>
       <c r="K173" s="17">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L173" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="17" t="s">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="J174" t="s">
         <v>40</v>
       </c>
-      <c r="K174" s="17">
-        <v>100</v>
+      <c r="K174" s="6">
+        <v>75</v>
       </c>
       <c r="L174" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="M174" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="J175" t="s">
         <v>40</v>
       </c>
-      <c r="K175" s="6">
+      <c r="K175" s="17">
+        <v>10</v>
+      </c>
+      <c r="L175" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="J176" t="s">
+        <v>40</v>
+      </c>
+      <c r="K176" s="17">
         <v>90</v>
       </c>
-      <c r="L175" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M175" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="5"/>
-      <c r="K176" s="5"/>
-      <c r="L176" s="5"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="5"/>
+      <c r="L176" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="6" t="s">
-        <v>62</v>
+      <c r="A177" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="J177" t="s">
         <v>40</v>
       </c>
-      <c r="K177" s="13">
+      <c r="K177" s="17">
+        <v>46</v>
+      </c>
+      <c r="L177" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="J178" t="s">
+        <v>40</v>
+      </c>
+      <c r="K178" s="17">
+        <v>100</v>
+      </c>
+      <c r="L178" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="J179" t="s">
+        <v>40</v>
+      </c>
+      <c r="K179" s="6">
+        <v>90</v>
+      </c>
+      <c r="L179" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M179" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="5"/>
+      <c r="K180" s="5"/>
+      <c r="L180" s="5"/>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J181" t="s">
+        <v>40</v>
+      </c>
+      <c r="K181" s="13">
         <f>8.5*20/(29.5+8.5)</f>
         <v>4.4736842105263159</v>
       </c>
-      <c r="L177" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="6" t="s">
+      <c r="L181" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J178" t="s">
+      <c r="J182" t="s">
         <v>40</v>
       </c>
-      <c r="K178" s="13">
+      <c r="K182" s="13">
         <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
         <v>2.981366459627329</v>
       </c>
-      <c r="L178" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
+      <c r="L182" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J179" t="s">
+      <c r="J183" t="s">
         <v>40</v>
       </c>
-      <c r="K179" s="13">
+      <c r="K183" s="13">
         <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
         <v>7.723292469352014</v>
       </c>
-      <c r="L179" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
+      <c r="L183" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J180" t="s">
+      <c r="J184" t="s">
         <v>40</v>
       </c>
-      <c r="K180">
+      <c r="K184">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="L180" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A181" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J181" t="s">
-        <v>40</v>
-      </c>
-      <c r="K181">
-        <v>0</v>
-      </c>
-      <c r="L181" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A182" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J182" t="s">
-        <v>40</v>
-      </c>
-      <c r="K182">
-        <v>20</v>
-      </c>
-      <c r="L182" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J183" t="s">
-        <v>40</v>
-      </c>
-      <c r="K183">
-        <v>20</v>
-      </c>
-      <c r="L183" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J184" t="s">
-        <v>40</v>
-      </c>
-      <c r="K184">
-        <v>20</v>
-      </c>
       <c r="L184" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J185" t="s">
         <v>40</v>
       </c>
       <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J186" t="s">
+        <v>40</v>
+      </c>
+      <c r="K186">
+        <v>20</v>
+      </c>
+      <c r="L186" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J187" t="s">
+        <v>40</v>
+      </c>
+      <c r="K187">
+        <v>20</v>
+      </c>
+      <c r="L187" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J188" t="s">
+        <v>40</v>
+      </c>
+      <c r="K188">
+        <v>20</v>
+      </c>
+      <c r="L188" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J189" t="s">
+        <v>40</v>
+      </c>
+      <c r="K189">
         <f>43</f>
         <v>43</v>
       </c>
-      <c r="L185" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
-      <c r="D186" s="4"/>
-      <c r="E186" s="4"/>
-      <c r="F186" s="4"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="5"/>
-      <c r="K186" s="5"/>
-      <c r="L186" s="5"/>
-      <c r="M186" s="5"/>
-      <c r="N186" s="5"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>54</v>
-      </c>
-      <c r="J187" t="s">
-        <v>40</v>
-      </c>
-      <c r="K187">
-        <v>37</v>
-      </c>
-      <c r="L187" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>95</v>
-      </c>
-      <c r="J188" t="s">
-        <v>40</v>
-      </c>
-      <c r="K188" s="17">
-        <v>43</v>
-      </c>
-      <c r="L188" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>275</v>
-      </c>
-      <c r="J189" t="s">
-        <v>40</v>
-      </c>
-      <c r="K189" s="17">
-        <v>36</v>
-      </c>
       <c r="L189" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -4811,90 +4828,81 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="J191" t="s">
         <v>40</v>
       </c>
       <c r="K191">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="L191" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" s="26" t="s">
-        <v>210</v>
+      <c r="A192" t="s">
+        <v>95</v>
       </c>
       <c r="J192" t="s">
         <v>40</v>
       </c>
-      <c r="K192">
-        <v>0.4</v>
+      <c r="K192" s="17">
+        <v>43</v>
       </c>
       <c r="L192" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="26" t="s">
-        <v>211</v>
+      <c r="A193" t="s">
+        <v>275</v>
       </c>
       <c r="J193" t="s">
         <v>40</v>
       </c>
-      <c r="K193" s="6">
-        <v>95</v>
+      <c r="K193" s="17">
+        <v>36</v>
       </c>
       <c r="L193" t="s">
         <v>38</v>
       </c>
-      <c r="M193" s="6" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="J194" t="s">
-        <v>40</v>
-      </c>
-      <c r="K194">
-        <v>100</v>
-      </c>
-      <c r="L194" t="s">
-        <v>38</v>
-      </c>
+      <c r="A194" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" s="4"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
+      <c r="H194" s="4"/>
+      <c r="I194" s="4"/>
+      <c r="J194" s="5"/>
+      <c r="K194" s="5"/>
+      <c r="L194" s="5"/>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="8"/>
-      <c r="G195" s="8"/>
-      <c r="H195" s="8"/>
-      <c r="I195" s="8"/>
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
       <c r="J195" t="s">
         <v>40</v>
       </c>
-      <c r="K195">
-        <v>100</v>
+      <c r="K195" s="17">
+        <v>12</v>
       </c>
       <c r="L195" t="s">
         <v>38</v>
       </c>
-      <c r="M195" s="8"/>
-      <c r="N195" s="8"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -4912,89 +4920,90 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="J197" t="s">
         <v>40</v>
       </c>
-      <c r="K197" s="15">
-        <v>52</v>
+      <c r="K197">
+        <v>5</v>
       </c>
       <c r="L197" t="s">
         <v>38</v>
       </c>
-      <c r="M197" s="24"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
-      <c r="D198" s="4"/>
-      <c r="E198" s="4"/>
-      <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="5"/>
-      <c r="K198" s="5"/>
-      <c r="L198" s="5"/>
-      <c r="M198" s="5"/>
-      <c r="N198" s="5"/>
+      <c r="A198" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="J198" t="s">
+        <v>40</v>
+      </c>
+      <c r="K198">
+        <v>0.4</v>
+      </c>
+      <c r="L198" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>224</v>
+      <c r="A199" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="J199" t="s">
         <v>40</v>
       </c>
       <c r="K199" s="6">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L199" t="s">
         <v>38</v>
       </c>
       <c r="M199" s="6" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>226</v>
+      <c r="A200" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="J200" t="s">
         <v>40</v>
       </c>
-      <c r="K200" s="27">
-        <f>K199</f>
-        <v>24</v>
-      </c>
-      <c r="L200" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M200" s="27" t="s">
-        <v>228</v>
+      <c r="K200">
+        <v>100</v>
+      </c>
+      <c r="L200" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>225</v>
-      </c>
+      <c r="A201" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="8"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="8"/>
       <c r="J201" t="s">
         <v>40</v>
       </c>
       <c r="K201">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="L201" t="s">
         <v>38</v>
       </c>
+      <c r="M201" s="8"/>
+      <c r="N201" s="8"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5012,287 +5021,246 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="J203" t="s">
         <v>40</v>
       </c>
-      <c r="K203">
-        <v>100</v>
+      <c r="K203" s="15">
+        <v>52</v>
       </c>
       <c r="L203" t="s">
         <v>38</v>
       </c>
+      <c r="M203" s="24"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>238</v>
-      </c>
-      <c r="J204" t="s">
-        <v>40</v>
-      </c>
-      <c r="K204">
-        <v>4</v>
-      </c>
-      <c r="L204" t="s">
-        <v>38</v>
-      </c>
-      <c r="M204" t="s">
-        <v>113</v>
-      </c>
+      <c r="A204" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="4"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4"/>
+      <c r="G204" s="4"/>
+      <c r="H204" s="4"/>
+      <c r="I204" s="4"/>
+      <c r="J204" s="5"/>
+      <c r="K204" s="5"/>
+      <c r="L204" s="5"/>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="J205" t="s">
         <v>40</v>
       </c>
-      <c r="K205">
-        <v>85</v>
+      <c r="K205" s="6">
+        <v>24</v>
       </c>
       <c r="L205" t="s">
         <v>38</v>
       </c>
-      <c r="M205" t="s">
-        <v>241</v>
+      <c r="M205" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="J206" t="s">
         <v>40</v>
       </c>
-      <c r="K206">
-        <v>22</v>
-      </c>
-      <c r="L206" t="s">
-        <v>38</v>
-      </c>
-      <c r="M206" t="s">
-        <v>242</v>
+      <c r="K206" s="27">
+        <f>K205</f>
+        <v>24</v>
+      </c>
+      <c r="L206" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M206" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>225</v>
+      </c>
+      <c r="J207" t="s">
+        <v>40</v>
+      </c>
+      <c r="K207">
+        <v>61</v>
+      </c>
+      <c r="L207" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="2"/>
-      <c r="J208" s="3"/>
-      <c r="K208" s="3"/>
-      <c r="L208" s="3"/>
-      <c r="M208" s="3"/>
-      <c r="N208" s="3"/>
+      <c r="A208" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4"/>
+      <c r="G208" s="4"/>
+      <c r="H208" s="4"/>
+      <c r="I208" s="4"/>
+      <c r="J208" s="5"/>
+      <c r="K208" s="5"/>
+      <c r="L208" s="5"/>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G209" s="7"/>
-      <c r="H209" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K209" s="7">
-        <v>-100</v>
-      </c>
-      <c r="L209" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M209" s="7" t="s">
-        <v>184</v>
+      <c r="A209" t="s">
+        <v>235</v>
+      </c>
+      <c r="J209" t="s">
+        <v>40</v>
+      </c>
+      <c r="K209">
+        <v>100</v>
+      </c>
+      <c r="L209" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G210" s="7"/>
-      <c r="H210" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K210" s="7">
-        <v>0</v>
-      </c>
-      <c r="L210" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M210" s="7" t="s">
-        <v>44</v>
+      <c r="A210" t="s">
+        <v>238</v>
+      </c>
+      <c r="J210" t="s">
+        <v>40</v>
+      </c>
+      <c r="K210">
+        <v>4</v>
+      </c>
+      <c r="L210" t="s">
+        <v>38</v>
+      </c>
+      <c r="M210" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A211" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
-      <c r="J211" s="5"/>
-      <c r="K211" s="5"/>
-      <c r="L211" s="5"/>
-      <c r="M211" s="5"/>
-      <c r="N211" s="5"/>
+      <c r="A211" t="s">
+        <v>236</v>
+      </c>
+      <c r="J211" t="s">
+        <v>40</v>
+      </c>
+      <c r="K211">
+        <v>85</v>
+      </c>
+      <c r="L211" t="s">
+        <v>38</v>
+      </c>
+      <c r="M211" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>186</v>
-      </c>
-      <c r="G212" t="s">
-        <v>87</v>
-      </c>
-      <c r="H212" t="s">
+        <v>239</v>
+      </c>
+      <c r="J212" t="s">
+        <v>40</v>
+      </c>
+      <c r="K212">
+        <v>22</v>
+      </c>
+      <c r="L212" t="s">
+        <v>38</v>
+      </c>
+      <c r="M212" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G215" s="7"/>
+      <c r="H215" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I215" s="7"/>
+      <c r="J215" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K215" s="7">
+        <v>-100</v>
+      </c>
+      <c r="L215" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M215" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G216" s="7"/>
+      <c r="H216" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J212" t="s">
+      <c r="I216" s="7"/>
+      <c r="J216" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K212" s="17">
-        <v>5.3</v>
-      </c>
-      <c r="L212" t="s">
-        <v>38</v>
-      </c>
-      <c r="M212" t="s">
-        <v>175</v>
-      </c>
-      <c r="N212" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>191</v>
-      </c>
-      <c r="G213" t="s">
-        <v>87</v>
-      </c>
-      <c r="H213" t="s">
-        <v>43</v>
-      </c>
-      <c r="J213" t="s">
-        <v>41</v>
-      </c>
-      <c r="K213" s="40">
-        <f>K212</f>
-        <v>5.3</v>
-      </c>
-      <c r="L213" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>187</v>
-      </c>
-      <c r="G214" t="s">
-        <v>87</v>
-      </c>
-      <c r="H214" t="s">
-        <v>43</v>
-      </c>
-      <c r="J214" t="s">
-        <v>41</v>
-      </c>
-      <c r="K214" s="17">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L214" t="s">
-        <v>38</v>
-      </c>
-      <c r="M214" t="s">
-        <v>175</v>
-      </c>
-      <c r="N214" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>192</v>
-      </c>
-      <c r="G215" t="s">
-        <v>87</v>
-      </c>
-      <c r="H215" t="s">
-        <v>43</v>
-      </c>
-      <c r="J215" t="s">
-        <v>41</v>
-      </c>
-      <c r="K215" s="40">
-        <f>K214</f>
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L215" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>188</v>
-      </c>
-      <c r="G216" t="s">
-        <v>87</v>
-      </c>
-      <c r="H216" t="s">
-        <v>43</v>
-      </c>
-      <c r="J216" t="s">
-        <v>41</v>
-      </c>
-      <c r="K216" s="17">
-        <v>12.7</v>
-      </c>
-      <c r="L216" t="s">
-        <v>38</v>
-      </c>
-      <c r="M216" t="s">
-        <v>175</v>
-      </c>
-      <c r="N216" t="s">
-        <v>98</v>
+      <c r="K216" s="7">
+        <v>0</v>
+      </c>
+      <c r="L216" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M216" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>193</v>
-      </c>
-      <c r="G217" t="s">
-        <v>87</v>
-      </c>
-      <c r="H217" t="s">
-        <v>43</v>
-      </c>
-      <c r="J217" t="s">
-        <v>41</v>
-      </c>
-      <c r="K217" s="40">
-        <f>K216</f>
-        <v>12.7</v>
-      </c>
-      <c r="L217" t="s">
-        <v>38</v>
-      </c>
+      <c r="A217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="5"/>
+      <c r="K217" s="5"/>
+      <c r="L217" s="5"/>
+      <c r="M217" s="5"/>
+      <c r="N217" s="5"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G218" t="s">
         <v>87</v>
@@ -5304,21 +5272,21 @@
         <v>41</v>
       </c>
       <c r="K218" s="17">
-        <v>24</v>
+        <v>5.3</v>
       </c>
       <c r="L218" t="s">
         <v>38</v>
       </c>
       <c r="M218" t="s">
-        <v>176</v>
-      </c>
-      <c r="N218" s="26" t="s">
-        <v>173</v>
+        <v>175</v>
+      </c>
+      <c r="N218" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G219" t="s">
         <v>87</v>
@@ -5331,16 +5299,15 @@
       </c>
       <c r="K219" s="40">
         <f>K218</f>
-        <v>24</v>
+        <v>5.3</v>
       </c>
       <c r="L219" t="s">
         <v>38</v>
       </c>
-      <c r="N219" s="26"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G220" t="s">
         <v>87</v>
@@ -5351,16 +5318,22 @@
       <c r="J220" t="s">
         <v>41</v>
       </c>
-      <c r="K220" s="6">
-        <v>10</v>
+      <c r="K220" s="17">
+        <v>4.9000000000000004</v>
       </c>
       <c r="L220" t="s">
         <v>38</v>
+      </c>
+      <c r="M220" t="s">
+        <v>175</v>
+      </c>
+      <c r="N220" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G221" t="s">
         <v>87</v>
@@ -5373,33 +5346,41 @@
       </c>
       <c r="K221" s="40">
         <f>K220</f>
-        <v>10</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L221" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A222" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
-      <c r="J222" s="5"/>
-      <c r="K222" s="5"/>
-      <c r="L222" s="5"/>
-      <c r="M222" s="5"/>
-      <c r="N222" s="5"/>
+      <c r="A222" t="s">
+        <v>188</v>
+      </c>
+      <c r="G222" t="s">
+        <v>87</v>
+      </c>
+      <c r="H222" t="s">
+        <v>43</v>
+      </c>
+      <c r="J222" t="s">
+        <v>41</v>
+      </c>
+      <c r="K222" s="17">
+        <v>12.7</v>
+      </c>
+      <c r="L222" t="s">
+        <v>38</v>
+      </c>
+      <c r="M222" t="s">
+        <v>175</v>
+      </c>
+      <c r="N222" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" s="17" t="s">
-        <v>99</v>
+      <c r="A223" t="s">
+        <v>193</v>
       </c>
       <c r="G223" t="s">
         <v>87</v>
@@ -5410,19 +5391,17 @@
       <c r="J223" t="s">
         <v>41</v>
       </c>
-      <c r="K223" s="17">
-        <v>12</v>
+      <c r="K223" s="40">
+        <f>K222</f>
+        <v>12.7</v>
       </c>
       <c r="L223" t="s">
         <v>38</v>
       </c>
-      <c r="N223" s="26" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" s="17" t="s">
-        <v>100</v>
+      <c r="A224" t="s">
+        <v>189</v>
       </c>
       <c r="G224" t="s">
         <v>87</v>
@@ -5434,18 +5413,21 @@
         <v>41</v>
       </c>
       <c r="K224" s="17">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L224" t="s">
         <v>38</v>
+      </c>
+      <c r="M224" t="s">
+        <v>176</v>
       </c>
       <c r="N224" s="26" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A225" s="17" t="s">
-        <v>216</v>
+      <c r="A225" t="s">
+        <v>194</v>
       </c>
       <c r="G225" t="s">
         <v>87</v>
@@ -5456,16 +5438,18 @@
       <c r="J225" t="s">
         <v>41</v>
       </c>
-      <c r="K225" s="17">
-        <v>0</v>
+      <c r="K225" s="40">
+        <f>K224</f>
+        <v>24</v>
       </c>
       <c r="L225" t="s">
         <v>38</v>
       </c>
+      <c r="N225" s="26"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A226" s="17" t="s">
-        <v>101</v>
+      <c r="A226" t="s">
+        <v>190</v>
       </c>
       <c r="G226" t="s">
         <v>87</v>
@@ -5476,60 +5460,55 @@
       <c r="J226" t="s">
         <v>41</v>
       </c>
-      <c r="K226" s="17">
-        <v>0</v>
+      <c r="K226" s="6">
+        <v>10</v>
       </c>
       <c r="L226" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A227" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
-      <c r="I227" s="4"/>
-      <c r="J227" s="5"/>
-      <c r="K227" s="5"/>
-      <c r="L227" s="5"/>
-      <c r="M227" s="5"/>
-      <c r="N227" s="5"/>
+      <c r="A227" t="s">
+        <v>195</v>
+      </c>
+      <c r="G227" t="s">
+        <v>87</v>
+      </c>
+      <c r="H227" t="s">
+        <v>43</v>
+      </c>
+      <c r="J227" t="s">
+        <v>41</v>
+      </c>
+      <c r="K227" s="40">
+        <f>K226</f>
+        <v>10</v>
+      </c>
+      <c r="L227" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A228" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="G228" t="s">
-        <v>87</v>
-      </c>
-      <c r="H228" t="s">
-        <v>43</v>
-      </c>
-      <c r="J228" t="s">
-        <v>41</v>
-      </c>
-      <c r="K228" s="17">
-        <v>25</v>
-      </c>
-      <c r="L228" t="s">
-        <v>38</v>
-      </c>
-      <c r="M228" t="s">
-        <v>178</v>
-      </c>
-      <c r="N228" s="26" t="s">
-        <v>173</v>
-      </c>
+      <c r="A228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4"/>
+      <c r="G228" s="4"/>
+      <c r="H228" s="4"/>
+      <c r="I228" s="4"/>
+      <c r="J228" s="5"/>
+      <c r="K228" s="5"/>
+      <c r="L228" s="5"/>
+      <c r="M228" s="5"/>
+      <c r="N228" s="5"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="G229" t="s">
         <v>87</v>
@@ -5541,13 +5520,10 @@
         <v>41</v>
       </c>
       <c r="K229" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L229" t="s">
         <v>38</v>
-      </c>
-      <c r="M229" t="s">
-        <v>179</v>
       </c>
       <c r="N229" s="26" t="s">
         <v>173</v>
@@ -5555,7 +5531,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="17" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G230" t="s">
         <v>87</v>
@@ -5567,13 +5543,10 @@
         <v>41</v>
       </c>
       <c r="K230" s="17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L230" t="s">
         <v>38</v>
-      </c>
-      <c r="M230" t="s">
-        <v>177</v>
       </c>
       <c r="N230" s="26" t="s">
         <v>173</v>
@@ -5581,7 +5554,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="G231" t="s">
         <v>87</v>
@@ -5593,21 +5566,15 @@
         <v>41</v>
       </c>
       <c r="K231" s="17">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L231" t="s">
         <v>38</v>
-      </c>
-      <c r="M231" t="s">
-        <v>181</v>
-      </c>
-      <c r="N231" s="26" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="17" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G232" t="s">
         <v>87</v>
@@ -5619,62 +5586,62 @@
         <v>41</v>
       </c>
       <c r="K232" s="17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L232" t="s">
         <v>38</v>
       </c>
-      <c r="M232" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="N232" s="26" t="s">
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B233" s="4"/>
+      <c r="C233" s="4"/>
+      <c r="D233" s="4"/>
+      <c r="E233" s="4"/>
+      <c r="F233" s="4"/>
+      <c r="G233" s="4"/>
+      <c r="H233" s="4"/>
+      <c r="I233" s="4"/>
+      <c r="J233" s="5"/>
+      <c r="K233" s="5"/>
+      <c r="L233" s="5"/>
+      <c r="M233" s="5"/>
+      <c r="N233" s="5"/>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A234" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G234" t="s">
+        <v>87</v>
+      </c>
+      <c r="H234" t="s">
+        <v>43</v>
+      </c>
+      <c r="J234" t="s">
+        <v>41</v>
+      </c>
+      <c r="K234" s="17">
+        <v>25</v>
+      </c>
+      <c r="L234" t="s">
+        <v>38</v>
+      </c>
+      <c r="M234" t="s">
+        <v>178</v>
+      </c>
+      <c r="N234" s="26" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="G233" t="s">
-        <v>87</v>
-      </c>
-      <c r="H233" t="s">
-        <v>43</v>
-      </c>
-      <c r="J233" t="s">
-        <v>41</v>
-      </c>
-      <c r="K233" s="6">
-        <f>AVERAGE(K229:K232)</f>
-        <v>13</v>
-      </c>
-      <c r="L233" t="s">
-        <v>38</v>
-      </c>
-      <c r="M233" s="26"/>
-      <c r="N233" s="26"/>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="4"/>
-      <c r="J234" s="5"/>
-      <c r="K234" s="5"/>
-      <c r="L234" s="5"/>
-      <c r="M234" s="5"/>
-      <c r="N234" s="5"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>249</v>
+        <v>147</v>
+      </c>
+      <c r="G235" t="s">
+        <v>87</v>
       </c>
       <c r="H235" t="s">
         <v>43</v>
@@ -5683,21 +5650,24 @@
         <v>41</v>
       </c>
       <c r="K235" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L235" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L235" t="s">
         <v>38</v>
       </c>
       <c r="M235" t="s">
-        <v>254</v>
-      </c>
-      <c r="N235" t="s">
+        <v>179</v>
+      </c>
+      <c r="N235" s="26" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="17" t="s">
-        <v>250</v>
+        <v>144</v>
+      </c>
+      <c r="G236" t="s">
+        <v>87</v>
       </c>
       <c r="H236" t="s">
         <v>43</v>
@@ -5706,21 +5676,24 @@
         <v>41</v>
       </c>
       <c r="K236" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L236" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L236" t="s">
         <v>38</v>
       </c>
       <c r="M236" t="s">
-        <v>254</v>
-      </c>
-      <c r="N236" t="s">
+        <v>177</v>
+      </c>
+      <c r="N236" s="26" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>251</v>
+        <v>107</v>
+      </c>
+      <c r="G237" t="s">
+        <v>87</v>
       </c>
       <c r="H237" t="s">
         <v>43</v>
@@ -5729,21 +5702,24 @@
         <v>41</v>
       </c>
       <c r="K237" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L237" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L237" t="s">
         <v>38</v>
       </c>
       <c r="M237" t="s">
-        <v>254</v>
-      </c>
-      <c r="N237" t="s">
+        <v>181</v>
+      </c>
+      <c r="N237" s="26" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="17" t="s">
-        <v>253</v>
+        <v>110</v>
+      </c>
+      <c r="G238" t="s">
+        <v>87</v>
       </c>
       <c r="H238" t="s">
         <v>43</v>
@@ -5752,87 +5728,85 @@
         <v>41</v>
       </c>
       <c r="K238" s="17">
+        <v>11</v>
+      </c>
+      <c r="L238" t="s">
+        <v>38</v>
+      </c>
+      <c r="M238" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="N238" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="G239" t="s">
+        <v>87</v>
+      </c>
+      <c r="H239" t="s">
+        <v>43</v>
+      </c>
+      <c r="J239" t="s">
+        <v>41</v>
+      </c>
+      <c r="K239" s="6">
+        <f>AVERAGE(K235:K238)</f>
+        <v>13</v>
+      </c>
+      <c r="L239" t="s">
+        <v>38</v>
+      </c>
+      <c r="M239" s="26"/>
+      <c r="N239" s="26"/>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
+      <c r="H240" s="4"/>
+      <c r="I240" s="4"/>
+      <c r="J240" s="5"/>
+      <c r="K240" s="5"/>
+      <c r="L240" s="5"/>
+      <c r="M240" s="5"/>
+      <c r="N240" s="5"/>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A241" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="H241" t="s">
+        <v>43</v>
+      </c>
+      <c r="J241" t="s">
+        <v>41</v>
+      </c>
+      <c r="K241" s="17">
         <v>7.9</v>
       </c>
-      <c r="L238" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M238" t="s">
+      <c r="L241" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M241" t="s">
         <v>254</v>
       </c>
-      <c r="N238" t="s">
+      <c r="N241" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-      <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
-      <c r="H239" s="4"/>
-      <c r="I239" s="4"/>
-      <c r="J239" s="5"/>
-      <c r="K239" s="5"/>
-      <c r="L239" s="5"/>
-      <c r="M239" s="5"/>
-      <c r="N239" s="5"/>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A240" s="6"/>
-      <c r="B240" t="s">
-        <v>81</v>
-      </c>
-      <c r="G240" t="s">
-        <v>87</v>
-      </c>
-      <c r="H240" t="s">
-        <v>43</v>
-      </c>
-      <c r="J240" t="s">
-        <v>41</v>
-      </c>
-      <c r="K240" s="15">
-        <v>17</v>
-      </c>
-      <c r="L240" t="s">
-        <v>38</v>
-      </c>
-      <c r="M240" t="s">
-        <v>174</v>
-      </c>
-      <c r="N240" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A241" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-      <c r="E241" s="4"/>
-      <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
-      <c r="H241" s="4"/>
-      <c r="I241" s="4"/>
-      <c r="J241" s="5"/>
-      <c r="K241" s="5"/>
-      <c r="L241" s="5"/>
-      <c r="M241" s="5"/>
-      <c r="N241" s="5"/>
-    </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>54</v>
-      </c>
-      <c r="G242" t="s">
-        <v>87</v>
+      <c r="A242" s="17" t="s">
+        <v>250</v>
       </c>
       <c r="H242" t="s">
         <v>43</v>
@@ -5840,19 +5814,22 @@
       <c r="J242" t="s">
         <v>41</v>
       </c>
-      <c r="K242" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="L242" t="s">
-        <v>38</v>
+      <c r="K242" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L242" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M242" t="s">
+        <v>254</v>
+      </c>
+      <c r="N242" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>95</v>
-      </c>
-      <c r="G243" t="s">
-        <v>87</v>
+      <c r="A243" s="17" t="s">
+        <v>251</v>
       </c>
       <c r="H243" t="s">
         <v>43</v>
@@ -5860,19 +5837,22 @@
       <c r="J243" t="s">
         <v>41</v>
       </c>
-      <c r="K243" s="6">
-        <v>15.4</v>
-      </c>
-      <c r="L243" t="s">
-        <v>38</v>
+      <c r="K243" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L243" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M243" t="s">
+        <v>254</v>
+      </c>
+      <c r="N243" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>275</v>
-      </c>
-      <c r="G244" t="s">
-        <v>87</v>
+      <c r="A244" s="17" t="s">
+        <v>253</v>
       </c>
       <c r="H244" t="s">
         <v>43</v>
@@ -5880,16 +5860,22 @@
       <c r="J244" t="s">
         <v>41</v>
       </c>
-      <c r="K244" s="6">
-        <v>0</v>
-      </c>
-      <c r="L244" t="s">
-        <v>38</v>
+      <c r="K244" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L244" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M244" t="s">
+        <v>254</v>
+      </c>
+      <c r="N244" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -5906,8 +5892,12 @@
       <c r="N245" s="5"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A246" s="6"/>
       <c r="B246" t="s">
-        <v>214</v>
+        <v>81</v>
+      </c>
+      <c r="G246" t="s">
+        <v>87</v>
       </c>
       <c r="H246" t="s">
         <v>43</v>
@@ -5915,22 +5905,22 @@
       <c r="J246" t="s">
         <v>41</v>
       </c>
-      <c r="K246">
-        <v>34.200000000000003</v>
+      <c r="K246" s="15">
+        <v>17</v>
       </c>
       <c r="L246" t="s">
         <v>38</v>
       </c>
       <c r="M246" t="s">
-        <v>221</v>
-      </c>
-      <c r="N246" s="26" t="s">
-        <v>222</v>
+        <v>174</v>
+      </c>
+      <c r="N246" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -5948,7 +5938,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="G248" t="s">
         <v>87</v>
@@ -5959,34 +5949,39 @@
       <c r="J248" t="s">
         <v>41</v>
       </c>
-      <c r="K248" s="23">
-        <v>1</v>
+      <c r="K248" s="6">
+        <v>2.4</v>
       </c>
       <c r="L248" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B249" s="4"/>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="4"/>
-      <c r="J249" s="5"/>
-      <c r="K249" s="5"/>
-      <c r="L249" s="5"/>
-      <c r="M249" s="5"/>
-      <c r="N249" s="5"/>
+      <c r="A249" t="s">
+        <v>95</v>
+      </c>
+      <c r="G249" t="s">
+        <v>87</v>
+      </c>
+      <c r="H249" t="s">
+        <v>43</v>
+      </c>
+      <c r="J249" t="s">
+        <v>41</v>
+      </c>
+      <c r="K249" s="6">
+        <v>15.4</v>
+      </c>
+      <c r="L249" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>235</v>
+        <v>275</v>
+      </c>
+      <c r="G250" t="s">
+        <v>87</v>
       </c>
       <c r="H250" t="s">
         <v>43</v>
@@ -5994,45 +5989,37 @@
       <c r="J250" t="s">
         <v>41</v>
       </c>
-      <c r="K250" s="17">
-        <v>24.7</v>
+      <c r="K250" s="6">
+        <v>0</v>
       </c>
       <c r="L250" t="s">
         <v>38</v>
       </c>
-      <c r="M250" t="s">
-        <v>243</v>
-      </c>
-      <c r="N250" s="26" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>238</v>
-      </c>
-      <c r="H251" t="s">
-        <v>43</v>
-      </c>
-      <c r="J251" t="s">
-        <v>41</v>
-      </c>
-      <c r="K251" s="17">
-        <v>8</v>
-      </c>
-      <c r="L251" t="s">
-        <v>38</v>
-      </c>
-      <c r="M251" t="s">
-        <v>172</v>
-      </c>
-      <c r="N251" s="26" t="s">
-        <v>173</v>
-      </c>
+      <c r="A251" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="4"/>
+      <c r="D251" s="4"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="4"/>
+      <c r="G251" s="4"/>
+      <c r="H251" s="4"/>
+      <c r="I251" s="4"/>
+      <c r="J251" s="5"/>
+      <c r="K251" s="5"/>
+      <c r="L251" s="5"/>
+      <c r="M251" s="5"/>
+      <c r="N251" s="5"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>236</v>
+        <v>15</v>
+      </c>
+      <c r="G252" t="s">
+        <v>87</v>
       </c>
       <c r="H252" t="s">
         <v>43</v>
@@ -6040,431 +6027,365 @@
       <c r="J252" t="s">
         <v>41</v>
       </c>
-      <c r="K252">
-        <v>7.9</v>
+      <c r="K252" s="17">
+        <v>19.399999999999999</v>
       </c>
       <c r="L252" t="s">
         <v>38</v>
       </c>
       <c r="M252" t="s">
-        <v>256</v>
+        <v>337</v>
       </c>
       <c r="N252" s="26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="4"/>
+      <c r="D253" s="4"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="4"/>
+      <c r="G253" s="4"/>
+      <c r="H253" s="4"/>
+      <c r="I253" s="4"/>
+      <c r="J253" s="5"/>
+      <c r="K253" s="5"/>
+      <c r="L253" s="5"/>
+      <c r="M253" s="5"/>
+      <c r="N253" s="5"/>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>214</v>
+      </c>
+      <c r="H254" t="s">
+        <v>43</v>
+      </c>
+      <c r="J254" t="s">
+        <v>41</v>
+      </c>
+      <c r="K254">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="L254" t="s">
+        <v>38</v>
+      </c>
+      <c r="M254" t="s">
+        <v>221</v>
+      </c>
+      <c r="N254" s="26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="4"/>
+      <c r="D255" s="4"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="4"/>
+      <c r="G255" s="4"/>
+      <c r="H255" s="4"/>
+      <c r="I255" s="4"/>
+      <c r="J255" s="5"/>
+      <c r="K255" s="5"/>
+      <c r="L255" s="5"/>
+      <c r="M255" s="5"/>
+      <c r="N255" s="5"/>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>132</v>
+      </c>
+      <c r="G256" t="s">
+        <v>87</v>
+      </c>
+      <c r="H256" t="s">
+        <v>43</v>
+      </c>
+      <c r="J256" t="s">
+        <v>41</v>
+      </c>
+      <c r="K256" s="23">
+        <v>1</v>
+      </c>
+      <c r="L256" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="4"/>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4"/>
+      <c r="G257" s="4"/>
+      <c r="H257" s="4"/>
+      <c r="I257" s="4"/>
+      <c r="J257" s="5"/>
+      <c r="K257" s="5"/>
+      <c r="L257" s="5"/>
+      <c r="M257" s="5"/>
+      <c r="N257" s="5"/>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>235</v>
+      </c>
+      <c r="H258" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" t="s">
+        <v>41</v>
+      </c>
+      <c r="K258" s="17">
+        <v>24.7</v>
+      </c>
+      <c r="L258" t="s">
+        <v>38</v>
+      </c>
+      <c r="M258" t="s">
+        <v>243</v>
+      </c>
+      <c r="N258" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>239</v>
-      </c>
-      <c r="H253" t="s">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>238</v>
+      </c>
+      <c r="H259" t="s">
         <v>43</v>
       </c>
-      <c r="J253" t="s">
+      <c r="J259" t="s">
         <v>41</v>
       </c>
-      <c r="K253">
-        <v>4.7</v>
-      </c>
-      <c r="L253" t="s">
-        <v>38</v>
-      </c>
-      <c r="M253" t="s">
-        <v>244</v>
-      </c>
-      <c r="N253" s="26" t="s">
+      <c r="K259" s="17">
+        <v>8</v>
+      </c>
+      <c r="L259" t="s">
+        <v>38</v>
+      </c>
+      <c r="M259" t="s">
+        <v>172</v>
+      </c>
+      <c r="N259" s="26" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B256" s="2"/>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="3"/>
-      <c r="K256" s="3"/>
-      <c r="L256" s="3"/>
-      <c r="M256" s="3"/>
-      <c r="N256" s="3"/>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J257" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="K257" s="7">
-        <v>0</v>
-      </c>
-      <c r="L257" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M257" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J258" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K258" s="7">
-        <v>0</v>
-      </c>
-      <c r="L258" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M258" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A259" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
-      <c r="H259" s="4"/>
-      <c r="I259" s="4"/>
-      <c r="J259" s="5"/>
-      <c r="K259" s="5"/>
-      <c r="L259" s="5"/>
-      <c r="M259" s="5"/>
-      <c r="N259" s="5"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>186</v>
-      </c>
-      <c r="C260" t="s">
-        <v>37</v>
+        <v>236</v>
+      </c>
+      <c r="H260" t="s">
+        <v>43</v>
       </c>
       <c r="J260" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="K260">
-        <v>79</v>
+        <v>7.9</v>
       </c>
       <c r="L260" t="s">
         <v>38</v>
       </c>
-      <c r="N260" t="s">
-        <v>92</v>
+      <c r="M260" t="s">
+        <v>256</v>
+      </c>
+      <c r="N260" s="26" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>239</v>
+      </c>
+      <c r="H261" t="s">
+        <v>43</v>
+      </c>
+      <c r="J261" t="s">
+        <v>41</v>
+      </c>
+      <c r="K261">
+        <v>4.7</v>
+      </c>
+      <c r="L261" t="s">
+        <v>38</v>
+      </c>
+      <c r="M261" t="s">
+        <v>244</v>
+      </c>
+      <c r="N261" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="2"/>
+      <c r="I264" s="2"/>
+      <c r="J264" s="3"/>
+      <c r="K264" s="3"/>
+      <c r="L264" s="3"/>
+      <c r="M264" s="3"/>
+      <c r="N264" s="3"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J265" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K265" s="7">
+        <v>0</v>
+      </c>
+      <c r="L265" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M265" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J266" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K266" s="7">
+        <v>0</v>
+      </c>
+      <c r="L266" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M266" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="4"/>
+      <c r="H267" s="4"/>
+      <c r="I267" s="4"/>
+      <c r="J267" s="5"/>
+      <c r="K267" s="5"/>
+      <c r="L267" s="5"/>
+      <c r="M267" s="5"/>
+      <c r="N267" s="5"/>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>186</v>
       </c>
-      <c r="C261" t="s">
+      <c r="C268" t="s">
         <v>37</v>
       </c>
-      <c r="F261" t="s">
-        <v>116</v>
-      </c>
-      <c r="J261" t="s">
-        <v>86</v>
-      </c>
-      <c r="K261">
-        <v>19</v>
-      </c>
-      <c r="L261" t="s">
-        <v>38</v>
-      </c>
-      <c r="N261" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>186</v>
-      </c>
-      <c r="C262" t="s">
-        <v>37</v>
-      </c>
-      <c r="F262" t="s">
-        <v>117</v>
-      </c>
-      <c r="J262" t="s">
-        <v>86</v>
-      </c>
-      <c r="K262">
-        <v>2</v>
-      </c>
-      <c r="L262" t="s">
-        <v>38</v>
-      </c>
-      <c r="N262" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>191</v>
-      </c>
-      <c r="C263" t="s">
-        <v>37</v>
-      </c>
-      <c r="J263" t="s">
+      <c r="J268" t="s">
         <v>85</v>
       </c>
-      <c r="K263">
-        <v>100</v>
-      </c>
-      <c r="L263" t="s">
-        <v>38</v>
-      </c>
-      <c r="N263" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B264" s="8"/>
-      <c r="C264" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D264" s="8"/>
-      <c r="E264" s="8"/>
-      <c r="F264" s="8"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
-      <c r="I264" s="8"/>
-      <c r="J264" t="s">
-        <v>85</v>
-      </c>
-      <c r="K264" s="8">
-        <v>72</v>
-      </c>
-      <c r="L264" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M264" s="8"/>
-      <c r="N264" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B265" s="8"/>
-      <c r="C265" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D265" s="8"/>
-      <c r="E265" s="8"/>
-      <c r="F265" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G265" s="8"/>
-      <c r="H265" s="8"/>
-      <c r="I265" s="8"/>
-      <c r="J265" t="s">
-        <v>86</v>
-      </c>
-      <c r="K265" s="8">
-        <v>19</v>
-      </c>
-      <c r="L265" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M265" s="8"/>
-      <c r="N265" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B266" s="8"/>
-      <c r="C266" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D266" s="8"/>
-      <c r="E266" s="8"/>
-      <c r="F266" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G266" s="8"/>
-      <c r="H266" s="8"/>
-      <c r="I266" s="8"/>
-      <c r="J266" t="s">
-        <v>86</v>
-      </c>
-      <c r="K266" s="8">
-        <v>9</v>
-      </c>
-      <c r="L266" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M266" s="8"/>
-      <c r="N266" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B267" s="8"/>
-      <c r="C267" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D267" s="8"/>
-      <c r="E267" s="8"/>
-      <c r="F267" s="8"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
-      <c r="I267" s="8"/>
-      <c r="J267" t="s">
-        <v>85</v>
-      </c>
-      <c r="K267" s="9">
-        <v>91</v>
-      </c>
-      <c r="L267" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M267" s="8"/>
-      <c r="N267" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A268" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D268" s="8"/>
-      <c r="E268" s="8"/>
-      <c r="F268" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G268" s="8"/>
-      <c r="H268" s="8"/>
-      <c r="I268" s="8"/>
-      <c r="J268" t="s">
-        <v>86</v>
-      </c>
-      <c r="K268" s="9">
-        <v>9</v>
-      </c>
-      <c r="L268" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M268" s="8"/>
+      <c r="K268">
+        <v>79</v>
+      </c>
+      <c r="L268" t="s">
+        <v>38</v>
+      </c>
       <c r="N268" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>188</v>
-      </c>
-      <c r="B269" s="8"/>
-      <c r="C269" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D269" s="8"/>
-      <c r="E269" s="8"/>
-      <c r="F269" s="8"/>
-      <c r="G269" s="8"/>
-      <c r="H269" s="8"/>
-      <c r="I269" s="8"/>
+        <v>186</v>
+      </c>
+      <c r="C269" t="s">
+        <v>37</v>
+      </c>
+      <c r="F269" t="s">
+        <v>116</v>
+      </c>
       <c r="J269" t="s">
-        <v>85</v>
-      </c>
-      <c r="K269" s="9">
-        <v>80</v>
-      </c>
-      <c r="L269" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M269" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="K269">
+        <v>19</v>
+      </c>
+      <c r="L269" t="s">
+        <v>38</v>
+      </c>
       <c r="N269" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>188</v>
-      </c>
-      <c r="B270" s="8"/>
-      <c r="C270" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D270" s="8"/>
-      <c r="E270" s="8"/>
-      <c r="F270" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G270" s="8"/>
-      <c r="H270" s="8"/>
-      <c r="I270" s="8"/>
+        <v>186</v>
+      </c>
+      <c r="C270" t="s">
+        <v>37</v>
+      </c>
+      <c r="F270" t="s">
+        <v>117</v>
+      </c>
       <c r="J270" t="s">
         <v>86</v>
       </c>
-      <c r="K270" s="9">
-        <v>20</v>
-      </c>
-      <c r="L270" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M270" s="8"/>
+      <c r="K270">
+        <v>2</v>
+      </c>
+      <c r="L270" t="s">
+        <v>38</v>
+      </c>
       <c r="N270" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>193</v>
-      </c>
-      <c r="B271" s="8"/>
-      <c r="C271" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D271" s="8"/>
-      <c r="E271" s="8"/>
-      <c r="F271" s="9"/>
-      <c r="G271" s="8"/>
-      <c r="H271" s="8"/>
-      <c r="I271" s="8"/>
+        <v>191</v>
+      </c>
+      <c r="C271" t="s">
+        <v>37</v>
+      </c>
       <c r="J271" t="s">
         <v>85</v>
       </c>
-      <c r="K271" s="9">
+      <c r="K271">
         <v>100</v>
       </c>
-      <c r="L271" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M271" s="8"/>
+      <c r="L271" t="s">
+        <v>38</v>
+      </c>
       <c r="N271" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>189</v>
+      <c r="A272" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B272" s="8"/>
-      <c r="C272" s="9" t="s">
-        <v>91</v>
+      <c r="C272" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D272" s="8"/>
       <c r="E272" s="8"/>
@@ -6475,10 +6396,10 @@
       <c r="J272" t="s">
         <v>85</v>
       </c>
-      <c r="K272" s="9">
-        <v>53</v>
-      </c>
-      <c r="L272" s="9" t="s">
+      <c r="K272" s="8">
+        <v>72</v>
+      </c>
+      <c r="L272" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M272" s="8"/>
@@ -6487,17 +6408,17 @@
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>189</v>
+      <c r="A273" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B273" s="8"/>
-      <c r="C273" s="9" t="s">
-        <v>91</v>
+      <c r="C273" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D273" s="8"/>
       <c r="E273" s="8"/>
-      <c r="F273" s="9" t="s">
-        <v>121</v>
+      <c r="F273" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="G273" s="8"/>
       <c r="H273" s="8"/>
@@ -6505,10 +6426,10 @@
       <c r="J273" t="s">
         <v>86</v>
       </c>
-      <c r="K273" s="9">
-        <v>20</v>
-      </c>
-      <c r="L273" s="9" t="s">
+      <c r="K273" s="8">
+        <v>19</v>
+      </c>
+      <c r="L273" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M273" s="8"/>
@@ -6517,17 +6438,17 @@
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>189</v>
+      <c r="A274" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B274" s="8"/>
-      <c r="C274" s="9" t="s">
-        <v>91</v>
+      <c r="C274" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D274" s="8"/>
       <c r="E274" s="8"/>
-      <c r="F274" s="9" t="s">
-        <v>185</v>
+      <c r="F274" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="G274" s="8"/>
       <c r="H274" s="8"/>
@@ -6535,10 +6456,10 @@
       <c r="J274" t="s">
         <v>86</v>
       </c>
-      <c r="K274" s="9">
-        <v>27</v>
-      </c>
-      <c r="L274" s="9" t="s">
+      <c r="K274" s="8">
+        <v>9</v>
+      </c>
+      <c r="L274" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M274" s="8"/>
@@ -6547,16 +6468,16 @@
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>194</v>
+      <c r="A275" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="B275" s="8"/>
-      <c r="C275" s="9" t="s">
-        <v>91</v>
+      <c r="C275" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D275" s="8"/>
       <c r="E275" s="8"/>
-      <c r="F275" s="9"/>
+      <c r="F275" s="8"/>
       <c r="G275" s="8"/>
       <c r="H275" s="8"/>
       <c r="I275" s="8"/>
@@ -6564,9 +6485,9 @@
         <v>85</v>
       </c>
       <c r="K275" s="9">
-        <v>73</v>
-      </c>
-      <c r="L275" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L275" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M275" s="8"/>
@@ -6575,17 +6496,17 @@
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>194</v>
+      <c r="A276" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="B276" s="8"/>
-      <c r="C276" s="9" t="s">
-        <v>91</v>
+      <c r="C276" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D276" s="8"/>
       <c r="E276" s="8"/>
-      <c r="F276" s="9" t="s">
-        <v>185</v>
+      <c r="F276" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="G276" s="8"/>
       <c r="H276" s="8"/>
@@ -6594,7 +6515,7 @@
         <v>86</v>
       </c>
       <c r="K276" s="9">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L276" s="9" t="s">
         <v>38</v>
@@ -6606,168 +6527,185 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>297</v>
-      </c>
-      <c r="B277" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="B277" s="8"/>
       <c r="C277" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D277" s="10"/>
-      <c r="E277" s="10"/>
-      <c r="F277" s="10"/>
-      <c r="G277" s="10"/>
-      <c r="H277" s="10"/>
-      <c r="I277" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="D277" s="8"/>
+      <c r="E277" s="8"/>
+      <c r="F277" s="8"/>
+      <c r="G277" s="8"/>
+      <c r="H277" s="8"/>
+      <c r="I277" s="8"/>
       <c r="J277" t="s">
         <v>85</v>
       </c>
-      <c r="K277" s="20">
-        <v>100</v>
+      <c r="K277" s="9">
+        <v>80</v>
       </c>
       <c r="L277" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M277" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="N277" s="8"/>
+      <c r="M277" s="8"/>
+      <c r="N277" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>298</v>
-      </c>
-      <c r="B278" s="10"/>
-      <c r="C278" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D278" s="10"/>
-      <c r="E278" s="10"/>
-      <c r="F278" s="10"/>
-      <c r="G278" s="10"/>
-      <c r="H278" s="10"/>
-      <c r="I278" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="B278" s="8"/>
+      <c r="C278" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D278" s="8"/>
+      <c r="E278" s="8"/>
+      <c r="F278" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G278" s="8"/>
+      <c r="H278" s="8"/>
+      <c r="I278" s="8"/>
       <c r="J278" t="s">
-        <v>85</v>
-      </c>
-      <c r="K278" s="20">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K278" s="9">
+        <v>20</v>
       </c>
       <c r="L278" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M278" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="N278" s="8"/>
+      <c r="M278" s="8"/>
+      <c r="N278" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>299</v>
-      </c>
-      <c r="B279" s="10"/>
+        <v>193</v>
+      </c>
+      <c r="B279" s="8"/>
       <c r="C279" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D279" s="10"/>
-      <c r="E279" s="10"/>
-      <c r="F279" s="10"/>
-      <c r="G279" s="10"/>
-      <c r="H279" s="10"/>
-      <c r="I279" s="10"/>
+      <c r="D279" s="8"/>
+      <c r="E279" s="8"/>
+      <c r="F279" s="9"/>
+      <c r="G279" s="8"/>
+      <c r="H279" s="8"/>
+      <c r="I279" s="8"/>
       <c r="J279" t="s">
         <v>85</v>
       </c>
-      <c r="K279" s="20">
+      <c r="K279" s="9">
         <v>100</v>
       </c>
       <c r="L279" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M279" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="N279" s="8"/>
+      <c r="M279" s="8"/>
+      <c r="N279" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>300</v>
-      </c>
-      <c r="B280" s="10"/>
+        <v>189</v>
+      </c>
+      <c r="B280" s="8"/>
       <c r="C280" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D280" s="10"/>
-      <c r="E280" s="10"/>
-      <c r="F280" s="10"/>
-      <c r="G280" s="10"/>
-      <c r="H280" s="10"/>
-      <c r="I280" s="10"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="8"/>
+      <c r="F280" s="8"/>
+      <c r="G280" s="8"/>
+      <c r="H280" s="8"/>
+      <c r="I280" s="8"/>
       <c r="J280" t="s">
         <v>85</v>
       </c>
-      <c r="K280" s="20">
-        <v>100</v>
+      <c r="K280" s="9">
+        <v>53</v>
       </c>
       <c r="L280" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M280" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="N280" s="8"/>
+      <c r="M280" s="8"/>
+      <c r="N280" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-      <c r="E281" s="4"/>
-      <c r="F281" s="4"/>
-      <c r="G281" s="4"/>
-      <c r="H281" s="4"/>
-      <c r="I281" s="4"/>
-      <c r="J281" s="5"/>
-      <c r="K281" s="5"/>
-      <c r="L281" s="5"/>
-      <c r="M281" s="5"/>
-      <c r="N281" s="5"/>
+      <c r="A281" t="s">
+        <v>189</v>
+      </c>
+      <c r="B281" s="8"/>
+      <c r="C281" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D281" s="8"/>
+      <c r="E281" s="8"/>
+      <c r="F281" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G281" s="8"/>
+      <c r="H281" s="8"/>
+      <c r="I281" s="8"/>
+      <c r="J281" t="s">
+        <v>86</v>
+      </c>
+      <c r="K281" s="9">
+        <v>20</v>
+      </c>
+      <c r="L281" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M281" s="8"/>
+      <c r="N281" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="17" t="s">
-        <v>99</v>
+      <c r="A282" t="s">
+        <v>189</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D282" s="8"/>
       <c r="E282" s="8"/>
-      <c r="F282" s="9"/>
+      <c r="F282" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
       <c r="I282" s="8"/>
       <c r="J282" t="s">
-        <v>85</v>
-      </c>
-      <c r="K282" s="11">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K282" s="9">
+        <v>27</v>
       </c>
       <c r="L282" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M282" s="10" t="s">
-        <v>104</v>
+      <c r="M282" s="8"/>
+      <c r="N282" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" s="17" t="s">
-        <v>100</v>
+      <c r="A283" t="s">
+        <v>194</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D283" s="8"/>
       <c r="E283" s="8"/>
@@ -6779,25 +6717,28 @@
         <v>85</v>
       </c>
       <c r="K283" s="9">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="L283" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M283" s="8"/>
+      <c r="N283" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="17" t="s">
-        <v>100</v>
+      <c r="A284" t="s">
+        <v>194</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D284" s="8"/>
       <c r="E284" s="8"/>
       <c r="F284" s="9" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
@@ -6806,282 +6747,335 @@
         <v>86</v>
       </c>
       <c r="K284" s="9">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="L284" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M284" s="8"/>
+      <c r="N284" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A285" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B285" s="8"/>
-      <c r="C285" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D285" s="8"/>
-      <c r="E285" s="8"/>
-      <c r="F285" s="9"/>
-      <c r="G285" s="8"/>
-      <c r="H285" s="8"/>
-      <c r="I285" s="8"/>
+      <c r="A285" t="s">
+        <v>297</v>
+      </c>
+      <c r="B285" s="10"/>
+      <c r="C285" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D285" s="10"/>
+      <c r="E285" s="10"/>
+      <c r="F285" s="10"/>
+      <c r="G285" s="10"/>
+      <c r="H285" s="10"/>
+      <c r="I285" s="10"/>
       <c r="J285" t="s">
         <v>85</v>
       </c>
-      <c r="K285" s="18">
-        <v>20</v>
+      <c r="K285" s="20">
+        <v>100</v>
       </c>
       <c r="L285" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M285" s="10" t="s">
-        <v>217</v>
-      </c>
+      <c r="M285" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N285" s="8"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A286" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B286" s="8"/>
-      <c r="C286" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D286" s="8"/>
-      <c r="E286" s="8"/>
-      <c r="F286" s="9"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
-      <c r="I286" s="8"/>
+      <c r="A286" t="s">
+        <v>298</v>
+      </c>
+      <c r="B286" s="10"/>
+      <c r="C286" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D286" s="10"/>
+      <c r="E286" s="10"/>
+      <c r="F286" s="10"/>
+      <c r="G286" s="10"/>
+      <c r="H286" s="10"/>
+      <c r="I286" s="10"/>
       <c r="J286" t="s">
         <v>85</v>
       </c>
-      <c r="K286" s="18">
-        <v>19</v>
+      <c r="K286" s="20">
+        <v>100</v>
       </c>
       <c r="L286" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M286" s="19"/>
+      <c r="M286" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N286" s="8"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A287" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B287" s="8"/>
+      <c r="A287" t="s">
+        <v>299</v>
+      </c>
+      <c r="B287" s="10"/>
       <c r="C287" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D287" s="8"/>
-      <c r="E287" s="8"/>
-      <c r="F287" t="s">
-        <v>198</v>
-      </c>
-      <c r="G287" s="8"/>
-      <c r="H287" s="8"/>
-      <c r="I287" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="D287" s="10"/>
+      <c r="E287" s="10"/>
+      <c r="F287" s="10"/>
+      <c r="G287" s="10"/>
+      <c r="H287" s="10"/>
+      <c r="I287" s="10"/>
       <c r="J287" t="s">
-        <v>86</v>
-      </c>
-      <c r="K287" s="28">
-        <f>0.02*0.5*100/(844/1000)/0.9</f>
-        <v>1.3164823591363877</v>
+        <v>85</v>
+      </c>
+      <c r="K287" s="20">
+        <v>100</v>
       </c>
       <c r="L287" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M287" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="N287" s="9" t="s">
-        <v>200</v>
-      </c>
+      <c r="M287" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N287" s="8"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A288" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B288" s="4"/>
-      <c r="C288" s="4"/>
-      <c r="D288" s="4"/>
-      <c r="E288" s="4"/>
-      <c r="F288" s="4"/>
-      <c r="G288" s="4"/>
-      <c r="H288" s="4"/>
-      <c r="I288" s="4"/>
-      <c r="J288" s="5"/>
-      <c r="K288" s="5"/>
-      <c r="L288" s="5"/>
-      <c r="M288" s="5"/>
-      <c r="N288" s="5"/>
+      <c r="A288" t="s">
+        <v>300</v>
+      </c>
+      <c r="B288" s="10"/>
+      <c r="C288" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D288" s="10"/>
+      <c r="E288" s="10"/>
+      <c r="F288" s="10"/>
+      <c r="G288" s="10"/>
+      <c r="H288" s="10"/>
+      <c r="I288" s="10"/>
+      <c r="J288" t="s">
+        <v>85</v>
+      </c>
+      <c r="K288" s="20">
+        <v>100</v>
+      </c>
+      <c r="L288" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M288" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N288" s="8"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A289" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C289" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="J289" t="s">
-        <v>85</v>
-      </c>
-      <c r="K289" s="18">
-        <v>100</v>
-      </c>
-      <c r="L289" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A289" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B289" s="4"/>
+      <c r="C289" s="4"/>
+      <c r="D289" s="4"/>
+      <c r="E289" s="4"/>
+      <c r="F289" s="4"/>
+      <c r="G289" s="4"/>
+      <c r="H289" s="4"/>
+      <c r="I289" s="4"/>
+      <c r="J289" s="5"/>
+      <c r="K289" s="5"/>
+      <c r="L289" s="5"/>
+      <c r="M289" s="5"/>
+      <c r="N289" s="5"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" s="17" t="s">
-        <v>147</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B290" s="8"/>
       <c r="C290" s="9" t="s">
-        <v>153</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D290" s="8"/>
+      <c r="E290" s="8"/>
+      <c r="F290" s="9"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="8"/>
       <c r="J290" t="s">
         <v>85</v>
       </c>
-      <c r="K290" s="18">
+      <c r="K290" s="11">
         <v>100</v>
       </c>
-      <c r="L290" s="17" t="s">
-        <v>38</v>
+      <c r="L290" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M290" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>143</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B291" s="8"/>
       <c r="C291" s="9" t="s">
-        <v>149</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D291" s="8"/>
+      <c r="E291" s="8"/>
+      <c r="F291" s="9"/>
+      <c r="G291" s="8"/>
+      <c r="H291" s="8"/>
+      <c r="I291" s="8"/>
       <c r="J291" t="s">
         <v>85</v>
       </c>
-      <c r="K291" s="18">
-        <v>100</v>
-      </c>
-      <c r="L291" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="K291" s="9">
+        <v>50</v>
+      </c>
+      <c r="L291" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M291" s="8"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" s="17" t="s">
-        <v>144</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B292" s="8"/>
       <c r="C292" s="9" t="s">
-        <v>150</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D292" s="8"/>
+      <c r="E292" s="8"/>
+      <c r="F292" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G292" s="8"/>
+      <c r="H292" s="8"/>
+      <c r="I292" s="8"/>
       <c r="J292" t="s">
-        <v>85</v>
-      </c>
-      <c r="K292" s="18">
-        <v>100</v>
-      </c>
-      <c r="L292" s="17" t="s">
-        <v>38</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="K292" s="9">
+        <v>50</v>
+      </c>
+      <c r="L292" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M292" s="8"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C293" s="9" t="s">
-        <v>151</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B293" s="8"/>
+      <c r="C293" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D293" s="8"/>
+      <c r="E293" s="8"/>
+      <c r="F293" s="9"/>
+      <c r="G293" s="8"/>
+      <c r="H293" s="8"/>
+      <c r="I293" s="8"/>
       <c r="J293" t="s">
         <v>85</v>
       </c>
       <c r="K293" s="18">
-        <v>100</v>
-      </c>
-      <c r="L293" s="17" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="L293" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M293" s="10" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" s="17" t="s">
-        <v>146</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B294" s="8"/>
       <c r="C294" s="9" t="s">
-        <v>148</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D294" s="8"/>
+      <c r="E294" s="8"/>
+      <c r="F294" s="9"/>
+      <c r="G294" s="8"/>
+      <c r="H294" s="8"/>
+      <c r="I294" s="8"/>
       <c r="J294" t="s">
         <v>85</v>
       </c>
       <c r="K294" s="18">
-        <v>100</v>
-      </c>
-      <c r="L294" s="17" t="s">
-        <v>38</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="L294" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M294" s="19"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B295" s="8"/>
       <c r="C295" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D295" s="8"/>
       <c r="E295" s="8"/>
-      <c r="F295" s="9"/>
+      <c r="F295" t="s">
+        <v>198</v>
+      </c>
       <c r="G295" s="8"/>
       <c r="H295" s="8"/>
       <c r="I295" s="8"/>
       <c r="J295" t="s">
-        <v>85</v>
-      </c>
-      <c r="K295" s="18">
-        <v>100</v>
-      </c>
-      <c r="L295" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M295" s="10"/>
+        <v>86</v>
+      </c>
+      <c r="K295" s="28">
+        <f>0.02*0.5*100/(844/1000)/0.9</f>
+        <v>1.3164823591363877</v>
+      </c>
+      <c r="L295" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M295" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="N295" s="9" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A296" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B296" s="8"/>
-      <c r="C296" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D296" s="8"/>
-      <c r="E296" s="8"/>
-      <c r="F296" s="9"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="8"/>
-      <c r="J296" t="s">
-        <v>85</v>
-      </c>
-      <c r="K296" s="18">
-        <v>100</v>
-      </c>
-      <c r="L296" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M296" s="10"/>
+      <c r="A296" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296" s="4"/>
+      <c r="C296" s="4"/>
+      <c r="D296" s="4"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="4"/>
+      <c r="G296" s="4"/>
+      <c r="H296" s="4"/>
+      <c r="I296" s="4"/>
+      <c r="J296" s="5"/>
+      <c r="K296" s="5"/>
+      <c r="L296" s="5"/>
+      <c r="M296" s="5"/>
+      <c r="N296" s="5"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B297" s="8"/>
+        <v>141</v>
+      </c>
       <c r="C297" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D297" s="8"/>
-      <c r="E297" s="8"/>
-      <c r="F297" s="9"/>
-      <c r="G297" s="8"/>
-      <c r="H297" s="8"/>
-      <c r="I297" s="8"/>
+        <v>142</v>
+      </c>
       <c r="J297" t="s">
         <v>85</v>
       </c>
@@ -7091,37 +7085,35 @@
       <c r="L297" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M297" s="10"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A298" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B298" s="4"/>
-      <c r="C298" s="4"/>
-      <c r="D298" s="4"/>
-      <c r="E298" s="4"/>
-      <c r="F298" s="4"/>
-      <c r="G298" s="4"/>
-      <c r="H298" s="4"/>
-      <c r="I298" s="4"/>
-      <c r="J298" s="5"/>
-      <c r="K298" s="5"/>
-      <c r="L298" s="5"/>
-      <c r="M298" s="5"/>
-      <c r="N298" s="5"/>
+      <c r="A298" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J298" t="s">
+        <v>85</v>
+      </c>
+      <c r="K298" s="18">
+        <v>100</v>
+      </c>
+      <c r="L298" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>246</v>
+        <v>149</v>
       </c>
       <c r="J299" t="s">
         <v>85</v>
       </c>
-      <c r="K299" s="17">
+      <c r="K299" s="18">
         <v>100</v>
       </c>
       <c r="L299" s="17" t="s">
@@ -7130,147 +7122,154 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="17" t="s">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="J300" t="s">
         <v>85</v>
       </c>
-      <c r="K300" s="17">
-        <v>65</v>
+      <c r="K300" s="18">
+        <v>100</v>
       </c>
       <c r="L300" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N300" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="C301" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F301" s="19" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="J301" t="s">
-        <v>86</v>
-      </c>
-      <c r="K301" s="17">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="K301" s="18">
+        <v>100</v>
       </c>
       <c r="L301" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N301" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" s="17" t="s">
-        <v>251</v>
+        <v>146</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="J302" t="s">
         <v>85</v>
       </c>
-      <c r="K302" s="17">
-        <v>22</v>
+      <c r="K302" s="18">
+        <v>100</v>
       </c>
       <c r="L302" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N302" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="17" t="s">
-        <v>251</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B303" s="8"/>
       <c r="C303" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F303" s="19" t="s">
-        <v>247</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D303" s="8"/>
+      <c r="E303" s="8"/>
+      <c r="F303" s="9"/>
+      <c r="G303" s="8"/>
+      <c r="H303" s="8"/>
+      <c r="I303" s="8"/>
       <c r="J303" t="s">
-        <v>86</v>
-      </c>
-      <c r="K303" s="17">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="K303" s="18">
+        <v>100</v>
       </c>
       <c r="L303" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N303" t="s">
-        <v>92</v>
-      </c>
+      <c r="M303" s="10"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" s="17" t="s">
-        <v>253</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B304" s="8"/>
       <c r="C304" s="9" t="s">
-        <v>255</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D304" s="8"/>
+      <c r="E304" s="8"/>
+      <c r="F304" s="9"/>
+      <c r="G304" s="8"/>
+      <c r="H304" s="8"/>
+      <c r="I304" s="8"/>
       <c r="J304" t="s">
         <v>85</v>
       </c>
-      <c r="K304" s="17">
+      <c r="K304" s="18">
         <v>100</v>
       </c>
       <c r="L304" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M304" s="10"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="17" t="s">
-        <v>262</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B305" s="8"/>
       <c r="C305" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="D305" s="8"/>
+      <c r="E305" s="8"/>
+      <c r="F305" s="9"/>
+      <c r="G305" s="8"/>
+      <c r="H305" s="8"/>
+      <c r="I305" s="8"/>
       <c r="J305" t="s">
         <v>85</v>
       </c>
-      <c r="K305" s="17">
+      <c r="K305" s="18">
         <v>100</v>
       </c>
       <c r="L305" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M305" s="10"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A306" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="C306" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J306" t="s">
-        <v>85</v>
-      </c>
-      <c r="K306" s="17">
-        <v>100</v>
-      </c>
-      <c r="L306" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A306" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B306" s="4"/>
+      <c r="C306" s="4"/>
+      <c r="D306" s="4"/>
+      <c r="E306" s="4"/>
+      <c r="F306" s="4"/>
+      <c r="G306" s="4"/>
+      <c r="H306" s="4"/>
+      <c r="I306" s="4"/>
+      <c r="J306" s="5"/>
+      <c r="K306" s="5"/>
+      <c r="L306" s="5"/>
+      <c r="M306" s="5"/>
+      <c r="N306" s="5"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="17" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="J307" t="s">
         <v>85</v>
@@ -7284,302 +7283,196 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="17" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="J308" t="s">
         <v>85</v>
       </c>
       <c r="K308" s="17">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L308" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="N308" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A309" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B309" s="4"/>
-      <c r="C309" s="4"/>
-      <c r="D309" s="4"/>
-      <c r="E309" s="4"/>
-      <c r="F309" s="4"/>
-      <c r="G309" s="4"/>
-      <c r="H309" s="4"/>
-      <c r="I309" s="4"/>
-      <c r="J309" s="5"/>
-      <c r="K309" s="5"/>
-      <c r="L309" s="5"/>
-      <c r="M309" s="5"/>
-      <c r="N309" s="5"/>
+      <c r="A309" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F309" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="J309" t="s">
+        <v>86</v>
+      </c>
+      <c r="K309" s="17">
+        <v>35</v>
+      </c>
+      <c r="L309" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N309" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A310" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B310" s="10"/>
-      <c r="C310" s="10"/>
-      <c r="D310" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E310" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F310" s="10"/>
-      <c r="G310" s="10"/>
-      <c r="H310" s="10"/>
-      <c r="I310" s="10"/>
+      <c r="A310" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C310" s="9" t="s">
+        <v>246</v>
+      </c>
       <c r="J310" t="s">
         <v>85</v>
       </c>
-      <c r="K310" s="12">
-        <f>100-K311</f>
-        <v>90.75</v>
-      </c>
-      <c r="L310" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M310" t="s">
-        <v>71</v>
-      </c>
-      <c r="N310" s="8" t="s">
-        <v>93</v>
+      <c r="K310" s="17">
+        <v>22</v>
+      </c>
+      <c r="L310" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N310" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A311" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B311" s="10"/>
-      <c r="C311" s="10"/>
-      <c r="D311" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E311" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F311" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G311" s="10"/>
-      <c r="H311" s="10"/>
-      <c r="I311" s="10"/>
+      <c r="A311" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C311" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F311" s="19" t="s">
+        <v>247</v>
+      </c>
       <c r="J311" t="s">
         <v>86</v>
       </c>
-      <c r="K311" s="12">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
-      </c>
-      <c r="L311" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N311" s="8" t="s">
-        <v>93</v>
+      <c r="K311" s="17">
+        <v>35</v>
+      </c>
+      <c r="L311" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N311" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A312" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B312" s="10"/>
-      <c r="C312" s="10"/>
-      <c r="D312" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E312" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F312" s="10"/>
-      <c r="G312" s="10"/>
-      <c r="H312" s="10"/>
-      <c r="I312" s="10"/>
+      <c r="A312" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>255</v>
+      </c>
       <c r="J312" t="s">
         <v>85</v>
       </c>
-      <c r="K312" s="12">
-        <f>100-K313</f>
-        <v>93.25</v>
-      </c>
-      <c r="L312" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M312" t="s">
-        <v>72</v>
-      </c>
-      <c r="N312" s="8" t="s">
-        <v>93</v>
+      <c r="K312" s="17">
+        <v>100</v>
+      </c>
+      <c r="L312" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A313" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B313" s="10"/>
-      <c r="C313" s="10"/>
-      <c r="D313" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E313" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F313" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G313" s="10"/>
-      <c r="H313" s="10"/>
-      <c r="I313" s="10"/>
+      <c r="A313" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="C313" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="J313" t="s">
-        <v>86</v>
-      </c>
-      <c r="K313" s="12">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
-      </c>
-      <c r="L313" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N313" s="8" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="K313" s="17">
+        <v>100</v>
+      </c>
+      <c r="L313" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A314" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B314" s="10"/>
-      <c r="C314" s="10"/>
-      <c r="D314" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E314" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F314" s="10"/>
-      <c r="G314" s="10"/>
-      <c r="H314" s="10"/>
-      <c r="I314" s="10"/>
+      <c r="A314" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="C314" s="9" t="s">
+        <v>268</v>
+      </c>
       <c r="J314" t="s">
         <v>85</v>
       </c>
-      <c r="K314" s="12">
-        <f>100-K315</f>
-        <v>97</v>
-      </c>
-      <c r="L314" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M314" t="s">
-        <v>73</v>
-      </c>
-      <c r="N314" s="8" t="s">
-        <v>93</v>
+      <c r="K314" s="17">
+        <v>100</v>
+      </c>
+      <c r="L314" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A315" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B315" s="10"/>
-      <c r="C315" s="10"/>
-      <c r="D315" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E315" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F315" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G315" s="10"/>
-      <c r="H315" s="10"/>
-      <c r="I315" s="10"/>
+      <c r="A315" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>270</v>
+      </c>
       <c r="J315" t="s">
-        <v>86</v>
-      </c>
-      <c r="K315" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
-      </c>
-      <c r="L315" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N315" s="8" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="K315" s="17">
+        <v>100</v>
+      </c>
+      <c r="L315" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A316" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B316" s="10"/>
-      <c r="C316" s="10"/>
-      <c r="D316" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E316" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F316" s="10"/>
-      <c r="G316" s="10"/>
-      <c r="H316" s="10"/>
-      <c r="I316" s="10"/>
+      <c r="A316" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="C316" s="9" t="s">
+        <v>271</v>
+      </c>
       <c r="J316" t="s">
         <v>85</v>
       </c>
-      <c r="K316" s="12">
-        <f>(100-K317)*0.1</f>
-        <v>9.7000000000000011</v>
-      </c>
-      <c r="L316" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M316" t="s">
-        <v>80</v>
-      </c>
-      <c r="N316" s="8" t="s">
-        <v>93</v>
+      <c r="K316" s="17">
+        <v>100</v>
+      </c>
+      <c r="L316" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A317" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B317" s="10"/>
-      <c r="C317" s="10"/>
-      <c r="D317" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E317" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F317" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G317" s="10"/>
-      <c r="H317" s="10"/>
-      <c r="I317" s="10"/>
-      <c r="J317" t="s">
-        <v>86</v>
-      </c>
-      <c r="K317" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
-      </c>
-      <c r="L317" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N317" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="A317" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="4"/>
+      <c r="C317" s="4"/>
+      <c r="D317" s="4"/>
+      <c r="E317" s="4"/>
+      <c r="F317" s="4"/>
+      <c r="G317" s="4"/>
+      <c r="H317" s="4"/>
+      <c r="I317" s="4"/>
+      <c r="J317" s="5"/>
+      <c r="K317" s="5"/>
+      <c r="L317" s="5"/>
+      <c r="M317" s="5"/>
+      <c r="N317" s="5"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B318" s="10"/>
       <c r="C318" s="10"/>
@@ -7589,21 +7482,22 @@
       <c r="E318" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F318" s="10" t="s">
-        <v>70</v>
-      </c>
+      <c r="F318" s="10"/>
       <c r="G318" s="10"/>
       <c r="H318" s="10"/>
       <c r="I318" s="10"/>
       <c r="J318" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K318" s="12">
-        <f>(100-K317)*0.9</f>
-        <v>87.3</v>
+        <f>100-K319</f>
+        <v>90.75</v>
       </c>
       <c r="L318" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M318" t="s">
+        <v>71</v>
       </c>
       <c r="N318" s="8" t="s">
         <v>93</v>
@@ -7611,7 +7505,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B319" s="10"/>
       <c r="C319" s="10"/>
@@ -7619,32 +7513,31 @@
         <v>79</v>
       </c>
       <c r="E319" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F319" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F319" s="10"/>
       <c r="G319" s="10"/>
       <c r="H319" s="10"/>
       <c r="I319" s="10"/>
       <c r="J319" t="s">
-        <v>85</v>
-      </c>
-      <c r="K319" s="10">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+        <v>86</v>
+      </c>
+      <c r="K319" s="12">
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="L319" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M319" t="s">
-        <v>78</v>
       </c>
       <c r="N319" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A320" s="11" t="s">
-        <v>69</v>
+      <c r="A320" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -7652,7 +7545,7 @@
         <v>79</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F320" s="10"/>
       <c r="G320" s="10"/>
@@ -7662,14 +7555,14 @@
         <v>85</v>
       </c>
       <c r="K320" s="12">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+        <f>100-K321</f>
+        <v>93.25</v>
       </c>
       <c r="L320" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M320" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N320" s="8" t="s">
         <v>93</v>
@@ -7677,7 +7570,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B321" s="10"/>
       <c r="C321" s="10"/>
@@ -7685,24 +7578,23 @@
         <v>79</v>
       </c>
       <c r="E321" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F321" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F321" s="10"/>
       <c r="G321" s="10"/>
       <c r="H321" s="10"/>
       <c r="I321" s="10"/>
       <c r="J321" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K321" s="12">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L321" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M321" t="s">
-        <v>75</v>
       </c>
       <c r="N321" s="8" t="s">
         <v>93</v>
@@ -7710,7 +7602,7 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B322" s="10"/>
       <c r="C322" s="10"/>
@@ -7718,7 +7610,7 @@
         <v>79</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F322" s="10"/>
       <c r="G322" s="10"/>
@@ -7727,15 +7619,15 @@
       <c r="J322" t="s">
         <v>85</v>
       </c>
-      <c r="K322" s="10">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+      <c r="K322" s="12">
+        <f>100-K323</f>
+        <v>97</v>
       </c>
       <c r="L322" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M322" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N322" s="8" t="s">
         <v>93</v>
@@ -7743,7 +7635,7 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B323" s="10"/>
       <c r="C323" s="10"/>
@@ -7751,293 +7643,304 @@
         <v>79</v>
       </c>
       <c r="E323" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F323" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F323" s="10"/>
       <c r="G323" s="10"/>
       <c r="H323" s="10"/>
       <c r="I323" s="10"/>
       <c r="J323" t="s">
+        <v>86</v>
+      </c>
+      <c r="K323" s="12">
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
+      </c>
+      <c r="L323" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N323" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A324" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B324" s="10"/>
+      <c r="C324" s="10"/>
+      <c r="D324" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E324" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F324" s="10"/>
+      <c r="G324" s="10"/>
+      <c r="H324" s="10"/>
+      <c r="I324" s="10"/>
+      <c r="J324" t="s">
         <v>85</v>
       </c>
-      <c r="K323" s="12">
+      <c r="K324" s="12">
+        <f>(100-K325)*0.1</f>
+        <v>9.7000000000000011</v>
+      </c>
+      <c r="L324" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M324" t="s">
+        <v>80</v>
+      </c>
+      <c r="N324" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A325" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B325" s="10"/>
+      <c r="C325" s="10"/>
+      <c r="D325" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E325" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F325" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G325" s="10"/>
+      <c r="H325" s="10"/>
+      <c r="I325" s="10"/>
+      <c r="J325" t="s">
+        <v>86</v>
+      </c>
+      <c r="K325" s="12">
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
+      </c>
+      <c r="L325" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N325" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A326" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B326" s="10"/>
+      <c r="C326" s="10"/>
+      <c r="D326" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E326" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F326" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G326" s="10"/>
+      <c r="H326" s="10"/>
+      <c r="I326" s="10"/>
+      <c r="J326" t="s">
+        <v>86</v>
+      </c>
+      <c r="K326" s="12">
+        <f>(100-K325)*0.9</f>
+        <v>87.3</v>
+      </c>
+      <c r="L326" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N326" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A327" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B327" s="10"/>
+      <c r="C327" s="10"/>
+      <c r="D327" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E327" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F327" s="10"/>
+      <c r="G327" s="10"/>
+      <c r="H327" s="10"/>
+      <c r="I327" s="10"/>
+      <c r="J327" t="s">
+        <v>85</v>
+      </c>
+      <c r="K327" s="10">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
+      </c>
+      <c r="L327" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M327" t="s">
+        <v>78</v>
+      </c>
+      <c r="N327" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A328" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B328" s="10"/>
+      <c r="C328" s="10"/>
+      <c r="D328" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E328" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F328" s="10"/>
+      <c r="G328" s="10"/>
+      <c r="H328" s="10"/>
+      <c r="I328" s="10"/>
+      <c r="J328" t="s">
+        <v>85</v>
+      </c>
+      <c r="K328" s="12">
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
+      </c>
+      <c r="L328" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M328" t="s">
+        <v>74</v>
+      </c>
+      <c r="N328" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A329" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B329" s="10"/>
+      <c r="C329" s="10"/>
+      <c r="D329" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E329" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F329" s="10"/>
+      <c r="G329" s="10"/>
+      <c r="H329" s="10"/>
+      <c r="I329" s="10"/>
+      <c r="J329" t="s">
+        <v>85</v>
+      </c>
+      <c r="K329" s="12">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
+      </c>
+      <c r="L329" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M329" t="s">
+        <v>75</v>
+      </c>
+      <c r="N329" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A330" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B330" s="10"/>
+      <c r="C330" s="10"/>
+      <c r="D330" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E330" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F330" s="10"/>
+      <c r="G330" s="10"/>
+      <c r="H330" s="10"/>
+      <c r="I330" s="10"/>
+      <c r="J330" t="s">
+        <v>85</v>
+      </c>
+      <c r="K330" s="10">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L330" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M330" t="s">
+        <v>76</v>
+      </c>
+      <c r="N330" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A331" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B331" s="10"/>
+      <c r="C331" s="10"/>
+      <c r="D331" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E331" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F331" s="10"/>
+      <c r="G331" s="10"/>
+      <c r="H331" s="10"/>
+      <c r="I331" s="10"/>
+      <c r="J331" t="s">
+        <v>85</v>
+      </c>
+      <c r="K331" s="12">
         <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
         <v>49.367088607594937</v>
       </c>
-      <c r="L323" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M323" t="s">
+      <c r="L331" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M331" t="s">
         <v>77</v>
       </c>
-      <c r="N323" s="8" t="s">
+      <c r="N331" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A324" s="10" t="s">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A332" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B324" s="8"/>
-      <c r="C324" s="8"/>
-      <c r="D324" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E324" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F324" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G324" s="8"/>
-      <c r="H324" s="8"/>
-      <c r="I324" s="8"/>
-      <c r="J324" t="s">
-        <v>86</v>
-      </c>
-      <c r="K324" s="14">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
-      </c>
-      <c r="L324" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M324" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N324" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A325" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B325" s="4"/>
-      <c r="C325" s="4"/>
-      <c r="D325" s="4"/>
-      <c r="E325" s="4"/>
-      <c r="F325" s="4"/>
-      <c r="G325" s="4"/>
-      <c r="H325" s="4"/>
-      <c r="I325" s="4"/>
-      <c r="J325" s="5"/>
-      <c r="K325" s="5"/>
-      <c r="L325" s="5"/>
-      <c r="M325" s="5"/>
-      <c r="N325" s="5"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A326" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B326" s="8"/>
-      <c r="C326" s="8"/>
-      <c r="D326" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E326" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F326" s="8"/>
-      <c r="G326" s="8"/>
-      <c r="H326" s="8"/>
-      <c r="I326" s="8"/>
-      <c r="J326" t="s">
-        <v>85</v>
-      </c>
-      <c r="K326" s="9">
-        <v>73</v>
-      </c>
-      <c r="L326" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M326" s="8"/>
-      <c r="N326" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A327" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B327" s="8"/>
-      <c r="C327" s="8"/>
-      <c r="D327" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E327" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F327" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G327" s="8"/>
-      <c r="H327" s="8"/>
-      <c r="I327" s="8"/>
-      <c r="J327" t="s">
-        <v>86</v>
-      </c>
-      <c r="K327" s="16">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="L327" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M327" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="N327" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A328" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B328" s="8"/>
-      <c r="C328" s="8"/>
-      <c r="D328" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E328" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F328" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="G328" s="8"/>
-      <c r="H328" s="8"/>
-      <c r="I328" s="8"/>
-      <c r="J328" t="s">
-        <v>86</v>
-      </c>
-      <c r="K328" s="16">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
-      </c>
-      <c r="L328" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M328" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="N328" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A329" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B329" s="8"/>
-      <c r="C329" s="8"/>
-      <c r="D329" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E329" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F329" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G329" s="8"/>
-      <c r="H329" s="8"/>
-      <c r="I329" s="8"/>
-      <c r="J329" t="s">
-        <v>86</v>
-      </c>
-      <c r="K329" s="16">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
-      </c>
-      <c r="L329" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M329" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="N329" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B330" s="8"/>
-      <c r="C330" s="8"/>
-      <c r="D330" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E330" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F330" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G330" s="8"/>
-      <c r="H330" s="8"/>
-      <c r="I330" s="8"/>
-      <c r="J330" t="s">
-        <v>86</v>
-      </c>
-      <c r="K330" s="9">
-        <v>18</v>
-      </c>
-      <c r="L330" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M330" s="8"/>
-      <c r="N330" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>95</v>
-      </c>
-      <c r="B331" s="8"/>
-      <c r="C331" s="8"/>
-      <c r="D331" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E331" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F331" s="8"/>
-      <c r="G331" s="8"/>
-      <c r="H331" s="8"/>
-      <c r="I331" s="8"/>
-      <c r="J331" t="s">
-        <v>85</v>
-      </c>
-      <c r="K331" s="9">
-        <v>71</v>
-      </c>
-      <c r="L331" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M331" s="8"/>
-      <c r="N331" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>95</v>
       </c>
       <c r="B332" s="8"/>
       <c r="C332" s="8"/>
-      <c r="D332" s="9" t="s">
+      <c r="D332" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E332" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F332" s="9" t="s">
-        <v>127</v>
+      <c r="E332" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F332" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="G332" s="8"/>
       <c r="H332" s="8"/>
@@ -8045,104 +7948,82 @@
       <c r="J332" t="s">
         <v>86</v>
       </c>
-      <c r="K332" s="16">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
-      </c>
-      <c r="L332" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M332" s="9" t="s">
-        <v>97</v>
+      <c r="K332" s="14">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="L332" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M332" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="N332" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>95</v>
-      </c>
-      <c r="B333" s="8"/>
-      <c r="C333" s="8"/>
-      <c r="D333" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E333" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F333" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G333" s="8"/>
-      <c r="H333" s="8"/>
-      <c r="I333" s="8"/>
-      <c r="J333" t="s">
-        <v>86</v>
-      </c>
-      <c r="K333" s="16">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
-      </c>
-      <c r="L333" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M333" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="N333" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="A333" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B333" s="4"/>
+      <c r="C333" s="4"/>
+      <c r="D333" s="4"/>
+      <c r="E333" s="4"/>
+      <c r="F333" s="4"/>
+      <c r="G333" s="4"/>
+      <c r="H333" s="4"/>
+      <c r="I333" s="4"/>
+      <c r="J333" s="5"/>
+      <c r="K333" s="5"/>
+      <c r="L333" s="5"/>
+      <c r="M333" s="5"/>
+      <c r="N333" s="5"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>95</v>
+      <c r="A334" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B334" s="8"/>
       <c r="C334" s="8"/>
-      <c r="D334" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E334" s="9" t="s">
+      <c r="D334" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E334" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F334" s="9" t="s">
-        <v>129</v>
-      </c>
+      <c r="F334" s="8"/>
       <c r="G334" s="8"/>
       <c r="H334" s="8"/>
       <c r="I334" s="8"/>
       <c r="J334" t="s">
-        <v>86</v>
-      </c>
-      <c r="K334" s="16">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
-      </c>
-      <c r="L334" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M334" s="9" t="s">
-        <v>97</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="K334" s="9">
+        <v>73</v>
+      </c>
+      <c r="L334" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M334" s="8"/>
       <c r="N334" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>95</v>
+      <c r="A335" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B335" s="8"/>
       <c r="C335" s="8"/>
-      <c r="D335" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E335" s="9" t="s">
+      <c r="D335" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E335" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F335" s="8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G335" s="8"/>
       <c r="H335" s="8"/>
@@ -8150,865 +8031,1183 @@
       <c r="J335" t="s">
         <v>86</v>
       </c>
-      <c r="K335" s="9">
-        <v>12</v>
-      </c>
-      <c r="L335" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M335" s="8"/>
+      <c r="K335" s="16">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="L335" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M335" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="N335" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>275</v>
+      <c r="A336" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B336" s="8"/>
       <c r="C336" s="8"/>
-      <c r="D336" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E336" s="9" t="s">
+      <c r="D336" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E336" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F336" s="8"/>
+      <c r="F336" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="G336" s="8"/>
       <c r="H336" s="8"/>
       <c r="I336" s="8"/>
       <c r="J336" t="s">
-        <v>85</v>
-      </c>
-      <c r="K336" s="9">
-        <v>77</v>
-      </c>
-      <c r="L336" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M336" s="8"/>
-      <c r="N336" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="K336" s="16">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
+      </c>
+      <c r="L336" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M336" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="N336" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A337" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B337" s="10"/>
-      <c r="C337" s="10"/>
-      <c r="D337" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E337" s="11" t="s">
+      <c r="A337" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B337" s="8"/>
+      <c r="C337" s="8"/>
+      <c r="D337" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E337" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F337" s="11" t="s">
-        <v>277</v>
+      <c r="F337" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="G337" s="8"/>
       <c r="H337" s="8"/>
       <c r="I337" s="8"/>
-      <c r="K337" s="9"/>
-      <c r="L337" s="9"/>
-      <c r="M337" s="8"/>
-      <c r="N337" s="8"/>
+      <c r="J337" t="s">
+        <v>86</v>
+      </c>
+      <c r="K337" s="16">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L337" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M337" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="N337" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B338" s="4"/>
-      <c r="C338" s="4"/>
-      <c r="D338" s="4"/>
-      <c r="E338" s="4"/>
-      <c r="F338" s="4"/>
-      <c r="G338" s="4"/>
-      <c r="H338" s="4"/>
-      <c r="I338" s="4"/>
-      <c r="J338" s="5"/>
-      <c r="K338" s="5"/>
-      <c r="L338" s="5"/>
-      <c r="M338" s="5"/>
-      <c r="N338" s="5"/>
+      <c r="A338" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B338" s="8"/>
+      <c r="C338" s="8"/>
+      <c r="D338" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E338" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F338" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G338" s="8"/>
+      <c r="H338" s="8"/>
+      <c r="I338" s="8"/>
+      <c r="J338" t="s">
+        <v>86</v>
+      </c>
+      <c r="K338" s="9">
+        <v>18</v>
+      </c>
+      <c r="L338" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M338" s="8"/>
+      <c r="N338" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>209</v>
-      </c>
-      <c r="C339" t="s">
-        <v>218</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B339" s="8"/>
+      <c r="C339" s="8"/>
+      <c r="D339" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E339" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F339" s="8"/>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="8"/>
       <c r="J339" t="s">
         <v>85</v>
       </c>
-      <c r="K339">
-        <v>100</v>
-      </c>
-      <c r="L339" t="s">
-        <v>38</v>
+      <c r="K339" s="9">
+        <v>71</v>
+      </c>
+      <c r="L339" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M339" s="8"/>
+      <c r="N339" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="C340" t="s">
-        <v>219</v>
-      </c>
+      <c r="A340" t="s">
+        <v>95</v>
+      </c>
+      <c r="B340" s="8"/>
+      <c r="C340" s="8"/>
+      <c r="D340" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E340" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F340" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G340" s="8"/>
+      <c r="H340" s="8"/>
+      <c r="I340" s="8"/>
       <c r="J340" t="s">
-        <v>85</v>
-      </c>
-      <c r="K340">
-        <v>100</v>
-      </c>
-      <c r="L340" t="s">
-        <v>38</v>
+        <v>86</v>
+      </c>
+      <c r="K340" s="16">
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
+      </c>
+      <c r="L340" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M340" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N340" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A341" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C341" t="s">
-        <v>220</v>
-      </c>
+      <c r="A341" t="s">
+        <v>95</v>
+      </c>
+      <c r="B341" s="8"/>
+      <c r="C341" s="8"/>
+      <c r="D341" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E341" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F341" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G341" s="8"/>
+      <c r="H341" s="8"/>
+      <c r="I341" s="8"/>
       <c r="J341" t="s">
-        <v>85</v>
-      </c>
-      <c r="K341">
-        <v>100</v>
-      </c>
-      <c r="L341" t="s">
-        <v>38</v>
+        <v>86</v>
+      </c>
+      <c r="K341" s="16">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
+      </c>
+      <c r="L341" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M341" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N341" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A342" s="6" t="s">
-        <v>212</v>
+      <c r="A342" t="s">
+        <v>95</v>
+      </c>
+      <c r="B342" s="8"/>
+      <c r="C342" s="8"/>
+      <c r="D342" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E342" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F342" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G342" s="8"/>
+      <c r="H342" s="8"/>
+      <c r="I342" s="8"/>
+      <c r="J342" t="s">
+        <v>86</v>
+      </c>
+      <c r="K342" s="16">
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
+      </c>
+      <c r="L342" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M342" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N342" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" s="6" t="s">
-        <v>213</v>
+      <c r="A343" t="s">
+        <v>95</v>
       </c>
       <c r="B343" s="8"/>
       <c r="C343" s="8"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="F343" s="8"/>
+      <c r="D343" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E343" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F343" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
       <c r="I343" s="8"/>
+      <c r="J343" t="s">
+        <v>86</v>
+      </c>
+      <c r="K343" s="9">
+        <v>12</v>
+      </c>
+      <c r="L343" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="M343" s="8"/>
-      <c r="N343" s="8"/>
+      <c r="N343" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A344" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B344" s="4"/>
-      <c r="C344" s="4"/>
-      <c r="D344" s="4"/>
-      <c r="E344" s="4"/>
-      <c r="F344" s="4"/>
-      <c r="G344" s="4"/>
-      <c r="H344" s="4"/>
-      <c r="I344" s="4"/>
-      <c r="J344" s="5"/>
-      <c r="K344" s="5"/>
-      <c r="L344" s="5"/>
-      <c r="M344" s="5"/>
-      <c r="N344" s="5"/>
+      <c r="A344" t="s">
+        <v>275</v>
+      </c>
+      <c r="B344" s="8"/>
+      <c r="C344" s="8"/>
+      <c r="D344" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E344" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F344" s="8"/>
+      <c r="G344" s="8"/>
+      <c r="H344" s="8"/>
+      <c r="I344" s="8"/>
+      <c r="J344" t="s">
+        <v>85</v>
+      </c>
+      <c r="K344" s="9">
+        <v>77</v>
+      </c>
+      <c r="L344" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M344" s="8"/>
+      <c r="N344" s="8"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>132</v>
-      </c>
-      <c r="C345" t="s">
-        <v>134</v>
-      </c>
-      <c r="H345" t="s">
-        <v>45</v>
-      </c>
-      <c r="J345" t="s">
-        <v>85</v>
-      </c>
-      <c r="K345" s="21">
-        <v>38</v>
-      </c>
-      <c r="L345" t="s">
-        <v>38</v>
-      </c>
-      <c r="M345" s="11"/>
-      <c r="N345" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="A345" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B345" s="10"/>
+      <c r="C345" s="10"/>
+      <c r="D345" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E345" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F345" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="G345" s="8"/>
+      <c r="H345" s="8"/>
+      <c r="I345" s="8"/>
+      <c r="K345" s="9"/>
+      <c r="L345" s="9"/>
+      <c r="M345" s="8"/>
+      <c r="N345" s="8"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>132</v>
-      </c>
-      <c r="C346" t="s">
-        <v>134</v>
-      </c>
-      <c r="F346" t="s">
-        <v>135</v>
-      </c>
-      <c r="H346" t="s">
-        <v>45</v>
-      </c>
-      <c r="J346" t="s">
-        <v>86</v>
-      </c>
-      <c r="K346" s="21">
-        <v>60</v>
-      </c>
-      <c r="L346" t="s">
-        <v>38</v>
-      </c>
-      <c r="N346" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="A346" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B346" s="4"/>
+      <c r="C346" s="4"/>
+      <c r="D346" s="4"/>
+      <c r="E346" s="4"/>
+      <c r="F346" s="4"/>
+      <c r="G346" s="4"/>
+      <c r="H346" s="4"/>
+      <c r="I346" s="4"/>
+      <c r="J346" s="5"/>
+      <c r="K346" s="5"/>
+      <c r="L346" s="5"/>
+      <c r="M346" s="5"/>
+      <c r="N346" s="5"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>132</v>
-      </c>
-      <c r="C347" t="s">
-        <v>134</v>
-      </c>
-      <c r="H347" t="s">
-        <v>43</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B347" s="8"/>
+      <c r="C347" s="8"/>
+      <c r="D347" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E347" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F347" s="8"/>
+      <c r="G347" s="8"/>
+      <c r="H347" s="8"/>
+      <c r="I347" s="8"/>
       <c r="J347" t="s">
         <v>85</v>
       </c>
-      <c r="K347" s="21">
-        <v>32</v>
-      </c>
-      <c r="L347" t="s">
-        <v>38</v>
-      </c>
-      <c r="M347" t="s">
-        <v>137</v>
-      </c>
+      <c r="K347" s="9">
+        <v>100</v>
+      </c>
+      <c r="L347" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M347" s="8"/>
       <c r="N347" s="8"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>132</v>
-      </c>
-      <c r="C348" t="s">
-        <v>134</v>
-      </c>
-      <c r="F348" t="s">
-        <v>136</v>
-      </c>
-      <c r="H348" t="s">
-        <v>43</v>
-      </c>
-      <c r="J348" t="s">
-        <v>86</v>
-      </c>
-      <c r="K348" s="21">
-        <v>68</v>
-      </c>
-      <c r="L348" t="s">
-        <v>38</v>
-      </c>
-      <c r="N348" s="8"/>
+      <c r="A348" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B348" s="4"/>
+      <c r="C348" s="4"/>
+      <c r="D348" s="4"/>
+      <c r="E348" s="4"/>
+      <c r="F348" s="4"/>
+      <c r="G348" s="4"/>
+      <c r="H348" s="4"/>
+      <c r="I348" s="4"/>
+      <c r="J348" s="5"/>
+      <c r="K348" s="5"/>
+      <c r="L348" s="5"/>
+      <c r="M348" s="5"/>
+      <c r="N348" s="5"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A349" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B349" s="4"/>
-      <c r="C349" s="4"/>
-      <c r="D349" s="4"/>
-      <c r="E349" s="4"/>
-      <c r="F349" s="4"/>
-      <c r="G349" s="4"/>
-      <c r="H349" s="4"/>
-      <c r="I349" s="4"/>
-      <c r="J349" s="5"/>
-      <c r="K349" s="5"/>
-      <c r="L349" s="5"/>
-      <c r="M349" s="5"/>
-      <c r="N349" s="5"/>
+      <c r="A349" t="s">
+        <v>209</v>
+      </c>
+      <c r="C349" t="s">
+        <v>218</v>
+      </c>
+      <c r="J349" t="s">
+        <v>85</v>
+      </c>
+      <c r="K349">
+        <v>100</v>
+      </c>
+      <c r="L349" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>224</v>
+      <c r="A350" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="C350" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="J350" t="s">
         <v>85</v>
       </c>
-      <c r="K350" s="21">
-        <v>13</v>
+      <c r="K350">
+        <v>100</v>
       </c>
       <c r="L350" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>224</v>
+      <c r="A351" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="C351" t="s">
-        <v>231</v>
-      </c>
-      <c r="F351" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="J351" t="s">
-        <v>86</v>
-      </c>
-      <c r="K351" s="21">
-        <v>7</v>
+        <v>85</v>
+      </c>
+      <c r="K351">
+        <v>100</v>
       </c>
       <c r="L351" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>224</v>
-      </c>
-      <c r="C352" t="s">
-        <v>231</v>
-      </c>
-      <c r="F352" t="s">
-        <v>234</v>
-      </c>
-      <c r="J352" t="s">
-        <v>86</v>
-      </c>
-      <c r="K352" s="21">
-        <v>4</v>
-      </c>
-      <c r="L352" t="s">
-        <v>38</v>
+      <c r="A352" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>226</v>
-      </c>
-      <c r="C353" t="s">
-        <v>231</v>
-      </c>
-      <c r="J353" t="s">
-        <v>85</v>
-      </c>
-      <c r="K353" s="23">
-        <v>13</v>
-      </c>
-      <c r="L353" t="s">
-        <v>38</v>
-      </c>
-      <c r="M353" t="s">
-        <v>232</v>
-      </c>
+      <c r="A353" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B353" s="8"/>
+      <c r="C353" s="8"/>
+      <c r="D353" s="9"/>
+      <c r="E353" s="9"/>
+      <c r="F353" s="8"/>
+      <c r="G353" s="8"/>
+      <c r="H353" s="8"/>
+      <c r="I353" s="8"/>
+      <c r="M353" s="8"/>
+      <c r="N353" s="8"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>226</v>
-      </c>
-      <c r="C354" t="s">
-        <v>231</v>
-      </c>
-      <c r="F354" t="s">
-        <v>233</v>
-      </c>
-      <c r="J354" t="s">
-        <v>86</v>
-      </c>
-      <c r="K354" s="21">
-        <v>7</v>
-      </c>
-      <c r="L354" t="s">
-        <v>38</v>
-      </c>
+      <c r="A354" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B354" s="4"/>
+      <c r="C354" s="4"/>
+      <c r="D354" s="4"/>
+      <c r="E354" s="4"/>
+      <c r="F354" s="4"/>
+      <c r="G354" s="4"/>
+      <c r="H354" s="4"/>
+      <c r="I354" s="4"/>
+      <c r="J354" s="5"/>
+      <c r="K354" s="5"/>
+      <c r="L354" s="5"/>
+      <c r="M354" s="5"/>
+      <c r="N354" s="5"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="C355" t="s">
-        <v>231</v>
-      </c>
-      <c r="F355" t="s">
-        <v>234</v>
+        <v>134</v>
+      </c>
+      <c r="H355" t="s">
+        <v>45</v>
       </c>
       <c r="J355" t="s">
+        <v>85</v>
+      </c>
+      <c r="K355" s="21">
+        <v>38</v>
+      </c>
+      <c r="L355" t="s">
+        <v>38</v>
+      </c>
+      <c r="M355" s="11"/>
+      <c r="N355" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>132</v>
+      </c>
+      <c r="C356" t="s">
+        <v>134</v>
+      </c>
+      <c r="F356" t="s">
+        <v>135</v>
+      </c>
+      <c r="H356" t="s">
+        <v>45</v>
+      </c>
+      <c r="J356" t="s">
         <v>86</v>
       </c>
-      <c r="K355" s="21">
-        <v>4</v>
-      </c>
-      <c r="L355" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A356" s="6" t="s">
-        <v>225</v>
+      <c r="K356" s="21">
+        <v>60</v>
+      </c>
+      <c r="L356" t="s">
+        <v>38</v>
+      </c>
+      <c r="N356" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A357" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B357" s="4"/>
-      <c r="C357" s="4"/>
-      <c r="D357" s="4"/>
-      <c r="E357" s="4"/>
-      <c r="F357" s="4"/>
-      <c r="G357" s="4"/>
-      <c r="H357" s="4"/>
-      <c r="I357" s="4"/>
-      <c r="J357" s="5"/>
-      <c r="K357" s="5"/>
-      <c r="L357" s="5"/>
-      <c r="M357" s="5"/>
-      <c r="N357" s="5"/>
+      <c r="A357" t="s">
+        <v>132</v>
+      </c>
+      <c r="C357" t="s">
+        <v>134</v>
+      </c>
+      <c r="H357" t="s">
+        <v>43</v>
+      </c>
+      <c r="J357" t="s">
+        <v>85</v>
+      </c>
+      <c r="K357" s="21">
+        <v>32</v>
+      </c>
+      <c r="L357" t="s">
+        <v>38</v>
+      </c>
+      <c r="M357" t="s">
+        <v>137</v>
+      </c>
+      <c r="N357" s="8"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>132</v>
+      </c>
+      <c r="C358" t="s">
+        <v>134</v>
+      </c>
+      <c r="F358" t="s">
+        <v>136</v>
+      </c>
+      <c r="H358" t="s">
+        <v>43</v>
+      </c>
+      <c r="J358" t="s">
+        <v>86</v>
+      </c>
+      <c r="K358" s="21">
+        <v>68</v>
+      </c>
+      <c r="L358" t="s">
+        <v>38</v>
+      </c>
+      <c r="N358" s="8"/>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B359" s="4"/>
+      <c r="C359" s="4"/>
+      <c r="D359" s="4"/>
+      <c r="E359" s="4"/>
+      <c r="F359" s="4"/>
+      <c r="G359" s="4"/>
+      <c r="H359" s="4"/>
+      <c r="I359" s="4"/>
+      <c r="J359" s="5"/>
+      <c r="K359" s="5"/>
+      <c r="L359" s="5"/>
+      <c r="M359" s="5"/>
+      <c r="N359" s="5"/>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>224</v>
+      </c>
+      <c r="C360" t="s">
+        <v>231</v>
+      </c>
+      <c r="J360" t="s">
+        <v>85</v>
+      </c>
+      <c r="K360" s="21">
+        <v>13</v>
+      </c>
+      <c r="L360" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>224</v>
+      </c>
+      <c r="C361" t="s">
+        <v>231</v>
+      </c>
+      <c r="F361" t="s">
+        <v>233</v>
+      </c>
+      <c r="J361" t="s">
+        <v>86</v>
+      </c>
+      <c r="K361" s="21">
+        <v>7</v>
+      </c>
+      <c r="L361" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>224</v>
+      </c>
+      <c r="C362" t="s">
+        <v>231</v>
+      </c>
+      <c r="F362" t="s">
+        <v>234</v>
+      </c>
+      <c r="J362" t="s">
+        <v>86</v>
+      </c>
+      <c r="K362" s="21">
+        <v>4</v>
+      </c>
+      <c r="L362" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>226</v>
+      </c>
+      <c r="C363" t="s">
+        <v>231</v>
+      </c>
+      <c r="J363" t="s">
+        <v>85</v>
+      </c>
+      <c r="K363" s="23">
+        <v>13</v>
+      </c>
+      <c r="L363" t="s">
+        <v>38</v>
+      </c>
+      <c r="M363" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>226</v>
+      </c>
+      <c r="C364" t="s">
+        <v>231</v>
+      </c>
+      <c r="F364" t="s">
+        <v>233</v>
+      </c>
+      <c r="J364" t="s">
+        <v>86</v>
+      </c>
+      <c r="K364" s="21">
+        <v>7</v>
+      </c>
+      <c r="L364" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>226</v>
+      </c>
+      <c r="C365" t="s">
+        <v>231</v>
+      </c>
+      <c r="F365" t="s">
+        <v>234</v>
+      </c>
+      <c r="J365" t="s">
+        <v>86</v>
+      </c>
+      <c r="K365" s="21">
+        <v>4</v>
+      </c>
+      <c r="L365" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A367" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B367" s="4"/>
+      <c r="C367" s="4"/>
+      <c r="D367" s="4"/>
+      <c r="E367" s="4"/>
+      <c r="F367" s="4"/>
+      <c r="G367" s="4"/>
+      <c r="H367" s="4"/>
+      <c r="I367" s="4"/>
+      <c r="J367" s="5"/>
+      <c r="K367" s="5"/>
+      <c r="L367" s="5"/>
+      <c r="M367" s="5"/>
+      <c r="N367" s="5"/>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
         <v>235</v>
       </c>
-      <c r="B358" s="10"/>
-      <c r="C358" s="8" t="s">
+      <c r="B368" s="10"/>
+      <c r="C368" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D358" s="10"/>
-      <c r="E358" s="10"/>
-      <c r="F358" s="10"/>
-      <c r="G358" s="10"/>
-      <c r="H358" s="10"/>
-      <c r="I358" s="10"/>
-      <c r="J358" t="s">
+      <c r="D368" s="10"/>
+      <c r="E368" s="10"/>
+      <c r="F368" s="10"/>
+      <c r="G368" s="10"/>
+      <c r="H368" s="10"/>
+      <c r="I368" s="10"/>
+      <c r="J368" t="s">
         <v>85</v>
       </c>
-      <c r="K358" s="20">
+      <c r="K368" s="20">
         <v>70</v>
       </c>
-      <c r="L358" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M358" s="8"/>
-      <c r="N358" s="8" t="s">
+      <c r="L368" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M368" s="8"/>
+      <c r="N368" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
         <v>238</v>
       </c>
-      <c r="B359" s="10"/>
-      <c r="C359" s="8" t="s">
+      <c r="B369" s="10"/>
+      <c r="C369" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D359" s="10"/>
-      <c r="E359" s="10"/>
-      <c r="F359" s="10"/>
-      <c r="G359" s="10"/>
-      <c r="H359" s="10"/>
-      <c r="I359" s="10"/>
-      <c r="J359" t="s">
+      <c r="D369" s="10"/>
+      <c r="E369" s="10"/>
+      <c r="F369" s="10"/>
+      <c r="G369" s="10"/>
+      <c r="H369" s="10"/>
+      <c r="I369" s="10"/>
+      <c r="J369" t="s">
         <v>85</v>
       </c>
-      <c r="K359" s="20">
+      <c r="K369" s="20">
         <f>655*0.7</f>
         <v>458.49999999999994</v>
       </c>
-      <c r="L359" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M359" s="8"/>
-      <c r="N359" s="8" t="s">
+      <c r="L369" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M369" s="8"/>
+      <c r="N369" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
         <v>238</v>
       </c>
-      <c r="B360" s="10"/>
-      <c r="C360" s="8" t="s">
+      <c r="B370" s="10"/>
+      <c r="C370" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D360" s="10"/>
-      <c r="E360" s="10"/>
-      <c r="F360" s="19" t="s">
+      <c r="D370" s="10"/>
+      <c r="E370" s="10"/>
+      <c r="F370" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G360" s="10"/>
-      <c r="H360" s="10"/>
-      <c r="I360" s="10"/>
-      <c r="J360" t="s">
-        <v>86</v>
-      </c>
-      <c r="K360" s="20">
-        <f>1*(K359/100)*0.2*100</f>
-        <v>91.699999999999989</v>
-      </c>
-      <c r="L360" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M360" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="N360" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B361" s="10"/>
-      <c r="C361" s="8"/>
-      <c r="D361" s="10"/>
-      <c r="E361" s="10"/>
-      <c r="F361" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G361" s="10"/>
-      <c r="H361" s="10"/>
-      <c r="I361" s="10"/>
-      <c r="K361" s="20"/>
-      <c r="L361" s="9"/>
-      <c r="M361" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="N361" s="8"/>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
-        <v>236</v>
-      </c>
-      <c r="B362" s="10"/>
-      <c r="C362" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D362" s="10"/>
-      <c r="E362" s="10"/>
-      <c r="F362" s="19"/>
-      <c r="G362" s="10"/>
-      <c r="H362" s="10"/>
-      <c r="I362" s="10"/>
-      <c r="J362" t="s">
-        <v>85</v>
-      </c>
-      <c r="K362" s="20">
-        <v>65</v>
-      </c>
-      <c r="L362" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M362" s="8"/>
-      <c r="N362" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
-        <v>236</v>
-      </c>
-      <c r="B363" s="10"/>
-      <c r="C363" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D363" s="10"/>
-      <c r="E363" s="10"/>
-      <c r="F363" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="G363" s="10"/>
-      <c r="H363" s="10"/>
-      <c r="I363" s="10"/>
-      <c r="J363" t="s">
-        <v>86</v>
-      </c>
-      <c r="K363" s="20">
-        <v>35</v>
-      </c>
-      <c r="L363" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M363" s="8"/>
-      <c r="N363" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>239</v>
-      </c>
-      <c r="B364" s="10"/>
-      <c r="C364" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D364" s="10"/>
-      <c r="E364" s="10"/>
-      <c r="F364" s="19"/>
-      <c r="G364" s="10"/>
-      <c r="H364" s="10"/>
-      <c r="I364" s="10"/>
-      <c r="J364" t="s">
-        <v>85</v>
-      </c>
-      <c r="K364" s="20">
-        <v>30</v>
-      </c>
-      <c r="L364" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M364" s="8"/>
-      <c r="N364" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>239</v>
-      </c>
-      <c r="B365" s="10"/>
-      <c r="C365" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D365" s="10"/>
-      <c r="E365" s="10"/>
-      <c r="F365" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G365" s="10"/>
-      <c r="H365" s="10"/>
-      <c r="I365" s="10"/>
-      <c r="J365" t="s">
-        <v>86</v>
-      </c>
-      <c r="K365" s="20">
-        <v>11</v>
-      </c>
-      <c r="L365" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M365" s="8"/>
-      <c r="N365" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A366" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B366" s="4"/>
-      <c r="C366" s="4"/>
-      <c r="D366" s="4"/>
-      <c r="E366" s="4"/>
-      <c r="F366" s="4"/>
-      <c r="G366" s="4"/>
-      <c r="H366" s="4"/>
-      <c r="I366" s="4"/>
-      <c r="J366" s="5"/>
-      <c r="K366" s="5"/>
-      <c r="L366" s="5"/>
-      <c r="M366" s="5"/>
-      <c r="N366" s="5"/>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>202</v>
-      </c>
-      <c r="B367" s="10"/>
-      <c r="C367" t="s">
-        <v>134</v>
-      </c>
-      <c r="J367" t="s">
-        <v>85</v>
-      </c>
-      <c r="K367" s="21">
-        <v>38</v>
-      </c>
-      <c r="L367" t="s">
-        <v>38</v>
-      </c>
-      <c r="M367" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="N367" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>202</v>
-      </c>
-      <c r="B368" s="10"/>
-      <c r="C368" t="s">
-        <v>134</v>
-      </c>
-      <c r="F368" t="s">
-        <v>135</v>
-      </c>
-      <c r="J368" t="s">
-        <v>86</v>
-      </c>
-      <c r="K368" s="21">
-        <v>60</v>
-      </c>
-      <c r="L368" t="s">
-        <v>38</v>
-      </c>
-      <c r="N368" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A369" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B369" s="10"/>
-      <c r="C369" t="s">
-        <v>37</v>
-      </c>
-      <c r="J369" t="s">
-        <v>85</v>
-      </c>
-      <c r="K369" s="15">
-        <v>33</v>
-      </c>
-      <c r="L369" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M369" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="N369" s="9" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A370" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B370" s="10"/>
-      <c r="C370" t="s">
-        <v>37</v>
-      </c>
-      <c r="F370" t="s">
-        <v>320</v>
-      </c>
+      <c r="G370" s="10"/>
+      <c r="H370" s="10"/>
+      <c r="I370" s="10"/>
       <c r="J370" t="s">
         <v>86</v>
       </c>
-      <c r="K370" s="15">
-        <v>298</v>
-      </c>
-      <c r="L370" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M370" s="17"/>
-      <c r="N370" s="9" t="s">
-        <v>323</v>
+      <c r="K370" s="20">
+        <f>1*(K369/100)*0.2*100</f>
+        <v>91.699999999999989</v>
+      </c>
+      <c r="L370" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M370" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N370" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A371" s="6"/>
       <c r="B371" s="10"/>
-      <c r="F371" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="K371" s="23"/>
-      <c r="L371" s="6"/>
-      <c r="M371" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="N371" s="9"/>
+      <c r="C371" s="8"/>
+      <c r="D371" s="10"/>
+      <c r="E371" s="10"/>
+      <c r="F371" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G371" s="10"/>
+      <c r="H371" s="10"/>
+      <c r="I371" s="10"/>
+      <c r="K371" s="20"/>
+      <c r="L371" s="9"/>
+      <c r="M371" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="N371" s="8"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A372" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B372" s="4"/>
-      <c r="C372" s="4"/>
-      <c r="D372" s="4"/>
-      <c r="E372" s="4"/>
-      <c r="F372" s="4"/>
-      <c r="G372" s="4"/>
-      <c r="H372" s="4"/>
-      <c r="I372" s="4"/>
-      <c r="J372" s="5"/>
-      <c r="K372" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="L372" s="5"/>
-      <c r="M372" s="5"/>
-      <c r="N372" s="5"/>
+      <c r="A372" t="s">
+        <v>236</v>
+      </c>
+      <c r="B372" s="10"/>
+      <c r="C372" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D372" s="10"/>
+      <c r="E372" s="10"/>
+      <c r="F372" s="19"/>
+      <c r="G372" s="10"/>
+      <c r="H372" s="10"/>
+      <c r="I372" s="10"/>
+      <c r="J372" t="s">
+        <v>85</v>
+      </c>
+      <c r="K372" s="20">
+        <v>65</v>
+      </c>
+      <c r="L372" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M372" s="8"/>
+      <c r="N372" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="B373" s="10"/>
-      <c r="C373" s="10"/>
-      <c r="D373" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="E373" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="F373" s="10"/>
+      <c r="C373" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D373" s="10"/>
+      <c r="E373" s="10"/>
+      <c r="F373" s="19" t="s">
+        <v>247</v>
+      </c>
       <c r="G373" s="10"/>
       <c r="H373" s="10"/>
       <c r="I373" s="10"/>
       <c r="J373" t="s">
-        <v>85</v>
-      </c>
-      <c r="K373" s="19">
-        <v>100</v>
-      </c>
-      <c r="L373" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K373" s="20">
+        <v>35</v>
+      </c>
+      <c r="L373" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M373" s="8"/>
-      <c r="N373" s="8"/>
+      <c r="N373" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>239</v>
+      </c>
       <c r="B374" s="10"/>
-      <c r="C374" s="10"/>
-      <c r="D374" s="19"/>
-      <c r="E374" s="19"/>
-      <c r="F374" s="10"/>
+      <c r="C374" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D374" s="10"/>
+      <c r="E374" s="10"/>
+      <c r="F374" s="19"/>
       <c r="G374" s="10"/>
       <c r="H374" s="10"/>
       <c r="I374" s="10"/>
-      <c r="K374" s="19"/>
-      <c r="L374" s="8"/>
+      <c r="J374" t="s">
+        <v>85</v>
+      </c>
+      <c r="K374" s="20">
+        <v>30</v>
+      </c>
+      <c r="L374" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="M374" s="8"/>
-      <c r="N374" s="8"/>
+      <c r="N374" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" s="2" t="s">
+      <c r="A375" t="s">
+        <v>239</v>
+      </c>
+      <c r="B375" s="10"/>
+      <c r="C375" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D375" s="10"/>
+      <c r="E375" s="10"/>
+      <c r="F375" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="G375" s="10"/>
+      <c r="H375" s="10"/>
+      <c r="I375" s="10"/>
+      <c r="J375" t="s">
+        <v>86</v>
+      </c>
+      <c r="K375" s="20">
+        <v>11</v>
+      </c>
+      <c r="L375" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M375" s="8"/>
+      <c r="N375" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B376" s="4"/>
+      <c r="C376" s="4"/>
+      <c r="D376" s="4"/>
+      <c r="E376" s="4"/>
+      <c r="F376" s="4"/>
+      <c r="G376" s="4"/>
+      <c r="H376" s="4"/>
+      <c r="I376" s="4"/>
+      <c r="J376" s="5"/>
+      <c r="K376" s="5"/>
+      <c r="L376" s="5"/>
+      <c r="M376" s="5"/>
+      <c r="N376" s="5"/>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>202</v>
+      </c>
+      <c r="B377" s="10"/>
+      <c r="C377" t="s">
+        <v>134</v>
+      </c>
+      <c r="J377" t="s">
+        <v>85</v>
+      </c>
+      <c r="K377" s="21">
+        <v>38</v>
+      </c>
+      <c r="L377" t="s">
+        <v>38</v>
+      </c>
+      <c r="M377" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="N377" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>202</v>
+      </c>
+      <c r="B378" s="10"/>
+      <c r="C378" t="s">
+        <v>134</v>
+      </c>
+      <c r="F378" t="s">
+        <v>135</v>
+      </c>
+      <c r="J378" t="s">
+        <v>86</v>
+      </c>
+      <c r="K378" s="21">
+        <v>60</v>
+      </c>
+      <c r="L378" t="s">
+        <v>38</v>
+      </c>
+      <c r="N378" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A379" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B379" s="10"/>
+      <c r="C379" t="s">
+        <v>37</v>
+      </c>
+      <c r="J379" t="s">
+        <v>85</v>
+      </c>
+      <c r="K379" s="15">
+        <v>33</v>
+      </c>
+      <c r="L379" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M379" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="N379" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A380" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B380" s="10"/>
+      <c r="C380" t="s">
+        <v>37</v>
+      </c>
+      <c r="F380" t="s">
+        <v>320</v>
+      </c>
+      <c r="J380" t="s">
+        <v>86</v>
+      </c>
+      <c r="K380" s="15">
+        <v>298</v>
+      </c>
+      <c r="L380" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M380" s="17"/>
+      <c r="N380" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A381" s="6"/>
+      <c r="B381" s="10"/>
+      <c r="F381" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="K381" s="23"/>
+      <c r="L381" s="6"/>
+      <c r="M381" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="N381" s="9"/>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B382" s="4"/>
+      <c r="C382" s="4"/>
+      <c r="D382" s="4"/>
+      <c r="E382" s="4"/>
+      <c r="F382" s="4"/>
+      <c r="G382" s="4"/>
+      <c r="H382" s="4"/>
+      <c r="I382" s="4"/>
+      <c r="J382" s="5"/>
+      <c r="K382" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="L382" s="5"/>
+      <c r="M382" s="5"/>
+      <c r="N382" s="5"/>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>280</v>
+      </c>
+      <c r="B383" s="10"/>
+      <c r="C383" s="10"/>
+      <c r="D383" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E383" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F383" s="10"/>
+      <c r="G383" s="10"/>
+      <c r="H383" s="10"/>
+      <c r="I383" s="10"/>
+      <c r="J383" t="s">
+        <v>85</v>
+      </c>
+      <c r="K383" s="19">
+        <v>100</v>
+      </c>
+      <c r="L383" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M383" s="8"/>
+      <c r="N383" s="8"/>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B384" s="10"/>
+      <c r="C384" s="10"/>
+      <c r="D384" s="19"/>
+      <c r="E384" s="19"/>
+      <c r="F384" s="10"/>
+      <c r="G384" s="10"/>
+      <c r="H384" s="10"/>
+      <c r="I384" s="10"/>
+      <c r="K384" s="19"/>
+      <c r="L384" s="8"/>
+      <c r="M384" s="8"/>
+      <c r="N384" s="8"/>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B375" s="2"/>
-      <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
-      <c r="E375" s="2"/>
-      <c r="F375" s="2"/>
-      <c r="G375" s="2"/>
-      <c r="H375" s="2"/>
-      <c r="I375" s="2"/>
-      <c r="J375" s="2"/>
-      <c r="K375" s="2"/>
-      <c r="L375" s="2"/>
-      <c r="M375" s="2"/>
-      <c r="N375" s="2"/>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="6" t="s">
+      <c r="B385" s="2"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
+      <c r="E385" s="2"/>
+      <c r="F385" s="2"/>
+      <c r="G385" s="2"/>
+      <c r="H385" s="2"/>
+      <c r="I385" s="2"/>
+      <c r="J385" s="2"/>
+      <c r="K385" s="2"/>
+      <c r="L385" s="2"/>
+      <c r="M385" s="2"/>
+      <c r="N385" s="2"/>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" s="6" t="s">
         <v>326</v>
       </c>
     </row>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="342">
   <si>
     <t>parameter</t>
   </si>
@@ -1077,7 +1077,19 @@
     <t>eggs</t>
   </si>
   <si>
-    <t>"Ägg"</t>
+    <t>Adjusted to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>adj factor:</t>
+  </si>
+  <si>
+    <t>Adjusted to match egg prod. statistics</t>
+  </si>
+  <si>
+    <t>Adjusted to match prod. statistics. "Ägg"</t>
+  </si>
+  <si>
+    <t>CHECK THIS! Should be wheat distillers grain???</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1241,6 +1253,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2645,11 +2660,14 @@
       <c r="J61" t="s">
         <v>18</v>
       </c>
-      <c r="K61">
-        <v>29.3</v>
+      <c r="K61" s="6">
+        <v>33.5</v>
       </c>
       <c r="L61" t="s">
         <v>19</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -4673,8 +4691,12 @@
       <c r="I180" s="4"/>
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
-      <c r="L180" s="5"/>
-      <c r="M180" s="5"/>
+      <c r="L180" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="M180" s="41">
+        <v>0.81799999999999995</v>
+      </c>
       <c r="N180" s="5"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -4685,8 +4707,8 @@
         <v>40</v>
       </c>
       <c r="K181" s="13">
-        <f>8.5*20/(29.5+8.5)</f>
-        <v>4.4736842105263159</v>
+        <f>8.5*20/(29.5+8.5)*$M$180</f>
+        <v>3.6594736842105262</v>
       </c>
       <c r="L181" t="s">
         <v>38</v>
@@ -4700,8 +4722,8 @@
         <v>40</v>
       </c>
       <c r="K182" s="13">
-        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
-        <v>2.981366459627329</v>
+        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)*$M$180</f>
+        <v>2.438757763975155</v>
       </c>
       <c r="L182" t="s">
         <v>38</v>
@@ -4715,8 +4737,8 @@
         <v>40</v>
       </c>
       <c r="K183" s="13">
-        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
-        <v>7.723292469352014</v>
+        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)*$M$180</f>
+        <v>6.317653239929947</v>
       </c>
       <c r="L183" t="s">
         <v>38</v>
@@ -4730,8 +4752,8 @@
         <v>40</v>
       </c>
       <c r="K184">
-        <f>60</f>
-        <v>60</v>
+        <f>60*$M$180</f>
+        <v>49.08</v>
       </c>
       <c r="L184" t="s">
         <v>38</v>
@@ -4745,6 +4767,7 @@
         <v>40</v>
       </c>
       <c r="K185">
+        <f>0*$M$180</f>
         <v>0</v>
       </c>
       <c r="L185" t="s">
@@ -4759,7 +4782,8 @@
         <v>40</v>
       </c>
       <c r="K186">
-        <v>20</v>
+        <f>20*$M$180</f>
+        <v>16.36</v>
       </c>
       <c r="L186" t="s">
         <v>38</v>
@@ -4773,7 +4797,8 @@
         <v>40</v>
       </c>
       <c r="K187">
-        <v>20</v>
+        <f>20*$M$180</f>
+        <v>16.36</v>
       </c>
       <c r="L187" t="s">
         <v>38</v>
@@ -4787,7 +4812,8 @@
         <v>40</v>
       </c>
       <c r="K188">
-        <v>20</v>
+        <f>20*$M$180</f>
+        <v>16.36</v>
       </c>
       <c r="L188" t="s">
         <v>38</v>
@@ -4801,8 +4827,8 @@
         <v>40</v>
       </c>
       <c r="K189">
-        <f>43</f>
-        <v>43</v>
+        <f>43*$M$180</f>
+        <v>35.173999999999999</v>
       </c>
       <c r="L189" t="s">
         <v>38</v>
@@ -4833,11 +4859,14 @@
       <c r="J191" t="s">
         <v>40</v>
       </c>
-      <c r="K191">
-        <v>37</v>
+      <c r="K191" s="6">
+        <v>37.5</v>
       </c>
       <c r="L191" t="s">
         <v>38</v>
+      </c>
+      <c r="M191" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -4847,11 +4876,14 @@
       <c r="J192" t="s">
         <v>40</v>
       </c>
-      <c r="K192" s="17">
-        <v>43</v>
+      <c r="K192" s="6">
+        <v>48.1</v>
       </c>
       <c r="L192" t="s">
         <v>38</v>
+      </c>
+      <c r="M192" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
@@ -4861,11 +4893,14 @@
       <c r="J193" t="s">
         <v>40</v>
       </c>
-      <c r="K193" s="17">
-        <v>36</v>
+      <c r="K193" s="6">
+        <v>46.1</v>
       </c>
       <c r="L193" t="s">
         <v>38</v>
+      </c>
+      <c r="M193" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -4893,11 +4928,14 @@
       <c r="J195" t="s">
         <v>40</v>
       </c>
-      <c r="K195" s="17">
-        <v>12</v>
+      <c r="K195" s="6">
+        <v>10</v>
       </c>
       <c r="L195" t="s">
         <v>38</v>
+      </c>
+      <c r="M195" s="6" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -5905,8 +5943,8 @@
       <c r="J246" t="s">
         <v>41</v>
       </c>
-      <c r="K246" s="15">
-        <v>17</v>
+      <c r="K246" s="29">
+        <v>15.75</v>
       </c>
       <c r="L246" t="s">
         <v>38</v>
@@ -5950,10 +5988,13 @@
         <v>41</v>
       </c>
       <c r="K248" s="6">
-        <v>2.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="L248" t="s">
         <v>38</v>
+      </c>
+      <c r="M248" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
@@ -5970,10 +6011,13 @@
         <v>41</v>
       </c>
       <c r="K249" s="6">
-        <v>15.4</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="L249" t="s">
         <v>38</v>
+      </c>
+      <c r="M249" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
@@ -5990,10 +6034,13 @@
         <v>41</v>
       </c>
       <c r="K250" s="6">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="L250" t="s">
         <v>38</v>
+      </c>
+      <c r="M250" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
@@ -6027,14 +6074,14 @@
       <c r="J252" t="s">
         <v>41</v>
       </c>
-      <c r="K252" s="17">
-        <v>19.399999999999999</v>
+      <c r="K252" s="6">
+        <v>16.5</v>
       </c>
       <c r="L252" t="s">
         <v>38</v>
       </c>
-      <c r="M252" t="s">
-        <v>337</v>
+      <c r="M252" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="N252" s="26" t="s">
         <v>222</v>
@@ -8984,17 +9031,19 @@
       <c r="G375" s="10"/>
       <c r="H375" s="10"/>
       <c r="I375" s="10"/>
-      <c r="J375" t="s">
+      <c r="J375" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K375" s="20">
+      <c r="K375" s="12">
         <v>11</v>
       </c>
-      <c r="L375" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M375" s="8"/>
-      <c r="N375" s="8" t="s">
+      <c r="L375" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M375" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="N375" s="10" t="s">
         <v>92</v>
       </c>
     </row>

--- a/data/prod_parameters/DemandAndConversions.xlsx
+++ b/data/prod_parameters/DemandAndConversions.xlsx
@@ -10,8 +10,9 @@
     <sheet name="default" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Trade" sheetId="4" r:id="rId3"/>
+    <sheet name="references" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="356">
   <si>
     <t>parameter</t>
   </si>
@@ -398,9 +399,6 @@
     <t>rye bran</t>
   </si>
   <si>
-    <t>oat offals</t>
-  </si>
-  <si>
     <t>potatoe offals</t>
   </si>
   <si>
@@ -743,28 +741,6 @@
     <t>sugar beet</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Higher factor for syrup than sugar?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Assumed from sugar beet for domestic prod</t>
-    </r>
-  </si>
-  <si>
     <t>sugar beet pulp</t>
   </si>
   <si>
@@ -1038,18 +1014,12 @@
     <t>Börjesson, P., Tufvesson, L., &amp; Lantz, M. (2010). Livscykelanalys av svenska biodrivmedel. (Environmental and Energy System Studies report no. 70; Vol. 70). Environmental and Energy Systems Studies, Lund university.</t>
   </si>
   <si>
-    <t>2.1 kg DM wheat --&gt; 1 L bioethanol + 0.8 kg DM distillers grain. Wheat 86% DM, distillers grain 11% DM. Bioethanol 21.3 MJ/L and 27.8 MJ/kg --&gt; 0.8 kg/L</t>
-  </si>
-  <si>
     <t>PROCESSING ENERGY USE</t>
   </si>
   <si>
     <t>Add processing energy use factors per food item</t>
   </si>
   <si>
-    <t>Baseds on assuming 600 000 tonnes cereals used</t>
-  </si>
-  <si>
     <t>Rice and products, refined</t>
   </si>
   <si>
@@ -1090,6 +1060,60 @@
   </si>
   <si>
     <t>CHECK THIS! Should be wheat distillers grain???</t>
+  </si>
+  <si>
+    <t>@ 90% DM</t>
+  </si>
+  <si>
+    <t>Tabell A18 in Börjesson et al (2010)</t>
+  </si>
+  <si>
+    <t>Börjesson et al (2010)</t>
+  </si>
+  <si>
+    <t>Based on assuming 600 000 tonnes cereals used</t>
+  </si>
+  <si>
+    <t>2.1 kg DM wheat --&gt; 1 L bioethanol + 0.8 kg DM distillers grain. Wheat 86% DM, distillers grain 90% DM. Bioethanol 21.3 MJ/L and 27.8 MJ/kg --&gt; 0.766 kg/L</t>
+  </si>
+  <si>
+    <t>havrekli??</t>
+  </si>
+  <si>
+    <t>oat bran</t>
+  </si>
+  <si>
+    <t>161 kg WS/t SB</t>
+  </si>
+  <si>
+    <t>Garcia Gonzalez, M. N., &amp; Björnsson, L. (2022). Life cycle assessment of the production of beet sugar and its by-products. Journal of Cleaner Production, 346, 131211. doi:https://doi.org/10.1016/j.jclepro.2022.131211</t>
+  </si>
+  <si>
+    <t>Garcia Gonzalez and Börjesson 2022</t>
+  </si>
+  <si>
+    <t>(90% DM) 6.4 kg DM PSBP and 25.2 kg DM DSBP per t wet weight sugar beet</t>
+  </si>
+  <si>
+    <t>(76% DM) 19 kg DM molasses per t wet weight sugar beet</t>
+  </si>
+  <si>
+    <t>Based on sugar but adjusted to 20% w.c. in syrup</t>
+  </si>
+  <si>
+    <t>https://fransverige.se/aktuellt/nya-siffror-visar-sveriges-sjalvforsorjningsgrad/</t>
+  </si>
+  <si>
+    <t>43.6% 2019. Adjusted to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>23.3% 2019. Adjusted to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>28.4% 2019. Adjusted to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>for 2019</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1256,6 +1280,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1669,7 +1695,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1685,15 +1711,15 @@
         <v>19</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1711,7 +1737,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1727,15 +1753,15 @@
         <v>19</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -1754,7 +1780,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1770,12 +1796,12 @@
         <v>19</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1811,7 +1837,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
@@ -1827,12 +1853,12 @@
         <v>19</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -1851,7 +1877,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -1867,12 +1893,12 @@
         <v>19</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1891,7 +1917,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -1907,12 +1933,12 @@
         <v>19</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
@@ -1983,7 +2009,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s">
         <v>103</v>
@@ -2020,7 +2046,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2038,7 +2064,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s">
         <v>108</v>
@@ -2055,7 +2081,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
         <v>108</v>
@@ -2072,7 +2098,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
         <v>108</v>
@@ -2089,7 +2115,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s">
         <v>108</v>
@@ -2106,7 +2132,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -2123,7 +2149,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
         <v>108</v>
@@ -2174,7 +2200,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s">
         <v>108</v>
@@ -2191,7 +2217,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s">
         <v>108</v>
@@ -2207,7 +2233,7 @@
         <v>19</v>
       </c>
       <c r="M35" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -2216,7 +2242,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2234,10 +2260,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
@@ -2251,10 +2277,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B39" t="s">
         <v>250</v>
-      </c>
-      <c r="B39" t="s">
-        <v>252</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -2268,10 +2294,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
@@ -2285,10 +2311,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -2302,10 +2328,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2318,15 +2344,15 @@
         <v>19</v>
       </c>
       <c r="M42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -2340,10 +2366,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C44" s="9"/>
       <c r="J44" t="s">
@@ -2356,15 +2382,15 @@
         <v>19</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J45" t="s">
         <v>18</v>
@@ -2377,7 +2403,7 @@
         <v>19</v>
       </c>
       <c r="M45" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -2617,7 +2643,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
@@ -2655,19 +2681,20 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J61" t="s">
         <v>18</v>
       </c>
       <c r="K61" s="6">
-        <v>33.5</v>
+        <f>29.3+1.6</f>
+        <v>30.900000000000002</v>
       </c>
       <c r="L61" t="s">
         <v>19</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -2708,10 +2735,10 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J64" t="s">
         <v>18</v>
@@ -2725,10 +2752,10 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J65" t="s">
         <v>18</v>
@@ -2742,10 +2769,10 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J66" t="s">
         <v>18</v>
@@ -2759,10 +2786,10 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J67" t="s">
         <v>18</v>
@@ -2776,10 +2803,10 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" t="s">
         <v>213</v>
-      </c>
-      <c r="B68" t="s">
-        <v>214</v>
       </c>
       <c r="J68" t="s">
         <v>18</v>
@@ -2829,10 +2856,10 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" t="s">
         <v>132</v>
-      </c>
-      <c r="B71" t="s">
-        <v>133</v>
       </c>
       <c r="J71" t="s">
         <v>18</v>
@@ -2845,15 +2872,15 @@
         <v>19</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J72" t="s">
         <v>18</v>
@@ -2866,15 +2893,15 @@
         <v>19</v>
       </c>
       <c r="M72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J73" t="s">
         <v>18</v>
@@ -2887,7 +2914,7 @@
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -2910,10 +2937,10 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B75" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J75" t="s">
         <v>18</v>
@@ -2927,10 +2954,10 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" t="s">
         <v>226</v>
-      </c>
-      <c r="B76" t="s">
-        <v>227</v>
       </c>
       <c r="J76" t="s">
         <v>18</v>
@@ -2942,15 +2969,15 @@
         <v>19</v>
       </c>
       <c r="M76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J77" t="s">
         <v>18</v>
@@ -2982,7 +3009,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B79" t="s">
         <v>112</v>
@@ -2999,7 +3026,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B80" t="s">
         <v>112</v>
@@ -3016,7 +3043,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B81" t="s">
         <v>112</v>
@@ -3031,12 +3058,12 @@
         <v>19</v>
       </c>
       <c r="M81" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B82" t="s">
         <v>112</v>
@@ -3051,7 +3078,7 @@
         <v>19</v>
       </c>
       <c r="M82" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -3128,7 +3155,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3146,48 +3173,50 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H89" t="s">
         <v>45</v>
       </c>
       <c r="J89" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K89" s="33">
-        <v>197000</v>
+        <f>600000*(K379/100)</f>
+        <v>188217.14285714284</v>
       </c>
       <c r="L89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M89" s="17" t="s">
-        <v>327</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N89" s="21"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H90" t="s">
         <v>45</v>
       </c>
       <c r="J90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K90" s="33">
         <v>10000</v>
       </c>
       <c r="L90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -3198,25 +3227,25 @@
         <v>101</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H92" t="s">
         <v>45</v>
       </c>
       <c r="J92" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K92" s="33">
         <v>34000</v>
       </c>
       <c r="L92" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M92" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N92" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -3224,25 +3253,25 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H94" t="s">
         <v>45</v>
       </c>
       <c r="J94" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K94" s="37">
         <v>355.5</v>
       </c>
       <c r="L94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M94" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -3250,7 +3279,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3268,132 +3297,132 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H97" t="s">
         <v>45</v>
       </c>
       <c r="J97" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K97" s="33">
         <v>558249.80000000005</v>
       </c>
       <c r="L97" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M97" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N97" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H98" t="s">
         <v>45</v>
       </c>
       <c r="J98" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K98" s="33">
         <v>304650.40000000002</v>
       </c>
       <c r="L98" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M98" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N98" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>297</v>
+      </c>
+      <c r="B99" t="s">
         <v>299</v>
-      </c>
-      <c r="B99" t="s">
-        <v>301</v>
       </c>
       <c r="H99" t="s">
         <v>45</v>
       </c>
       <c r="J99" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K99" s="33">
         <v>32965.800000000003</v>
       </c>
       <c r="L99" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M99" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N99" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B100" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H100" t="s">
         <v>45</v>
       </c>
       <c r="J100" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K100" s="33">
         <v>177249.6</v>
       </c>
       <c r="L100" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M100" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N100" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B101" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H101" t="s">
         <v>45</v>
       </c>
       <c r="J101" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K101" s="33">
         <v>22062.799999999999</v>
       </c>
       <c r="L101" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M101" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N101" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -3401,25 +3430,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H102" t="s">
         <v>45</v>
       </c>
       <c r="J102" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K102" s="33">
         <v>25000</v>
       </c>
       <c r="L102" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M102" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N102" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -3604,7 +3633,7 @@
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I114" t="s">
         <v>50</v>
@@ -3621,7 +3650,7 @@
     </row>
     <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I115" t="s">
         <v>51</v>
@@ -3638,7 +3667,7 @@
     </row>
     <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I116" t="s">
         <v>52</v>
@@ -3767,7 +3796,7 @@
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I123" t="s">
         <v>50</v>
@@ -3784,7 +3813,7 @@
     </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I124" t="s">
         <v>51</v>
@@ -3801,7 +3830,7 @@
     </row>
     <row r="125" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I125" t="s">
         <v>52</v>
@@ -3821,7 +3850,7 @@
     </row>
     <row r="126" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I126" t="s">
         <v>50</v>
@@ -3838,7 +3867,7 @@
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I127" t="s">
         <v>51</v>
@@ -3855,7 +3884,7 @@
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I128" t="s">
         <v>52</v>
@@ -3875,7 +3904,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I129" t="s">
         <v>50</v>
@@ -3892,7 +3921,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I130" t="s">
         <v>51</v>
@@ -3909,7 +3938,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I131" t="s">
         <v>52</v>
@@ -3929,7 +3958,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I132" t="s">
         <v>50</v>
@@ -3946,7 +3975,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I133" t="s">
         <v>51</v>
@@ -3963,7 +3992,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I134" t="s">
         <v>52</v>
@@ -4091,7 +4120,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J142" t="s">
         <v>40</v>
@@ -4105,7 +4134,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J143" t="s">
         <v>40</v>
@@ -4118,12 +4147,12 @@
         <v>38</v>
       </c>
       <c r="M143" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J144" t="s">
         <v>40</v>
@@ -4137,7 +4166,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J145" t="s">
         <v>40</v>
@@ -4150,12 +4179,12 @@
         <v>38</v>
       </c>
       <c r="M145" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J146" t="s">
         <v>40</v>
@@ -4169,7 +4198,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J147" t="s">
         <v>40</v>
@@ -4182,7 +4211,7 @@
         <v>38</v>
       </c>
       <c r="M147" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -4201,7 +4230,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J149" t="s">
         <v>40</v>
@@ -4215,7 +4244,7 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J150" t="s">
         <v>40</v>
@@ -4228,12 +4257,12 @@
         <v>38</v>
       </c>
       <c r="M150" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J151" t="s">
         <v>40</v>
@@ -4247,7 +4276,7 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J152" t="s">
         <v>40</v>
@@ -4260,12 +4289,12 @@
         <v>38</v>
       </c>
       <c r="M152" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J153" t="s">
         <v>40</v>
@@ -4277,12 +4306,12 @@
         <v>38</v>
       </c>
       <c r="M153" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J154" t="s">
         <v>40</v>
@@ -4295,7 +4324,7 @@
         <v>38</v>
       </c>
       <c r="M154" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
@@ -4346,7 +4375,7 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J158" t="s">
         <v>40</v>
@@ -4392,7 +4421,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J161" t="s">
         <v>40</v>
@@ -4406,7 +4435,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J162" t="s">
         <v>40</v>
@@ -4420,7 +4449,7 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J163" t="s">
         <v>40</v>
@@ -4434,7 +4463,7 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J164" t="s">
         <v>40</v>
@@ -4448,7 +4477,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J165" t="s">
         <v>40</v>
@@ -4460,12 +4489,12 @@
         <v>38</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J166" t="s">
         <v>40</v>
@@ -4479,7 +4508,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C167" s="9"/>
       <c r="J167" t="s">
@@ -4492,12 +4521,12 @@
         <v>38</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J168" t="s">
         <v>40</v>
@@ -4509,7 +4538,7 @@
         <v>38</v>
       </c>
       <c r="M168" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
@@ -4532,7 +4561,7 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J170" t="s">
         <v>40</v>
@@ -4546,7 +4575,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J171" t="s">
         <v>40</v>
@@ -4560,7 +4589,7 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J172" t="s">
         <v>40</v>
@@ -4574,7 +4603,7 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J173" t="s">
         <v>40</v>
@@ -4589,7 +4618,7 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J174" t="s">
         <v>40</v>
@@ -4601,12 +4630,12 @@
         <v>38</v>
       </c>
       <c r="M174" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J175" t="s">
         <v>40</v>
@@ -4648,7 +4677,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J178" t="s">
         <v>40</v>
@@ -4662,7 +4691,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J179" t="s">
         <v>40</v>
@@ -4674,7 +4703,7 @@
         <v>38</v>
       </c>
       <c r="M179" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -4692,7 +4721,7 @@
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
       <c r="L180" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M180" s="41">
         <v>0.81799999999999995</v>
@@ -4866,7 +4895,10 @@
         <v>38</v>
       </c>
       <c r="M191" s="6" t="s">
-        <v>337</v>
+        <v>353</v>
+      </c>
+      <c r="N191" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -4883,12 +4915,15 @@
         <v>38</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>337</v>
+        <v>352</v>
+      </c>
+      <c r="N192" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J193" t="s">
         <v>40</v>
@@ -4900,7 +4935,10 @@
         <v>38</v>
       </c>
       <c r="M193" s="6" t="s">
-        <v>337</v>
+        <v>354</v>
+      </c>
+      <c r="N193" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -4928,14 +4966,18 @@
       <c r="J195" t="s">
         <v>40</v>
       </c>
-      <c r="K195" s="6">
-        <v>10</v>
+      <c r="K195" s="17">
+        <f>2.5</f>
+        <v>2.5</v>
       </c>
       <c r="L195" t="s">
         <v>38</v>
       </c>
-      <c r="M195" s="6" t="s">
-        <v>339</v>
+      <c r="M195" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="N195" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -4958,7 +5000,7 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J197" t="s">
         <v>40</v>
@@ -4972,7 +5014,7 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J198" t="s">
         <v>40</v>
@@ -4986,7 +5028,7 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J199" t="s">
         <v>40</v>
@@ -4998,12 +5040,12 @@
         <v>38</v>
       </c>
       <c r="M199" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J200" t="s">
         <v>40</v>
@@ -5017,7 +5059,7 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -5059,7 +5101,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J203" t="s">
         <v>40</v>
@@ -5092,7 +5134,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J205" t="s">
         <v>40</v>
@@ -5104,12 +5146,12 @@
         <v>38</v>
       </c>
       <c r="M205" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J206" t="s">
         <v>40</v>
@@ -5122,12 +5164,12 @@
         <v>38</v>
       </c>
       <c r="M206" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J207" t="s">
         <v>40</v>
@@ -5159,7 +5201,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J209" t="s">
         <v>40</v>
@@ -5173,7 +5215,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J210" t="s">
         <v>40</v>
@@ -5190,7 +5232,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J211" t="s">
         <v>40</v>
@@ -5202,12 +5244,12 @@
         <v>38</v>
       </c>
       <c r="M211" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J212" t="s">
         <v>40</v>
@@ -5219,12 +5261,12 @@
         <v>38</v>
       </c>
       <c r="M212" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -5256,7 +5298,7 @@
         <v>46</v>
       </c>
       <c r="M215" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
@@ -5298,7 +5340,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G218" t="s">
         <v>87</v>
@@ -5316,7 +5358,7 @@
         <v>38</v>
       </c>
       <c r="M218" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N218" t="s">
         <v>98</v>
@@ -5324,7 +5366,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G219" t="s">
         <v>87</v>
@@ -5345,7 +5387,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G220" t="s">
         <v>87</v>
@@ -5363,7 +5405,7 @@
         <v>38</v>
       </c>
       <c r="M220" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N220" t="s">
         <v>98</v>
@@ -5371,7 +5413,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G221" t="s">
         <v>87</v>
@@ -5392,7 +5434,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G222" t="s">
         <v>87</v>
@@ -5410,7 +5452,7 @@
         <v>38</v>
       </c>
       <c r="M222" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N222" t="s">
         <v>98</v>
@@ -5418,7 +5460,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G223" t="s">
         <v>87</v>
@@ -5439,7 +5481,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G224" t="s">
         <v>87</v>
@@ -5457,15 +5499,15 @@
         <v>38</v>
       </c>
       <c r="M224" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N224" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G225" t="s">
         <v>87</v>
@@ -5487,7 +5529,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G226" t="s">
         <v>87</v>
@@ -5507,7 +5549,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G227" t="s">
         <v>87</v>
@@ -5564,7 +5606,7 @@
         <v>38</v>
       </c>
       <c r="N229" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
@@ -5587,12 +5629,12 @@
         <v>38</v>
       </c>
       <c r="N230" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G231" t="s">
         <v>87</v>
@@ -5650,7 +5692,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G234" t="s">
         <v>87</v>
@@ -5668,15 +5710,15 @@
         <v>38</v>
       </c>
       <c r="M234" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N234" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G235" t="s">
         <v>87</v>
@@ -5694,15 +5736,15 @@
         <v>38</v>
       </c>
       <c r="M235" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N235" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G236" t="s">
         <v>87</v>
@@ -5720,10 +5762,10 @@
         <v>38</v>
       </c>
       <c r="M236" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N236" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
@@ -5746,10 +5788,10 @@
         <v>38</v>
       </c>
       <c r="M237" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N237" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
@@ -5772,15 +5814,15 @@
         <v>38</v>
       </c>
       <c r="M238" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N238" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G239" t="s">
         <v>87</v>
@@ -5821,7 +5863,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H241" t="s">
         <v>43</v>
@@ -5836,15 +5878,15 @@
         <v>38</v>
       </c>
       <c r="M241" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N241" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H242" t="s">
         <v>43</v>
@@ -5859,15 +5901,15 @@
         <v>38</v>
       </c>
       <c r="M242" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N242" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H243" t="s">
         <v>43</v>
@@ -5882,15 +5924,15 @@
         <v>38</v>
       </c>
       <c r="M243" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N243" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H244" t="s">
         <v>43</v>
@@ -5905,10 +5947,10 @@
         <v>38</v>
       </c>
       <c r="M244" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N244" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
@@ -5950,7 +5992,7 @@
         <v>38</v>
       </c>
       <c r="M246" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N246" t="s">
         <v>94</v>
@@ -5994,7 +6036,7 @@
         <v>38</v>
       </c>
       <c r="M248" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
@@ -6017,12 +6059,12 @@
         <v>38</v>
       </c>
       <c r="M249" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G250" t="s">
         <v>87</v>
@@ -6040,7 +6082,7 @@
         <v>38</v>
       </c>
       <c r="M250" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
@@ -6081,10 +6123,10 @@
         <v>38</v>
       </c>
       <c r="M252" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N252" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
@@ -6107,7 +6149,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H254" t="s">
         <v>43</v>
@@ -6122,10 +6164,10 @@
         <v>38</v>
       </c>
       <c r="M254" t="s">
+        <v>220</v>
+      </c>
+      <c r="N254" s="26" t="s">
         <v>221</v>
-      </c>
-      <c r="N254" s="26" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
@@ -6148,7 +6190,7 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G256" t="s">
         <v>87</v>
@@ -6186,7 +6228,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H258" t="s">
         <v>43</v>
@@ -6201,15 +6243,15 @@
         <v>38</v>
       </c>
       <c r="M258" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N258" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H259" t="s">
         <v>43</v>
@@ -6224,15 +6266,15 @@
         <v>38</v>
       </c>
       <c r="M259" t="s">
+        <v>171</v>
+      </c>
+      <c r="N259" s="26" t="s">
         <v>172</v>
-      </c>
-      <c r="N259" s="26" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H260" t="s">
         <v>43</v>
@@ -6247,15 +6289,15 @@
         <v>38</v>
       </c>
       <c r="M260" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N260" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H261" t="s">
         <v>43</v>
@@ -6270,10 +6312,10 @@
         <v>38</v>
       </c>
       <c r="M261" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N261" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
@@ -6342,7 +6384,7 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C268" t="s">
         <v>37</v>
@@ -6362,7 +6404,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C269" t="s">
         <v>37</v>
@@ -6385,7 +6427,7 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C270" t="s">
         <v>37</v>
@@ -6408,7 +6450,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C271" t="s">
         <v>37</v>
@@ -6428,7 +6470,7 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B272" s="8"/>
       <c r="C272" s="8" t="s">
@@ -6456,7 +6498,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8" t="s">
@@ -6486,7 +6528,7 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8" t="s">
@@ -6516,7 +6558,7 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8" t="s">
@@ -6544,7 +6586,7 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8" t="s">
@@ -6574,7 +6616,7 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="9" t="s">
@@ -6602,7 +6644,7 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="9" t="s">
@@ -6632,7 +6674,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="9" t="s">
@@ -6660,7 +6702,7 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="9" t="s">
@@ -6688,7 +6730,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="9" t="s">
@@ -6697,7 +6739,7 @@
       <c r="D281" s="8"/>
       <c r="E281" s="8"/>
       <c r="F281" s="9" t="s">
-        <v>121</v>
+        <v>344</v>
       </c>
       <c r="G281" s="8"/>
       <c r="H281" s="8"/>
@@ -6711,14 +6753,16 @@
       <c r="L281" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M281" s="8"/>
+      <c r="M281" s="10" t="s">
+        <v>343</v>
+      </c>
       <c r="N281" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="9" t="s">
@@ -6727,7 +6771,7 @@
       <c r="D282" s="8"/>
       <c r="E282" s="8"/>
       <c r="F282" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
@@ -6748,7 +6792,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="9" t="s">
@@ -6776,7 +6820,7 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="9" t="s">
@@ -6785,7 +6829,7 @@
       <c r="D284" s="8"/>
       <c r="E284" s="8"/>
       <c r="F284" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
@@ -6806,7 +6850,7 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B285" s="10"/>
       <c r="C285" s="9" t="s">
@@ -6828,13 +6872,13 @@
         <v>38</v>
       </c>
       <c r="M285" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N285" s="8"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B286" s="10"/>
       <c r="C286" s="8" t="s">
@@ -6856,13 +6900,13 @@
         <v>38</v>
       </c>
       <c r="M286" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N286" s="8"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B287" s="10"/>
       <c r="C287" s="9" t="s">
@@ -6884,13 +6928,13 @@
         <v>38</v>
       </c>
       <c r="M287" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N287" s="8"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B288" s="10"/>
       <c r="C288" s="9" t="s">
@@ -6912,7 +6956,7 @@
         <v>38</v>
       </c>
       <c r="M288" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N288" s="8"/>
     </row>
@@ -6997,7 +7041,7 @@
       <c r="D292" s="8"/>
       <c r="E292" s="8"/>
       <c r="F292" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G292" s="8"/>
       <c r="H292" s="8"/>
@@ -7015,7 +7059,7 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B293" s="8"/>
       <c r="C293" s="11" t="s">
@@ -7037,7 +7081,7 @@
         <v>38</v>
       </c>
       <c r="M293" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
@@ -7076,7 +7120,7 @@
       <c r="D295" s="8"/>
       <c r="E295" s="8"/>
       <c r="F295" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G295" s="8"/>
       <c r="H295" s="8"/>
@@ -7092,10 +7136,10 @@
         <v>38</v>
       </c>
       <c r="M295" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="N295" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="N295" s="9" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
@@ -7118,10 +7162,10 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C297" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="C297" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="J297" t="s">
         <v>85</v>
@@ -7135,10 +7179,10 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J298" t="s">
         <v>85</v>
@@ -7152,10 +7196,10 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J299" t="s">
         <v>85</v>
@@ -7169,10 +7213,10 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J300" t="s">
         <v>85</v>
@@ -7186,10 +7230,10 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C301" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J301" t="s">
         <v>85</v>
@@ -7203,10 +7247,10 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J302" t="s">
         <v>85</v>
@@ -7270,11 +7314,11 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B305" s="8"/>
       <c r="C305" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D305" s="8"/>
       <c r="E305" s="8"/>
@@ -7313,10 +7357,10 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J307" t="s">
         <v>85</v>
@@ -7330,10 +7374,10 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J308" t="s">
         <v>85</v>
@@ -7350,13 +7394,13 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C309" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F309" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J309" t="s">
         <v>86</v>
@@ -7373,10 +7417,10 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J310" t="s">
         <v>85</v>
@@ -7393,13 +7437,13 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F311" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J311" t="s">
         <v>86</v>
@@ -7416,10 +7460,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C312" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="C312" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="J312" t="s">
         <v>85</v>
@@ -7433,10 +7477,10 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J313" t="s">
         <v>85</v>
@@ -7450,10 +7494,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J314" t="s">
         <v>85</v>
@@ -7467,10 +7511,10 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C315" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J315" t="s">
         <v>85</v>
@@ -7484,10 +7528,10 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J316" t="s">
         <v>85</v>
@@ -8070,7 +8114,7 @@
         <v>55</v>
       </c>
       <c r="F335" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G335" s="8"/>
       <c r="H335" s="8"/>
@@ -8105,7 +8149,7 @@
         <v>55</v>
       </c>
       <c r="F336" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G336" s="8"/>
       <c r="H336" s="8"/>
@@ -8140,7 +8184,7 @@
         <v>55</v>
       </c>
       <c r="F337" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G337" s="8"/>
       <c r="H337" s="8"/>
@@ -8175,7 +8219,7 @@
         <v>55</v>
       </c>
       <c r="F338" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G338" s="8"/>
       <c r="H338" s="8"/>
@@ -8237,7 +8281,7 @@
         <v>55</v>
       </c>
       <c r="F340" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
@@ -8272,7 +8316,7 @@
         <v>55</v>
       </c>
       <c r="F341" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G341" s="8"/>
       <c r="H341" s="8"/>
@@ -8307,7 +8351,7 @@
         <v>55</v>
       </c>
       <c r="F342" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
@@ -8342,7 +8386,7 @@
         <v>55</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
@@ -8363,12 +8407,12 @@
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
       <c r="D344" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E344" s="9" t="s">
         <v>55</v>
@@ -8391,18 +8435,18 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B345" s="10"/>
       <c r="C345" s="10"/>
       <c r="D345" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E345" s="11" t="s">
         <v>55</v>
       </c>
       <c r="F345" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G345" s="8"/>
       <c r="H345" s="8"/>
@@ -8437,10 +8481,10 @@
       <c r="B347" s="8"/>
       <c r="C347" s="8"/>
       <c r="D347" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E347" s="9" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F347" s="8"/>
       <c r="G347" s="8"/>
@@ -8478,10 +8522,10 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C349" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J349" t="s">
         <v>85</v>
@@ -8495,10 +8539,10 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C350" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J350" t="s">
         <v>85</v>
@@ -8512,10 +8556,10 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C351" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J351" t="s">
         <v>85</v>
@@ -8529,12 +8573,12 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B353" s="8"/>
       <c r="C353" s="8"/>
@@ -8567,10 +8611,10 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C355" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H355" t="s">
         <v>45</v>
@@ -8591,13 +8635,13 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C356" t="s">
+        <v>133</v>
+      </c>
+      <c r="F356" t="s">
         <v>134</v>
-      </c>
-      <c r="F356" t="s">
-        <v>135</v>
       </c>
       <c r="H356" t="s">
         <v>45</v>
@@ -8617,10 +8661,10 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C357" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H357" t="s">
         <v>43</v>
@@ -8635,19 +8679,19 @@
         <v>38</v>
       </c>
       <c r="M357" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N357" s="8"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C358" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F358" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>43</v>
@@ -8683,96 +8727,119 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C360" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J360" t="s">
         <v>85</v>
       </c>
-      <c r="K360" s="21">
-        <v>13</v>
+      <c r="K360" s="22">
+        <f>161/1000*100</f>
+        <v>16.100000000000001</v>
       </c>
       <c r="L360" t="s">
         <v>38</v>
+      </c>
+      <c r="M360" t="s">
+        <v>345</v>
+      </c>
+      <c r="N360" s="17" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C361" t="s">
+        <v>230</v>
+      </c>
+      <c r="F361" t="s">
         <v>231</v>
-      </c>
-      <c r="F361" t="s">
-        <v>233</v>
       </c>
       <c r="J361" t="s">
         <v>86</v>
       </c>
-      <c r="K361" s="21">
-        <v>7</v>
+      <c r="K361" s="22">
+        <f>(6.4+25.2)/1000/0.9*100</f>
+        <v>3.5111111111111115</v>
       </c>
       <c r="L361" t="s">
         <v>38</v>
+      </c>
+      <c r="M361" t="s">
+        <v>348</v>
+      </c>
+      <c r="N361" s="17" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C362" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F362" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J362" t="s">
         <v>86</v>
       </c>
-      <c r="K362" s="21">
-        <v>4</v>
+      <c r="K362" s="22">
+        <f>19/1000/0.76*100</f>
+        <v>2.5</v>
       </c>
       <c r="L362" t="s">
         <v>38</v>
+      </c>
+      <c r="M362" t="s">
+        <v>349</v>
+      </c>
+      <c r="N362" s="17" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C363" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J363" t="s">
         <v>85</v>
       </c>
-      <c r="K363" s="23">
-        <v>13</v>
+      <c r="K363" s="43">
+        <f>K360/0.8</f>
+        <v>20.125</v>
       </c>
       <c r="L363" t="s">
         <v>38</v>
       </c>
-      <c r="M363" t="s">
-        <v>232</v>
+      <c r="M363" s="17" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C364" t="s">
+        <v>230</v>
+      </c>
+      <c r="F364" t="s">
         <v>231</v>
-      </c>
-      <c r="F364" t="s">
-        <v>233</v>
       </c>
       <c r="J364" t="s">
         <v>86</v>
       </c>
-      <c r="K364" s="21">
-        <v>7</v>
+      <c r="K364" s="43">
+        <f>K361</f>
+        <v>3.5111111111111115</v>
       </c>
       <c r="L364" t="s">
         <v>38</v>
@@ -8780,19 +8847,20 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C365" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F365" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J365" t="s">
         <v>86</v>
       </c>
-      <c r="K365" s="21">
-        <v>4</v>
+      <c r="K365" s="43">
+        <f>K362</f>
+        <v>2.5</v>
       </c>
       <c r="L365" t="s">
         <v>38</v>
@@ -8800,7 +8868,7 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
@@ -8823,11 +8891,11 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B368" s="10"/>
       <c r="C368" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D368" s="10"/>
       <c r="E368" s="10"/>
@@ -8851,7 +8919,7 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B369" s="10"/>
       <c r="C369" s="8" t="s">
@@ -8880,7 +8948,7 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B370" s="10"/>
       <c r="C370" s="8" t="s">
@@ -8889,7 +8957,7 @@
       <c r="D370" s="10"/>
       <c r="E370" s="10"/>
       <c r="F370" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G370" s="10"/>
       <c r="H370" s="10"/>
@@ -8917,7 +8985,7 @@
       <c r="D371" s="10"/>
       <c r="E371" s="10"/>
       <c r="F371" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G371" s="10"/>
       <c r="H371" s="10"/>
@@ -8925,17 +8993,17 @@
       <c r="K371" s="20"/>
       <c r="L371" s="9"/>
       <c r="M371" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N371" s="8"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B372" s="10"/>
       <c r="C372" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D372" s="10"/>
       <c r="E372" s="10"/>
@@ -8959,16 +9027,16 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B373" s="10"/>
       <c r="C373" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D373" s="10"/>
       <c r="E373" s="10"/>
       <c r="F373" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G373" s="10"/>
       <c r="H373" s="10"/>
@@ -8989,7 +9057,7 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B374" s="10"/>
       <c r="C374" s="9" t="s">
@@ -9017,7 +9085,7 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B375" s="10"/>
       <c r="C375" s="9" t="s">
@@ -9026,7 +9094,7 @@
       <c r="D375" s="10"/>
       <c r="E375" s="10"/>
       <c r="F375" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G375" s="10"/>
       <c r="H375" s="10"/>
@@ -9041,7 +9109,7 @@
         <v>38</v>
       </c>
       <c r="M375" s="10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N375" s="10" t="s">
         <v>92</v>
@@ -9049,7 +9117,7 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -9067,11 +9135,11 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B377" s="10"/>
       <c r="C377" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J377" t="s">
         <v>85</v>
@@ -9083,7 +9151,7 @@
         <v>38</v>
       </c>
       <c r="M377" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N377" s="8" t="s">
         <v>92</v>
@@ -9091,14 +9159,14 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B378" s="10"/>
       <c r="C378" t="s">
+        <v>133</v>
+      </c>
+      <c r="F378" t="s">
         <v>134</v>
-      </c>
-      <c r="F378" t="s">
-        <v>135</v>
       </c>
       <c r="J378" t="s">
         <v>86</v>
@@ -9115,7 +9183,7 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B379" s="10"/>
       <c r="C379" t="s">
@@ -9125,59 +9193,63 @@
         <v>85</v>
       </c>
       <c r="K379" s="15">
-        <v>33</v>
+        <f>(1*0.766) / (2.1/0.86) * 100</f>
+        <v>31.369523809523809</v>
       </c>
       <c r="L379" s="17" t="s">
         <v>38</v>
       </c>
       <c r="M379" s="17" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="N379" s="9" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B380" s="10"/>
       <c r="C380" t="s">
         <v>37</v>
       </c>
       <c r="F380" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J380" t="s">
         <v>86</v>
       </c>
       <c r="K380" s="15">
-        <v>298</v>
+        <f>(0.8/0.9) / (2.1/0.86) * 100</f>
+        <v>36.402116402116405</v>
       </c>
       <c r="L380" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M380" s="17"/>
+      <c r="M380" s="42" t="s">
+        <v>338</v>
+      </c>
       <c r="N380" s="9" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="10"/>
       <c r="F381" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K381" s="23"/>
       <c r="L381" s="6"/>
       <c r="M381" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N381" s="9"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -9189,7 +9261,7 @@
       <c r="I382" s="4"/>
       <c r="J382" s="5"/>
       <c r="K382" s="38" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L382" s="5"/>
       <c r="M382" s="5"/>
@@ -9197,15 +9269,15 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B383" s="10"/>
       <c r="C383" s="10"/>
       <c r="D383" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E383" s="19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F383" s="10"/>
       <c r="G383" s="10"/>
@@ -9239,7 +9311,7 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -9257,7 +9329,7 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9273,72 +9345,72 @@
   <sheetData>
     <row r="8" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E8" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E15" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E23" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -9357,23 +9429,23 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -9381,18 +9453,18 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C5" s="25" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -9412,7 +9484,7 @@
         <v>2020</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I7">
         <v>2016</v>
@@ -9430,7 +9502,7 @@
         <v>2020</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="O7">
         <v>2016</v>
@@ -9448,15 +9520,15 @@
         <v>2020</v>
       </c>
       <c r="T7" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C8" s="34">
         <v>142352</v>
@@ -9523,10 +9595,10 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C9" s="33">
         <v>11521</v>
@@ -9593,10 +9665,10 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C10" s="33">
         <v>77862</v>
@@ -9663,10 +9735,10 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" s="33">
         <v>2564</v>
@@ -9733,10 +9805,10 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C12" s="33">
         <v>32168</v>
@@ -9803,18 +9875,18 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C14" s="25" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -9834,7 +9906,7 @@
         <v>2020</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I16">
         <v>2016</v>
@@ -9852,7 +9924,7 @@
         <v>2020</v>
       </c>
       <c r="N16" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="O16">
         <v>2016</v>
@@ -9870,15 +9942,15 @@
         <v>2020</v>
       </c>
       <c r="T16" s="32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="33">
         <v>9962</v>
@@ -9950,4 +10022,24 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>